--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C323B1E1-EB1E-4863-B899-2787DEAE3D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65E82A8-0E2E-430C-A4E1-CF205044C7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="7">
   <si>
     <t>Status</t>
   </si>
@@ -47,6 +47,12 @@
   <si>
     <t>Processar</t>
   </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
 </sst>
 </file>
 
@@ -56,13 +62,19 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -155,14 +167,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -174,31 +187,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 7" xfId="3" xr:uid="{2CBC3EC7-8173-4475-9FEF-478FE291540A}"/>
     <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -511,7 +537,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -536,230 +562,1063 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>721473134</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="9"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>726704111</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>675174076</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>686093000</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>685864641</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>684905130</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>682907179</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>682906676</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="9"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>633612399</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>171142924</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="9"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>633322825</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>798020867</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="9"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>797672270</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="9"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>797672262</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>782904274</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>786553150</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="9"/>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>760859243</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>773510932</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="9"/>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>781785997</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>781430685</v>
+      </c>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="9"/>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>780625145</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="9"/>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>764465336</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="9"/>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>757353937</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D24"/>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>756966457</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D25"/>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>748642000</v>
+      </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D26"/>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>751238407</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D27"/>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>749500207</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D28"/>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>748368358</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D29"/>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>748368341</v>
+      </c>
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D30"/>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>747736803</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D31"/>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>747687196</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D32"/>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>747524159</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>747521247</v>
+      </c>
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D34"/>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>735481727</v>
+      </c>
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D35"/>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>728807490</v>
+      </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D36"/>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>746786155</v>
+      </c>
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D37"/>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>739821316</v>
+      </c>
+      <c r="B38" t="s">
+        <v>5</v>
+      </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>763557323</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>178907261</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>178545657</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>178474163</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>178117531</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>177997784</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>177846312</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>800909495</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>870049172</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>870169699</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>874169612</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>871095737</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="11">
+        <v>801399878</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="11">
+        <v>801275821</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="11">
+        <v>689160897</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>764396663</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="11">
+        <v>773182880</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="11">
+        <v>764503268</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="11">
+        <v>757634294</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="11">
+        <v>756814954</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>748320623</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="11">
+        <v>754192031</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>753833114</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>752613525</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>752545396</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="11">
+        <v>751840293</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="11">
+        <v>748832866</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="11">
+        <v>748599226</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="11">
+        <v>743143418</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="11">
+        <v>742036878</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="11">
+        <v>729571319</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="11">
+        <v>731657767</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="11">
+        <v>703014740</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="11">
+        <v>709078707</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="11">
+        <v>686999081</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="11">
+        <v>171825320</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="11">
+        <v>672628652</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="11">
+        <v>674507912</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="11">
+        <v>683573897</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="11">
+        <v>682539345</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="11">
+        <v>669294765</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="11">
+        <v>644157012</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="11">
+        <v>174360176</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="11">
+        <v>178759340</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="11">
+        <v>698337403</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="11">
+        <v>742043700</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="11">
+        <v>178667162</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="11">
+        <v>178667014</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="11">
+        <v>178546457</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="11">
+        <v>840221802</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="11">
+        <v>876663075</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="11">
+        <v>871111336</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="11">
+        <v>870321522</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="11">
+        <v>868305024</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="11">
+        <v>824854016</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A50">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51:A93">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
@@ -780,31 +1639,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65E82A8-0E2E-430C-A4E1-CF205044C7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCD009E-1773-4091-9141-0DEE7545A02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="136">
   <si>
     <t>Status</t>
   </si>
@@ -48,10 +48,397 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>713969552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>812853657</t>
+  </si>
+  <si>
+    <t>816433837</t>
+  </si>
+  <si>
+    <t>815907971</t>
+  </si>
+  <si>
+    <t>815192053</t>
+  </si>
+  <si>
+    <t>814180257</t>
+  </si>
+  <si>
+    <t>812511693</t>
+  </si>
+  <si>
+    <t>807324243</t>
+  </si>
+  <si>
+    <t>810457709</t>
+  </si>
+  <si>
+    <t>810054811</t>
+  </si>
+  <si>
+    <t>807324235</t>
+  </si>
+  <si>
+    <t>807081835</t>
+  </si>
+  <si>
+    <t>807081777</t>
+  </si>
+  <si>
+    <t>806909895</t>
+  </si>
+  <si>
+    <t>793176235</t>
+  </si>
+  <si>
+    <t>806847947</t>
+  </si>
+  <si>
+    <t>806847889</t>
+  </si>
+  <si>
+    <t>805086638</t>
+  </si>
+  <si>
+    <t>805086596</t>
+  </si>
+  <si>
+    <t>804368847</t>
+  </si>
+  <si>
+    <t>804368078</t>
+  </si>
+  <si>
+    <t>798433573</t>
+  </si>
+  <si>
+    <t>798014134</t>
+  </si>
+  <si>
+    <t>797118399</t>
+  </si>
+  <si>
+    <t>797118233</t>
+  </si>
+  <si>
+    <t>796846743</t>
+  </si>
+  <si>
+    <t>790228799</t>
+  </si>
+  <si>
+    <t>787513286</t>
+  </si>
+  <si>
+    <t>746481393</t>
+  </si>
+  <si>
+    <t>785053459</t>
+  </si>
+  <si>
+    <t>787513278</t>
+  </si>
+  <si>
+    <t>787231285</t>
+  </si>
+  <si>
+    <t>779620230</t>
+  </si>
+  <si>
+    <t>778909634</t>
+  </si>
+  <si>
+    <t>766833481</t>
+  </si>
+  <si>
+    <t>769902168</t>
+  </si>
+  <si>
+    <t>769100854</t>
+  </si>
+  <si>
+    <t>769100748</t>
+  </si>
+  <si>
+    <t>769100730</t>
+  </si>
+  <si>
+    <t>769100722</t>
+  </si>
+  <si>
+    <t>750836425</t>
+  </si>
+  <si>
+    <t>715468249</t>
+  </si>
+  <si>
+    <t>714443318</t>
+  </si>
+  <si>
+    <t>714443078</t>
+  </si>
+  <si>
+    <t>714076092</t>
+  </si>
+  <si>
+    <t>713969776</t>
+  </si>
+  <si>
+    <t>710882667</t>
+  </si>
+  <si>
+    <t>709036432</t>
+  </si>
+  <si>
+    <t>709035939</t>
+  </si>
+  <si>
+    <t>709035715</t>
+  </si>
+  <si>
+    <t>828154611</t>
+  </si>
+  <si>
+    <t>827469754</t>
+  </si>
+  <si>
+    <t>827469697</t>
+  </si>
+  <si>
+    <t>827469630</t>
+  </si>
+  <si>
+    <t>827214879</t>
+  </si>
+  <si>
+    <t>827000542</t>
+  </si>
+  <si>
+    <t>827000302</t>
+  </si>
+  <si>
+    <t>826773362</t>
+  </si>
+  <si>
+    <t>826524823</t>
+  </si>
+  <si>
+    <t>826459061</t>
+  </si>
+  <si>
+    <t>826100764</t>
+  </si>
+  <si>
+    <t>825897022</t>
+  </si>
+  <si>
+    <t>822870410</t>
+  </si>
+  <si>
+    <t>822758185</t>
+  </si>
+  <si>
+    <t>821660317</t>
+  </si>
+  <si>
+    <t>821136821</t>
+  </si>
+  <si>
+    <t>819133665</t>
+  </si>
+  <si>
+    <t>818212148</t>
+  </si>
+  <si>
+    <t>818501094</t>
+  </si>
+  <si>
+    <t>818294161</t>
+  </si>
+  <si>
+    <t>817992054</t>
+  </si>
+  <si>
+    <t>817760386</t>
+  </si>
+  <si>
+    <t>816866713</t>
+  </si>
+  <si>
+    <t>816863272</t>
+  </si>
+  <si>
+    <t>816863165</t>
+  </si>
+  <si>
+    <t>816863041</t>
+  </si>
+  <si>
+    <t>816862985</t>
+  </si>
+  <si>
+    <t>816787232</t>
+  </si>
+  <si>
+    <t>821136722</t>
+  </si>
+  <si>
+    <t>821054891</t>
+  </si>
+  <si>
+    <t>821054883</t>
+  </si>
+  <si>
+    <t>821054875</t>
+  </si>
+  <si>
+    <t>819133772</t>
+  </si>
+  <si>
+    <t>818618336</t>
+  </si>
+  <si>
+    <t>818738209</t>
+  </si>
+  <si>
+    <t>818738183</t>
+  </si>
+  <si>
+    <t>818618096</t>
+  </si>
+  <si>
+    <t>818618088</t>
+  </si>
+  <si>
+    <t>818618062</t>
+  </si>
+  <si>
+    <t>818618054</t>
+  </si>
+  <si>
+    <t>818618047</t>
+  </si>
+  <si>
+    <t>818501680</t>
+  </si>
+  <si>
+    <t>818501409</t>
+  </si>
+  <si>
+    <t>818501250</t>
+  </si>
+  <si>
+    <t>759899978</t>
+  </si>
+  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
+    <t>878142474</t>
+  </si>
+  <si>
+    <t>864648401</t>
+  </si>
+  <si>
+    <t>871916486</t>
+  </si>
+  <si>
+    <t>789948845</t>
+  </si>
+  <si>
+    <t>839737578</t>
+  </si>
+  <si>
+    <t>864648294</t>
+  </si>
+  <si>
+    <t>758494854</t>
+  </si>
+  <si>
+    <t>752321848</t>
+  </si>
+  <si>
+    <t>745051833</t>
+  </si>
+  <si>
+    <t>744238050</t>
+  </si>
+  <si>
+    <t>741705259</t>
+  </si>
+  <si>
+    <t>740148170</t>
+  </si>
+  <si>
+    <t>739095184</t>
+  </si>
+  <si>
+    <t>738416241</t>
+  </si>
+  <si>
+    <t>735362505</t>
+  </si>
+  <si>
+    <t>732760586</t>
+  </si>
+  <si>
+    <t>732132109</t>
+  </si>
+  <si>
+    <t>731546119</t>
+  </si>
+  <si>
+    <t>729662860</t>
+  </si>
+  <si>
+    <t>701913828</t>
+  </si>
+  <si>
+    <t>684557055</t>
+  </si>
+  <si>
+    <t>174379044</t>
+  </si>
+  <si>
+    <t>672676057</t>
+  </si>
+  <si>
+    <t>682504778</t>
+  </si>
+  <si>
+    <t>681643791</t>
+  </si>
+  <si>
+    <t>175210164</t>
+  </si>
+  <si>
+    <t>173869490</t>
+  </si>
+  <si>
+    <t>171816782</t>
+  </si>
+  <si>
+    <t>178766048</t>
+  </si>
+  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>871854539</t>
+  </si>
+  <si>
+    <t>877288724</t>
+  </si>
+  <si>
+    <t>178733402</t>
+  </si>
+  <si>
+    <t>177842436</t>
   </si>
 </sst>
 </file>
@@ -62,19 +449,13 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -167,15 +548,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -187,44 +567,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="3">
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 7" xfId="3" xr:uid="{2CBC3EC7-8173-4475-9FEF-478FE291540A}"/>
     <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -537,7 +904,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -562,23 +929,23 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>721473134</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="9"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>726704111</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -586,11 +953,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>675174076</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -598,11 +965,11 @@
       <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>686093000</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -610,11 +977,11 @@
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>685864641</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -622,11 +989,11 @@
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>684905130</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -634,11 +1001,11 @@
       <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>682907179</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
+      <c r="A8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -646,11 +1013,11 @@
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>682906676</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -658,11 +1025,11 @@
       <c r="D9" s="9"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>633612399</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -670,11 +1037,11 @@
       <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>171142924</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -682,11 +1049,11 @@
       <c r="D11" s="9"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>633322825</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -694,11 +1061,11 @@
       <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>798020867</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -706,11 +1073,11 @@
       <c r="D13" s="9"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>797672270</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -718,11 +1085,11 @@
       <c r="D14" s="9"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>797672262</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -730,11 +1097,11 @@
       <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>782904274</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -742,11 +1109,11 @@
       <c r="D16" s="9"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>786553150</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
+      <c r="A17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -754,11 +1121,11 @@
       <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>760859243</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
+      <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -766,11 +1133,11 @@
       <c r="D18" s="9"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>773510932</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
+      <c r="A19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -778,11 +1145,11 @@
       <c r="D19" s="9"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>781785997</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
+      <c r="A20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -790,11 +1157,11 @@
       <c r="D20" s="9"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>781430685</v>
-      </c>
-      <c r="B21" t="s">
-        <v>5</v>
+      <c r="A21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -802,11 +1169,11 @@
       <c r="D21" s="9"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>780625145</v>
-      </c>
-      <c r="B22" t="s">
-        <v>5</v>
+      <c r="A22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -814,11 +1181,11 @@
       <c r="D22" s="9"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>764465336</v>
-      </c>
-      <c r="B23" t="s">
-        <v>5</v>
+      <c r="A23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -826,11 +1193,11 @@
       <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>757353937</v>
-      </c>
-      <c r="B24" t="s">
-        <v>5</v>
+      <c r="A24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -838,11 +1205,11 @@
       <c r="D24"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>756966457</v>
-      </c>
-      <c r="B25" t="s">
-        <v>5</v>
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -850,11 +1217,11 @@
       <c r="D25"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>748642000</v>
-      </c>
-      <c r="B26" t="s">
-        <v>5</v>
+      <c r="A26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -862,11 +1229,11 @@
       <c r="D26"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>751238407</v>
-      </c>
-      <c r="B27" t="s">
-        <v>5</v>
+      <c r="A27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -874,11 +1241,11 @@
       <c r="D27"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>749500207</v>
-      </c>
-      <c r="B28" t="s">
-        <v>5</v>
+      <c r="A28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -886,11 +1253,11 @@
       <c r="D28"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>748368358</v>
-      </c>
-      <c r="B29" t="s">
-        <v>5</v>
+      <c r="A29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -898,11 +1265,11 @@
       <c r="D29"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>748368341</v>
-      </c>
-      <c r="B30" t="s">
-        <v>5</v>
+      <c r="A30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -910,11 +1277,11 @@
       <c r="D30"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>747736803</v>
-      </c>
-      <c r="B31" t="s">
-        <v>5</v>
+      <c r="A31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -922,11 +1289,11 @@
       <c r="D31"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>747687196</v>
-      </c>
-      <c r="B32" t="s">
-        <v>5</v>
+      <c r="A32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -934,11 +1301,11 @@
       <c r="D32"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>747524159</v>
-      </c>
-      <c r="B33" t="s">
-        <v>5</v>
+      <c r="A33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -946,11 +1313,11 @@
       <c r="D33"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>747521247</v>
-      </c>
-      <c r="B34" t="s">
-        <v>5</v>
+      <c r="A34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -958,11 +1325,11 @@
       <c r="D34"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>735481727</v>
-      </c>
-      <c r="B35" t="s">
-        <v>5</v>
+      <c r="A35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -970,11 +1337,11 @@
       <c r="D35"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>728807490</v>
-      </c>
-      <c r="B36" t="s">
-        <v>5</v>
+      <c r="A36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -982,11 +1349,11 @@
       <c r="D36"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>746786155</v>
-      </c>
-      <c r="B37" t="s">
-        <v>5</v>
+      <c r="A37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -994,11 +1361,11 @@
       <c r="D37"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>739821316</v>
-      </c>
-      <c r="B38" t="s">
-        <v>5</v>
+      <c r="A38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1006,10 +1373,10 @@
       <c r="D38"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>763557323</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="A39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="5" t="s">
@@ -1017,10 +1384,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>178907261</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="A40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="5" t="s">
@@ -1028,10 +1395,10 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>178545657</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="A41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="5" t="s">
@@ -1039,10 +1406,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>178474163</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="A42" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -1050,10 +1417,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>178117531</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="A43" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="5" t="s">
@@ -1061,10 +1428,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>177997784</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="A44" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="5" t="s">
@@ -1072,10 +1439,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>177846312</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="A45" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="5" t="s">
@@ -1083,10 +1450,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>800909495</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="A46" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -1094,10 +1461,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>870049172</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="A47" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="5" t="s">
@@ -1105,10 +1472,10 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>870169699</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="A48" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="5" t="s">
@@ -1116,10 +1483,10 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>874169612</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="A49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="5" t="s">
@@ -1127,10 +1494,10 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>871095737</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="A50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="5" t="s">
@@ -1138,351 +1505,351 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>801399878</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>5</v>
+      <c r="A51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="11">
-        <v>801275821</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>5</v>
+      <c r="A52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="11">
-        <v>689160897</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>5</v>
+      <c r="A53" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
-        <v>764396663</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>5</v>
+      <c r="A54" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="11">
-        <v>773182880</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>5</v>
+      <c r="A55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="11">
-        <v>764503268</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>5</v>
+      <c r="A56" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="11">
-        <v>757634294</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>5</v>
+      <c r="A57" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="11">
-        <v>756814954</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>5</v>
+      <c r="A58" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="11">
-        <v>748320623</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>5</v>
+      <c r="A59" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="11">
-        <v>754192031</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>5</v>
+      <c r="A60" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="11">
-        <v>753833114</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>5</v>
+      <c r="A61" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="11">
-        <v>752613525</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>5</v>
+      <c r="A62" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="11">
-        <v>752545396</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>5</v>
+      <c r="A63" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
-        <v>751840293</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>5</v>
+      <c r="A64" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="11">
-        <v>748832866</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>5</v>
+      <c r="A65" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="11">
-        <v>748599226</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>5</v>
+      <c r="A66" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="11">
-        <v>743143418</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>5</v>
+      <c r="A67" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="11">
-        <v>742036878</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>5</v>
+      <c r="A68" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="11">
-        <v>729571319</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>5</v>
+      <c r="A69" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="11">
-        <v>731657767</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>5</v>
+      <c r="A70" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="11">
-        <v>703014740</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>5</v>
+      <c r="A71" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="11">
-        <v>709078707</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>5</v>
+      <c r="A72" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="11">
-        <v>686999081</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>5</v>
+      <c r="A73" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="11">
-        <v>171825320</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>5</v>
+      <c r="A74" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="11">
-        <v>672628652</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>5</v>
+      <c r="A75" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="11">
-        <v>674507912</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>5</v>
+      <c r="A76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="11">
-        <v>683573897</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>5</v>
+      <c r="A77" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="11">
-        <v>682539345</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>5</v>
+      <c r="A78" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="11">
-        <v>669294765</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>5</v>
+      <c r="A79" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="11">
-        <v>644157012</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>5</v>
+      <c r="A80" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="11">
-        <v>174360176</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>5</v>
+      <c r="A81" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="11">
-        <v>178759340</v>
-      </c>
-      <c r="B82" s="11" t="s">
+      <c r="A82" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="5" t="s">
@@ -1490,10 +1857,10 @@
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="11">
-        <v>698337403</v>
-      </c>
-      <c r="B83" s="11" t="s">
+      <c r="A83" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="5" t="s">
@@ -1501,10 +1868,10 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="11">
-        <v>742043700</v>
-      </c>
-      <c r="B84" s="11" t="s">
+      <c r="A84" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="5" t="s">
@@ -1512,10 +1879,10 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="11">
-        <v>178667162</v>
-      </c>
-      <c r="B85" s="11" t="s">
+      <c r="A85" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="5" t="s">
@@ -1523,10 +1890,10 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="11">
-        <v>178667014</v>
-      </c>
-      <c r="B86" s="11" t="s">
+      <c r="A86" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="5" t="s">
@@ -1534,10 +1901,10 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="11">
-        <v>178546457</v>
-      </c>
-      <c r="B87" s="11" t="s">
+      <c r="A87" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="5" t="s">
@@ -1545,10 +1912,10 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="11">
-        <v>840221802</v>
-      </c>
-      <c r="B88" s="11" t="s">
+      <c r="A88" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="5" t="s">
@@ -1556,10 +1923,10 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="11">
-        <v>876663075</v>
-      </c>
-      <c r="B89" s="11" t="s">
+      <c r="A89" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C89" s="5" t="s">
@@ -1567,10 +1934,10 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="11">
-        <v>871111336</v>
-      </c>
-      <c r="B90" s="11" t="s">
+      <c r="A90" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C90" s="5" t="s">
@@ -1578,10 +1945,10 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="11">
-        <v>870321522</v>
-      </c>
-      <c r="B91" s="11" t="s">
+      <c r="A91" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="5" t="s">
@@ -1589,10 +1956,10 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="11">
-        <v>868305024</v>
-      </c>
-      <c r="B92" s="11" t="s">
+      <c r="A92" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="5" t="s">
@@ -1600,25 +1967,415 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="11">
-        <v>824854016</v>
-      </c>
-      <c r="B93" s="11" t="s">
+      <c r="A93" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C129" s="5" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A50">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A51:A93">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9FFF33-5CC2-465E-8CBA-18AC10AB3E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E82FA4-7CE9-4E26-ABF3-8A552B28F3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="111">
   <si>
     <t>Status</t>
   </si>
@@ -48,121 +48,322 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>859589701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>878676000</t>
-  </si>
-  <si>
-    <t>878224355</t>
-  </si>
-  <si>
-    <t>877547657</t>
-  </si>
-  <si>
-    <t>844231377</t>
-  </si>
-  <si>
-    <t>832777613</t>
-  </si>
-  <si>
-    <t>823005578</t>
-  </si>
-  <si>
-    <t>783930849</t>
-  </si>
-  <si>
-    <t>816940765</t>
-  </si>
-  <si>
-    <t>815818582</t>
-  </si>
-  <si>
-    <t>786640700</t>
-  </si>
-  <si>
-    <t>765590363</t>
-  </si>
-  <si>
-    <t>762973885</t>
-  </si>
-  <si>
-    <t>762338832</t>
-  </si>
-  <si>
-    <t>758562395</t>
-  </si>
-  <si>
-    <t>755128323</t>
-  </si>
-  <si>
-    <t>753193816</t>
-  </si>
-  <si>
-    <t>752743934</t>
-  </si>
-  <si>
-    <t>687916043</t>
-  </si>
-  <si>
-    <t>731256776</t>
-  </si>
-  <si>
-    <t>741002889</t>
-  </si>
-  <si>
-    <t>660918164</t>
-  </si>
-  <si>
-    <t>177847575</t>
+    <t>859469961</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>771074402</t>
-  </si>
-  <si>
-    <t>825320843</t>
-  </si>
-  <si>
-    <t>870679234</t>
-  </si>
-  <si>
-    <t>870007584</t>
-  </si>
-  <si>
-    <t>870669201</t>
-  </si>
-  <si>
-    <t>870644279</t>
-  </si>
-  <si>
-    <t>818916086</t>
-  </si>
-  <si>
-    <t>179328756</t>
-  </si>
-  <si>
-    <t>178863415</t>
-  </si>
-  <si>
-    <t>178719435</t>
-  </si>
-  <si>
-    <t>178701219</t>
-  </si>
-  <si>
-    <t>178561985</t>
-  </si>
-  <si>
-    <t>178552687</t>
-  </si>
-  <si>
-    <t>178242883</t>
+    <t>759085263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>788188997</t>
+  </si>
+  <si>
+    <t>787118532</t>
+  </si>
+  <si>
+    <t>785246988</t>
+  </si>
+  <si>
+    <t>751645395</t>
+  </si>
+  <si>
+    <t>883778932</t>
+  </si>
+  <si>
+    <t>653653984</t>
+  </si>
+  <si>
+    <t>718779105</t>
+  </si>
+  <si>
+    <t>696697329</t>
+  </si>
+  <si>
+    <t>690716299</t>
+  </si>
+  <si>
+    <t>680815580</t>
+  </si>
+  <si>
+    <t>887767352</t>
+  </si>
+  <si>
+    <t>889037796</t>
+  </si>
+  <si>
+    <t>888585175</t>
+  </si>
+  <si>
+    <t>887607954</t>
+  </si>
+  <si>
+    <t>886146426</t>
+  </si>
+  <si>
+    <t>884101613</t>
+  </si>
+  <si>
+    <t>883454286</t>
+  </si>
+  <si>
+    <t>882745916</t>
+  </si>
+  <si>
+    <t>878092885</t>
+  </si>
+  <si>
+    <t>879817421</t>
+  </si>
+  <si>
+    <t>882685492</t>
+  </si>
+  <si>
+    <t>880914068</t>
+  </si>
+  <si>
+    <t>879321572</t>
+  </si>
+  <si>
+    <t>878690456</t>
+  </si>
+  <si>
+    <t>878170962</t>
+  </si>
+  <si>
+    <t>878142466</t>
+  </si>
+  <si>
+    <t>877104418</t>
+  </si>
+  <si>
+    <t>875752382</t>
+  </si>
+  <si>
+    <t>874548153</t>
+  </si>
+  <si>
+    <t>862057589</t>
+  </si>
+  <si>
+    <t>870744897</t>
+  </si>
+  <si>
+    <t>870298647</t>
+  </si>
+  <si>
+    <t>862460361</t>
+  </si>
+  <si>
+    <t>859649448</t>
+  </si>
+  <si>
+    <t>811342686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>726558491</t>
+  </si>
+  <si>
+    <t>724084961</t>
+  </si>
+  <si>
+    <t>787446966</t>
+  </si>
+  <si>
+    <t>806946202</t>
+  </si>
+  <si>
+    <t>791060423</t>
+  </si>
+  <si>
+    <t>888133802</t>
+  </si>
+  <si>
+    <t>675904563</t>
+  </si>
+  <si>
+    <t>701040432</t>
+  </si>
+  <si>
+    <t>702631148</t>
+  </si>
+  <si>
+    <t>678244660</t>
+  </si>
+  <si>
+    <t>659245868</t>
+  </si>
+  <si>
+    <t>874414786</t>
+  </si>
+  <si>
+    <t>879936692</t>
+  </si>
+  <si>
+    <t>881263192</t>
+  </si>
+  <si>
+    <t>878326358</t>
+  </si>
+  <si>
+    <t>867135299</t>
+  </si>
+  <si>
+    <t>837050891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>878144280</t>
+  </si>
+  <si>
+    <t>810285159</t>
+  </si>
+  <si>
+    <t>863841866</t>
+  </si>
+  <si>
+    <t>863264978</t>
+  </si>
+  <si>
+    <t>877220388</t>
+  </si>
+  <si>
+    <t>878704497</t>
+  </si>
+  <si>
+    <t>178561126</t>
+  </si>
+  <si>
+    <t>661875884</t>
+  </si>
+  <si>
+    <t>778510622</t>
+  </si>
+  <si>
+    <t>693442299</t>
+  </si>
+  <si>
+    <t>732218924</t>
+  </si>
+  <si>
+    <t>878432388</t>
+  </si>
+  <si>
+    <t>880512607</t>
+  </si>
+  <si>
+    <t>879121303</t>
+  </si>
+  <si>
+    <t>879029837</t>
+  </si>
+  <si>
+    <t>878300809</t>
+  </si>
+  <si>
+    <t>674717479</t>
+  </si>
+  <si>
+    <t>873804862</t>
+  </si>
+  <si>
+    <t>873962264</t>
+  </si>
+  <si>
+    <t>811453624</t>
+  </si>
+  <si>
+    <t>771299157</t>
+  </si>
+  <si>
+    <t>879762544</t>
+  </si>
+  <si>
+    <t>880757624</t>
+  </si>
+  <si>
+    <t>885219323</t>
+  </si>
+  <si>
+    <t>852658925</t>
+  </si>
+  <si>
+    <t>810321830</t>
+  </si>
+  <si>
+    <t>812392490</t>
+  </si>
+  <si>
+    <t>767136157</t>
+  </si>
+  <si>
+    <t>766982718</t>
+  </si>
+  <si>
+    <t>756306779</t>
+  </si>
+  <si>
+    <t>736541438</t>
+  </si>
+  <si>
+    <t>733029981</t>
+  </si>
+  <si>
+    <t>730349978</t>
+  </si>
+  <si>
+    <t>725937134</t>
+  </si>
+  <si>
+    <t>725186955</t>
+  </si>
+  <si>
+    <t>724383249</t>
+  </si>
+  <si>
+    <t>717402576</t>
+  </si>
+  <si>
+    <t>715449553</t>
+  </si>
+  <si>
+    <t>706878760</t>
+  </si>
+  <si>
+    <t>697689226</t>
+  </si>
+  <si>
+    <t>853397879</t>
+  </si>
+  <si>
+    <t>890389236</t>
+  </si>
+  <si>
+    <t>887568842</t>
+  </si>
+  <si>
+    <t>673462259</t>
+  </si>
+  <si>
+    <t>175765720</t>
+  </si>
+  <si>
+    <t>175242449</t>
+  </si>
+  <si>
+    <t>172089397</t>
+  </si>
+  <si>
+    <t>171994720</t>
   </si>
 </sst>
 </file>
@@ -628,7 +829,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -669,7 +870,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -678,10 +879,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -690,10 +891,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -702,10 +903,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -714,10 +915,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -726,10 +927,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -738,10 +939,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -750,10 +951,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -762,10 +963,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -774,10 +975,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -786,10 +987,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -798,10 +999,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -810,10 +1011,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -822,10 +1023,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -834,10 +1035,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -846,10 +1047,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -858,10 +1059,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -870,10 +1071,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -882,10 +1083,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -894,10 +1095,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -906,10 +1107,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -918,10 +1119,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -933,7 +1134,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -945,7 +1146,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -957,7 +1158,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -969,7 +1170,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -981,7 +1182,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -993,7 +1194,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1005,7 +1206,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1017,7 +1218,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1029,7 +1230,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1041,7 +1242,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1053,7 +1254,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1065,7 +1266,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1077,7 +1278,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1089,12 +1290,727 @@
         <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1119,31 +2035,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43FFB51-0BBE-4E7F-A083-E7502D540B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEBD372-FA25-466D-B0AA-03788D0E06EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="50">
   <si>
     <t>Status</t>
   </si>
@@ -48,82 +48,139 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>686215223</t>
+    <t>805279159</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>824363562</t>
-  </si>
-  <si>
-    <t>835162607</t>
-  </si>
-  <si>
-    <t>820607301</t>
-  </si>
-  <si>
-    <t>889946376</t>
-  </si>
-  <si>
-    <t>752764005</t>
-  </si>
-  <si>
-    <t>755911595</t>
-  </si>
-  <si>
-    <t>760333975</t>
-  </si>
-  <si>
-    <t>760246821</t>
-  </si>
-  <si>
-    <t>757921147</t>
-  </si>
-  <si>
-    <t>752707384</t>
-  </si>
-  <si>
-    <t>728659834</t>
-  </si>
-  <si>
-    <t>716983519</t>
-  </si>
-  <si>
-    <t>705707614</t>
-  </si>
-  <si>
-    <t>178894519</t>
+    <t>702852140</t>
+  </si>
+  <si>
+    <t>769889035</t>
+  </si>
+  <si>
+    <t>804306565</t>
+  </si>
+  <si>
+    <t>759929080</t>
+  </si>
+  <si>
+    <t>756105874</t>
+  </si>
+  <si>
+    <t>754717431</t>
+  </si>
+  <si>
+    <t>753865488</t>
+  </si>
+  <si>
+    <t>722613837</t>
+  </si>
+  <si>
+    <t>736769518</t>
+  </si>
+  <si>
+    <t>753068489</t>
+  </si>
+  <si>
+    <t>741474773</t>
+  </si>
+  <si>
+    <t>709600542</t>
+  </si>
+  <si>
+    <t>706536517</t>
+  </si>
+  <si>
+    <t>694045190</t>
+  </si>
+  <si>
+    <t>688195944</t>
+  </si>
+  <si>
+    <t>687913925</t>
+  </si>
+  <si>
+    <t>687382113</t>
+  </si>
+  <si>
+    <t>686597786</t>
+  </si>
+  <si>
+    <t>685866737</t>
+  </si>
+  <si>
+    <t>684372810</t>
+  </si>
+  <si>
+    <t>683857258</t>
+  </si>
+  <si>
+    <t>176477481</t>
+  </si>
+  <si>
+    <t>177002106</t>
+  </si>
+  <si>
+    <t>176990921</t>
+  </si>
+  <si>
+    <t>176789778</t>
+  </si>
+  <si>
+    <t>172371761</t>
+  </si>
+  <si>
+    <t>880372424</t>
+  </si>
+  <si>
+    <t>874807153</t>
+  </si>
+  <si>
+    <t>849723584</t>
+  </si>
+  <si>
+    <t>851712244</t>
+  </si>
+  <si>
+    <t>844549539</t>
+  </si>
+  <si>
+    <t>827846944</t>
+  </si>
+  <si>
+    <t>877222905</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>858053733</t>
-  </si>
-  <si>
-    <t>743909123</t>
-  </si>
-  <si>
-    <t>178756940</t>
-  </si>
-  <si>
-    <t>178675959</t>
-  </si>
-  <si>
-    <t>178675827</t>
-  </si>
-  <si>
-    <t>178585083</t>
-  </si>
-  <si>
-    <t>178566877</t>
-  </si>
-  <si>
-    <t>178561118</t>
-  </si>
-  <si>
-    <t>178446682</t>
+    <t>177864729</t>
+  </si>
+  <si>
+    <t>179904069</t>
+  </si>
+  <si>
+    <t>179903863</t>
+  </si>
+  <si>
+    <t>179655406</t>
+  </si>
+  <si>
+    <t>178675967</t>
+  </si>
+  <si>
+    <t>178549253</t>
+  </si>
+  <si>
+    <t>178549246</t>
+  </si>
+  <si>
+    <t>876960422</t>
+  </si>
+  <si>
+    <t>876657440</t>
   </si>
 </sst>
 </file>
@@ -589,7 +646,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -786,7 +843,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -795,10 +852,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -807,10 +864,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -819,10 +876,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -831,10 +888,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -843,10 +900,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -855,10 +912,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -867,10 +924,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -879,10 +936,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -891,67 +948,237 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="5"/>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D26"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="5"/>
+      <c r="A27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D27"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="5"/>
+      <c r="A28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D28"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C29" s="5"/>
+      <c r="A29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D29"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C30" s="5"/>
+      <c r="A30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D30"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C31" s="5"/>
+      <c r="A31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D31"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="5"/>
+      <c r="A32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D32"/>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="5"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="5"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D34"/>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="5"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D35"/>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="5"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D36"/>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="5"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D37"/>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="5"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C27FD7-9A7D-4AFE-8BB5-67290ABF3930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5076DBC8-6FC9-454A-B0DC-2FC8B408716D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="49">
   <si>
     <t>Status</t>
   </si>
@@ -48,199 +48,136 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>737988182</t>
+    <t>704859846</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>775942976</t>
-  </si>
-  <si>
-    <t>839530551</t>
-  </si>
-  <si>
-    <t>865301208</t>
-  </si>
-  <si>
-    <t>846947533</t>
-  </si>
-  <si>
-    <t>848597641</t>
-  </si>
-  <si>
-    <t>813791468</t>
-  </si>
-  <si>
-    <t>798688671</t>
-  </si>
-  <si>
-    <t>794553283</t>
-  </si>
-  <si>
-    <t>786081129</t>
-  </si>
-  <si>
-    <t>759710399</t>
-  </si>
-  <si>
-    <t>747961856</t>
-  </si>
-  <si>
-    <t>752673917</t>
-  </si>
-  <si>
-    <t>751898119</t>
-  </si>
-  <si>
-    <t>748328006</t>
-  </si>
-  <si>
-    <t>748069998</t>
-  </si>
-  <si>
-    <t>734198280</t>
-  </si>
-  <si>
-    <t>705949836</t>
-  </si>
-  <si>
-    <t>687707772</t>
-  </si>
-  <si>
-    <t>690522853</t>
-  </si>
-  <si>
-    <t>704057748</t>
-  </si>
-  <si>
-    <t>685794699</t>
-  </si>
-  <si>
-    <t>650489465</t>
-  </si>
-  <si>
-    <t>633613363</t>
-  </si>
-  <si>
-    <t>624941344</t>
-  </si>
-  <si>
-    <t>622673295</t>
-  </si>
-  <si>
-    <t>171967387</t>
-  </si>
-  <si>
-    <t>171956950</t>
-  </si>
-  <si>
-    <t>177775172</t>
+    <t>861259020</t>
+  </si>
+  <si>
+    <t>880072917</t>
+  </si>
+  <si>
+    <t>876185921</t>
+  </si>
+  <si>
+    <t>861231532</t>
+  </si>
+  <si>
+    <t>782074888</t>
+  </si>
+  <si>
+    <t>819602545</t>
+  </si>
+  <si>
+    <t>836098719</t>
+  </si>
+  <si>
+    <t>844747216</t>
+  </si>
+  <si>
+    <t>842865077</t>
+  </si>
+  <si>
+    <t>835671532</t>
+  </si>
+  <si>
+    <t>827765870</t>
+  </si>
+  <si>
+    <t>817542503</t>
+  </si>
+  <si>
+    <t>808648038</t>
+  </si>
+  <si>
+    <t>804537821</t>
+  </si>
+  <si>
+    <t>788614497</t>
+  </si>
+  <si>
+    <t>764191320</t>
+  </si>
+  <si>
+    <t>760754196</t>
+  </si>
+  <si>
+    <t>756813865</t>
+  </si>
+  <si>
+    <t>756647883</t>
+  </si>
+  <si>
+    <t>755905332</t>
+  </si>
+  <si>
+    <t>755441031</t>
+  </si>
+  <si>
+    <t>752870976</t>
+  </si>
+  <si>
+    <t>745839369</t>
+  </si>
+  <si>
+    <t>740256544</t>
+  </si>
+  <si>
+    <t>737112080</t>
+  </si>
+  <si>
+    <t>735632287</t>
+  </si>
+  <si>
+    <t>734872264</t>
+  </si>
+  <si>
+    <t>734008216</t>
+  </si>
+  <si>
+    <t>722286873</t>
+  </si>
+  <si>
+    <t>721594418</t>
+  </si>
+  <si>
+    <t>711077747</t>
+  </si>
+  <si>
+    <t>653180830</t>
+  </si>
+  <si>
+    <t>666980283</t>
+  </si>
+  <si>
+    <t>689455222</t>
+  </si>
+  <si>
+    <t>689245904</t>
+  </si>
+  <si>
+    <t>175132061</t>
+  </si>
+  <si>
+    <t>883523320</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>797114174</t>
-  </si>
-  <si>
-    <t>179533850</t>
-  </si>
-  <si>
-    <t>179121367</t>
-  </si>
-  <si>
-    <t>178971234</t>
-  </si>
-  <si>
-    <t>177776170</t>
-  </si>
-  <si>
-    <t>751894258</t>
-  </si>
-  <si>
-    <t>804763138</t>
-  </si>
-  <si>
-    <t>804733446</t>
-  </si>
-  <si>
-    <t>799563485</t>
-  </si>
-  <si>
-    <t>789825340</t>
-  </si>
-  <si>
-    <t>789808262</t>
-  </si>
-  <si>
-    <t>785119045</t>
-  </si>
-  <si>
-    <t>769488614</t>
-  </si>
-  <si>
-    <t>759361417</t>
-  </si>
-  <si>
-    <t>752841928</t>
-  </si>
-  <si>
-    <t>748321266</t>
-  </si>
-  <si>
-    <t>741343192</t>
-  </si>
-  <si>
-    <t>661876148</t>
-  </si>
-  <si>
-    <t>683259752</t>
-  </si>
-  <si>
-    <t>737727689</t>
-  </si>
-  <si>
-    <t>716797323</t>
-  </si>
-  <si>
-    <t>716931823</t>
-  </si>
-  <si>
-    <t>174708143</t>
-  </si>
-  <si>
-    <t>886424617</t>
-  </si>
-  <si>
-    <t>883564894</t>
-  </si>
-  <si>
-    <t>850699608</t>
-  </si>
-  <si>
-    <t>849837483</t>
-  </si>
-  <si>
-    <t>877308233</t>
-  </si>
-  <si>
-    <t>821942293</t>
-  </si>
-  <si>
-    <t>178371989</t>
-  </si>
-  <si>
-    <t>179000231</t>
-  </si>
-  <si>
-    <t>178940908</t>
-  </si>
-  <si>
-    <t>178551648</t>
-  </si>
-  <si>
-    <t>876731187</t>
+    <t>179230309</t>
+  </si>
+  <si>
+    <t>179029545</t>
+  </si>
+  <si>
+    <t>178587022</t>
+  </si>
+  <si>
+    <t>178553560</t>
   </si>
 </sst>
 </file>
@@ -706,7 +643,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1071,7 +1008,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1080,10 +1017,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1092,10 +1029,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1104,10 +1041,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1116,10 +1053,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1128,10 +1065,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1140,7 +1077,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>6</v>
@@ -1152,7 +1089,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>6</v>
@@ -1164,7 +1101,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>6</v>
@@ -1176,10 +1113,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1190,7 +1127,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1201,7 +1138,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1212,7 +1149,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1223,240 +1160,9 @@
         <v>48</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5076DBC8-6FC9-454A-B0DC-2FC8B408716D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC19A29A-C5EB-4658-B706-A0DBCA3E5D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="87">
   <si>
     <t>Status</t>
   </si>
@@ -178,6 +178,120 @@
   </si>
   <si>
     <t>178553560</t>
+  </si>
+  <si>
+    <t>809022142</t>
+  </si>
+  <si>
+    <t>691378743</t>
+  </si>
+  <si>
+    <t>771280819</t>
+  </si>
+  <si>
+    <t>754689507</t>
+  </si>
+  <si>
+    <t>748848508</t>
+  </si>
+  <si>
+    <t>746915911</t>
+  </si>
+  <si>
+    <t>745244982</t>
+  </si>
+  <si>
+    <t>739763187</t>
+  </si>
+  <si>
+    <t>716030410</t>
+  </si>
+  <si>
+    <t>707764225</t>
+  </si>
+  <si>
+    <t>708419894</t>
+  </si>
+  <si>
+    <t>702636014</t>
+  </si>
+  <si>
+    <t>626181840</t>
+  </si>
+  <si>
+    <t>177225616</t>
+  </si>
+  <si>
+    <t>859587770</t>
+  </si>
+  <si>
+    <t>859588166</t>
+  </si>
+  <si>
+    <t>871967703</t>
+  </si>
+  <si>
+    <t>836428825</t>
+  </si>
+  <si>
+    <t>807931344</t>
+  </si>
+  <si>
+    <t>774357457</t>
+  </si>
+  <si>
+    <t>783352549</t>
+  </si>
+  <si>
+    <t>781894765</t>
+  </si>
+  <si>
+    <t>781436484</t>
+  </si>
+  <si>
+    <t>780994814</t>
+  </si>
+  <si>
+    <t>873688000</t>
+  </si>
+  <si>
+    <t>859613469</t>
+  </si>
+  <si>
+    <t>178547778</t>
+  </si>
+  <si>
+    <t>179568369</t>
+  </si>
+  <si>
+    <t>179301845</t>
+  </si>
+  <si>
+    <t>179230804</t>
+  </si>
+  <si>
+    <t>179039148</t>
+  </si>
+  <si>
+    <t>178774208</t>
+  </si>
+  <si>
+    <t>178774083</t>
+  </si>
+  <si>
+    <t>178774034</t>
+  </si>
+  <si>
+    <t>178774026</t>
+  </si>
+  <si>
+    <t>863620161</t>
+  </si>
+  <si>
+    <t>825094968</t>
+  </si>
+  <si>
+    <t>810680698</t>
   </si>
 </sst>
 </file>
@@ -643,7 +757,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1163,6 +1277,424 @@
         <v>44</v>
       </c>
       <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A50870-1DFE-4644-956B-7D0D61AA5752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50D6E1B-28E7-4FA3-A03A-63AE29C2B98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RegularizarIncidencias" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
   <si>
     <t>Status</t>
   </si>
@@ -48,103 +48,103 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>828571053</t>
+    <t>176338824</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>800432233</t>
-  </si>
-  <si>
-    <t>803671985</t>
-  </si>
-  <si>
-    <t>806406363</t>
-  </si>
-  <si>
-    <t>759248903</t>
-  </si>
-  <si>
-    <t>762099962</t>
-  </si>
-  <si>
-    <t>760128987</t>
-  </si>
-  <si>
-    <t>690450097</t>
-  </si>
-  <si>
-    <t>737114847</t>
-  </si>
-  <si>
-    <t>737110951</t>
-  </si>
-  <si>
-    <t>735226262</t>
-  </si>
-  <si>
-    <t>733511095</t>
-  </si>
-  <si>
-    <t>696228380</t>
-  </si>
-  <si>
-    <t>693327615</t>
-  </si>
-  <si>
-    <t>692943180</t>
-  </si>
-  <si>
-    <t>859072112</t>
-  </si>
-  <si>
-    <t>174697940</t>
-  </si>
-  <si>
-    <t>872024447</t>
-  </si>
-  <si>
-    <t>892820337</t>
-  </si>
-  <si>
-    <t>844525307</t>
-  </si>
-  <si>
-    <t>844847180</t>
-  </si>
-  <si>
-    <t>835406459</t>
-  </si>
-  <si>
-    <t>839905514</t>
-  </si>
-  <si>
-    <t>825767993</t>
-  </si>
-  <si>
-    <t>860358401</t>
+    <t>797673351</t>
+  </si>
+  <si>
+    <t>845251853</t>
+  </si>
+  <si>
+    <t>852895527</t>
+  </si>
+  <si>
+    <t>848757005</t>
+  </si>
+  <si>
+    <t>835678867</t>
+  </si>
+  <si>
+    <t>834155263</t>
+  </si>
+  <si>
+    <t>828204895</t>
+  </si>
+  <si>
+    <t>814686196</t>
+  </si>
+  <si>
+    <t>753432701</t>
+  </si>
+  <si>
+    <t>766493625</t>
+  </si>
+  <si>
+    <t>782559185</t>
+  </si>
+  <si>
+    <t>781991454</t>
+  </si>
+  <si>
+    <t>765243294</t>
+  </si>
+  <si>
+    <t>755803644</t>
+  </si>
+  <si>
+    <t>727278362</t>
+  </si>
+  <si>
+    <t>734030830</t>
+  </si>
+  <si>
+    <t>693719209</t>
+  </si>
+  <si>
+    <t>697646457</t>
+  </si>
+  <si>
+    <t>715590471</t>
+  </si>
+  <si>
+    <t>175547102</t>
+  </si>
+  <si>
+    <t>819813472</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>178135020</t>
-  </si>
-  <si>
-    <t>884454350</t>
-  </si>
-  <si>
-    <t>884188123</t>
-  </si>
-  <si>
-    <t>881235075</t>
-  </si>
-  <si>
-    <t>884102918</t>
-  </si>
-  <si>
-    <t>857587871</t>
+    <t>883010070</t>
+  </si>
+  <si>
+    <t>883782629</t>
+  </si>
+  <si>
+    <t>879998643</t>
+  </si>
+  <si>
+    <t>862225913</t>
+  </si>
+  <si>
+    <t>801354873</t>
+  </si>
+  <si>
+    <t>179064393</t>
+  </si>
+  <si>
+    <t>179711506</t>
+  </si>
+  <si>
+    <t>178737791</t>
+  </si>
+  <si>
+    <t>178546739</t>
   </si>
 </sst>
 </file>
@@ -891,7 +891,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -900,10 +900,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -939,7 +939,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -951,7 +951,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -963,7 +963,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -975,7 +975,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -987,7 +987,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -999,7 +999,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1007,39 +1007,27 @@
       <c r="D32"/>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C33" s="5"/>
       <c r="D33"/>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C34" s="5"/>
       <c r="D34"/>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C35" s="5"/>
       <c r="D35"/>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C36" s="5"/>
       <c r="D36"/>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C37" s="5"/>
       <c r="D37"/>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C38" s="5"/>
       <c r="D38"/>
     </row>
   </sheetData>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50D6E1B-28E7-4FA3-A03A-63AE29C2B98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5FFA52-2066-43B6-8C49-46126232FC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="41">
   <si>
     <t>Status</t>
   </si>
@@ -48,103 +48,112 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>176338824</t>
+    <t>872023654</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>797673351</t>
-  </si>
-  <si>
-    <t>845251853</t>
-  </si>
-  <si>
-    <t>852895527</t>
-  </si>
-  <si>
-    <t>848757005</t>
-  </si>
-  <si>
-    <t>835678867</t>
-  </si>
-  <si>
-    <t>834155263</t>
-  </si>
-  <si>
-    <t>828204895</t>
-  </si>
-  <si>
-    <t>814686196</t>
-  </si>
-  <si>
-    <t>753432701</t>
-  </si>
-  <si>
-    <t>766493625</t>
-  </si>
-  <si>
-    <t>782559185</t>
-  </si>
-  <si>
-    <t>781991454</t>
-  </si>
-  <si>
-    <t>765243294</t>
-  </si>
-  <si>
-    <t>755803644</t>
-  </si>
-  <si>
-    <t>727278362</t>
-  </si>
-  <si>
-    <t>734030830</t>
-  </si>
-  <si>
-    <t>693719209</t>
-  </si>
-  <si>
-    <t>697646457</t>
-  </si>
-  <si>
-    <t>715590471</t>
-  </si>
-  <si>
-    <t>175547102</t>
-  </si>
-  <si>
-    <t>819813472</t>
+    <t>849724954</t>
+  </si>
+  <si>
+    <t>837228968</t>
+  </si>
+  <si>
+    <t>832993657</t>
+  </si>
+  <si>
+    <t>832991933</t>
+  </si>
+  <si>
+    <t>804813602</t>
+  </si>
+  <si>
+    <t>787183031</t>
+  </si>
+  <si>
+    <t>797254749</t>
+  </si>
+  <si>
+    <t>790232957</t>
+  </si>
+  <si>
+    <t>733178515</t>
+  </si>
+  <si>
+    <t>757772185</t>
+  </si>
+  <si>
+    <t>777207204</t>
+  </si>
+  <si>
+    <t>775605912</t>
+  </si>
+  <si>
+    <t>765996461</t>
+  </si>
+  <si>
+    <t>764872812</t>
+  </si>
+  <si>
+    <t>760522262</t>
+  </si>
+  <si>
+    <t>742957925</t>
+  </si>
+  <si>
+    <t>750890679</t>
+  </si>
+  <si>
+    <t>741338010</t>
+  </si>
+  <si>
+    <t>740191220</t>
+  </si>
+  <si>
+    <t>728409800</t>
+  </si>
+  <si>
+    <t>698942236</t>
+  </si>
+  <si>
+    <t>695523351</t>
+  </si>
+  <si>
+    <t>695478861</t>
+  </si>
+  <si>
+    <t>693898318</t>
+  </si>
+  <si>
+    <t>590660738</t>
+  </si>
+  <si>
+    <t>173223912</t>
+  </si>
+  <si>
+    <t>178790816</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>883010070</t>
-  </si>
-  <si>
-    <t>883782629</t>
-  </si>
-  <si>
-    <t>879998643</t>
-  </si>
-  <si>
-    <t>862225913</t>
-  </si>
-  <si>
-    <t>801354873</t>
-  </si>
-  <si>
-    <t>179064393</t>
-  </si>
-  <si>
-    <t>179711506</t>
-  </si>
-  <si>
-    <t>178737791</t>
-  </si>
-  <si>
-    <t>178546739</t>
+    <t>823361815</t>
+  </si>
+  <si>
+    <t>867129359</t>
+  </si>
+  <si>
+    <t>179805639</t>
+  </si>
+  <si>
+    <t>179436328</t>
+  </si>
+  <si>
+    <t>179108570</t>
+  </si>
+  <si>
+    <t>179028315</t>
   </si>
 </sst>
 </file>
@@ -891,7 +900,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -900,10 +909,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -912,10 +921,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -924,10 +933,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -936,10 +945,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -948,10 +957,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -960,10 +969,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -975,7 +984,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -987,7 +996,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -999,34 +1008,58 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D32"/>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="5"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="5"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D34"/>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="5"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D35"/>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C36" s="5"/>
       <c r="D36"/>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C37" s="5"/>
       <c r="D37"/>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C38" s="5"/>
       <c r="D38"/>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5FFA52-2066-43B6-8C49-46126232FC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CC5978-9F58-448B-8AA4-140613282CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RegularizarIncidencias" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="60">
   <si>
     <t>Status</t>
   </si>
@@ -48,112 +48,169 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>872023654</t>
+    <t>847466061</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>849724954</t>
-  </si>
-  <si>
-    <t>837228968</t>
-  </si>
-  <si>
-    <t>832993657</t>
-  </si>
-  <si>
-    <t>832991933</t>
-  </si>
-  <si>
-    <t>804813602</t>
-  </si>
-  <si>
-    <t>787183031</t>
-  </si>
-  <si>
-    <t>797254749</t>
-  </si>
-  <si>
-    <t>790232957</t>
-  </si>
-  <si>
-    <t>733178515</t>
-  </si>
-  <si>
-    <t>757772185</t>
-  </si>
-  <si>
-    <t>777207204</t>
-  </si>
-  <si>
-    <t>775605912</t>
-  </si>
-  <si>
-    <t>765996461</t>
-  </si>
-  <si>
-    <t>764872812</t>
-  </si>
-  <si>
-    <t>760522262</t>
-  </si>
-  <si>
-    <t>742957925</t>
-  </si>
-  <si>
-    <t>750890679</t>
-  </si>
-  <si>
-    <t>741338010</t>
-  </si>
-  <si>
-    <t>740191220</t>
-  </si>
-  <si>
-    <t>728409800</t>
-  </si>
-  <si>
-    <t>698942236</t>
-  </si>
-  <si>
-    <t>695523351</t>
-  </si>
-  <si>
-    <t>695478861</t>
-  </si>
-  <si>
-    <t>693898318</t>
-  </si>
-  <si>
-    <t>590660738</t>
-  </si>
-  <si>
-    <t>173223912</t>
-  </si>
-  <si>
-    <t>178790816</t>
+    <t>735928578</t>
+  </si>
+  <si>
+    <t>741396091</t>
+  </si>
+  <si>
+    <t>748791302</t>
+  </si>
+  <si>
+    <t>746816077</t>
+  </si>
+  <si>
+    <t>746629173</t>
+  </si>
+  <si>
+    <t>745881452</t>
+  </si>
+  <si>
+    <t>705940579</t>
+  </si>
+  <si>
+    <t>704740400</t>
+  </si>
+  <si>
+    <t>697729881</t>
+  </si>
+  <si>
+    <t>696172646</t>
+  </si>
+  <si>
+    <t>695575328</t>
+  </si>
+  <si>
+    <t>173739669</t>
+  </si>
+  <si>
+    <t>177566167</t>
+  </si>
+  <si>
+    <t>839830282</t>
+  </si>
+  <si>
+    <t>762745085</t>
+  </si>
+  <si>
+    <t>753848864</t>
+  </si>
+  <si>
+    <t>825291531</t>
+  </si>
+  <si>
+    <t>827947148</t>
+  </si>
+  <si>
+    <t>825278660</t>
+  </si>
+  <si>
+    <t>814205658</t>
+  </si>
+  <si>
+    <t>818689667</t>
+  </si>
+  <si>
+    <t>809648268</t>
+  </si>
+  <si>
+    <t>800488607</t>
+  </si>
+  <si>
+    <t>799486141</t>
+  </si>
+  <si>
+    <t>779650708</t>
+  </si>
+  <si>
+    <t>778592869</t>
+  </si>
+  <si>
+    <t>768004792</t>
+  </si>
+  <si>
+    <t>776515847</t>
+  </si>
+  <si>
+    <t>771603952</t>
+  </si>
+  <si>
+    <t>765940360</t>
+  </si>
+  <si>
+    <t>764739730</t>
+  </si>
+  <si>
+    <t>765595545</t>
+  </si>
+  <si>
+    <t>855691717</t>
+  </si>
+  <si>
+    <t>876877964</t>
+  </si>
+  <si>
+    <t>869028377</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>823361815</t>
-  </si>
-  <si>
-    <t>867129359</t>
-  </si>
-  <si>
-    <t>179805639</t>
-  </si>
-  <si>
-    <t>179436328</t>
-  </si>
-  <si>
-    <t>179108570</t>
-  </si>
-  <si>
-    <t>179028315</t>
+    <t>177939265</t>
+  </si>
+  <si>
+    <t>179309210</t>
+  </si>
+  <si>
+    <t>179153758</t>
+  </si>
+  <si>
+    <t>179150952</t>
+  </si>
+  <si>
+    <t>179104454</t>
+  </si>
+  <si>
+    <t>178738112</t>
+  </si>
+  <si>
+    <t>178732685</t>
+  </si>
+  <si>
+    <t>178732669</t>
+  </si>
+  <si>
+    <t>178595546</t>
+  </si>
+  <si>
+    <t>178554428</t>
+  </si>
+  <si>
+    <t>178554410</t>
+  </si>
+  <si>
+    <t>178554402</t>
+  </si>
+  <si>
+    <t>178364836</t>
+  </si>
+  <si>
+    <t>178044917</t>
+  </si>
+  <si>
+    <t>834839742</t>
+  </si>
+  <si>
+    <t>794130306</t>
+  </si>
+  <si>
+    <t>798878850</t>
   </si>
 </sst>
 </file>
@@ -619,7 +676,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -972,7 +1029,7 @@
         <v>33</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -981,10 +1038,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -993,10 +1050,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1005,10 +1062,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1017,10 +1074,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1029,10 +1086,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1041,27 +1098,227 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="5"/>
+      <c r="B36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D36"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="5"/>
+      <c r="A37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D37"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="5"/>
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1794CE0B-6D60-4F12-A65C-AFBBDC0B1724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EF7B7A-DEF4-41D9-A95E-54F753DE7660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="54">
   <si>
     <t>Status</t>
   </si>
@@ -48,145 +48,151 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>845957970</t>
+    <t>827180781</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>872054337</t>
-  </si>
-  <si>
-    <t>864887710</t>
-  </si>
-  <si>
-    <t>842421475</t>
-  </si>
-  <si>
-    <t>838357030</t>
-  </si>
-  <si>
-    <t>828418917</t>
-  </si>
-  <si>
-    <t>800859005</t>
-  </si>
-  <si>
-    <t>828204903</t>
-  </si>
-  <si>
-    <t>810939995</t>
-  </si>
-  <si>
-    <t>787997778</t>
-  </si>
-  <si>
-    <t>753923444</t>
-  </si>
-  <si>
-    <t>783386596</t>
-  </si>
-  <si>
-    <t>782268738</t>
-  </si>
-  <si>
-    <t>778929897</t>
-  </si>
-  <si>
-    <t>776720108</t>
-  </si>
-  <si>
-    <t>709749521</t>
-  </si>
-  <si>
-    <t>748751249</t>
-  </si>
-  <si>
-    <t>736846217</t>
-  </si>
-  <si>
-    <t>733459220</t>
-  </si>
-  <si>
-    <t>901919740</t>
-  </si>
-  <si>
-    <t>880915149</t>
-  </si>
-  <si>
-    <t>880915131</t>
-  </si>
-  <si>
-    <t>872054352</t>
-  </si>
-  <si>
-    <t>877183479</t>
+    <t>880880400</t>
+  </si>
+  <si>
+    <t>844728299</t>
+  </si>
+  <si>
+    <t>877510499</t>
+  </si>
+  <si>
+    <t>880880384</t>
+  </si>
+  <si>
+    <t>841604204</t>
+  </si>
+  <si>
+    <t>783903762</t>
+  </si>
+  <si>
+    <t>782452829</t>
+  </si>
+  <si>
+    <t>751898804</t>
+  </si>
+  <si>
+    <t>769572391</t>
+  </si>
+  <si>
+    <t>782071249</t>
+  </si>
+  <si>
+    <t>780248039</t>
+  </si>
+  <si>
+    <t>779147739</t>
+  </si>
+  <si>
+    <t>777744495</t>
+  </si>
+  <si>
+    <t>777114236</t>
+  </si>
+  <si>
+    <t>776712006</t>
+  </si>
+  <si>
+    <t>776025193</t>
+  </si>
+  <si>
+    <t>770337487</t>
+  </si>
+  <si>
+    <t>764188961</t>
+  </si>
+  <si>
+    <t>760041792</t>
+  </si>
+  <si>
+    <t>756474809</t>
+  </si>
+  <si>
+    <t>755003880</t>
+  </si>
+  <si>
+    <t>749368746</t>
+  </si>
+  <si>
+    <t>733498020</t>
+  </si>
+  <si>
+    <t>723900332</t>
+  </si>
+  <si>
+    <t>718864188</t>
+  </si>
+  <si>
+    <t>711790778</t>
+  </si>
+  <si>
+    <t>709724938</t>
+  </si>
+  <si>
+    <t>705400863</t>
+  </si>
+  <si>
+    <t>688948599</t>
+  </si>
+  <si>
+    <t>684664414</t>
+  </si>
+  <si>
+    <t>177002114</t>
+  </si>
+  <si>
+    <t>178367334</t>
+  </si>
+  <si>
+    <t>177627498</t>
+  </si>
+  <si>
+    <t>909114484</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>870670118</t>
-  </si>
-  <si>
-    <t>792648317</t>
-  </si>
-  <si>
-    <t>845869274</t>
-  </si>
-  <si>
-    <t>812557183</t>
-  </si>
-  <si>
-    <t>824297125</t>
-  </si>
-  <si>
-    <t>821563453</t>
-  </si>
-  <si>
-    <t>806845909</t>
-  </si>
-  <si>
-    <t>179450808</t>
-  </si>
-  <si>
-    <t>179399195</t>
-  </si>
-  <si>
-    <t>179331768</t>
-  </si>
-  <si>
-    <t>179065853</t>
-  </si>
-  <si>
-    <t>903348690</t>
-  </si>
-  <si>
-    <t>903437584</t>
-  </si>
-  <si>
-    <t>903425860</t>
-  </si>
-  <si>
-    <t>903365827</t>
-  </si>
-  <si>
-    <t>903351827</t>
-  </si>
-  <si>
-    <t>902746928</t>
-  </si>
-  <si>
-    <t>902738503</t>
-  </si>
-  <si>
-    <t>902586126</t>
-  </si>
-  <si>
-    <t>896624404</t>
-  </si>
-  <si>
-    <t>896624396</t>
+    <t>709707081</t>
+  </si>
+  <si>
+    <t>880020650</t>
+  </si>
+  <si>
+    <t>869705263</t>
+  </si>
+  <si>
+    <t>778784466</t>
+  </si>
+  <si>
+    <t>180815536</t>
+  </si>
+  <si>
+    <t>179718626</t>
+  </si>
+  <si>
+    <t>179533397</t>
+  </si>
+  <si>
+    <t>179443449</t>
+  </si>
+  <si>
+    <t>179337773</t>
+  </si>
+  <si>
+    <t>179333541</t>
+  </si>
+  <si>
+    <t>179200161</t>
+  </si>
+  <si>
+    <t>179144088</t>
   </si>
 </sst>
 </file>
@@ -652,7 +658,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -957,7 +963,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -966,10 +972,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -978,10 +984,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -990,10 +996,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1002,10 +1008,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1014,10 +1020,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1026,10 +1032,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1038,10 +1044,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1050,10 +1056,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1062,10 +1068,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1074,10 +1080,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1086,10 +1092,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1101,7 +1107,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1113,7 +1119,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1125,7 +1131,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1136,7 +1142,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1147,7 +1153,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1158,7 +1164,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1169,7 +1175,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1180,7 +1186,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1191,7 +1197,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1202,9 +1208,31 @@
         <v>51</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C46" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1231,31 +1259,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E999BBB4-667B-4B4D-BAF3-43D02F00A467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D266DD5C-D631-469A-ABF0-497A11D556D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="52">
   <si>
     <t>Status</t>
   </si>
@@ -48,181 +48,145 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>904375494</t>
+    <t>802034292</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>764578013</t>
-  </si>
-  <si>
-    <t>792155438</t>
-  </si>
-  <si>
-    <t>813997289</t>
-  </si>
-  <si>
-    <t>817542511</t>
-  </si>
-  <si>
-    <t>809365848</t>
-  </si>
-  <si>
-    <t>798264887</t>
-  </si>
-  <si>
-    <t>797114182</t>
-  </si>
-  <si>
-    <t>790234425</t>
-  </si>
-  <si>
-    <t>788580888</t>
-  </si>
-  <si>
-    <t>788408171</t>
-  </si>
-  <si>
-    <t>788318651</t>
-  </si>
-  <si>
-    <t>785509849</t>
-  </si>
-  <si>
-    <t>766099893</t>
-  </si>
-  <si>
-    <t>764988279</t>
-  </si>
-  <si>
-    <t>734244944</t>
-  </si>
-  <si>
-    <t>648233488</t>
-  </si>
-  <si>
-    <t>922583277</t>
-  </si>
-  <si>
-    <t>908765393</t>
-  </si>
-  <si>
-    <t>881907889</t>
-  </si>
-  <si>
-    <t>826381927</t>
-  </si>
-  <si>
-    <t>825642840</t>
-  </si>
-  <si>
-    <t>872131432</t>
-  </si>
-  <si>
-    <t>860812662</t>
-  </si>
-  <si>
-    <t>852874316</t>
-  </si>
-  <si>
-    <t>851053441</t>
-  </si>
-  <si>
-    <t>837130008</t>
+    <t>827902002</t>
+  </si>
+  <si>
+    <t>920368085</t>
+  </si>
+  <si>
+    <t>885547889</t>
+  </si>
+  <si>
+    <t>855377846</t>
+  </si>
+  <si>
+    <t>872112705</t>
+  </si>
+  <si>
+    <t>865612554</t>
+  </si>
+  <si>
+    <t>843657945</t>
+  </si>
+  <si>
+    <t>803068836</t>
+  </si>
+  <si>
+    <t>809681517</t>
+  </si>
+  <si>
+    <t>790500585</t>
+  </si>
+  <si>
+    <t>720022338</t>
+  </si>
+  <si>
+    <t>785601364</t>
+  </si>
+  <si>
+    <t>770580128</t>
+  </si>
+  <si>
+    <t>690378827</t>
+  </si>
+  <si>
+    <t>180009817</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>824388049</t>
-  </si>
-  <si>
-    <t>723897264</t>
-  </si>
-  <si>
-    <t>784852059</t>
-  </si>
-  <si>
-    <t>810974091</t>
-  </si>
-  <si>
-    <t>789216128</t>
-  </si>
-  <si>
-    <t>789232356</t>
-  </si>
-  <si>
-    <t>776215927</t>
-  </si>
-  <si>
-    <t>748320649</t>
-  </si>
-  <si>
-    <t>178764910</t>
-  </si>
-  <si>
-    <t>179555226</t>
-  </si>
-  <si>
-    <t>178792762</t>
-  </si>
-  <si>
-    <t>178765065</t>
-  </si>
-  <si>
-    <t>175953227</t>
-  </si>
-  <si>
-    <t>878439094</t>
-  </si>
-  <si>
-    <t>921202762</t>
-  </si>
-  <si>
-    <t>915711513</t>
-  </si>
-  <si>
-    <t>914175132</t>
-  </si>
-  <si>
-    <t>914147222</t>
-  </si>
-  <si>
-    <t>909332698</t>
-  </si>
-  <si>
-    <t>913629923</t>
-  </si>
-  <si>
-    <t>901689491</t>
-  </si>
-  <si>
-    <t>896478678</t>
-  </si>
-  <si>
-    <t>892090097</t>
-  </si>
-  <si>
-    <t>886455363</t>
-  </si>
-  <si>
-    <t>885344923</t>
-  </si>
-  <si>
-    <t>862064320</t>
-  </si>
-  <si>
-    <t>874037934</t>
-  </si>
-  <si>
-    <t>875873741</t>
-  </si>
-  <si>
-    <t>865622843</t>
-  </si>
-  <si>
-    <t>829755747</t>
+    <t>812401119</t>
+  </si>
+  <si>
+    <t>884877048</t>
+  </si>
+  <si>
+    <t>915779148</t>
+  </si>
+  <si>
+    <t>915450492</t>
+  </si>
+  <si>
+    <t>915017796</t>
+  </si>
+  <si>
+    <t>893645154</t>
+  </si>
+  <si>
+    <t>909445086</t>
+  </si>
+  <si>
+    <t>884410337</t>
+  </si>
+  <si>
+    <t>882407640</t>
+  </si>
+  <si>
+    <t>873720340</t>
+  </si>
+  <si>
+    <t>864974955</t>
+  </si>
+  <si>
+    <t>871074021</t>
+  </si>
+  <si>
+    <t>862507534</t>
+  </si>
+  <si>
+    <t>859992681</t>
+  </si>
+  <si>
+    <t>855394445</t>
+  </si>
+  <si>
+    <t>855106344</t>
+  </si>
+  <si>
+    <t>832880631</t>
+  </si>
+  <si>
+    <t>832441558</t>
+  </si>
+  <si>
+    <t>831737402</t>
+  </si>
+  <si>
+    <t>826229613</t>
+  </si>
+  <si>
+    <t>818722302</t>
+  </si>
+  <si>
+    <t>816575074</t>
+  </si>
+  <si>
+    <t>796711103</t>
+  </si>
+  <si>
+    <t>801505037</t>
+  </si>
+  <si>
+    <t>787608573</t>
+  </si>
+  <si>
+    <t>786628291</t>
+  </si>
+  <si>
+    <t>179698927</t>
+  </si>
+  <si>
+    <t>179319003</t>
+  </si>
+  <si>
+    <t>179316678</t>
   </si>
 </sst>
 </file>
@@ -688,7 +652,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -897,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -906,10 +870,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -918,10 +882,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -930,10 +894,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -942,10 +906,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -954,10 +918,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -966,10 +930,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -978,10 +942,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -990,10 +954,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -1002,10 +966,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -1014,10 +978,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1026,10 +990,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1041,7 +1005,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1053,7 +1017,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1065,7 +1029,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1077,7 +1041,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1089,7 +1053,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1101,7 +1065,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1113,7 +1077,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1125,7 +1089,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1137,7 +1101,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1149,7 +1113,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1161,7 +1125,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1172,7 +1136,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1183,7 +1147,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1194,7 +1158,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1205,7 +1169,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1216,7 +1180,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1227,7 +1191,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1238,141 +1202,9 @@
         <v>51</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22891A01-8C6B-4EA9-8D77-72C575DEBCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D73B60-2E77-4751-A2C0-36464EC1252C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="177">
   <si>
     <t>Status</t>
   </si>
@@ -48,481 +48,520 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>790505071</t>
-  </si>
-  <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>791711637</t>
-  </si>
-  <si>
-    <t>792875688</t>
-  </si>
-  <si>
-    <t>792443305</t>
-  </si>
-  <si>
-    <t>793385372</t>
-  </si>
-  <si>
-    <t>796600645</t>
-  </si>
-  <si>
-    <t>797200940</t>
-  </si>
-  <si>
-    <t>799306554</t>
-  </si>
-  <si>
-    <t>800798344</t>
-  </si>
-  <si>
-    <t>802107403</t>
-  </si>
-  <si>
-    <t>801844113</t>
-  </si>
-  <si>
-    <t>802999346</t>
-  </si>
-  <si>
-    <t>803953599</t>
-  </si>
-  <si>
-    <t>804319485</t>
-  </si>
-  <si>
-    <t>804464877</t>
-  </si>
-  <si>
-    <t>804646846</t>
-  </si>
-  <si>
-    <t>805379744</t>
-  </si>
-  <si>
-    <t>806642538</t>
-  </si>
-  <si>
-    <t>806637264</t>
-  </si>
-  <si>
-    <t>807214972</t>
-  </si>
-  <si>
-    <t>808624690</t>
-  </si>
-  <si>
-    <t>810548994</t>
-  </si>
-  <si>
-    <t>812124638</t>
-  </si>
-  <si>
-    <t>814984583</t>
-  </si>
-  <si>
-    <t>815435031</t>
-  </si>
-  <si>
-    <t>816830503</t>
-  </si>
-  <si>
-    <t>816161859</t>
-  </si>
-  <si>
-    <t>818322780</t>
-  </si>
-  <si>
-    <t>819826151</t>
-  </si>
-  <si>
-    <t>818312518</t>
-  </si>
-  <si>
-    <t>818719258</t>
-  </si>
-  <si>
-    <t>818936043</t>
-  </si>
-  <si>
-    <t>820237216</t>
-  </si>
-  <si>
-    <t>821362146</t>
-  </si>
-  <si>
-    <t>822867168</t>
-  </si>
-  <si>
-    <t>827109616</t>
-  </si>
-  <si>
-    <t>831845999</t>
-  </si>
-  <si>
-    <t>832929453</t>
-  </si>
-  <si>
-    <t>836177166</t>
-  </si>
-  <si>
-    <t>840927242</t>
-  </si>
-  <si>
-    <t>840842656</t>
-  </si>
-  <si>
-    <t>841072303</t>
-  </si>
-  <si>
-    <t>841582293</t>
-  </si>
-  <si>
-    <t>841570991</t>
-  </si>
-  <si>
-    <t>842988929</t>
-  </si>
-  <si>
-    <t>843569033</t>
-  </si>
-  <si>
-    <t>847235383</t>
-  </si>
-  <si>
-    <t>848186007</t>
-  </si>
-  <si>
-    <t>707716027</t>
-  </si>
-  <si>
-    <t>724447887</t>
-  </si>
-  <si>
-    <t>840956506</t>
-  </si>
-  <si>
-    <t>667077915</t>
-  </si>
-  <si>
-    <t>667077402</t>
-  </si>
-  <si>
-    <t>667076370</t>
-  </si>
-  <si>
-    <t>671724585</t>
-  </si>
-  <si>
-    <t>671630063</t>
-  </si>
-  <si>
-    <t>672021122</t>
-  </si>
-  <si>
-    <t>674545870</t>
-  </si>
-  <si>
-    <t>677469318</t>
-  </si>
-  <si>
-    <t>676952520</t>
-  </si>
-  <si>
-    <t>678513882</t>
-  </si>
-  <si>
-    <t>679675946</t>
-  </si>
-  <si>
-    <t>678295118</t>
-  </si>
-  <si>
-    <t>681028688</t>
-  </si>
-  <si>
-    <t>834776431</t>
-  </si>
-  <si>
-    <t>681960930</t>
-  </si>
-  <si>
-    <t>683241842</t>
-  </si>
-  <si>
-    <t>688514409</t>
-  </si>
-  <si>
-    <t>688909815</t>
-  </si>
-  <si>
-    <t>688902778</t>
-  </si>
-  <si>
-    <t>690649482</t>
-  </si>
-  <si>
-    <t>689951394</t>
-  </si>
-  <si>
-    <t>693798161</t>
-  </si>
-  <si>
-    <t>694105200</t>
-  </si>
-  <si>
-    <t>695367205</t>
-  </si>
-  <si>
-    <t>694386206</t>
-  </si>
-  <si>
-    <t>695757322</t>
-  </si>
-  <si>
-    <t>695881882</t>
-  </si>
-  <si>
-    <t>698232414</t>
-  </si>
-  <si>
-    <t>698796046</t>
-  </si>
-  <si>
-    <t>701575833</t>
-  </si>
-  <si>
-    <t>704960735</t>
-  </si>
-  <si>
-    <t>708738921</t>
-  </si>
-  <si>
-    <t>708881374</t>
-  </si>
-  <si>
-    <t>709802122</t>
-  </si>
-  <si>
-    <t>710417225</t>
-  </si>
-  <si>
-    <t>714475104</t>
-  </si>
-  <si>
-    <t>714344805</t>
-  </si>
-  <si>
-    <t>715836700</t>
-  </si>
-  <si>
-    <t>717830263</t>
-  </si>
-  <si>
-    <t>723912915</t>
-  </si>
-  <si>
-    <t>724160985</t>
-  </si>
-  <si>
-    <t>729389654</t>
-  </si>
-  <si>
-    <t>729759393</t>
-  </si>
-  <si>
-    <t>730447574</t>
-  </si>
-  <si>
-    <t>732401389</t>
-  </si>
-  <si>
-    <t>731716332</t>
-  </si>
-  <si>
-    <t>732467810</t>
-  </si>
-  <si>
-    <t>736821012</t>
-  </si>
-  <si>
-    <t>871135004</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>874651684</t>
-  </si>
-  <si>
-    <t>920752874</t>
-  </si>
-  <si>
-    <t>905320283</t>
-  </si>
-  <si>
-    <t>883773446</t>
-  </si>
-  <si>
-    <t>854860289</t>
-  </si>
-  <si>
-    <t>852027394</t>
-  </si>
-  <si>
-    <t>848188094</t>
-  </si>
-  <si>
-    <t>844847198</t>
-  </si>
-  <si>
-    <t>830947663</t>
-  </si>
-  <si>
-    <t>825768009</t>
-  </si>
-  <si>
-    <t>784222972</t>
-  </si>
-  <si>
-    <t>799847151</t>
-  </si>
-  <si>
-    <t>814198176</t>
-  </si>
-  <si>
-    <t>809648276</t>
-  </si>
-  <si>
-    <t>809608387</t>
-  </si>
-  <si>
-    <t>806308858</t>
-  </si>
-  <si>
-    <t>796906778</t>
-  </si>
-  <si>
-    <t>787994759</t>
-  </si>
-  <si>
-    <t>784413092</t>
-  </si>
-  <si>
-    <t>770603409</t>
-  </si>
-  <si>
-    <t>771226382</t>
-  </si>
-  <si>
-    <t>769676358</t>
-  </si>
-  <si>
-    <t>748766577</t>
-  </si>
-  <si>
-    <t>762279572</t>
-  </si>
-  <si>
-    <t>764541672</t>
-  </si>
-  <si>
-    <t>763835083</t>
-  </si>
-  <si>
-    <t>756683508</t>
-  </si>
-  <si>
-    <t>746982887</t>
-  </si>
-  <si>
-    <t>731080689</t>
-  </si>
-  <si>
-    <t>731389064</t>
-  </si>
-  <si>
-    <t>743584215</t>
-  </si>
-  <si>
-    <t>734370616</t>
-  </si>
-  <si>
-    <t>731544460</t>
-  </si>
-  <si>
-    <t>722539321</t>
-  </si>
-  <si>
-    <t>720965759</t>
-  </si>
-  <si>
-    <t>712791361</t>
-  </si>
-  <si>
-    <t>719982575</t>
-  </si>
-  <si>
-    <t>692227238</t>
-  </si>
-  <si>
-    <t>692190972</t>
-  </si>
-  <si>
-    <t>172087755</t>
-  </si>
-  <si>
-    <t>629276696</t>
-  </si>
-  <si>
-    <t>178799601</t>
-  </si>
-  <si>
-    <t>178335844</t>
-  </si>
-  <si>
-    <t>178174672</t>
-  </si>
-  <si>
-    <t>179361674</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>883619987</t>
-  </si>
-  <si>
-    <t>891327672</t>
-  </si>
-  <si>
-    <t>855118364</t>
-  </si>
-  <si>
-    <t>799358589</t>
-  </si>
-  <si>
-    <t>822897678</t>
-  </si>
-  <si>
-    <t>799927250</t>
-  </si>
-  <si>
-    <t>805660077</t>
-  </si>
-  <si>
-    <t>791429073</t>
-  </si>
-  <si>
-    <t>781643022</t>
-  </si>
-  <si>
-    <t>179319300</t>
-  </si>
-  <si>
-    <t>179319292</t>
+    <t>688909823</t>
+  </si>
+  <si>
+    <t>692846540</t>
+  </si>
+  <si>
+    <t>692776440</t>
+  </si>
+  <si>
+    <t>692044096</t>
+  </si>
+  <si>
+    <t>694418348</t>
+  </si>
+  <si>
+    <t>693798179</t>
+  </si>
+  <si>
+    <t>695367213</t>
+  </si>
+  <si>
+    <t>694260211</t>
+  </si>
+  <si>
+    <t>695757330</t>
+  </si>
+  <si>
+    <t>698796053</t>
+  </si>
+  <si>
+    <t>701109757</t>
+  </si>
+  <si>
+    <t>701223871</t>
+  </si>
+  <si>
+    <t>702582523</t>
+  </si>
+  <si>
+    <t>702141965</t>
+  </si>
+  <si>
+    <t>702751714</t>
+  </si>
+  <si>
+    <t>703216550</t>
+  </si>
+  <si>
+    <t>705011983</t>
+  </si>
+  <si>
+    <t>708064146</t>
+  </si>
+  <si>
+    <t>708738939</t>
+  </si>
+  <si>
+    <t>710236765</t>
+  </si>
+  <si>
+    <t>714523069</t>
+  </si>
+  <si>
+    <t>710224241</t>
+  </si>
+  <si>
+    <t>738459258</t>
+  </si>
+  <si>
+    <t>738515323</t>
+  </si>
+  <si>
+    <t>744454624</t>
+  </si>
+  <si>
+    <t>740198936</t>
+  </si>
+  <si>
+    <t>742842358</t>
+  </si>
+  <si>
+    <t>745346159</t>
+  </si>
+  <si>
+    <t>746988686</t>
+  </si>
+  <si>
+    <t>751250865</t>
+  </si>
+  <si>
+    <t>754064263</t>
+  </si>
+  <si>
+    <t>758803724</t>
+  </si>
+  <si>
+    <t>759015740</t>
+  </si>
+  <si>
+    <t>761352222</t>
+  </si>
+  <si>
+    <t>762562993</t>
+  </si>
+  <si>
+    <t>765368471</t>
+  </si>
+  <si>
+    <t>768934220</t>
+  </si>
+  <si>
+    <t>771400490</t>
+  </si>
+  <si>
+    <t>770533127</t>
+  </si>
+  <si>
+    <t>771788985</t>
+  </si>
+  <si>
+    <t>774464428</t>
+  </si>
+  <si>
+    <t>782983096</t>
+  </si>
+  <si>
+    <t>784135760</t>
+  </si>
+  <si>
+    <t>788454068</t>
+  </si>
+  <si>
+    <t>788736621</t>
+  </si>
+  <si>
+    <t>794439319</t>
+  </si>
+  <si>
+    <t>796070989</t>
+  </si>
+  <si>
+    <t>801656277</t>
+  </si>
+  <si>
+    <t>801618178</t>
+  </si>
+  <si>
+    <t>802045876</t>
+  </si>
+  <si>
+    <t>803955842</t>
+  </si>
+  <si>
+    <t>803562838</t>
+  </si>
+  <si>
+    <t>805379751</t>
+  </si>
+  <si>
+    <t>806637272</t>
+  </si>
+  <si>
+    <t>807214980</t>
+  </si>
+  <si>
+    <t>809721727</t>
+  </si>
+  <si>
+    <t>810656193</t>
+  </si>
+  <si>
+    <t>812124646</t>
+  </si>
+  <si>
+    <t>811863566</t>
+  </si>
+  <si>
+    <t>815713429</t>
+  </si>
+  <si>
+    <t>815435049</t>
+  </si>
+  <si>
+    <t>821033317</t>
+  </si>
+  <si>
+    <t>822864363</t>
+  </si>
+  <si>
+    <t>825048295</t>
+  </si>
+  <si>
+    <t>822295980</t>
+  </si>
+  <si>
+    <t>823074517</t>
+  </si>
+  <si>
+    <t>823298603</t>
+  </si>
+  <si>
+    <t>826795845</t>
+  </si>
+  <si>
+    <t>826134417</t>
+  </si>
+  <si>
+    <t>828047559</t>
+  </si>
+  <si>
+    <t>828500144</t>
+  </si>
+  <si>
+    <t>830848390</t>
+  </si>
+  <si>
+    <t>830880864</t>
+  </si>
+  <si>
+    <t>833184363</t>
+  </si>
+  <si>
+    <t>834178802</t>
+  </si>
+  <si>
+    <t>833639085</t>
+  </si>
+  <si>
+    <t>836519912</t>
+  </si>
+  <si>
+    <t>842399705</t>
+  </si>
+  <si>
+    <t>846628414</t>
+  </si>
+  <si>
+    <t>847520487</t>
+  </si>
+  <si>
+    <t>848982892</t>
+  </si>
+  <si>
+    <t>849516830</t>
+  </si>
+  <si>
+    <t>855372029</t>
+  </si>
+  <si>
+    <t>853420390</t>
+  </si>
+  <si>
+    <t>853950933</t>
+  </si>
+  <si>
+    <t>854447319</t>
+  </si>
+  <si>
+    <t>860459449</t>
+  </si>
+  <si>
+    <t>861115750</t>
+  </si>
+  <si>
+    <t>863113993</t>
+  </si>
+  <si>
+    <t>862205394</t>
+  </si>
+  <si>
+    <t>862343047</t>
+  </si>
+  <si>
+    <t>864196757</t>
+  </si>
+  <si>
+    <t>865541894</t>
+  </si>
+  <si>
+    <t>868261813</t>
+  </si>
+  <si>
+    <t>870477258</t>
+  </si>
+  <si>
+    <t>870136953</t>
+  </si>
+  <si>
+    <t>873038008</t>
+  </si>
+  <si>
+    <t>872543875</t>
+  </si>
+  <si>
+    <t>874218476</t>
+  </si>
+  <si>
+    <t>876562731</t>
+  </si>
+  <si>
+    <t>177002122</t>
+  </si>
+  <si>
+    <t>920650102</t>
+  </si>
+  <si>
+    <t>178591081</t>
+  </si>
+  <si>
+    <t>177237330</t>
+  </si>
+  <si>
+    <t>177091786</t>
+  </si>
+  <si>
+    <t>801032495</t>
+  </si>
+  <si>
+    <t>788064313</t>
+  </si>
+  <si>
+    <t>724590827</t>
+  </si>
+  <si>
+    <t>762040743</t>
+  </si>
+  <si>
+    <t>781689488</t>
+  </si>
+  <si>
+    <t>735675773</t>
+  </si>
+  <si>
+    <t>756105882</t>
+  </si>
+  <si>
+    <t>746685191</t>
+  </si>
+  <si>
+    <t>839897869</t>
+  </si>
+  <si>
+    <t>908905817</t>
+  </si>
+  <si>
+    <t>914237437</t>
+  </si>
+  <si>
+    <t>908904448</t>
+  </si>
+  <si>
+    <t>895813842</t>
+  </si>
+  <si>
+    <t>895778771</t>
+  </si>
+  <si>
+    <t>889338814</t>
+  </si>
+  <si>
+    <t>855099150</t>
+  </si>
+  <si>
+    <t>875946471</t>
+  </si>
+  <si>
+    <t>849713080</t>
+  </si>
+  <si>
+    <t>836887368</t>
+  </si>
+  <si>
+    <t>825270865</t>
+  </si>
+  <si>
+    <t>835766100</t>
+  </si>
+  <si>
+    <t>830292177</t>
+  </si>
+  <si>
+    <t>815553064</t>
+  </si>
+  <si>
+    <t>790963510</t>
+  </si>
+  <si>
+    <t>790857134</t>
+  </si>
+  <si>
+    <t>790813095</t>
+  </si>
+  <si>
+    <t>930910322</t>
+  </si>
+  <si>
+    <t>921403436</t>
+  </si>
+  <si>
+    <t>920620543</t>
+  </si>
+  <si>
+    <t>918796727</t>
+  </si>
+  <si>
+    <t>782295285</t>
+  </si>
+  <si>
+    <t>784888699</t>
+  </si>
+  <si>
+    <t>753837719</t>
+  </si>
+  <si>
+    <t>179965086</t>
+  </si>
+  <si>
+    <t>179959196</t>
+  </si>
+  <si>
+    <t>179949585</t>
+  </si>
+  <si>
+    <t>179949197</t>
+  </si>
+  <si>
+    <t>177300393</t>
+  </si>
+  <si>
+    <t>179515543</t>
+  </si>
+  <si>
+    <t>179949080</t>
+  </si>
+  <si>
+    <t>179948835</t>
+  </si>
+  <si>
+    <t>179948702</t>
+  </si>
+  <si>
+    <t>179948678</t>
+  </si>
+  <si>
+    <t>179948660</t>
+  </si>
+  <si>
+    <t>179948645</t>
+  </si>
+  <si>
+    <t>179948512</t>
+  </si>
+  <si>
+    <t>179906510</t>
+  </si>
+  <si>
+    <t>179630532</t>
+  </si>
+  <si>
+    <t>179618958</t>
+  </si>
+  <si>
+    <t>179532803</t>
+  </si>
+  <si>
+    <t>179515576</t>
+  </si>
+  <si>
+    <t>179457043</t>
+  </si>
+  <si>
+    <t>179320167</t>
+  </si>
+  <si>
+    <t>179316728</t>
+  </si>
+  <si>
+    <t>839392952</t>
+  </si>
+  <si>
+    <t>888645003</t>
+  </si>
+  <si>
+    <t>909142543</t>
+  </si>
+  <si>
+    <t>891090320</t>
+  </si>
+  <si>
+    <t>876837562</t>
+  </si>
+  <si>
+    <t>883437026</t>
+  </si>
+  <si>
+    <t>862509175</t>
+  </si>
+  <si>
+    <t>858159696</t>
+  </si>
+  <si>
+    <t>839384835</t>
+  </si>
+  <si>
+    <t>796745390</t>
   </si>
 </sst>
 </file>
@@ -988,7 +1027,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1014,10 +1053,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -1026,10 +1065,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -1038,10 +1077,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -1050,10 +1089,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -1062,10 +1101,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -1074,10 +1113,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -1086,10 +1125,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -1098,10 +1137,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1110,10 +1149,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -1122,10 +1161,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -1134,10 +1173,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -1146,10 +1185,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -1158,10 +1197,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -1170,10 +1209,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -1182,10 +1221,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -1194,10 +1233,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -1206,10 +1245,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -1218,10 +1257,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -1230,10 +1269,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -1242,10 +1281,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -1254,10 +1293,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -1266,10 +1305,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -1278,10 +1317,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -1290,10 +1329,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -1302,10 +1341,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -1314,10 +1353,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1326,10 +1365,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1338,10 +1377,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1350,10 +1389,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1362,10 +1401,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1374,10 +1413,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1386,10 +1425,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1398,10 +1437,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1410,10 +1449,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1422,10 +1461,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1434,10 +1473,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1446,10 +1485,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1458,10 +1497,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1469,10 +1508,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1480,10 +1519,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1491,10 +1530,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1502,10 +1541,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1513,10 +1552,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1524,10 +1563,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1535,10 +1574,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
@@ -1546,10 +1585,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>4</v>
@@ -1557,10 +1596,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>4</v>
@@ -1568,10 +1607,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>4</v>
@@ -1579,10 +1618,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>4</v>
@@ -1590,10 +1629,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>4</v>
@@ -1601,10 +1640,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>4</v>
@@ -1612,10 +1651,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>4</v>
@@ -1623,10 +1662,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
@@ -1634,10 +1673,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>4</v>
@@ -1645,10 +1684,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>4</v>
@@ -1656,10 +1695,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>4</v>
@@ -1667,10 +1706,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>4</v>
@@ -1678,10 +1717,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>4</v>
@@ -1689,10 +1728,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>4</v>
@@ -1700,10 +1739,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
@@ -1711,10 +1750,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
@@ -1722,10 +1761,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
@@ -1733,10 +1772,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>4</v>
@@ -1744,10 +1783,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
@@ -1755,10 +1794,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
@@ -1766,10 +1805,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>4</v>
@@ -1777,10 +1816,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>4</v>
@@ -1788,10 +1827,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>4</v>
@@ -1799,10 +1838,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>4</v>
@@ -1810,10 +1849,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>4</v>
@@ -1821,10 +1860,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
@@ -1832,10 +1871,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
@@ -1843,10 +1882,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
@@ -1854,10 +1893,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>4</v>
@@ -1865,10 +1904,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>4</v>
@@ -1876,10 +1915,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
@@ -1887,10 +1926,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>4</v>
@@ -1898,10 +1937,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>4</v>
@@ -1909,10 +1948,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>4</v>
@@ -1920,10 +1959,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>4</v>
@@ -1931,10 +1970,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>4</v>
@@ -1942,10 +1981,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>4</v>
@@ -1953,10 +1992,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
@@ -1964,10 +2003,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>4</v>
@@ -1975,10 +2014,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
@@ -1986,10 +2025,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>4</v>
@@ -1997,10 +2036,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>4</v>
@@ -2008,10 +2047,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>4</v>
@@ -2019,10 +2058,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>4</v>
@@ -2030,10 +2069,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>4</v>
@@ -2041,10 +2080,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>4</v>
@@ -2052,10 +2091,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>4</v>
@@ -2063,10 +2102,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>4</v>
@@ -2074,10 +2113,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>4</v>
@@ -2085,10 +2124,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>4</v>
@@ -2096,10 +2135,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>4</v>
@@ -2107,10 +2146,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>4</v>
@@ -2118,10 +2157,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>4</v>
@@ -2129,10 +2168,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>4</v>
@@ -2140,10 +2179,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>106</v>
+        <v>5</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>4</v>
@@ -2151,10 +2190,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>4</v>
@@ -2162,10 +2201,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>4</v>
@@ -2173,10 +2212,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>4</v>
@@ -2184,10 +2223,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>4</v>
@@ -2195,10 +2234,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>4</v>
@@ -2206,10 +2245,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>4</v>
@@ -2217,10 +2256,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>4</v>
@@ -2228,10 +2267,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>4</v>
@@ -2239,10 +2278,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>4</v>
@@ -2250,10 +2289,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>4</v>
@@ -2261,10 +2300,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>4</v>
@@ -2272,10 +2311,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>4</v>
@@ -2283,10 +2322,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>4</v>
@@ -2294,10 +2333,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>4</v>
@@ -2305,10 +2344,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>4</v>
@@ -2316,10 +2355,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>4</v>
@@ -2327,10 +2366,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>4</v>
@@ -2338,10 +2377,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>4</v>
@@ -2349,10 +2388,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>4</v>
@@ -2360,10 +2399,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>4</v>
@@ -2371,10 +2410,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>4</v>
@@ -2382,10 +2421,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>4</v>
@@ -2393,10 +2432,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>4</v>
@@ -2404,10 +2443,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>4</v>
@@ -2415,10 +2454,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>4</v>
@@ -2426,10 +2465,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>4</v>
@@ -2437,10 +2476,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>4</v>
@@ -2448,10 +2487,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>4</v>
@@ -2459,10 +2498,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>4</v>
@@ -2470,10 +2509,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>4</v>
@@ -2481,10 +2520,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>4</v>
@@ -2492,10 +2531,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>4</v>
@@ -2503,10 +2542,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>4</v>
@@ -2514,10 +2553,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>4</v>
@@ -2525,10 +2564,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>4</v>
@@ -2536,10 +2575,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>4</v>
@@ -2547,10 +2586,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>4</v>
@@ -2558,10 +2597,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>4</v>
@@ -2569,10 +2608,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>4</v>
@@ -2580,10 +2619,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>4</v>
@@ -2591,10 +2630,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>4</v>
@@ -2602,10 +2641,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>4</v>
@@ -2613,10 +2652,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>4</v>
@@ -2624,10 +2663,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>4</v>
@@ -2635,10 +2674,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>4</v>
@@ -2649,7 +2688,7 @@
         <v>153</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>4</v>
@@ -2660,7 +2699,7 @@
         <v>154</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>4</v>
@@ -2671,7 +2710,7 @@
         <v>155</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>4</v>
@@ -2682,7 +2721,7 @@
         <v>156</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>4</v>
@@ -2693,7 +2732,7 @@
         <v>157</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>4</v>
@@ -2704,7 +2743,7 @@
         <v>158</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>4</v>
@@ -2715,7 +2754,7 @@
         <v>159</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C153" s="5" t="s">
         <v>4</v>
@@ -2726,7 +2765,7 @@
         <v>160</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>4</v>
@@ -2737,7 +2776,7 @@
         <v>161</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>4</v>
@@ -2748,7 +2787,7 @@
         <v>162</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>4</v>
@@ -2759,9 +2798,152 @@
         <v>163</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C157" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2788,31 +2970,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D4D0F5-B212-41FC-A52E-10FA9C2123A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9513B38F-DC67-44FF-9AE6-B1B987B2159F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="148">
   <si>
     <t>Status</t>
   </si>
@@ -48,172 +48,433 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>711435036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>712547060</t>
+  </si>
+  <si>
+    <t>713550998</t>
+  </si>
+  <si>
+    <t>713903361</t>
+  </si>
+  <si>
+    <t>718659521</t>
+  </si>
+  <si>
+    <t>719201737</t>
+  </si>
+  <si>
+    <t>722809401</t>
+  </si>
+  <si>
+    <t>724116375</t>
+  </si>
+  <si>
+    <t>728187380</t>
+  </si>
+  <si>
+    <t>726700119</t>
+  </si>
+  <si>
+    <t>861221764</t>
+  </si>
+  <si>
+    <t>732293927</t>
+  </si>
+  <si>
+    <t>738459050</t>
+  </si>
+  <si>
+    <t>738902091</t>
+  </si>
+  <si>
+    <t>760789119</t>
+  </si>
+  <si>
+    <t>740567726</t>
+  </si>
+  <si>
+    <t>739984254</t>
+  </si>
+  <si>
+    <t>740455369</t>
+  </si>
+  <si>
+    <t>740087352</t>
+  </si>
+  <si>
+    <t>742898251</t>
+  </si>
+  <si>
+    <t>748712373</t>
+  </si>
+  <si>
+    <t>751071378</t>
+  </si>
+  <si>
+    <t>753377955</t>
+  </si>
+  <si>
+    <t>754952434</t>
+  </si>
+  <si>
+    <t>760695563</t>
+  </si>
+  <si>
+    <t>757071455</t>
+  </si>
+  <si>
+    <t>756958660</t>
+  </si>
+  <si>
+    <t>756956318</t>
+  </si>
+  <si>
+    <t>757059435</t>
+  </si>
+  <si>
+    <t>759015757</t>
+  </si>
+  <si>
+    <t>759485414</t>
+  </si>
+  <si>
+    <t>759564424</t>
+  </si>
+  <si>
+    <t>762203333</t>
+  </si>
+  <si>
+    <t>761911191</t>
+  </si>
+  <si>
+    <t>764477869</t>
+  </si>
+  <si>
+    <t>767145257</t>
+  </si>
+  <si>
+    <t>767582020</t>
+  </si>
+  <si>
+    <t>768935789</t>
+  </si>
+  <si>
+    <t>771384900</t>
+  </si>
+  <si>
+    <t>773758507</t>
+  </si>
+  <si>
+    <t>773449016</t>
+  </si>
+  <si>
+    <t>774621316</t>
+  </si>
+  <si>
+    <t>775071966</t>
+  </si>
+  <si>
+    <t>781343896</t>
+  </si>
+  <si>
+    <t>780632794</t>
+  </si>
+  <si>
+    <t>782403483</t>
+  </si>
+  <si>
+    <t>784085999</t>
+  </si>
+  <si>
+    <t>787434699</t>
+  </si>
+  <si>
+    <t>788347866</t>
+  </si>
+  <si>
+    <t>789341314</t>
+  </si>
+  <si>
+    <t>789356890</t>
+  </si>
+  <si>
+    <t>790490837</t>
+  </si>
+  <si>
+    <t>790033710</t>
+  </si>
+  <si>
+    <t>790367753</t>
+  </si>
+  <si>
+    <t>791955630</t>
+  </si>
+  <si>
+    <t>792144382</t>
+  </si>
+  <si>
+    <t>792221321</t>
+  </si>
+  <si>
+    <t>792209474</t>
+  </si>
+  <si>
+    <t>795622608</t>
+  </si>
+  <si>
+    <t>796074601</t>
+  </si>
+  <si>
+    <t>797609017</t>
+  </si>
+  <si>
+    <t>800216024</t>
+  </si>
+  <si>
+    <t>801009634</t>
+  </si>
+  <si>
+    <t>902051568</t>
+  </si>
+  <si>
+    <t>801923883</t>
+  </si>
+  <si>
+    <t>803436447</t>
+  </si>
+  <si>
+    <t>804612038</t>
+  </si>
+  <si>
+    <t>805486119</t>
+  </si>
+  <si>
+    <t>809800620</t>
+  </si>
+  <si>
+    <t>809721735</t>
+  </si>
+  <si>
+    <t>809705621</t>
+  </si>
+  <si>
+    <t>811863574</t>
+  </si>
+  <si>
+    <t>813612730</t>
+  </si>
+  <si>
+    <t>814071860</t>
+  </si>
+  <si>
+    <t>820703787</t>
+  </si>
+  <si>
+    <t>823049162</t>
+  </si>
+  <si>
+    <t>822693010</t>
+  </si>
+  <si>
+    <t>825978939</t>
+  </si>
+  <si>
+    <t>828843114</t>
+  </si>
+  <si>
+    <t>828828446</t>
+  </si>
+  <si>
+    <t>830734426</t>
+  </si>
+  <si>
+    <t>830231050</t>
+  </si>
+  <si>
+    <t>829727993</t>
+  </si>
+  <si>
+    <t>830880872</t>
+  </si>
+  <si>
+    <t>831170513</t>
+  </si>
+  <si>
+    <t>831331941</t>
+  </si>
+  <si>
+    <t>836739981</t>
+  </si>
+  <si>
+    <t>833185782</t>
+  </si>
+  <si>
+    <t>832183564</t>
+  </si>
+  <si>
+    <t>835444062</t>
+  </si>
+  <si>
+    <t>836238281</t>
+  </si>
+  <si>
+    <t>835959234</t>
+  </si>
+  <si>
+    <t>836547384</t>
+  </si>
+  <si>
+    <t>842096368</t>
+  </si>
+  <si>
+    <t>841262979</t>
+  </si>
+  <si>
+    <t>843408166</t>
+  </si>
+  <si>
+    <t>845454259</t>
+  </si>
+  <si>
+    <t>846899734</t>
+  </si>
+  <si>
+    <t>845026370</t>
+  </si>
+  <si>
+    <t>847181959</t>
+  </si>
+  <si>
+    <t>794770069</t>
+  </si>
+  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
+    <t>765638063</t>
+  </si>
+  <si>
+    <t>771390469</t>
+  </si>
+  <si>
+    <t>909106480</t>
+  </si>
+  <si>
+    <t>735751491</t>
+  </si>
+  <si>
+    <t>924771086</t>
+  </si>
+  <si>
+    <t>924291895</t>
+  </si>
+  <si>
+    <t>905302257</t>
+  </si>
+  <si>
+    <t>892468087</t>
+  </si>
+  <si>
+    <t>835397054</t>
+  </si>
+  <si>
+    <t>882056645</t>
+  </si>
+  <si>
+    <t>862359365</t>
+  </si>
+  <si>
+    <t>862331604</t>
+  </si>
+  <si>
+    <t>852098825</t>
+  </si>
+  <si>
+    <t>847118373</t>
+  </si>
+  <si>
+    <t>835734942</t>
+  </si>
+  <si>
+    <t>835672753</t>
+  </si>
+  <si>
+    <t>726327889</t>
+  </si>
+  <si>
+    <t>733036838</t>
+  </si>
+  <si>
+    <t>726858818</t>
+  </si>
+  <si>
+    <t>725362523</t>
+  </si>
+  <si>
+    <t>706457466</t>
+  </si>
+  <si>
+    <t>709158350</t>
+  </si>
+  <si>
+    <t>819144993</t>
+  </si>
+  <si>
+    <t>809813326</t>
+  </si>
+  <si>
+    <t>814056556</t>
+  </si>
+  <si>
+    <t>813077538</t>
+  </si>
+  <si>
+    <t>798396291</t>
+  </si>
+  <si>
+    <t>797673831</t>
+  </si>
+  <si>
+    <t>796330284</t>
+  </si>
+  <si>
+    <t>792248340</t>
+  </si>
+  <si>
+    <t>789128414</t>
+  </si>
+  <si>
+    <t>783464716</t>
+  </si>
+  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>820165797</t>
-  </si>
-  <si>
-    <t>783464948</t>
-  </si>
-  <si>
-    <t>791492139</t>
-  </si>
-  <si>
-    <t>794185177</t>
-  </si>
-  <si>
-    <t>778065825</t>
-  </si>
-  <si>
-    <t>773189091</t>
-  </si>
-  <si>
-    <t>767751500</t>
-  </si>
-  <si>
-    <t>726591385</t>
-  </si>
-  <si>
-    <t>767132081</t>
-  </si>
-  <si>
-    <t>764787606</t>
-  </si>
-  <si>
-    <t>760479679</t>
-  </si>
-  <si>
-    <t>759343597</t>
-  </si>
-  <si>
-    <t>757957562</t>
-  </si>
-  <si>
-    <t>754620015</t>
-  </si>
-  <si>
-    <t>877921415</t>
-  </si>
-  <si>
-    <t>931165892</t>
-  </si>
-  <si>
-    <t>924066834</t>
-  </si>
-  <si>
-    <t>930093434</t>
-  </si>
-  <si>
-    <t>929396459</t>
-  </si>
-  <si>
-    <t>923014694</t>
-  </si>
-  <si>
-    <t>921988162</t>
-  </si>
-  <si>
-    <t>920650144</t>
-  </si>
-  <si>
-    <t>664576265</t>
-  </si>
-  <si>
-    <t>178336529</t>
-  </si>
-  <si>
-    <t>172459137</t>
-  </si>
-  <si>
-    <t>892736020</t>
-  </si>
-  <si>
-    <t>909565834</t>
-  </si>
-  <si>
-    <t>909562039</t>
-  </si>
-  <si>
-    <t>877904098</t>
-  </si>
-  <si>
-    <t>864669738</t>
-  </si>
-  <si>
-    <t>856052315</t>
-  </si>
-  <si>
-    <t>852309172</t>
-  </si>
-  <si>
-    <t>844885982</t>
-  </si>
-  <si>
-    <t>842747366</t>
-  </si>
-  <si>
-    <t>844840490</t>
-  </si>
-  <si>
-    <t>827298948</t>
-  </si>
-  <si>
-    <t>813664087</t>
-  </si>
-  <si>
-    <t>808011971</t>
-  </si>
-  <si>
-    <t>810729925</t>
-  </si>
-  <si>
-    <t>800625471</t>
-  </si>
-  <si>
-    <t>792003604</t>
-  </si>
-  <si>
-    <t>827418108</t>
-  </si>
-  <si>
-    <t>179436716</t>
-  </si>
-  <si>
-    <t>930488857</t>
-  </si>
-  <si>
-    <t>179436336</t>
-  </si>
-  <si>
-    <t>888756503</t>
-  </si>
-  <si>
-    <t>912979949</t>
-  </si>
-  <si>
-    <t>927798995</t>
-  </si>
-  <si>
-    <t>850304696</t>
-  </si>
-  <si>
-    <t>858176559</t>
-  </si>
-  <si>
-    <t>847652850</t>
-  </si>
-  <si>
-    <t>817510385</t>
-  </si>
-  <si>
-    <t>819379219</t>
-  </si>
-  <si>
-    <t>813081746</t>
+    <t>179313790</t>
+  </si>
+  <si>
+    <t>921269498</t>
+  </si>
+  <si>
+    <t>179899764</t>
+  </si>
+  <si>
+    <t>179915875</t>
+  </si>
+  <si>
+    <t>179721620</t>
+  </si>
+  <si>
+    <t>179522507</t>
+  </si>
+  <si>
+    <t>807935220</t>
   </si>
 </sst>
 </file>
@@ -679,7 +940,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -705,10 +966,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -717,10 +978,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -729,10 +990,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -741,10 +1002,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -753,10 +1014,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -765,10 +1026,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -777,10 +1038,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -789,10 +1050,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -801,10 +1062,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -813,10 +1074,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -825,10 +1086,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -837,10 +1098,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -849,10 +1110,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -861,10 +1122,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -873,10 +1134,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -885,10 +1146,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -897,10 +1158,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -909,10 +1170,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -921,10 +1182,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -933,10 +1194,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -945,10 +1206,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -957,10 +1218,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -969,10 +1230,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -981,10 +1242,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -993,10 +1254,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -1005,10 +1266,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1017,10 +1278,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1029,10 +1290,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1041,10 +1302,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1053,10 +1314,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1065,10 +1326,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1077,10 +1338,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1089,10 +1350,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1101,10 +1362,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1113,10 +1374,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1125,10 +1386,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1137,10 +1398,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1149,10 +1410,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1160,10 +1421,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1171,7 +1432,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>6</v>
@@ -1182,7 +1443,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>6</v>
@@ -1193,7 +1454,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>6</v>
@@ -1204,7 +1465,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>6</v>
@@ -1215,7 +1476,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>6</v>
@@ -1226,7 +1487,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>6</v>
@@ -1237,7 +1498,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>6</v>
@@ -1248,7 +1509,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>6</v>
@@ -1259,7 +1520,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>6</v>
@@ -1270,7 +1531,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>6</v>
@@ -1281,7 +1542,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>6</v>
@@ -1292,7 +1553,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>6</v>
@@ -1303,7 +1564,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>6</v>
@@ -1314,7 +1575,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>6</v>
@@ -1325,359 +1586,960 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C56" s="5"/>
+      <c r="B56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C57" s="5"/>
+      <c r="A57" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C58" s="5"/>
+      <c r="A58" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C59" s="5"/>
+      <c r="A59" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C60" s="5"/>
+      <c r="A60" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C61" s="5"/>
+      <c r="A61" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C62" s="5"/>
+      <c r="A62" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C63" s="5"/>
+      <c r="A63" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C64" s="5"/>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C65" s="5"/>
-    </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C66" s="5"/>
-    </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C67" s="5"/>
-    </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C68" s="5"/>
-    </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C69" s="5"/>
-    </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C70" s="5"/>
-    </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C71" s="5"/>
-    </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C72" s="5"/>
-    </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C73" s="5"/>
-    </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C74" s="5"/>
-    </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C75" s="5"/>
-    </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C76" s="5"/>
-    </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C77" s="5"/>
-    </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C78" s="5"/>
-    </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C79" s="5"/>
-    </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C80" s="5"/>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C81" s="5"/>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C82" s="5"/>
-    </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C83" s="5"/>
-    </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C84" s="5"/>
-    </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C85" s="5"/>
-    </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C86" s="5"/>
-    </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C87" s="5"/>
-    </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C88" s="5"/>
-    </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C89" s="5"/>
-    </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C90" s="5"/>
-    </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C91" s="5"/>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C92" s="5"/>
-    </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C93" s="5"/>
-    </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C94" s="5"/>
-    </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C95" s="5"/>
-    </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C96" s="5"/>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C97" s="5"/>
-    </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C98" s="5"/>
-    </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C99" s="5"/>
-    </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C100" s="5"/>
-    </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C101" s="5"/>
-    </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C102" s="5"/>
-    </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C103" s="5"/>
-    </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C104" s="5"/>
-    </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C105" s="5"/>
-    </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C106" s="5"/>
-    </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C107" s="5"/>
-    </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C108" s="5"/>
-    </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C109" s="5"/>
-    </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C110" s="5"/>
-    </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C111" s="5"/>
-    </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C112" s="5"/>
-    </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C113" s="5"/>
-    </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C114" s="5"/>
-    </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C115" s="5"/>
-    </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C116" s="5"/>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C117" s="5"/>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C118" s="5"/>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C119" s="5"/>
-    </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C120" s="5"/>
-    </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C121" s="5"/>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C122" s="5"/>
-    </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C123" s="5"/>
-    </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C124" s="5"/>
-    </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C125" s="5"/>
-    </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C126" s="5"/>
-    </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C127" s="5"/>
-    </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C128" s="5"/>
-    </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C129" s="5"/>
-    </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C130" s="5"/>
-    </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C131" s="5"/>
-    </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C132" s="5"/>
-    </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C133" s="5"/>
-    </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C134" s="5"/>
-    </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C135" s="5"/>
-    </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C136" s="5"/>
-    </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C137" s="5"/>
-    </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C138" s="5"/>
-    </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C139" s="5"/>
-    </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C140" s="5"/>
-    </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C141" s="5"/>
-    </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C142" s="5"/>
-    </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C143" s="5"/>
-    </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C144" s="5"/>
-    </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C145" s="5"/>
-    </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C146" s="5"/>
-    </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C147" s="5"/>
-    </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C148" s="5"/>
-    </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C149" s="5"/>
-    </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C150" s="5"/>
-    </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C151" s="5"/>
-    </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C152" s="5"/>
-    </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C153" s="5"/>
-    </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C154" s="5"/>
-    </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C155" s="5"/>
-    </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C156" s="5"/>
-    </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C157" s="5"/>
-    </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C158" s="5"/>
-    </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C159" s="5"/>
-    </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C160" s="5"/>
-    </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C161" s="5"/>
-    </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C162" s="5"/>
-    </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C163" s="5"/>
-    </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C164" s="5"/>
-    </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C165" s="5"/>
-    </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C166" s="5"/>
-    </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C167" s="5"/>
-    </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C168" s="5"/>
-    </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C169" s="5"/>
-    </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C170" s="5"/>
+      <c r="A64" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD949736-BF90-422F-818C-D9F44964C95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4E3BD-D63F-4082-9706-F22782CD0434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="148">
   <si>
     <t>Status</t>
   </si>
@@ -48,163 +48,433 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>654167810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>654585532</t>
+  </si>
+  <si>
+    <t>655400095</t>
+  </si>
+  <si>
+    <t>659142180</t>
+  </si>
+  <si>
+    <t>666221837</t>
+  </si>
+  <si>
+    <t>669451985</t>
+  </si>
+  <si>
+    <t>670249568</t>
+  </si>
+  <si>
+    <t>672531104</t>
+  </si>
+  <si>
+    <t>675919439</t>
+  </si>
+  <si>
+    <t>689797086</t>
+  </si>
+  <si>
+    <t>692522422</t>
+  </si>
+  <si>
+    <t>697190191</t>
+  </si>
+  <si>
+    <t>711656482</t>
+  </si>
+  <si>
+    <t>709471878</t>
+  </si>
+  <si>
+    <t>713055147</t>
+  </si>
+  <si>
+    <t>715054478</t>
+  </si>
+  <si>
+    <t>715454587</t>
+  </si>
+  <si>
+    <t>719831285</t>
+  </si>
+  <si>
+    <t>718080611</t>
+  </si>
+  <si>
+    <t>722612532</t>
+  </si>
+  <si>
+    <t>726015716</t>
+  </si>
+  <si>
+    <t>732430164</t>
+  </si>
+  <si>
+    <t>732424472</t>
+  </si>
+  <si>
+    <t>731862870</t>
+  </si>
+  <si>
+    <t>731802603</t>
+  </si>
+  <si>
+    <t>736056031</t>
+  </si>
+  <si>
+    <t>738311780</t>
+  </si>
+  <si>
+    <t>741497196</t>
+  </si>
+  <si>
+    <t>742808466</t>
+  </si>
+  <si>
+    <t>746887433</t>
+  </si>
+  <si>
+    <t>747432809</t>
+  </si>
+  <si>
+    <t>748979543</t>
+  </si>
+  <si>
+    <t>748536558</t>
+  </si>
+  <si>
+    <t>755518424</t>
+  </si>
+  <si>
+    <t>756520932</t>
+  </si>
+  <si>
+    <t>774623098</t>
+  </si>
+  <si>
+    <t>595801675</t>
+  </si>
+  <si>
+    <t>599738899</t>
+  </si>
+  <si>
+    <t>600014926</t>
+  </si>
+  <si>
+    <t>601902426</t>
+  </si>
+  <si>
+    <t>603356712</t>
+  </si>
+  <si>
+    <t>603941158</t>
+  </si>
+  <si>
+    <t>606159121</t>
+  </si>
+  <si>
+    <t>610042743</t>
+  </si>
+  <si>
+    <t>616960203</t>
+  </si>
+  <si>
+    <t>617623636</t>
+  </si>
+  <si>
+    <t>618129617</t>
+  </si>
+  <si>
+    <t>618573780</t>
+  </si>
+  <si>
+    <t>622602302</t>
+  </si>
+  <si>
+    <t>621002884</t>
+  </si>
+  <si>
+    <t>625567908</t>
+  </si>
+  <si>
+    <t>627178910</t>
+  </si>
+  <si>
+    <t>638126536</t>
+  </si>
+  <si>
+    <t>640197137</t>
+  </si>
+  <si>
+    <t>643856630</t>
+  </si>
+  <si>
+    <t>646429062</t>
+  </si>
+  <si>
+    <t>653944417</t>
+  </si>
+  <si>
+    <t>654167828</t>
+  </si>
+  <si>
+    <t>654585540</t>
+  </si>
+  <si>
+    <t>657448290</t>
+  </si>
+  <si>
+    <t>655400103</t>
+  </si>
+  <si>
+    <t>665462168</t>
+  </si>
+  <si>
+    <t>670249576</t>
+  </si>
+  <si>
+    <t>672531112</t>
+  </si>
+  <si>
+    <t>675023422</t>
+  </si>
+  <si>
+    <t>675919447</t>
+  </si>
+  <si>
+    <t>678623665</t>
+  </si>
+  <si>
+    <t>680330119</t>
+  </si>
+  <si>
+    <t>681161281</t>
+  </si>
+  <si>
+    <t>683036507</t>
+  </si>
+  <si>
+    <t>692522430</t>
+  </si>
+  <si>
+    <t>694921663</t>
+  </si>
+  <si>
+    <t>696152960</t>
+  </si>
+  <si>
+    <t>697190209</t>
+  </si>
+  <si>
+    <t>702992961</t>
+  </si>
+  <si>
+    <t>707351064</t>
+  </si>
+  <si>
+    <t>707500140</t>
+  </si>
+  <si>
+    <t>711656490</t>
+  </si>
+  <si>
+    <t>709471886</t>
+  </si>
+  <si>
+    <t>720702137</t>
+  </si>
+  <si>
+    <t>715054486</t>
+  </si>
+  <si>
+    <t>715454595</t>
+  </si>
+  <si>
+    <t>716695139</t>
+  </si>
+  <si>
+    <t>719831293</t>
+  </si>
+  <si>
+    <t>717958908</t>
+  </si>
+  <si>
+    <t>718080629</t>
+  </si>
+  <si>
+    <t>722612540</t>
+  </si>
+  <si>
+    <t>723511576</t>
+  </si>
+  <si>
+    <t>803392905</t>
+  </si>
+  <si>
+    <t>732569169</t>
+  </si>
+  <si>
+    <t>733848893</t>
+  </si>
+  <si>
+    <t>735758447</t>
+  </si>
+  <si>
+    <t>738311798</t>
+  </si>
+  <si>
+    <t>745910749</t>
+  </si>
+  <si>
+    <t>749391268</t>
+  </si>
+  <si>
+    <t>750292025</t>
+  </si>
+  <si>
+    <t>752237572</t>
+  </si>
+  <si>
+    <t>754457426</t>
+  </si>
+  <si>
+    <t>752638480</t>
+  </si>
+  <si>
+    <t>753078512</t>
+  </si>
+  <si>
+    <t>735674958</t>
+  </si>
+  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
+    <t>885622575</t>
+  </si>
+  <si>
+    <t>917425831</t>
+  </si>
+  <si>
+    <t>929273559</t>
+  </si>
+  <si>
+    <t>923259661</t>
+  </si>
+  <si>
+    <t>904096660</t>
+  </si>
+  <si>
+    <t>826884946</t>
+  </si>
+  <si>
+    <t>840722767</t>
+  </si>
+  <si>
+    <t>845766264</t>
+  </si>
+  <si>
+    <t>832659472</t>
+  </si>
+  <si>
+    <t>832652659</t>
+  </si>
+  <si>
+    <t>809608395</t>
+  </si>
+  <si>
+    <t>807044163</t>
+  </si>
+  <si>
+    <t>806053744</t>
+  </si>
+  <si>
+    <t>802853949</t>
+  </si>
+  <si>
+    <t>801226535</t>
+  </si>
+  <si>
+    <t>773812239</t>
+  </si>
+  <si>
+    <t>729872618</t>
+  </si>
+  <si>
+    <t>179429885</t>
+  </si>
+  <si>
+    <t>177071481</t>
+  </si>
+  <si>
+    <t>178601070</t>
+  </si>
+  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>807360551</t>
-  </si>
-  <si>
-    <t>799557743</t>
-  </si>
-  <si>
-    <t>797670209</t>
-  </si>
-  <si>
-    <t>797470717</t>
-  </si>
-  <si>
-    <t>796841330</t>
-  </si>
-  <si>
-    <t>793898184</t>
-  </si>
-  <si>
-    <t>777639679</t>
-  </si>
-  <si>
-    <t>789886235</t>
-  </si>
-  <si>
-    <t>790655850</t>
-  </si>
-  <si>
-    <t>731488718</t>
-  </si>
-  <si>
-    <t>758808871</t>
-  </si>
-  <si>
-    <t>753485329</t>
-  </si>
-  <si>
-    <t>731537266</t>
-  </si>
-  <si>
-    <t>728416284</t>
-  </si>
-  <si>
-    <t>869839609</t>
-  </si>
-  <si>
-    <t>174369110</t>
-  </si>
-  <si>
-    <t>178617365</t>
-  </si>
-  <si>
-    <t>174379358</t>
-  </si>
-  <si>
-    <t>917476982</t>
-  </si>
-  <si>
-    <t>931234565</t>
-  </si>
-  <si>
-    <t>929407538</t>
-  </si>
-  <si>
-    <t>916511771</t>
-  </si>
-  <si>
-    <t>905735381</t>
-  </si>
-  <si>
-    <t>902850076</t>
-  </si>
-  <si>
-    <t>902719537</t>
-  </si>
-  <si>
-    <t>823663608</t>
-  </si>
-  <si>
-    <t>839213349</t>
-  </si>
-  <si>
-    <t>802324495</t>
-  </si>
-  <si>
-    <t>181625314</t>
-  </si>
-  <si>
-    <t>762728396</t>
-  </si>
-  <si>
-    <t>181625280</t>
-  </si>
-  <si>
-    <t>181623756</t>
-  </si>
-  <si>
-    <t>899582922</t>
-  </si>
-  <si>
-    <t>922738343</t>
-  </si>
-  <si>
-    <t>179992452</t>
-  </si>
-  <si>
-    <t>179992296</t>
-  </si>
-  <si>
-    <t>179991926</t>
-  </si>
-  <si>
-    <t>179991660</t>
-  </si>
-  <si>
-    <t>179991173</t>
-  </si>
-  <si>
-    <t>179990886</t>
-  </si>
-  <si>
-    <t>179945815</t>
-  </si>
-  <si>
-    <t>179882752</t>
-  </si>
-  <si>
-    <t>904876517</t>
-  </si>
-  <si>
-    <t>869002570</t>
-  </si>
-  <si>
-    <t>889587840</t>
-  </si>
-  <si>
-    <t>888489592</t>
-  </si>
-  <si>
-    <t>879876062</t>
-  </si>
-  <si>
-    <t>872306547</t>
-  </si>
-  <si>
-    <t>868542089</t>
-  </si>
-  <si>
-    <t>849884816</t>
-  </si>
-  <si>
-    <t>815778844</t>
+    <t>899949733</t>
+  </si>
+  <si>
+    <t>922394808</t>
+  </si>
+  <si>
+    <t>920068909</t>
+  </si>
+  <si>
+    <t>888305202</t>
+  </si>
+  <si>
+    <t>873837300</t>
+  </si>
+  <si>
+    <t>801800578</t>
+  </si>
+  <si>
+    <t>848492124</t>
+  </si>
+  <si>
+    <t>865699866</t>
+  </si>
+  <si>
+    <t>852482904</t>
+  </si>
+  <si>
+    <t>850362249</t>
+  </si>
+  <si>
+    <t>845783079</t>
+  </si>
+  <si>
+    <t>836360663</t>
+  </si>
+  <si>
+    <t>806760983</t>
+  </si>
+  <si>
+    <t>793314521</t>
+  </si>
+  <si>
+    <t>792175642</t>
+  </si>
+  <si>
+    <t>790054641</t>
+  </si>
+  <si>
+    <t>766167518</t>
+  </si>
+  <si>
+    <t>179840917</t>
+  </si>
+  <si>
+    <t>179581321</t>
   </si>
 </sst>
 </file>
@@ -670,7 +940,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -696,10 +966,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -708,10 +978,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -720,10 +990,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -732,10 +1002,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -744,10 +1014,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -756,10 +1026,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -768,10 +1038,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -780,10 +1050,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -792,10 +1062,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -804,10 +1074,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -816,10 +1086,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -828,10 +1098,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -840,10 +1110,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -852,10 +1122,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -864,10 +1134,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -876,10 +1146,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -888,10 +1158,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -900,10 +1170,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -912,10 +1182,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -924,10 +1194,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -936,10 +1206,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -948,10 +1218,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -960,10 +1230,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -972,10 +1242,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -984,10 +1254,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -996,10 +1266,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1008,7 +1278,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>6</v>
@@ -1020,7 +1290,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>6</v>
@@ -1032,7 +1302,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>6</v>
@@ -1044,7 +1314,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>6</v>
@@ -1056,7 +1326,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>6</v>
@@ -1068,7 +1338,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>6</v>
@@ -1080,7 +1350,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>6</v>
@@ -1092,7 +1362,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>6</v>
@@ -1104,7 +1374,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>6</v>
@@ -1116,7 +1386,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>6</v>
@@ -1128,7 +1398,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>6</v>
@@ -1140,7 +1410,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>6</v>
@@ -1151,7 +1421,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>6</v>
@@ -1162,7 +1432,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>6</v>
@@ -1173,7 +1443,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>6</v>
@@ -1184,7 +1454,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>6</v>
@@ -1195,7 +1465,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>6</v>
@@ -1206,7 +1476,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>6</v>
@@ -1217,7 +1487,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>6</v>
@@ -1228,7 +1498,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>6</v>
@@ -1239,7 +1509,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>6</v>
@@ -1250,7 +1520,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>6</v>
@@ -1261,7 +1531,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>6</v>
@@ -1272,7 +1542,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>6</v>
@@ -1283,245 +1553,993 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C53" s="5"/>
+      <c r="B53" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C54" s="5"/>
+      <c r="A54" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C55" s="5"/>
+      <c r="A55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C56" s="5"/>
+      <c r="A56" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C57" s="5"/>
+      <c r="A57" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C58" s="5"/>
+      <c r="A58" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C59" s="5"/>
+      <c r="A59" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C60" s="5"/>
+      <c r="A60" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C61" s="5"/>
+      <c r="A61" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C62" s="5"/>
+      <c r="A62" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C63" s="5"/>
+      <c r="A63" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C64" s="5"/>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C65" s="5"/>
-    </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C66" s="5"/>
-    </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C67" s="5"/>
-    </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C68" s="5"/>
-    </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C69" s="5"/>
-    </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C70" s="5"/>
-    </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C71" s="5"/>
-    </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C72" s="5"/>
-    </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C73" s="5"/>
-    </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C74" s="5"/>
-    </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C75" s="5"/>
-    </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C76" s="5"/>
-    </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C77" s="5"/>
-    </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C78" s="5"/>
-    </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C79" s="5"/>
-    </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C80" s="5"/>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C81" s="5"/>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C82" s="5"/>
-    </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C83" s="5"/>
-    </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C84" s="5"/>
-    </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C85" s="5"/>
-    </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C86" s="5"/>
-    </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C87" s="5"/>
-    </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C88" s="5"/>
-    </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C89" s="5"/>
-    </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C90" s="5"/>
-    </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C91" s="5"/>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C92" s="5"/>
-    </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C93" s="5"/>
-    </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C94" s="5"/>
-    </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C95" s="5"/>
-    </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C96" s="5"/>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C97" s="5"/>
-    </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C98" s="5"/>
-    </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C99" s="5"/>
-    </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C100" s="5"/>
-    </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C101" s="5"/>
-    </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C102" s="5"/>
-    </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C103" s="5"/>
-    </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C104" s="5"/>
-    </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C105" s="5"/>
-    </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C106" s="5"/>
-    </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C107" s="5"/>
-    </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C108" s="5"/>
-    </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C109" s="5"/>
-    </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C110" s="5"/>
-    </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C111" s="5"/>
-    </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C112" s="5"/>
-    </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C113" s="5"/>
-    </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C114" s="5"/>
-    </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C115" s="5"/>
-    </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C116" s="5"/>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C117" s="5"/>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C118" s="5"/>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C119" s="5"/>
-    </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C120" s="5"/>
-    </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C121" s="5"/>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C122" s="5"/>
-    </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C123" s="5"/>
-    </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C124" s="5"/>
-    </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C125" s="5"/>
-    </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C126" s="5"/>
-    </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C127" s="5"/>
-    </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C128" s="5"/>
-    </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C129" s="5"/>
+      <c r="A64" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1546,31 +2564,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45BFD16-621C-482C-AD7E-3A715B5594AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE066ED9-08D5-4A07-9028-4B5CA0D10133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="58">
   <si>
     <t>Status</t>
   </si>
@@ -48,100 +48,163 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>933876074</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>786081145</t>
-  </si>
-  <si>
-    <t>810979330</t>
-  </si>
-  <si>
-    <t>832307569</t>
-  </si>
-  <si>
-    <t>828660187</t>
-  </si>
-  <si>
-    <t>815294719</t>
-  </si>
-  <si>
-    <t>815046911</t>
-  </si>
-  <si>
-    <t>804236184</t>
-  </si>
-  <si>
-    <t>799712918</t>
-  </si>
-  <si>
-    <t>803537525</t>
-  </si>
-  <si>
-    <t>799119924</t>
-  </si>
-  <si>
-    <t>770440554</t>
-  </si>
-  <si>
-    <t>174328868</t>
-  </si>
-  <si>
-    <t>733456168</t>
-  </si>
-  <si>
-    <t>705741019</t>
-  </si>
-  <si>
-    <t>176860553</t>
-  </si>
-  <si>
-    <t>176860439</t>
-  </si>
-  <si>
-    <t>181625009</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>886862345</t>
-  </si>
-  <si>
-    <t>903717431</t>
-  </si>
-  <si>
-    <t>896373259</t>
-  </si>
-  <si>
-    <t>798682526</t>
-  </si>
-  <si>
-    <t>814223933</t>
-  </si>
-  <si>
-    <t>850109103</t>
-  </si>
-  <si>
-    <t>880986405</t>
-  </si>
-  <si>
-    <t>857442499</t>
-  </si>
-  <si>
-    <t>817516689</t>
-  </si>
-  <si>
-    <t>803132574</t>
-  </si>
-  <si>
-    <t>180009403</t>
-  </si>
-  <si>
-    <t>179519875</t>
+    <t>884964440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>848558833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>936616360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
+  </si>
+  <si>
+    <t>936428030</t>
+  </si>
+  <si>
+    <t>937807745</t>
+  </si>
+  <si>
+    <t>776643334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>898150267</t>
+  </si>
+  <si>
+    <t>797563081</t>
+  </si>
+  <si>
+    <t>752481436</t>
+  </si>
+  <si>
+    <t>926502638</t>
+  </si>
+  <si>
+    <t>837798408</t>
+  </si>
+  <si>
+    <t>861108771</t>
+  </si>
+  <si>
+    <t>846548661</t>
+  </si>
+  <si>
+    <t>954623173</t>
+  </si>
+  <si>
+    <t>835720529</t>
+  </si>
+  <si>
+    <t>825641339</t>
+  </si>
+  <si>
+    <t>736595855</t>
+  </si>
+  <si>
+    <t>793771423</t>
+  </si>
+  <si>
+    <t>812732497</t>
+  </si>
+  <si>
+    <t>809051133</t>
+  </si>
+  <si>
+    <t>805313644</t>
+  </si>
+  <si>
+    <t>804065682</t>
+  </si>
+  <si>
+    <t>786653067</t>
+  </si>
+  <si>
+    <t>777994934</t>
+  </si>
+  <si>
+    <t>766608685</t>
+  </si>
+  <si>
+    <t>769737119</t>
+  </si>
+  <si>
+    <t>751896758</t>
+  </si>
+  <si>
+    <t>723834614</t>
+  </si>
+  <si>
+    <t>178199661</t>
+  </si>
+  <si>
+    <t>175832884</t>
+  </si>
+  <si>
+    <t>175782949</t>
+  </si>
+  <si>
+    <t>901919757</t>
+  </si>
+  <si>
+    <t>937880130</t>
+  </si>
+  <si>
+    <t>867221875</t>
+  </si>
+  <si>
+    <t>844941231</t>
+  </si>
+  <si>
+    <t>847640590</t>
+  </si>
+  <si>
+    <t>827797444</t>
+  </si>
+  <si>
+    <t>178734194</t>
+  </si>
+  <si>
+    <t>745778955</t>
+  </si>
+  <si>
+    <t>804536898</t>
+  </si>
+  <si>
+    <t>931184125</t>
+  </si>
+  <si>
+    <t>898095306</t>
+  </si>
+  <si>
+    <t>923758019</t>
+  </si>
+  <si>
+    <t>868105739</t>
+  </si>
+  <si>
+    <t>857011039</t>
+  </si>
+  <si>
+    <t>856377365</t>
+  </si>
+  <si>
+    <t>752667984</t>
   </si>
 </sst>
 </file>
@@ -607,7 +670,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -633,10 +696,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -648,7 +711,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -657,10 +720,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -672,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -681,10 +744,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -693,10 +756,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -705,10 +768,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -717,10 +780,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -729,10 +792,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -741,10 +804,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -753,10 +816,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -765,10 +828,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -777,10 +840,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -789,10 +852,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -801,10 +864,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -813,10 +876,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -825,10 +888,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -837,10 +900,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -849,10 +912,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -861,10 +924,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -873,10 +936,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -885,10 +948,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -897,10 +960,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -909,10 +972,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -921,10 +984,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -933,10 +996,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -945,10 +1008,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -957,10 +1020,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -969,10 +1032,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -981,10 +1044,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -992,32 +1055,220 @@
       <c r="D31"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="5"/>
+      <c r="A32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D32"/>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="5"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="5"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D34"/>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="5"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D35"/>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="5"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D36"/>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="5"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D37"/>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="5"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1042,31 +1293,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4167FD99-16F2-4312-9BD5-4B97EA8CA39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88023778-0650-48DB-A226-E5C634291429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="55">
   <si>
     <t>Status</t>
   </si>
@@ -48,109 +48,154 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>849713098</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>925431458</t>
-  </si>
-  <si>
-    <t>925333100</t>
-  </si>
-  <si>
-    <t>904796004</t>
-  </si>
-  <si>
-    <t>870319781</t>
-  </si>
-  <si>
-    <t>869834469</t>
-  </si>
-  <si>
-    <t>849505833</t>
-  </si>
-  <si>
-    <t>847712126</t>
-  </si>
-  <si>
-    <t>839577917</t>
-  </si>
-  <si>
-    <t>797621400</t>
-  </si>
-  <si>
-    <t>836428841</t>
-  </si>
-  <si>
-    <t>835766118</t>
-  </si>
-  <si>
-    <t>830302679</t>
-  </si>
-  <si>
-    <t>827765896</t>
-  </si>
-  <si>
-    <t>825270873</t>
-  </si>
-  <si>
-    <t>814960906</t>
-  </si>
-  <si>
-    <t>814220913</t>
-  </si>
-  <si>
-    <t>806390898</t>
-  </si>
-  <si>
-    <t>803068844</t>
-  </si>
-  <si>
-    <t>797795956</t>
-  </si>
-  <si>
-    <t>794163315</t>
-  </si>
-  <si>
-    <t>790301216</t>
-  </si>
-  <si>
-    <t>746218761</t>
-  </si>
-  <si>
-    <t>177107822</t>
-  </si>
-  <si>
-    <t>735064796</t>
-  </si>
-  <si>
-    <t>944883952</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>948220581</t>
-  </si>
-  <si>
-    <t>948029297</t>
-  </si>
-  <si>
-    <t>948010362</t>
-  </si>
-  <si>
-    <t>947720425</t>
-  </si>
-  <si>
-    <t>947370452</t>
-  </si>
-  <si>
-    <t>947225797</t>
-  </si>
-  <si>
-    <t>945113193</t>
+    <t>956987063</t>
+  </si>
+  <si>
+    <t>738449333</t>
+  </si>
+  <si>
+    <t>179587872</t>
+  </si>
+  <si>
+    <t>719936415</t>
+  </si>
+  <si>
+    <t>179360940</t>
+  </si>
+  <si>
+    <t>177954413</t>
+  </si>
+  <si>
+    <t>177923830</t>
+  </si>
+  <si>
+    <t>177236647</t>
+  </si>
+  <si>
+    <t>915745123</t>
+  </si>
+  <si>
+    <t>892744263</t>
+  </si>
+  <si>
+    <t>899343556</t>
+  </si>
+  <si>
+    <t>877921423</t>
+  </si>
+  <si>
+    <t>869630230</t>
+  </si>
+  <si>
+    <t>829464530</t>
+  </si>
+  <si>
+    <t>840350296</t>
+  </si>
+  <si>
+    <t>834976866</t>
+  </si>
+  <si>
+    <t>829755754</t>
+  </si>
+  <si>
+    <t>744849245</t>
+  </si>
+  <si>
+    <t>805912684</t>
+  </si>
+  <si>
+    <t>819606413</t>
+  </si>
+  <si>
+    <t>816337616</t>
+  </si>
+  <si>
+    <t>814056564</t>
+  </si>
+  <si>
+    <t>809659752</t>
+  </si>
+  <si>
+    <t>808648152</t>
+  </si>
+  <si>
+    <t>807928050</t>
+  </si>
+  <si>
+    <t>807626803</t>
+  </si>
+  <si>
+    <t>791730025</t>
+  </si>
+  <si>
+    <t>801754155</t>
+  </si>
+  <si>
+    <t>800720348</t>
+  </si>
+  <si>
+    <t>789931718</t>
+  </si>
+  <si>
+    <t>787692262</t>
+  </si>
+  <si>
+    <t>749081273</t>
+  </si>
+  <si>
+    <t>862870957</t>
+  </si>
+  <si>
+    <t>862698564</t>
+  </si>
+  <si>
+    <t>862390626</t>
+  </si>
+  <si>
+    <t>819015656</t>
+  </si>
+  <si>
+    <t>888575036</t>
+  </si>
+  <si>
+    <t>919771968</t>
+  </si>
+  <si>
+    <t>920051467</t>
+  </si>
+  <si>
+    <t>865141067</t>
+  </si>
+  <si>
+    <t>872669951</t>
+  </si>
+  <si>
+    <t>845794498</t>
+  </si>
+  <si>
+    <t>948070416</t>
+  </si>
+  <si>
+    <t>947259275</t>
+  </si>
+  <si>
+    <t>947962506</t>
+  </si>
+  <si>
+    <t>947868588</t>
+  </si>
+  <si>
+    <t>847602517</t>
+  </si>
+  <si>
+    <t>935197180</t>
   </si>
 </sst>
 </file>
@@ -616,7 +661,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -642,10 +687,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -654,10 +699,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -666,10 +711,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -678,10 +723,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -690,10 +735,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -702,10 +747,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -714,10 +759,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -726,10 +771,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -738,10 +783,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -750,10 +795,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -762,10 +807,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -774,10 +819,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -786,10 +831,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -798,10 +843,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -810,10 +855,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -822,10 +867,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -834,10 +879,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -846,10 +891,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -858,10 +903,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -870,10 +915,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -882,10 +927,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -894,10 +939,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -906,10 +951,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -918,10 +963,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -930,10 +975,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -942,10 +987,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -957,7 +1002,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -969,7 +1014,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -981,7 +1026,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -993,7 +1038,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1005,7 +1050,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1017,7 +1062,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1029,7 +1074,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1037,20 +1082,173 @@
       <c r="D34"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="5"/>
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D35"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="5"/>
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D36"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="5"/>
+      <c r="A37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D37"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="5"/>
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1075,31 +1273,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88023778-0650-48DB-A226-E5C634291429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7EB647-1858-408C-892A-D12809FEE5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="309">
   <si>
     <t>Status</t>
   </si>
@@ -54,148 +54,910 @@
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>956987063</t>
-  </si>
-  <si>
-    <t>738449333</t>
-  </si>
-  <si>
-    <t>179587872</t>
-  </si>
-  <si>
-    <t>719936415</t>
-  </si>
-  <si>
-    <t>179360940</t>
-  </si>
-  <si>
-    <t>177954413</t>
-  </si>
-  <si>
-    <t>177923830</t>
-  </si>
-  <si>
     <t>177236647</t>
   </si>
   <si>
-    <t>915745123</t>
-  </si>
-  <si>
-    <t>892744263</t>
-  </si>
-  <si>
-    <t>899343556</t>
-  </si>
-  <si>
-    <t>877921423</t>
-  </si>
-  <si>
-    <t>869630230</t>
-  </si>
-  <si>
-    <t>829464530</t>
-  </si>
-  <si>
-    <t>840350296</t>
-  </si>
-  <si>
-    <t>834976866</t>
-  </si>
-  <si>
-    <t>829755754</t>
-  </si>
-  <si>
-    <t>744849245</t>
-  </si>
-  <si>
-    <t>805912684</t>
-  </si>
-  <si>
-    <t>819606413</t>
-  </si>
-  <si>
-    <t>816337616</t>
-  </si>
-  <si>
-    <t>814056564</t>
-  </si>
-  <si>
-    <t>809659752</t>
-  </si>
-  <si>
-    <t>808648152</t>
-  </si>
-  <si>
-    <t>807928050</t>
-  </si>
-  <si>
-    <t>807626803</t>
-  </si>
-  <si>
-    <t>791730025</t>
-  </si>
-  <si>
-    <t>801754155</t>
-  </si>
-  <si>
-    <t>800720348</t>
-  </si>
-  <si>
-    <t>789931718</t>
-  </si>
-  <si>
-    <t>787692262</t>
-  </si>
-  <si>
-    <t>749081273</t>
-  </si>
-  <si>
-    <t>862870957</t>
-  </si>
-  <si>
-    <t>862698564</t>
-  </si>
-  <si>
-    <t>862390626</t>
-  </si>
-  <si>
-    <t>819015656</t>
-  </si>
-  <si>
-    <t>888575036</t>
-  </si>
-  <si>
-    <t>919771968</t>
-  </si>
-  <si>
-    <t>920051467</t>
-  </si>
-  <si>
-    <t>865141067</t>
-  </si>
-  <si>
-    <t>872669951</t>
-  </si>
-  <si>
-    <t>845794498</t>
-  </si>
-  <si>
-    <t>948070416</t>
-  </si>
-  <si>
-    <t>947259275</t>
-  </si>
-  <si>
-    <t>947962506</t>
-  </si>
-  <si>
-    <t>947868588</t>
-  </si>
-  <si>
-    <t>847602517</t>
-  </si>
-  <si>
-    <t>935197180</t>
+    <t>849713098</t>
+  </si>
+  <si>
+    <t>925431458</t>
+  </si>
+  <si>
+    <t>925333100</t>
+  </si>
+  <si>
+    <t>904796004</t>
+  </si>
+  <si>
+    <t>870319781</t>
+  </si>
+  <si>
+    <t>869834469</t>
+  </si>
+  <si>
+    <t>849505833</t>
+  </si>
+  <si>
+    <t>847712126</t>
+  </si>
+  <si>
+    <t>839577917</t>
+  </si>
+  <si>
+    <t>797621400</t>
+  </si>
+  <si>
+    <t>836428841</t>
+  </si>
+  <si>
+    <t>835766118</t>
+  </si>
+  <si>
+    <t>830302679</t>
+  </si>
+  <si>
+    <t>827765896</t>
+  </si>
+  <si>
+    <t>825270873</t>
+  </si>
+  <si>
+    <t>814960906</t>
+  </si>
+  <si>
+    <t>814220913</t>
+  </si>
+  <si>
+    <t>806390898</t>
+  </si>
+  <si>
+    <t>803068844</t>
+  </si>
+  <si>
+    <t>797795956</t>
+  </si>
+  <si>
+    <t>794163315</t>
+  </si>
+  <si>
+    <t>790301216</t>
+  </si>
+  <si>
+    <t>746218761</t>
+  </si>
+  <si>
+    <t>177107822</t>
+  </si>
+  <si>
+    <t>735064796</t>
+  </si>
+  <si>
+    <t>944883952</t>
+  </si>
+  <si>
+    <t>948220581</t>
+  </si>
+  <si>
+    <t>948029297</t>
+  </si>
+  <si>
+    <t>948010362</t>
+  </si>
+  <si>
+    <t>947720425</t>
+  </si>
+  <si>
+    <t>947370452</t>
+  </si>
+  <si>
+    <t>947225797</t>
+  </si>
+  <si>
+    <t>945113193</t>
+  </si>
+  <si>
+    <t>955670751</t>
+  </si>
+  <si>
+    <t>752613533</t>
+  </si>
+  <si>
+    <t>745411755</t>
+  </si>
+  <si>
+    <t>746766629</t>
+  </si>
+  <si>
+    <t>745631584</t>
+  </si>
+  <si>
+    <t>708419910</t>
+  </si>
+  <si>
+    <t>727678751</t>
+  </si>
+  <si>
+    <t>708872324</t>
+  </si>
+  <si>
+    <t>772957035</t>
+  </si>
+  <si>
+    <t>768054342</t>
+  </si>
+  <si>
+    <t>905826040</t>
+  </si>
+  <si>
+    <t>865399988</t>
+  </si>
+  <si>
+    <t>862862640</t>
+  </si>
+  <si>
+    <t>786580914</t>
+  </si>
+  <si>
+    <t>815520071</t>
+  </si>
+  <si>
+    <t>817580164</t>
+  </si>
+  <si>
+    <t>816699908</t>
+  </si>
+  <si>
+    <t>816669802</t>
+  </si>
+  <si>
+    <t>816003648</t>
+  </si>
+  <si>
+    <t>810729933</t>
+  </si>
+  <si>
+    <t>813320631</t>
+  </si>
+  <si>
+    <t>790760593</t>
+  </si>
+  <si>
+    <t>790500593</t>
+  </si>
+  <si>
+    <t>790281376</t>
+  </si>
+  <si>
+    <t>906446855</t>
+  </si>
+  <si>
+    <t>930495175</t>
+  </si>
+  <si>
+    <t>846298010</t>
+  </si>
+  <si>
+    <t>831737410</t>
+  </si>
+  <si>
+    <t>836887376</t>
+  </si>
+  <si>
+    <t>822459552</t>
+  </si>
+  <si>
+    <t>745692347</t>
+  </si>
+  <si>
+    <t>178554428</t>
+  </si>
+  <si>
+    <t>CREDITO A MENOR</t>
+  </si>
+  <si>
+    <t>792107728</t>
+  </si>
+  <si>
+    <t>CREDITO A MAIOR</t>
+  </si>
+  <si>
+    <t>796552333</t>
+  </si>
+  <si>
+    <t>180814356</t>
+  </si>
+  <si>
+    <t>180814778</t>
+  </si>
+  <si>
+    <t>175547110</t>
+  </si>
+  <si>
+    <t>177994997</t>
+  </si>
+  <si>
+    <t>178540195</t>
+  </si>
+  <si>
+    <t>178566497</t>
+  </si>
+  <si>
+    <t>178725002</t>
+  </si>
+  <si>
+    <t>179485713</t>
+  </si>
+  <si>
+    <t>179586643</t>
+  </si>
+  <si>
+    <t>179770924</t>
+  </si>
+  <si>
+    <t>708387588</t>
+  </si>
+  <si>
+    <t>721854507</t>
+  </si>
+  <si>
+    <t>748976747</t>
+  </si>
+  <si>
+    <t>754673469</t>
+  </si>
+  <si>
+    <t>754674418</t>
+  </si>
+  <si>
+    <t>759655503</t>
+  </si>
+  <si>
+    <t>764124750</t>
+  </si>
+  <si>
+    <t>770587214</t>
+  </si>
+  <si>
+    <t>785488861</t>
+  </si>
+  <si>
+    <t>792003596</t>
+  </si>
+  <si>
+    <t>792955761</t>
+  </si>
+  <si>
+    <t>797185976</t>
+  </si>
+  <si>
+    <t>797673369</t>
+  </si>
+  <si>
+    <t>798903799</t>
+  </si>
+  <si>
+    <t>799483312</t>
+  </si>
+  <si>
+    <t>799712900</t>
+  </si>
+  <si>
+    <t>800078440</t>
+  </si>
+  <si>
+    <t>813406117</t>
+  </si>
+  <si>
+    <t>815869346</t>
+  </si>
+  <si>
+    <t>821448010</t>
+  </si>
+  <si>
+    <t>837079569</t>
+  </si>
+  <si>
+    <t>843530548</t>
+  </si>
+  <si>
+    <t>846717837</t>
+  </si>
+  <si>
+    <t>847025248</t>
+  </si>
+  <si>
+    <t>849117324</t>
+  </si>
+  <si>
+    <t>854634445</t>
+  </si>
+  <si>
+    <t>858619996</t>
+  </si>
+  <si>
+    <t>862176744</t>
+  </si>
+  <si>
+    <t>862348863</t>
+  </si>
+  <si>
+    <t>869290415</t>
+  </si>
+  <si>
+    <t>870325648</t>
+  </si>
+  <si>
+    <t>873320661</t>
+  </si>
+  <si>
+    <t>875686606</t>
+  </si>
+  <si>
+    <t>876011127</t>
+  </si>
+  <si>
+    <t>878438047</t>
+  </si>
+  <si>
+    <t>882989241</t>
+  </si>
+  <si>
+    <t>884232871</t>
+  </si>
+  <si>
+    <t>895379968</t>
+  </si>
+  <si>
+    <t>903402281</t>
+  </si>
+  <si>
+    <t>903440471</t>
+  </si>
+  <si>
+    <t>905216564</t>
+  </si>
+  <si>
+    <t>905885905</t>
+  </si>
+  <si>
+    <t>178351668</t>
+  </si>
+  <si>
+    <t>179319979</t>
+  </si>
+  <si>
+    <t>179453398</t>
+  </si>
+  <si>
+    <t>179586460</t>
+  </si>
+  <si>
+    <t>179842954</t>
+  </si>
+  <si>
+    <t>711722359</t>
+  </si>
+  <si>
+    <t>723777714</t>
+  </si>
+  <si>
+    <t>755665951</t>
+  </si>
+  <si>
+    <t>762264186</t>
+  </si>
+  <si>
+    <t>765004548</t>
+  </si>
+  <si>
+    <t>766333284</t>
+  </si>
+  <si>
+    <t>768207718</t>
+  </si>
+  <si>
+    <t>769012059</t>
+  </si>
+  <si>
+    <t>780405258</t>
+  </si>
+  <si>
+    <t>783258472</t>
+  </si>
+  <si>
+    <t>790229292</t>
+  </si>
+  <si>
+    <t>797631623</t>
+  </si>
+  <si>
+    <t>817693769</t>
+  </si>
+  <si>
+    <t>828657282</t>
+  </si>
+  <si>
+    <t>829039308</t>
+  </si>
+  <si>
+    <t>829242142</t>
+  </si>
+  <si>
+    <t>840503688</t>
+  </si>
+  <si>
+    <t>843904032</t>
+  </si>
+  <si>
+    <t>849632686</t>
+  </si>
+  <si>
+    <t>849728963</t>
+  </si>
+  <si>
+    <t>854248782</t>
+  </si>
+  <si>
+    <t>860643927</t>
+  </si>
+  <si>
+    <t>863156828</t>
+  </si>
+  <si>
+    <t>882627759</t>
+  </si>
+  <si>
+    <t>883885729</t>
+  </si>
+  <si>
+    <t>887072811</t>
+  </si>
+  <si>
+    <t>887072944</t>
+  </si>
+  <si>
+    <t>891147740</t>
+  </si>
+  <si>
+    <t>897801563</t>
+  </si>
+  <si>
+    <t>908769148</t>
+  </si>
+  <si>
+    <t>908771037</t>
+  </si>
+  <si>
+    <t>908993110</t>
+  </si>
+  <si>
+    <t>909711206</t>
+  </si>
+  <si>
+    <t>912624792</t>
+  </si>
+  <si>
+    <t>916261021</t>
+  </si>
+  <si>
+    <t>916262763</t>
+  </si>
+  <si>
+    <t>917039129</t>
+  </si>
+  <si>
+    <t>917425906</t>
+  </si>
+  <si>
+    <t>914237577</t>
+  </si>
+  <si>
+    <t>DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>826916565</t>
+  </si>
+  <si>
+    <t>718726213</t>
+  </si>
+  <si>
+    <t>921374710</t>
+  </si>
+  <si>
+    <t>INCIDENCIA DESCONHECIDA</t>
+  </si>
+  <si>
+    <t>180799706</t>
+  </si>
+  <si>
+    <t>173633367</t>
+  </si>
+  <si>
+    <t>177649971</t>
+  </si>
+  <si>
+    <t>720703515</t>
+  </si>
+  <si>
+    <t>740163039</t>
+  </si>
+  <si>
+    <t>765412295</t>
+  </si>
+  <si>
+    <t>779509862</t>
+  </si>
+  <si>
+    <t>779744014</t>
+  </si>
+  <si>
+    <t>802899686</t>
+  </si>
+  <si>
+    <t>803988868</t>
+  </si>
+  <si>
+    <t>805105958</t>
+  </si>
+  <si>
+    <t>818036208</t>
+  </si>
+  <si>
+    <t>819303359</t>
+  </si>
+  <si>
+    <t>862114190</t>
+  </si>
+  <si>
+    <t>892410543</t>
+  </si>
+  <si>
+    <t>893767800</t>
+  </si>
+  <si>
+    <t>896358847</t>
+  </si>
+  <si>
+    <t>896358938</t>
+  </si>
+  <si>
+    <t>896358979</t>
+  </si>
+  <si>
+    <t>903823940</t>
+  </si>
+  <si>
+    <t>905298570</t>
+  </si>
+  <si>
+    <t>906837152</t>
+  </si>
+  <si>
+    <t>908976545</t>
+  </si>
+  <si>
+    <t>910442288</t>
+  </si>
+  <si>
+    <t>914979822</t>
+  </si>
+  <si>
+    <t>915329837</t>
+  </si>
+  <si>
+    <t>920916230</t>
+  </si>
+  <si>
+    <t>926073929</t>
+  </si>
+  <si>
+    <t>934567847</t>
+  </si>
+  <si>
+    <t>935402614</t>
+  </si>
+  <si>
+    <t>943910848</t>
+  </si>
+  <si>
+    <t>899127835</t>
+  </si>
+  <si>
+    <t>923972024</t>
+  </si>
+  <si>
+    <t>927605745</t>
+  </si>
+  <si>
+    <t>927605893</t>
+  </si>
+  <si>
+    <t>941598264</t>
+  </si>
+  <si>
+    <t>942857636</t>
+  </si>
+  <si>
+    <t>944200942</t>
+  </si>
+  <si>
+    <t>819382445</t>
+  </si>
+  <si>
+    <t>175020076</t>
+  </si>
+  <si>
+    <t>178834838</t>
+  </si>
+  <si>
+    <t>179594670</t>
+  </si>
+  <si>
+    <t>663307175</t>
+  </si>
+  <si>
+    <t>725812535</t>
+  </si>
+  <si>
+    <t>732923028</t>
+  </si>
+  <si>
+    <t>740386127</t>
+  </si>
+  <si>
+    <t>759346194</t>
+  </si>
+  <si>
+    <t>778035596</t>
+  </si>
+  <si>
+    <t>795094055</t>
+  </si>
+  <si>
+    <t>797811407</t>
+  </si>
+  <si>
+    <t>804763153</t>
+  </si>
+  <si>
+    <t>806060525</t>
+  </si>
+  <si>
+    <t>810974950</t>
+  </si>
+  <si>
+    <t>819769492</t>
+  </si>
+  <si>
+    <t>820839961</t>
+  </si>
+  <si>
+    <t>822566976</t>
+  </si>
+  <si>
+    <t>828967699</t>
+  </si>
+  <si>
+    <t>839096355</t>
+  </si>
+  <si>
+    <t>839147042</t>
+  </si>
+  <si>
+    <t>844615405</t>
+  </si>
+  <si>
+    <t>844878086</t>
+  </si>
+  <si>
+    <t>849659390</t>
+  </si>
+  <si>
+    <t>850845698</t>
+  </si>
+  <si>
+    <t>852018906</t>
+  </si>
+  <si>
+    <t>857656445</t>
+  </si>
+  <si>
+    <t>867010377</t>
+  </si>
+  <si>
+    <t>883700084</t>
+  </si>
+  <si>
+    <t>891521696</t>
+  </si>
+  <si>
+    <t>897225524</t>
+  </si>
+  <si>
+    <t>897805028</t>
+  </si>
+  <si>
+    <t>899198638</t>
+  </si>
+  <si>
+    <t>899752251</t>
+  </si>
+  <si>
+    <t>916119450</t>
+  </si>
+  <si>
+    <t>941732368</t>
+  </si>
+  <si>
+    <t>948477678</t>
+  </si>
+  <si>
+    <t>785197744</t>
+  </si>
+  <si>
+    <t>176365199</t>
+  </si>
+  <si>
+    <t>179297852</t>
+  </si>
+  <si>
+    <t>179709237</t>
+  </si>
+  <si>
+    <t>659196343</t>
+  </si>
+  <si>
+    <t>744570999</t>
+  </si>
+  <si>
+    <t>746670821</t>
+  </si>
+  <si>
+    <t>750250635</t>
+  </si>
+  <si>
+    <t>774272573</t>
+  </si>
+  <si>
+    <t>774283422</t>
+  </si>
+  <si>
+    <t>776712014</t>
+  </si>
+  <si>
+    <t>778450258</t>
+  </si>
+  <si>
+    <t>784016952</t>
+  </si>
+  <si>
+    <t>789445545</t>
+  </si>
+  <si>
+    <t>794203558</t>
+  </si>
+  <si>
+    <t>794253496</t>
+  </si>
+  <si>
+    <t>800523973</t>
+  </si>
+  <si>
+    <t>803322373</t>
+  </si>
+  <si>
+    <t>805279175</t>
+  </si>
+  <si>
+    <t>805662966</t>
+  </si>
+  <si>
+    <t>807886076</t>
+  </si>
+  <si>
+    <t>812066185</t>
+  </si>
+  <si>
+    <t>816306108</t>
+  </si>
+  <si>
+    <t>821149873</t>
+  </si>
+  <si>
+    <t>826658738</t>
+  </si>
+  <si>
+    <t>829230048</t>
+  </si>
+  <si>
+    <t>829833684</t>
+  </si>
+  <si>
+    <t>847822511</t>
+  </si>
+  <si>
+    <t>849724970</t>
+  </si>
+  <si>
+    <t>850025978</t>
+  </si>
+  <si>
+    <t>855099168</t>
+  </si>
+  <si>
+    <t>868189170</t>
+  </si>
+  <si>
+    <t>869738173</t>
+  </si>
+  <si>
+    <t>873119360</t>
+  </si>
+  <si>
+    <t>891147757</t>
+  </si>
+  <si>
+    <t>891480463</t>
+  </si>
+  <si>
+    <t>898905454</t>
+  </si>
+  <si>
+    <t>948043330</t>
+  </si>
+  <si>
+    <t>948751932</t>
+  </si>
+  <si>
+    <t>956625382</t>
+  </si>
+  <si>
+    <t>957226834</t>
+  </si>
+  <si>
+    <t>968740468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
+  </si>
+  <si>
+    <t>968998991</t>
+  </si>
+  <si>
+    <t>968824775</t>
+  </si>
+  <si>
+    <t>968805972</t>
+  </si>
+  <si>
+    <t>968781512</t>
+  </si>
+  <si>
+    <t>968469159</t>
+  </si>
+  <si>
+    <t>968428007</t>
+  </si>
+  <si>
+    <t>968391668</t>
+  </si>
+  <si>
+    <t>970139105</t>
+  </si>
+  <si>
+    <t>970894147</t>
+  </si>
+  <si>
+    <t>970936633</t>
+  </si>
+  <si>
+    <t>972250298</t>
+  </si>
+  <si>
+    <t>972718419</t>
+  </si>
+  <si>
+    <t>972283273</t>
   </si>
 </sst>
 </file>
@@ -661,7 +1423,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D362"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -687,7 +1449,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>5</v>
@@ -699,7 +1461,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>5</v>
@@ -711,7 +1473,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
@@ -723,7 +1485,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -735,7 +1497,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>5</v>
@@ -747,7 +1509,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>5</v>
@@ -759,7 +1521,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>5</v>
@@ -771,7 +1533,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>5</v>
@@ -783,7 +1545,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>5</v>
@@ -795,7 +1557,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>5</v>
@@ -807,7 +1569,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>5</v>
@@ -819,7 +1581,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>5</v>
@@ -831,7 +1593,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>5</v>
@@ -843,7 +1605,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>5</v>
@@ -855,7 +1617,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>5</v>
@@ -867,7 +1629,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>5</v>
@@ -879,7 +1641,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>5</v>
@@ -891,7 +1653,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>5</v>
@@ -903,7 +1665,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>5</v>
@@ -915,7 +1677,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>5</v>
@@ -927,7 +1689,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>5</v>
@@ -939,7 +1701,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>5</v>
@@ -951,7 +1713,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>5</v>
@@ -963,7 +1725,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>5</v>
@@ -975,7 +1737,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>5</v>
@@ -987,10 +1749,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -999,10 +1761,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1011,10 +1773,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1023,10 +1785,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1035,10 +1797,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1047,10 +1809,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1059,10 +1821,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1071,10 +1833,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1083,7 +1845,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>5</v>
@@ -1095,10 +1857,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1107,10 +1869,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1119,10 +1881,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1131,10 +1893,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1142,10 +1904,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1153,10 +1915,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1164,10 +1926,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1175,10 +1937,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1186,10 +1948,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1197,10 +1959,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1208,10 +1970,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
@@ -1219,10 +1981,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>4</v>
@@ -1230,10 +1992,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>4</v>
@@ -1241,12 +2003,3455 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C328" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C334" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C335" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C336" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C337" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C338" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C339" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B343" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B344" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C344" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B345" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C345" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B348" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C348" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C349" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B350" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C350" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B351" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C354" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C355" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C356" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C360" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C362" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1273,31 +5478,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DEDA10-A9C3-4C1C-B70B-CEE0D9D3A62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F755D6CD-F4F0-4F37-9A79-3C0F0D365018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="225">
   <si>
     <t>Status</t>
   </si>
@@ -48,535 +48,664 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>912177585</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>938922956</t>
-  </si>
-  <si>
-    <t>796148488</t>
-  </si>
-  <si>
-    <t>808690113</t>
-  </si>
-  <si>
-    <t>823005602</t>
-  </si>
-  <si>
-    <t>804522385</t>
-  </si>
-  <si>
-    <t>789467952</t>
-  </si>
-  <si>
-    <t>751785712</t>
-  </si>
-  <si>
-    <t>753193824</t>
-  </si>
-  <si>
-    <t>772967463</t>
-  </si>
-  <si>
-    <t>938922840</t>
-  </si>
-  <si>
-    <t>912177577</t>
-  </si>
-  <si>
-    <t>896478686</t>
-  </si>
-  <si>
-    <t>877074686</t>
-  </si>
-  <si>
-    <t>882879905</t>
-  </si>
-  <si>
-    <t>853291718</t>
-  </si>
-  <si>
-    <t>830520569</t>
-  </si>
-  <si>
-    <t>839987595</t>
-  </si>
-  <si>
-    <t>845954209</t>
-  </si>
-  <si>
-    <t>836642292</t>
-  </si>
-  <si>
-    <t>836373997</t>
-  </si>
-  <si>
-    <t>825814001</t>
-  </si>
-  <si>
-    <t>824422152</t>
-  </si>
-  <si>
-    <t>844838056</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>847040130</t>
-  </si>
-  <si>
-    <t>944793474</t>
-  </si>
-  <si>
-    <t>781871797</t>
-  </si>
-  <si>
-    <t>181623970</t>
-  </si>
-  <si>
-    <t>182435960</t>
-  </si>
-  <si>
-    <t>182435622</t>
-  </si>
-  <si>
-    <t>182435572</t>
-  </si>
-  <si>
-    <t>182434641</t>
-  </si>
-  <si>
-    <t>182434633</t>
-  </si>
-  <si>
-    <t>179941293</t>
-  </si>
-  <si>
-    <t>950068050</t>
-  </si>
-  <si>
-    <t>953830472</t>
-  </si>
-  <si>
-    <t>952985293</t>
-  </si>
-  <si>
-    <t>902629512</t>
-  </si>
-  <si>
-    <t>931168201</t>
-  </si>
-  <si>
-    <t>926952460</t>
-  </si>
-  <si>
-    <t>924508132</t>
-  </si>
-  <si>
-    <t>898499466</t>
-  </si>
-  <si>
-    <t>871095760</t>
-  </si>
-  <si>
-    <t>959428834</t>
-  </si>
-  <si>
-    <t>958589438</t>
-  </si>
-  <si>
-    <t>956291136</t>
-  </si>
-  <si>
-    <t>955056860</t>
-  </si>
-  <si>
-    <t>954843383</t>
-  </si>
-  <si>
-    <t>953971359</t>
-  </si>
-  <si>
-    <t>953873472</t>
-  </si>
-  <si>
-    <t>953835778</t>
-  </si>
-  <si>
-    <t>890720927</t>
-  </si>
-  <si>
-    <t>184865891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
-  </si>
-  <si>
-    <t>185614249</t>
-  </si>
-  <si>
-    <t>925525770</t>
-  </si>
-  <si>
-    <t>176870446</t>
-  </si>
-  <si>
-    <t>179690445</t>
-  </si>
-  <si>
-    <t>179326297</t>
-  </si>
-  <si>
-    <t>955485895</t>
-  </si>
-  <si>
-    <t>944763394</t>
-  </si>
-  <si>
-    <t>886470339</t>
-  </si>
-  <si>
-    <t>873846939</t>
-  </si>
-  <si>
-    <t>846947566</t>
-  </si>
-  <si>
-    <t>856038264</t>
-  </si>
-  <si>
-    <t>844922389</t>
-  </si>
-  <si>
-    <t>817210655</t>
-  </si>
-  <si>
-    <t>841502408</t>
-  </si>
-  <si>
-    <t>825217767</t>
-  </si>
-  <si>
-    <t>823361831</t>
-  </si>
-  <si>
-    <t>753797749</t>
-  </si>
-  <si>
-    <t>783453537</t>
-  </si>
-  <si>
-    <t>791076296</t>
-  </si>
-  <si>
-    <t>810958730</t>
-  </si>
-  <si>
-    <t>804090425</t>
-  </si>
-  <si>
-    <t>802834675</t>
-  </si>
-  <si>
-    <t>798688689</t>
-  </si>
-  <si>
-    <t>796277428</t>
-  </si>
-  <si>
-    <t>788334757</t>
-  </si>
-  <si>
-    <t>753126832</t>
-  </si>
-  <si>
-    <t>752893432</t>
-  </si>
-  <si>
-    <t>752704076</t>
-  </si>
-  <si>
-    <t>751788724</t>
-  </si>
-  <si>
-    <t>829684541</t>
-  </si>
-  <si>
-    <t>953855271</t>
-  </si>
-  <si>
-    <t>931179513</t>
-  </si>
-  <si>
-    <t>908993136</t>
-  </si>
-  <si>
-    <t>899388122</t>
-  </si>
-  <si>
-    <t>897612127</t>
-  </si>
-  <si>
-    <t>954655803</t>
-  </si>
-  <si>
-    <t>185652389</t>
-  </si>
-  <si>
-    <t>185651431</t>
-  </si>
-  <si>
-    <t>188835262</t>
-  </si>
-  <si>
-    <t>188789535</t>
-  </si>
-  <si>
-    <t>188745909</t>
-  </si>
-  <si>
-    <t>188713949</t>
-  </si>
-  <si>
-    <t>188353829</t>
-  </si>
-  <si>
-    <t>947576942</t>
-  </si>
-  <si>
-    <t>844879985</t>
-  </si>
-  <si>
-    <t>883739850</t>
-  </si>
-  <si>
-    <t>901942353</t>
-  </si>
-  <si>
-    <t>873954857</t>
-  </si>
-  <si>
-    <t>868152475</t>
-  </si>
-  <si>
-    <t>824952166</t>
-  </si>
-  <si>
-    <t>824029262</t>
-  </si>
-  <si>
-    <t>821851585</t>
-  </si>
-  <si>
-    <t>821559683</t>
-  </si>
-  <si>
-    <t>907441129</t>
-  </si>
-  <si>
-    <t>920914433</t>
-  </si>
-  <si>
-    <t>933410825</t>
-  </si>
-  <si>
-    <t>926770128</t>
-  </si>
-  <si>
-    <t>919345599</t>
-  </si>
-  <si>
-    <t>913673251</t>
-  </si>
-  <si>
-    <t>950360820</t>
-  </si>
-  <si>
-    <t>950360762</t>
-  </si>
-  <si>
-    <t>950360747</t>
-  </si>
-  <si>
-    <t>180994133</t>
-  </si>
-  <si>
-    <t>967842208</t>
-  </si>
-  <si>
-    <t>818030946</t>
-  </si>
-  <si>
-    <t>814776898</t>
-  </si>
-  <si>
-    <t>812732505</t>
-  </si>
-  <si>
-    <t>811502024</t>
-  </si>
-  <si>
-    <t>810285118</t>
-  </si>
-  <si>
-    <t>802948285</t>
-  </si>
-  <si>
-    <t>805277229</t>
-  </si>
-  <si>
-    <t>758597888</t>
-  </si>
-  <si>
-    <t>796330292</t>
-  </si>
-  <si>
-    <t>793641766</t>
-  </si>
-  <si>
-    <t>782118578</t>
-  </si>
-  <si>
-    <t>754763377</t>
-  </si>
-  <si>
-    <t>179899848</t>
-  </si>
-  <si>
-    <t>175837404</t>
-  </si>
-  <si>
-    <t>175834708</t>
-  </si>
-  <si>
-    <t>182435754</t>
-  </si>
-  <si>
-    <t>823257591</t>
-  </si>
-  <si>
-    <t>875390514</t>
-  </si>
-  <si>
-    <t>900203336</t>
-  </si>
-  <si>
-    <t>898732254</t>
-  </si>
-  <si>
-    <t>886255102</t>
-  </si>
-  <si>
-    <t>895202640</t>
-  </si>
-  <si>
-    <t>892033949</t>
-  </si>
-  <si>
-    <t>889787689</t>
-  </si>
-  <si>
-    <t>882519063</t>
-  </si>
-  <si>
-    <t>878600265</t>
-  </si>
-  <si>
-    <t>880399427</t>
-  </si>
-  <si>
-    <t>880585850</t>
-  </si>
-  <si>
-    <t>871541607</t>
-  </si>
-  <si>
-    <t>870007618</t>
-  </si>
-  <si>
-    <t>865980068</t>
-  </si>
-  <si>
-    <t>865700334</t>
-  </si>
-  <si>
-    <t>854686684</t>
-  </si>
-  <si>
-    <t>857865665</t>
-  </si>
-  <si>
-    <t>856471986</t>
-  </si>
-  <si>
-    <t>845730070</t>
-  </si>
-  <si>
-    <t>844880256</t>
-  </si>
-  <si>
-    <t>837306210</t>
-  </si>
-  <si>
-    <t>834851523</t>
-  </si>
-  <si>
-    <t>822918243</t>
-  </si>
-  <si>
-    <t>938419128</t>
-  </si>
-  <si>
-    <t>917851937</t>
-  </si>
-  <si>
-    <t>933621645</t>
-  </si>
-  <si>
-    <t>936914526</t>
-  </si>
-  <si>
-    <t>935916944</t>
-  </si>
-  <si>
-    <t>934501358</t>
-  </si>
-  <si>
-    <t>924712387</t>
-  </si>
-  <si>
-    <t>907686566</t>
-  </si>
-  <si>
-    <t>906139518</t>
-  </si>
-  <si>
-    <t>906654102</t>
-  </si>
-  <si>
-    <t>960437097</t>
-  </si>
-  <si>
-    <t>961251802</t>
-  </si>
-  <si>
-    <t>961108028</t>
-  </si>
-  <si>
-    <t>940609971</t>
-  </si>
-  <si>
-    <t>937604290</t>
-  </si>
-  <si>
-    <t>948881994</t>
-  </si>
-  <si>
-    <t>190151856</t>
+    <t>756647891</t>
+  </si>
+  <si>
+    <t>879876070</t>
+  </si>
+  <si>
+    <t>776784880</t>
+  </si>
+  <si>
+    <t>822457010</t>
+  </si>
+  <si>
+    <t>809578341</t>
+  </si>
+  <si>
+    <t>802911085</t>
+  </si>
+  <si>
+    <t>754717449</t>
+  </si>
+  <si>
+    <t>972283117</t>
+  </si>
+  <si>
+    <t>177002130</t>
+  </si>
+  <si>
+    <t>179825090</t>
+  </si>
+  <si>
+    <t>179499383</t>
+  </si>
+  <si>
+    <t>969853039</t>
+  </si>
+  <si>
+    <t>949172906</t>
+  </si>
+  <si>
+    <t>864695782</t>
+  </si>
+  <si>
+    <t>846738155</t>
+  </si>
+  <si>
+    <t>849713106</t>
+  </si>
+  <si>
+    <t>830330019</t>
+  </si>
+  <si>
+    <t>828660195</t>
+  </si>
+  <si>
+    <t>827776034</t>
+  </si>
+  <si>
+    <t>827185467</t>
+  </si>
+  <si>
+    <t>827181458</t>
+  </si>
+  <si>
+    <t>825567054</t>
+  </si>
+  <si>
+    <t>825309127</t>
+  </si>
+  <si>
+    <t>827494612</t>
+  </si>
+  <si>
+    <t>821389719</t>
+  </si>
+  <si>
+    <t>824776896</t>
+  </si>
+  <si>
+    <t>823988195</t>
+  </si>
+  <si>
+    <t>823468495</t>
+  </si>
+  <si>
+    <t>823388800</t>
+  </si>
+  <si>
+    <t>815986744</t>
+  </si>
+  <si>
+    <t>816931624</t>
+  </si>
+  <si>
+    <t>816236719</t>
+  </si>
+  <si>
+    <t>816065308</t>
+  </si>
+  <si>
+    <t>810929889</t>
+  </si>
+  <si>
+    <t>776247318</t>
+  </si>
+  <si>
+    <t>749162297</t>
+  </si>
+  <si>
+    <t>768056198</t>
+  </si>
+  <si>
+    <t>938264391</t>
+  </si>
+  <si>
+    <t>966132429</t>
+  </si>
+  <si>
+    <t>177107830</t>
+  </si>
+  <si>
+    <t>174573125</t>
+  </si>
+  <si>
+    <t>961261165</t>
+  </si>
+  <si>
+    <t>960995078</t>
+  </si>
+  <si>
+    <t>960721037</t>
+  </si>
+  <si>
+    <t>960567711</t>
+  </si>
+  <si>
+    <t>960335903</t>
+  </si>
+  <si>
+    <t>960304156</t>
+  </si>
+  <si>
+    <t>960292989</t>
+  </si>
+  <si>
+    <t>960245359</t>
+  </si>
+  <si>
+    <t>959910351</t>
+  </si>
+  <si>
+    <t>955905397</t>
+  </si>
+  <si>
+    <t>941538674</t>
+  </si>
+  <si>
+    <t>940961232</t>
+  </si>
+  <si>
+    <t>940724655</t>
+  </si>
+  <si>
+    <t>940579158</t>
+  </si>
+  <si>
+    <t>937852493</t>
+  </si>
+  <si>
+    <t>934802483</t>
+  </si>
+  <si>
+    <t>908809209</t>
+  </si>
+  <si>
+    <t>927896021</t>
+  </si>
+  <si>
+    <t>933418463</t>
+  </si>
+  <si>
+    <t>934790415</t>
+  </si>
+  <si>
+    <t>933892766</t>
+  </si>
+  <si>
+    <t>933710919</t>
+  </si>
+  <si>
+    <t>933575312</t>
+  </si>
+  <si>
+    <t>933070009</t>
+  </si>
+  <si>
+    <t>933033429</t>
+  </si>
+  <si>
+    <t>932297678</t>
+  </si>
+  <si>
+    <t>931974186</t>
+  </si>
+  <si>
+    <t>931620995</t>
+  </si>
+  <si>
+    <t>931184133</t>
+  </si>
+  <si>
+    <t>930901453</t>
+  </si>
+  <si>
+    <t>930763218</t>
+  </si>
+  <si>
+    <t>930678937</t>
+  </si>
+  <si>
+    <t>930159284</t>
+  </si>
+  <si>
+    <t>929619280</t>
+  </si>
+  <si>
+    <t>929870586</t>
+  </si>
+  <si>
+    <t>929814485</t>
+  </si>
+  <si>
+    <t>929417412</t>
+  </si>
+  <si>
+    <t>929011090</t>
+  </si>
+  <si>
+    <t>928478803</t>
+  </si>
+  <si>
+    <t>928477037</t>
+  </si>
+  <si>
+    <t>928213481</t>
+  </si>
+  <si>
+    <t>928129240</t>
+  </si>
+  <si>
+    <t>924996741</t>
+  </si>
+  <si>
+    <t>927074090</t>
+  </si>
+  <si>
+    <t>926842604</t>
+  </si>
+  <si>
+    <t>918679980</t>
+  </si>
+  <si>
+    <t>922391069</t>
+  </si>
+  <si>
+    <t>923076040</t>
+  </si>
+  <si>
+    <t>919964373</t>
+  </si>
+  <si>
+    <t>921422436</t>
+  </si>
+  <si>
+    <t>920345075</t>
+  </si>
+  <si>
+    <t>919303275</t>
+  </si>
+  <si>
+    <t>916215563</t>
+  </si>
+  <si>
+    <t>915746014</t>
+  </si>
+  <si>
+    <t>913079012</t>
+  </si>
+  <si>
+    <t>912587064</t>
+  </si>
+  <si>
+    <t>911454977</t>
+  </si>
+  <si>
+    <t>911830358</t>
+  </si>
+  <si>
+    <t>912325465</t>
+  </si>
+  <si>
+    <t>912072174</t>
+  </si>
+  <si>
+    <t>909567491</t>
+  </si>
+  <si>
+    <t>909065538</t>
+  </si>
+  <si>
+    <t>908040920</t>
+  </si>
+  <si>
+    <t>906784990</t>
+  </si>
+  <si>
+    <t>906439496</t>
+  </si>
+  <si>
+    <t>906087980</t>
+  </si>
+  <si>
+    <t>828967988</t>
+  </si>
+  <si>
+    <t>879427387</t>
+  </si>
+  <si>
+    <t>883925004</t>
+  </si>
+  <si>
+    <t>889838912</t>
+  </si>
+  <si>
+    <t>888914722</t>
+  </si>
+  <si>
+    <t>888870346</t>
+  </si>
+  <si>
+    <t>887716276</t>
+  </si>
+  <si>
+    <t>884108212</t>
+  </si>
+  <si>
+    <t>881798395</t>
+  </si>
+  <si>
+    <t>882383262</t>
+  </si>
+  <si>
+    <t>878345788</t>
+  </si>
+  <si>
+    <t>877880017</t>
+  </si>
+  <si>
+    <t>872728740</t>
+  </si>
+  <si>
+    <t>877308266</t>
+  </si>
+  <si>
+    <t>877222939</t>
+  </si>
+  <si>
+    <t>875455184</t>
+  </si>
+  <si>
+    <t>874761780</t>
+  </si>
+  <si>
+    <t>874739976</t>
+  </si>
+  <si>
+    <t>874699840</t>
+  </si>
+  <si>
+    <t>874106978</t>
+  </si>
+  <si>
+    <t>874066529</t>
+  </si>
+  <si>
+    <t>873255040</t>
+  </si>
+  <si>
+    <t>872275924</t>
+  </si>
+  <si>
+    <t>872188333</t>
+  </si>
+  <si>
+    <t>872081678</t>
+  </si>
+  <si>
+    <t>871994178</t>
+  </si>
+  <si>
+    <t>904130865</t>
+  </si>
+  <si>
+    <t>900635990</t>
+  </si>
+  <si>
+    <t>901637995</t>
+  </si>
+  <si>
+    <t>900729496</t>
+  </si>
+  <si>
+    <t>900286711</t>
+  </si>
+  <si>
+    <t>898461961</t>
+  </si>
+  <si>
+    <t>898289214</t>
+  </si>
+  <si>
+    <t>898267079</t>
+  </si>
+  <si>
+    <t>897777268</t>
+  </si>
+  <si>
+    <t>897720094</t>
+  </si>
+  <si>
+    <t>897587881</t>
+  </si>
+  <si>
+    <t>897266270</t>
+  </si>
+  <si>
+    <t>894962897</t>
+  </si>
+  <si>
+    <t>894574122</t>
+  </si>
+  <si>
+    <t>891246666</t>
+  </si>
+  <si>
+    <t>892627914</t>
+  </si>
+  <si>
+    <t>892066295</t>
+  </si>
+  <si>
+    <t>905729202</t>
+  </si>
+  <si>
+    <t>903750432</t>
+  </si>
+  <si>
+    <t>903739161</t>
+  </si>
+  <si>
+    <t>903403016</t>
+  </si>
+  <si>
+    <t>903184087</t>
+  </si>
+  <si>
+    <t>865886653</t>
+  </si>
+  <si>
+    <t>869767412</t>
+  </si>
+  <si>
+    <t>870639980</t>
+  </si>
+  <si>
+    <t>869037683</t>
+  </si>
+  <si>
+    <t>868071402</t>
+  </si>
+  <si>
+    <t>867583985</t>
+  </si>
+  <si>
+    <t>867577912</t>
+  </si>
+  <si>
+    <t>866535002</t>
+  </si>
+  <si>
+    <t>866126646</t>
+  </si>
+  <si>
+    <t>864426394</t>
+  </si>
+  <si>
+    <t>861475055</t>
+  </si>
+  <si>
+    <t>863251488</t>
+  </si>
+  <si>
+    <t>863750661</t>
+  </si>
+  <si>
+    <t>862118977</t>
+  </si>
+  <si>
+    <t>854052093</t>
+  </si>
+  <si>
+    <t>861121832</t>
+  </si>
+  <si>
+    <t>856901107</t>
+  </si>
+  <si>
+    <t>852518962</t>
+  </si>
+  <si>
+    <t>848432005</t>
+  </si>
+  <si>
+    <t>850447057</t>
+  </si>
+  <si>
+    <t>852236490</t>
+  </si>
+  <si>
+    <t>851293583</t>
+  </si>
+  <si>
+    <t>847673963</t>
+  </si>
+  <si>
+    <t>846558850</t>
+  </si>
+  <si>
+    <t>846863219</t>
+  </si>
+  <si>
+    <t>846486540</t>
+  </si>
+  <si>
+    <t>845491830</t>
+  </si>
+  <si>
+    <t>845464506</t>
+  </si>
+  <si>
+    <t>843888102</t>
+  </si>
+  <si>
+    <t>841576485</t>
+  </si>
+  <si>
+    <t>843714423</t>
+  </si>
+  <si>
+    <t>843652383</t>
+  </si>
+  <si>
+    <t>843589791</t>
+  </si>
+  <si>
+    <t>841658895</t>
+  </si>
+  <si>
+    <t>837190093</t>
+  </si>
+  <si>
+    <t>837098304</t>
+  </si>
+  <si>
+    <t>834367801</t>
+  </si>
+  <si>
+    <t>832842243</t>
+  </si>
+  <si>
+    <t>831929678</t>
+  </si>
+  <si>
+    <t>830946798</t>
+  </si>
+  <si>
+    <t>827940838</t>
+  </si>
+  <si>
+    <t>617737972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>610247102</t>
+  </si>
+  <si>
+    <t>609961093</t>
+  </si>
+  <si>
+    <t>563482532</t>
+  </si>
+  <si>
+    <t>564038549</t>
+  </si>
+  <si>
+    <t>747116469</t>
+  </si>
+  <si>
+    <t>740421163</t>
+  </si>
+  <si>
+    <t>738331598</t>
+  </si>
+  <si>
+    <t>727847281</t>
+  </si>
+  <si>
+    <t>572428823</t>
+  </si>
+  <si>
+    <t>720129331</t>
+  </si>
+  <si>
+    <t>720129323</t>
+  </si>
+  <si>
+    <t>713243545</t>
+  </si>
+  <si>
+    <t>681631358</t>
+  </si>
+  <si>
+    <t>681631341</t>
+  </si>
+  <si>
+    <t>680900424</t>
+  </si>
+  <si>
+    <t>680528290</t>
+  </si>
+  <si>
+    <t>678948856</t>
+  </si>
+  <si>
+    <t>704789910</t>
+  </si>
+  <si>
+    <t>704029663</t>
+  </si>
+  <si>
+    <t>688609365</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1171,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D732"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1068,10 +1197,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -1080,10 +1209,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -1092,10 +1221,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -1104,10 +1233,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -1116,10 +1245,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -1128,10 +1257,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -1140,10 +1269,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -1152,10 +1281,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1164,10 +1293,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -1176,10 +1305,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -1188,10 +1317,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -1200,10 +1329,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -1212,10 +1341,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -1224,10 +1353,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -1236,10 +1365,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -1248,10 +1377,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -1260,10 +1389,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -1272,10 +1401,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -1284,10 +1413,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -1296,10 +1425,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -1308,10 +1437,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -1320,10 +1449,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -1332,10 +1461,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -1344,10 +1473,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -1359,7 +1488,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -1371,7 +1500,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1383,7 +1512,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1395,7 +1524,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1407,7 +1536,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1419,7 +1548,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1431,7 +1560,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1443,7 +1572,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1455,7 +1584,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1467,7 +1596,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1479,7 +1608,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1491,7 +1620,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1503,7 +1632,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1515,7 +1644,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1526,7 +1655,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1537,7 +1666,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1548,7 +1677,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1559,7 +1688,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1570,7 +1699,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1581,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1592,7 +1721,7 @@
         <v>51</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
@@ -1603,7 +1732,7 @@
         <v>52</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>4</v>
@@ -1614,7 +1743,7 @@
         <v>53</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>4</v>
@@ -1625,7 +1754,7 @@
         <v>54</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>4</v>
@@ -1636,7 +1765,7 @@
         <v>55</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>4</v>
@@ -1647,7 +1776,7 @@
         <v>56</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>4</v>
@@ -1658,7 +1787,7 @@
         <v>57</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>4</v>
@@ -1680,7 +1809,7 @@
         <v>59</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
@@ -1688,10 +1817,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>4</v>
@@ -1699,7 +1828,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>6</v>
@@ -1710,7 +1839,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>6</v>
@@ -1721,7 +1850,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>6</v>
@@ -1732,7 +1861,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>6</v>
@@ -1743,7 +1872,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>6</v>
@@ -1754,7 +1883,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>6</v>
@@ -1765,7 +1894,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>6</v>
@@ -1776,7 +1905,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>6</v>
@@ -1787,7 +1916,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>6</v>
@@ -1798,7 +1927,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>6</v>
@@ -1809,7 +1938,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>6</v>
@@ -1820,7 +1949,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>6</v>
@@ -1831,7 +1960,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>6</v>
@@ -1842,7 +1971,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>6</v>
@@ -1853,7 +1982,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>6</v>
@@ -1864,7 +1993,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>6</v>
@@ -1875,7 +2004,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>6</v>
@@ -1886,7 +2015,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>6</v>
@@ -1897,7 +2026,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>6</v>
@@ -1908,7 +2037,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>6</v>
@@ -1919,7 +2048,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>6</v>
@@ -1930,7 +2059,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>6</v>
@@ -1941,7 +2070,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>6</v>
@@ -1952,7 +2081,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>6</v>
@@ -1963,7 +2092,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>6</v>
@@ -1974,7 +2103,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>6</v>
@@ -1985,7 +2114,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>6</v>
@@ -1996,7 +2125,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>6</v>
@@ -2007,10 +2136,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
@@ -2018,10 +2147,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>4</v>
@@ -2029,10 +2158,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
@@ -2040,10 +2169,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>4</v>
@@ -2051,10 +2180,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>4</v>
@@ -2062,10 +2191,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>4</v>
@@ -2073,10 +2202,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>4</v>
@@ -2084,10 +2213,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>4</v>
@@ -2095,10 +2224,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>4</v>
@@ -2106,10 +2235,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>4</v>
@@ -2117,10 +2246,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>4</v>
@@ -2128,10 +2257,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>4</v>
@@ -2139,10 +2268,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>4</v>
@@ -2150,10 +2279,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>4</v>
@@ -2161,7 +2290,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>6</v>
@@ -2172,7 +2301,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>6</v>
@@ -2183,7 +2312,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>6</v>
@@ -2194,7 +2323,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>6</v>
@@ -2205,7 +2334,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>6</v>
@@ -2216,7 +2345,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>6</v>
@@ -2227,7 +2356,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>6</v>
@@ -2238,7 +2367,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>6</v>
@@ -2249,7 +2378,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>6</v>
@@ -2260,7 +2389,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>6</v>
@@ -2271,7 +2400,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>6</v>
@@ -2282,7 +2411,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>6</v>
@@ -2293,7 +2422,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>6</v>
@@ -2304,7 +2433,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>6</v>
@@ -2315,7 +2444,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>6</v>
@@ -2326,7 +2455,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>6</v>
@@ -2337,7 +2466,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>6</v>
@@ -2348,7 +2477,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>6</v>
@@ -2359,7 +2488,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>6</v>
@@ -2370,7 +2499,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>6</v>
@@ -2381,7 +2510,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>6</v>
@@ -2392,7 +2521,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>6</v>
@@ -2403,7 +2532,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>6</v>
@@ -2414,7 +2543,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>6</v>
@@ -2425,7 +2554,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>6</v>
@@ -2436,7 +2565,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>6</v>
@@ -2447,7 +2576,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>6</v>
@@ -2458,7 +2587,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>6</v>
@@ -2469,7 +2598,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>6</v>
@@ -2480,7 +2609,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>6</v>
@@ -2491,7 +2620,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>6</v>
@@ -2502,7 +2631,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>6</v>
@@ -2513,7 +2642,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>6</v>
@@ -2524,7 +2653,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>6</v>
@@ -2535,7 +2664,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>6</v>
@@ -2546,7 +2675,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>6</v>
@@ -2557,10 +2686,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>4</v>
@@ -2568,10 +2697,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>4</v>
@@ -2579,10 +2708,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>4</v>
@@ -2590,10 +2719,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>4</v>
@@ -2601,10 +2730,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>4</v>
@@ -2612,10 +2741,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>4</v>
@@ -2623,10 +2752,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>4</v>
@@ -2634,10 +2763,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>4</v>
@@ -2645,10 +2774,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>4</v>
@@ -2656,10 +2785,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>4</v>
@@ -2667,10 +2796,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>4</v>
@@ -2678,10 +2807,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>4</v>
@@ -2689,10 +2818,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>4</v>
@@ -2700,10 +2829,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>4</v>
@@ -2711,10 +2840,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>4</v>
@@ -2722,10 +2851,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>4</v>
@@ -2733,10 +2862,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>4</v>
@@ -2744,10 +2873,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>4</v>
@@ -2755,10 +2884,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>4</v>
@@ -2766,10 +2895,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C153" s="5" t="s">
         <v>4</v>
@@ -2777,10 +2906,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>4</v>
@@ -2788,10 +2917,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>4</v>
@@ -2799,10 +2928,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>4</v>
@@ -2810,10 +2939,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>4</v>
@@ -2821,10 +2950,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>4</v>
@@ -2832,10 +2961,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C159" s="5" t="s">
         <v>4</v>
@@ -2843,10 +2972,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C160" s="5" t="s">
         <v>4</v>
@@ -2854,10 +2983,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C161" s="5" t="s">
         <v>4</v>
@@ -2865,10 +2994,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C162" s="5" t="s">
         <v>4</v>
@@ -2876,10 +3005,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>4</v>
@@ -2887,10 +3016,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C164" s="5" t="s">
         <v>4</v>
@@ -2898,10 +3027,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>4</v>
@@ -2909,10 +3038,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C166" s="5" t="s">
         <v>4</v>
@@ -2920,10 +3049,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C167" s="5" t="s">
         <v>4</v>
@@ -2931,10 +3060,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>4</v>
@@ -2942,10 +3071,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>4</v>
@@ -2953,10 +3082,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>4</v>
@@ -2964,10 +3093,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>4</v>
@@ -2975,10 +3104,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C172" s="5" t="s">
         <v>4</v>
@@ -2986,10 +3115,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>4</v>
@@ -2997,7 +3126,7 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>6</v>
@@ -3008,12 +3137,6139 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B175" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C175" s="5" t="s">
+      <c r="B176" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C328" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C334" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C335" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C336" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C337" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C338" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C339" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B343" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B344" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C344" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B345" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C345" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B348" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C348" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C349" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B350" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C350" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B351" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C354" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C355" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C356" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C360" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B363" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C363" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B364" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C364" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C365" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B366" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C366" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C367" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B368" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C368" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B369" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C369" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C370" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C371" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C372" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C374" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C375" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C376" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C377" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C378" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C379" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C380" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C381" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C382" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C383" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C385" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C386" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C387" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C388" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C389" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C390" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B391" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C391" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B392" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C392" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B393" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C393" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C394" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B395" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C396" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C398" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B399" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C399" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C400" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B401" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C402" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C403" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C404" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C405" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C407" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C408" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C409" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C410" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B411" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C411" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B412" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C412" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B413" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C413" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B414" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C414" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B415" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C415" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C416" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A417" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A418" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C418" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A419" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C419" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A420" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B420" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C420" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C422" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A423" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C423" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A424" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C424" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C425" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A426" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B426" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C426" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C427" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B428" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A429" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B429" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C429" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A430" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B430" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C430" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C431" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C432" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C433" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B434" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C434" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B435" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C435" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B436" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C436" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A437" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C437" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A438" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C438" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A439" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B439" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A440" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B440" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C440" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A441" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C441" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A442" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B442" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C442" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A443" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B443" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C443" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A444" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B444" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C444" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A445" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B445" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C445" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B446" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C446" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B447" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C447" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B448" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C448" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A449" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B449" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C449" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A450" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B450" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A451" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B451" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C451" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A452" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C452" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A453" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B453" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C453" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A454" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B454" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C454" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A455" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B455" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C455" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A456" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B456" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C456" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A457" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B457" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A458" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B458" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C458" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A459" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B459" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C459" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A460" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B460" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C460" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B461" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B462" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C462" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A463" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B463" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C463" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A464" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B464" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C464" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A465" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B465" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C465" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A466" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B466" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C466" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A467" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B467" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C467" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B468" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C468" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A469" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B469" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C469" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A470" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B470" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C470" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A471" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B471" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C471" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A472" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B472" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A473" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B473" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C473" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A474" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B474" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C474" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A475" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B475" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C475" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B476" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C476" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B477" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C477" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A478" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B478" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C478" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A479" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B479" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C479" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B480" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C480" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B481" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C481" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B482" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C482" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B483" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B484" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C484" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B485" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C485" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B486" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C486" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A487" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B487" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C487" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A488" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B488" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C488" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A489" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B489" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C489" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B490" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C490" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A491" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B491" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C491" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A492" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B492" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C492" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A493" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B493" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C493" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A494" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B494" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C494" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A495" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B495" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C495" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A496" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B496" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C496" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A497" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B497" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C497" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A498" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B498" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C498" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A499" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B499" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C499" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A500" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B500" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C500" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A501" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B501" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C501" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A502" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B502" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C502" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A503" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B503" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C503" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A504" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B504" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C504" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A505" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B505" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A506" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B506" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C506" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A507" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B507" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C507" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A508" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B508" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C508" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A509" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B509" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C509" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A510" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B510" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C510" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A511" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B511" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C511" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A512" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B512" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C512" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A513" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B513" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C513" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A514" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B514" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C514" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A515" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B515" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C515" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A516" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B516" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C516" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A517" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B517" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C517" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A518" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B518" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C518" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A519" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B519" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C519" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A520" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C520" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A521" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B521" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A522" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B522" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C522" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A523" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B523" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A524" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C524" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A525" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B525" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C525" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A526" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B526" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C526" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A527" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B527" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A528" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B528" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A529" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B529" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A530" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C530" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A531" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B531" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A532" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B532" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A533" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B533" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A534" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B534" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A535" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B535" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A536" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B536" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A537" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B537" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A538" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B538" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A539" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B539" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C539" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A540" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B540" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A541" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B541" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A542" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B542" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C542" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A543" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B543" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A544" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B544" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C544" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A545" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B545" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A546" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B546" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C546" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A547" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B547" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C547" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A548" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B548" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C548" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A549" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B549" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A550" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B550" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C550" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A551" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B551" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A552" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B552" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C552" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A553" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B553" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C553" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A554" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B554" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C554" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A555" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B555" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A556" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B556" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C556" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A557" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B557" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C557" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A558" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B558" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A559" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B559" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C559" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A560" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B560" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A561" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B561" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A562" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B562" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C562" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A563" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B563" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C563" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A564" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B564" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C564" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A565" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B565" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C565" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A566" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B566" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C566" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A567" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B567" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C567" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A568" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B568" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C568" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A569" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B569" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C569" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A570" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B570" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C570" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A571" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B571" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A572" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B572" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C572" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A573" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B573" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A574" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B574" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C574" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A575" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B575" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C575" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A576" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B576" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C576" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A577" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B577" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C577" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A578" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B578" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C578" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A579" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B579" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C579" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A580" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B580" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C580" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A581" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B581" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C581" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A582" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B582" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C582" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A583" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B583" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C583" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A584" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B584" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C584" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A585" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B585" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C585" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A586" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B586" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C586" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A587" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B587" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C587" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A588" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B588" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C588" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A589" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B589" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C589" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A590" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B590" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C590" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A591" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B591" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C591" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A592" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B592" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C592" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A593" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B593" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C593" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A594" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B594" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C594" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A595" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B595" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C595" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A596" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B596" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C596" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A597" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B597" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C597" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A598" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B598" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C598" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A599" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B599" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C599" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A600" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B600" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C600" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A601" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B601" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C601" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A602" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B602" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C602" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A603" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B603" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C603" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A604" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B604" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C604" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A605" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B605" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C605" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A606" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B606" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C606" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A607" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B607" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C607" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A608" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B608" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C608" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A609" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B609" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C609" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A610" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B610" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C610" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A611" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B611" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C611" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A612" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B612" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C612" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A613" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B613" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C613" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A614" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B614" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C614" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A615" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B615" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C615" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A616" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B616" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C616" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A617" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B617" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C617" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A618" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B618" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C618" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A619" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B619" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C619" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A620" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B620" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C620" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A621" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B621" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C621" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A622" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B622" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C622" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A623" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B623" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C623" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A624" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B624" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C624" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A625" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B625" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C625" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A626" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B626" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C626" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A627" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B627" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C627" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A628" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B628" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C628" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A629" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B629" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C629" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A630" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B630" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C630" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A631" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B631" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C631" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A632" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B632" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C632" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A633" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B633" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C633" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A634" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B634" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C634" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A635" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B635" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C635" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A636" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B636" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C636" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A637" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B637" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C637" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A638" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B638" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C638" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A639" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B639" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C639" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A640" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B640" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C640" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A641" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B641" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C641" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A642" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B642" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C642" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A643" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B643" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C643" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A644" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B644" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C644" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A645" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B645" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C645" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A646" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B646" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C646" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A647" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B647" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C647" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A648" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B648" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C648" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A649" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B649" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C649" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A650" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B650" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C650" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A651" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B651" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C651" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A652" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B652" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C652" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A653" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B653" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C653" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A654" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B654" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C654" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A655" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B655" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C655" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A656" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B656" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C656" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A657" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B657" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C657" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A658" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B658" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C658" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A659" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B659" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C659" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A660" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B660" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C660" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A661" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B661" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C661" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A662" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B662" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C662" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A663" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B663" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C663" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A664" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B664" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C664" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A665" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B665" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C665" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A666" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B666" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C666" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A667" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B667" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C667" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A668" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B668" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C668" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A669" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B669" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C669" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A670" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B670" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C670" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A671" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B671" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C671" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A672" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B672" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C672" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A673" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B673" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C673" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A674" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B674" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C674" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A675" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B675" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C675" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A676" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B676" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C676" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A677" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B677" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C677" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A678" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B678" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C678" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A679" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B679" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C679" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A680" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B680" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C680" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A681" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B681" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C681" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A682" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B682" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C682" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A683" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B683" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C683" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A684" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B684" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C684" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A685" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B685" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C685" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A686" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B686" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C686" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A687" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B687" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C687" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A688" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B688" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C688" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A689" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B689" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C689" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A690" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B690" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C690" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A691" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B691" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C691" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A692" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B692" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C692" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A693" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B693" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C693" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A694" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B694" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C694" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A695" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B695" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C695" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A696" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B696" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C696" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A697" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B697" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C697" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A698" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B698" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C698" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A699" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B699" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C699" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A700" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B700" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C700" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A701" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B701" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C701" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A702" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B702" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C702" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A703" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B703" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C703" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A704" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B704" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C704" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A705" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B705" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C705" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A706" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B706" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C706" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A707" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B707" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C707" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A708" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B708" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C708" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A709" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B709" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C709" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A710" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B710" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C710" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A711" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B711" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C711" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A712" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B712" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C712" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A713" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B713" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C713" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A714" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B714" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C714" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A715" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B715" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C715" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A716" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B716" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C716" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A717" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B717" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C717" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A718" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B718" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C718" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A719" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B719" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C719" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A720" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B720" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C720" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A721" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B721" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C721" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A722" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B722" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C722" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A723" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B723" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C723" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A724" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B724" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C724" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A725" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B725" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C725" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A726" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B726" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C726" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A727" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B727" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C727" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A728" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B728" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C728" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A729" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B729" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C729" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A730" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B730" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C730" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A731" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B731" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C731" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A732" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B732" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C732" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3040,31 +9296,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C5A756-9AB3-4744-88B0-E7B0655D5C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412F15E4-A55B-4EAB-AB82-16B63EFA5491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="66">
   <si>
     <t>Status</t>
   </si>
@@ -48,151 +48,187 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>196142149</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
   </si>
   <si>
-    <t>195941699</t>
-  </si>
-  <si>
-    <t>819231824</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>959521927</t>
-  </si>
-  <si>
-    <t>925600508</t>
-  </si>
-  <si>
-    <t>903306961</t>
-  </si>
-  <si>
-    <t>913140640</t>
-  </si>
-  <si>
-    <t>902103625</t>
-  </si>
-  <si>
-    <t>902103617</t>
-  </si>
-  <si>
-    <t>867189759</t>
-  </si>
-  <si>
-    <t>856716612</t>
-  </si>
-  <si>
-    <t>855632463</t>
-  </si>
-  <si>
-    <t>846231649</t>
-  </si>
-  <si>
-    <t>846231565</t>
-  </si>
-  <si>
-    <t>834164778</t>
-  </si>
-  <si>
-    <t>832343051</t>
-  </si>
-  <si>
-    <t>831507128</t>
-  </si>
-  <si>
-    <t>828157879</t>
-  </si>
-  <si>
-    <t>830293373</t>
-  </si>
-  <si>
-    <t>829570344</t>
-  </si>
-  <si>
-    <t>819155403</t>
-  </si>
-  <si>
-    <t>817254950</t>
-  </si>
-  <si>
-    <t>815547579</t>
-  </si>
-  <si>
-    <t>809643764</t>
-  </si>
-  <si>
-    <t>808469849</t>
-  </si>
-  <si>
-    <t>750305777</t>
-  </si>
-  <si>
-    <t>764059410</t>
-  </si>
-  <si>
-    <t>758721330</t>
-  </si>
-  <si>
-    <t>665649087</t>
-  </si>
-  <si>
-    <t>173739693</t>
-  </si>
-  <si>
-    <t>179455542</t>
-  </si>
-  <si>
-    <t>179336700</t>
-  </si>
-  <si>
-    <t>939875930</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>876282389</t>
-  </si>
-  <si>
-    <t>914856012</t>
-  </si>
-  <si>
-    <t>926511514</t>
-  </si>
-  <si>
-    <t>923639441</t>
-  </si>
-  <si>
-    <t>919056261</t>
-  </si>
-  <si>
-    <t>917259438</t>
-  </si>
-  <si>
-    <t>915430668</t>
-  </si>
-  <si>
-    <t>903348716</t>
-  </si>
-  <si>
-    <t>888088386</t>
-  </si>
-  <si>
-    <t>899309680</t>
-  </si>
-  <si>
-    <t>836363964</t>
-  </si>
-  <si>
-    <t>836052716</t>
-  </si>
-  <si>
-    <t>835496468</t>
+    <t>197047107</t>
+  </si>
+  <si>
+    <t>197544715</t>
+  </si>
+  <si>
+    <t>197240744</t>
+  </si>
+  <si>
+    <t>946844937</t>
+  </si>
+  <si>
+    <t>974535449</t>
+  </si>
+  <si>
+    <t>792379822</t>
+  </si>
+  <si>
+    <t>833910122</t>
+  </si>
+  <si>
+    <t>831284793</t>
+  </si>
+  <si>
+    <t>830914051</t>
+  </si>
+  <si>
+    <t>830901447</t>
+  </si>
+  <si>
+    <t>830292193</t>
+  </si>
+  <si>
+    <t>818462370</t>
+  </si>
+  <si>
+    <t>818068946</t>
+  </si>
+  <si>
+    <t>797254756</t>
+  </si>
+  <si>
+    <t>795736499</t>
+  </si>
+  <si>
+    <t>764872820</t>
+  </si>
+  <si>
+    <t>777018361</t>
+  </si>
+  <si>
+    <t>757772193</t>
+  </si>
+  <si>
+    <t>962922526</t>
+  </si>
+  <si>
+    <t>939763771</t>
+  </si>
+  <si>
+    <t>936653462</t>
+  </si>
+  <si>
+    <t>932677747</t>
+  </si>
+  <si>
+    <t>914635606</t>
+  </si>
+  <si>
+    <t>922710714</t>
+  </si>
+  <si>
+    <t>930407402</t>
+  </si>
+  <si>
+    <t>905944512</t>
+  </si>
+  <si>
+    <t>858641768</t>
+  </si>
+  <si>
+    <t>853664815</t>
+  </si>
+  <si>
+    <t>903668147</t>
+  </si>
+  <si>
+    <t>867221883</t>
+  </si>
+  <si>
+    <t>867010385</t>
+  </si>
+  <si>
+    <t>856544527</t>
+  </si>
+  <si>
+    <t>861478232</t>
+  </si>
+  <si>
+    <t>851297089</t>
+  </si>
+  <si>
+    <t>803322381</t>
+  </si>
+  <si>
+    <t>824027878</t>
+  </si>
+  <si>
+    <t>835933635</t>
+  </si>
+  <si>
+    <t>967205331</t>
+  </si>
+  <si>
+    <t>967708037</t>
+  </si>
+  <si>
+    <t>967367388</t>
+  </si>
+  <si>
+    <t>967283718</t>
+  </si>
+  <si>
+    <t>966721270</t>
+  </si>
+  <si>
+    <t>966679494</t>
+  </si>
+  <si>
+    <t>911615734</t>
+  </si>
+  <si>
+    <t>934102173</t>
+  </si>
+  <si>
+    <t>966664868</t>
+  </si>
+  <si>
+    <t>966508651</t>
+  </si>
+  <si>
+    <t>927834683</t>
+  </si>
+  <si>
+    <t>931901221</t>
+  </si>
+  <si>
+    <t>923327880</t>
+  </si>
+  <si>
+    <t>911621740</t>
+  </si>
+  <si>
+    <t>903442865</t>
+  </si>
+  <si>
+    <t>901225155</t>
+  </si>
+  <si>
+    <t>884706684</t>
+  </si>
+  <si>
+    <t>875111548</t>
+  </si>
+  <si>
+    <t>872264084</t>
+  </si>
+  <si>
+    <t>871876433</t>
+  </si>
+  <si>
+    <t>900866793</t>
   </si>
 </sst>
 </file>
@@ -658,7 +694,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -684,10 +720,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -696,10 +732,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -708,10 +744,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -720,10 +756,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -732,10 +768,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -744,10 +780,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -756,10 +792,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -768,10 +804,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -780,10 +816,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -792,10 +828,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -804,10 +840,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -816,10 +852,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -828,10 +864,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -840,10 +876,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -852,10 +888,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -864,10 +900,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -876,10 +912,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -888,10 +924,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -900,10 +936,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -912,10 +948,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -924,10 +960,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -936,10 +972,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -948,10 +984,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -960,10 +996,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -972,10 +1008,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -984,10 +1020,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -996,10 +1032,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1008,10 +1044,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1020,10 +1056,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1032,10 +1068,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1044,10 +1080,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1056,10 +1092,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1068,10 +1104,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1083,7 +1119,7 @@
         <v>41</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1095,7 +1131,7 @@
         <v>42</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1107,7 +1143,7 @@
         <v>43</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1119,7 +1155,7 @@
         <v>44</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1131,7 +1167,7 @@
         <v>45</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1142,7 +1178,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1153,7 +1189,7 @@
         <v>47</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1164,7 +1200,7 @@
         <v>48</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1175,7 +1211,7 @@
         <v>49</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1186,7 +1222,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1197,7 +1233,7 @@
         <v>51</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1208,7 +1244,7 @@
         <v>52</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
@@ -1219,9 +1255,141 @@
         <v>53</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1248,31 +1416,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412F15E4-A55B-4EAB-AB82-16B63EFA5491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B64840-EF30-42FD-9AFB-4512C5671C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="48">
   <si>
     <t>Status</t>
   </si>
@@ -48,187 +48,133 @@
     <t>Processar</t>
   </si>
   <si>
-    <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>197047107</t>
-  </si>
-  <si>
-    <t>197544715</t>
-  </si>
-  <si>
-    <t>197240744</t>
-  </si>
-  <si>
-    <t>946844937</t>
-  </si>
-  <si>
-    <t>974535449</t>
-  </si>
-  <si>
-    <t>792379822</t>
-  </si>
-  <si>
-    <t>833910122</t>
-  </si>
-  <si>
-    <t>831284793</t>
-  </si>
-  <si>
-    <t>830914051</t>
-  </si>
-  <si>
-    <t>830901447</t>
-  </si>
-  <si>
-    <t>830292193</t>
-  </si>
-  <si>
-    <t>818462370</t>
-  </si>
-  <si>
-    <t>818068946</t>
-  </si>
-  <si>
-    <t>797254756</t>
-  </si>
-  <si>
-    <t>795736499</t>
-  </si>
-  <si>
-    <t>764872820</t>
-  </si>
-  <si>
-    <t>777018361</t>
-  </si>
-  <si>
-    <t>757772193</t>
-  </si>
-  <si>
-    <t>962922526</t>
-  </si>
-  <si>
-    <t>939763771</t>
-  </si>
-  <si>
-    <t>936653462</t>
-  </si>
-  <si>
-    <t>932677747</t>
-  </si>
-  <si>
-    <t>914635606</t>
-  </si>
-  <si>
-    <t>922710714</t>
-  </si>
-  <si>
-    <t>930407402</t>
-  </si>
-  <si>
-    <t>905944512</t>
-  </si>
-  <si>
-    <t>858641768</t>
-  </si>
-  <si>
-    <t>853664815</t>
-  </si>
-  <si>
-    <t>903668147</t>
-  </si>
-  <si>
-    <t>867221883</t>
-  </si>
-  <si>
-    <t>867010385</t>
-  </si>
-  <si>
-    <t>856544527</t>
-  </si>
-  <si>
-    <t>861478232</t>
-  </si>
-  <si>
-    <t>851297089</t>
-  </si>
-  <si>
-    <t>803322381</t>
-  </si>
-  <si>
-    <t>824027878</t>
-  </si>
-  <si>
-    <t>835933635</t>
-  </si>
-  <si>
-    <t>967205331</t>
-  </si>
-  <si>
-    <t>967708037</t>
-  </si>
-  <si>
-    <t>967367388</t>
-  </si>
-  <si>
-    <t>967283718</t>
-  </si>
-  <si>
-    <t>966721270</t>
-  </si>
-  <si>
-    <t>966679494</t>
-  </si>
-  <si>
-    <t>911615734</t>
-  </si>
-  <si>
-    <t>934102173</t>
-  </si>
-  <si>
-    <t>966664868</t>
-  </si>
-  <si>
-    <t>966508651</t>
-  </si>
-  <si>
-    <t>927834683</t>
-  </si>
-  <si>
-    <t>931901221</t>
-  </si>
-  <si>
-    <t>923327880</t>
-  </si>
-  <si>
-    <t>911621740</t>
-  </si>
-  <si>
-    <t>903442865</t>
-  </si>
-  <si>
-    <t>901225155</t>
-  </si>
-  <si>
-    <t>884706684</t>
-  </si>
-  <si>
-    <t>875111548</t>
-  </si>
-  <si>
-    <t>872264084</t>
-  </si>
-  <si>
-    <t>871876433</t>
-  </si>
-  <si>
-    <t>900866793</t>
+    <t>927024947</t>
+  </si>
+  <si>
+    <t>841878253</t>
+  </si>
+  <si>
+    <t>852096811</t>
+  </si>
+  <si>
+    <t>850154562</t>
+  </si>
+  <si>
+    <t>839999038</t>
+  </si>
+  <si>
+    <t>839059072</t>
+  </si>
+  <si>
+    <t>838742835</t>
+  </si>
+  <si>
+    <t>835976881</t>
+  </si>
+  <si>
+    <t>834404059</t>
+  </si>
+  <si>
+    <t>833937117</t>
+  </si>
+  <si>
+    <t>802512651</t>
+  </si>
+  <si>
+    <t>822373860</t>
+  </si>
+  <si>
+    <t>814287102</t>
+  </si>
+  <si>
+    <t>813171026</t>
+  </si>
+  <si>
+    <t>799119932</t>
+  </si>
+  <si>
+    <t>794224463</t>
+  </si>
+  <si>
+    <t>764419564</t>
+  </si>
+  <si>
+    <t>763330622</t>
+  </si>
+  <si>
+    <t>759361425</t>
+  </si>
+  <si>
+    <t>763294307</t>
+  </si>
+  <si>
+    <t>760899108</t>
+  </si>
+  <si>
+    <t>704859879</t>
+  </si>
+  <si>
+    <t>958342259</t>
+  </si>
+  <si>
+    <t>181475702</t>
+  </si>
+  <si>
+    <t>175175292</t>
+  </si>
+  <si>
+    <t>974599494</t>
+  </si>
+  <si>
+    <t>974525770</t>
+  </si>
+  <si>
+    <t>974525648</t>
+  </si>
+  <si>
+    <t>951343312</t>
+  </si>
+  <si>
+    <t>958342218</t>
+  </si>
+  <si>
+    <t>941233334</t>
+  </si>
+  <si>
+    <t>940002896</t>
+  </si>
+  <si>
+    <t>892357298</t>
+  </si>
+  <si>
+    <t>884500483</t>
+  </si>
+  <si>
+    <t>882406667</t>
+  </si>
+  <si>
+    <t>881141851</t>
+  </si>
+  <si>
+    <t>859214136</t>
+  </si>
+  <si>
+    <t>853623175</t>
+  </si>
+  <si>
+    <t>852660590</t>
+  </si>
+  <si>
+    <t>823465020</t>
+  </si>
+  <si>
+    <t>827145115</t>
   </si>
 </sst>
 </file>
@@ -694,7 +640,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -720,7 +666,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>5</v>
@@ -732,7 +678,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>5</v>
@@ -744,7 +690,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
@@ -756,10 +702,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -768,10 +714,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -780,10 +726,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -792,10 +738,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -804,10 +750,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -816,10 +762,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -828,10 +774,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -840,10 +786,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -852,10 +798,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -864,10 +810,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -876,10 +822,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -888,10 +834,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -900,10 +846,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -912,10 +858,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -924,10 +870,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -936,10 +882,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -948,10 +894,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -960,10 +906,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -972,10 +918,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -984,10 +930,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -996,10 +942,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -1008,10 +954,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -1020,10 +966,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1032,10 +978,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1044,10 +990,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1056,10 +1002,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1068,10 +1014,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1080,10 +1026,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1092,10 +1038,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1104,10 +1050,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1116,10 +1062,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1128,10 +1074,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1140,10 +1086,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1152,10 +1098,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1164,10 +1110,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1175,10 +1121,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1186,10 +1132,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1197,199 +1143,12 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1416,31 +1175,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B64840-EF30-42FD-9AFB-4512C5671C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A37885-ECE9-40EA-BC96-9FB169DD3264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="69">
   <si>
     <t>Status</t>
   </si>
@@ -54,127 +54,190 @@
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>927024947</t>
-  </si>
-  <si>
-    <t>841878253</t>
-  </si>
-  <si>
-    <t>852096811</t>
-  </si>
-  <si>
-    <t>850154562</t>
-  </si>
-  <si>
-    <t>839999038</t>
-  </si>
-  <si>
-    <t>839059072</t>
-  </si>
-  <si>
-    <t>838742835</t>
-  </si>
-  <si>
-    <t>835976881</t>
-  </si>
-  <si>
-    <t>834404059</t>
-  </si>
-  <si>
-    <t>833937117</t>
-  </si>
-  <si>
-    <t>802512651</t>
-  </si>
-  <si>
-    <t>822373860</t>
-  </si>
-  <si>
-    <t>814287102</t>
-  </si>
-  <si>
-    <t>813171026</t>
-  </si>
-  <si>
-    <t>799119932</t>
-  </si>
-  <si>
-    <t>794224463</t>
-  </si>
-  <si>
-    <t>764419564</t>
-  </si>
-  <si>
-    <t>763330622</t>
-  </si>
-  <si>
-    <t>759361425</t>
-  </si>
-  <si>
-    <t>763294307</t>
-  </si>
-  <si>
-    <t>760899108</t>
-  </si>
-  <si>
-    <t>704859879</t>
-  </si>
-  <si>
-    <t>958342259</t>
-  </si>
-  <si>
-    <t>181475702</t>
-  </si>
-  <si>
-    <t>175175292</t>
-  </si>
-  <si>
-    <t>974599494</t>
-  </si>
-  <si>
-    <t>974525770</t>
-  </si>
-  <si>
-    <t>974525648</t>
-  </si>
-  <si>
-    <t>951343312</t>
-  </si>
-  <si>
-    <t>958342218</t>
-  </si>
-  <si>
-    <t>941233334</t>
-  </si>
-  <si>
-    <t>940002896</t>
-  </si>
-  <si>
-    <t>892357298</t>
-  </si>
-  <si>
-    <t>884500483</t>
-  </si>
-  <si>
-    <t>882406667</t>
-  </si>
-  <si>
-    <t>881141851</t>
-  </si>
-  <si>
-    <t>859214136</t>
-  </si>
-  <si>
-    <t>853623175</t>
-  </si>
-  <si>
-    <t>852660590</t>
-  </si>
-  <si>
-    <t>823465020</t>
-  </si>
-  <si>
-    <t>827145115</t>
+    <t>766992824</t>
+  </si>
+  <si>
+    <t>808105369</t>
+  </si>
+  <si>
+    <t>815152537</t>
+  </si>
+  <si>
+    <t>824583128</t>
+  </si>
+  <si>
+    <t>828975775</t>
+  </si>
+  <si>
+    <t>810991582</t>
+  </si>
+  <si>
+    <t>807860972</t>
+  </si>
+  <si>
+    <t>803751571</t>
+  </si>
+  <si>
+    <t>786492326</t>
+  </si>
+  <si>
+    <t>948478874</t>
+  </si>
+  <si>
+    <t>942008529</t>
+  </si>
+  <si>
+    <t>944875909</t>
+  </si>
+  <si>
+    <t>944040645</t>
+  </si>
+  <si>
+    <t>941599783</t>
+  </si>
+  <si>
+    <t>918618749</t>
+  </si>
+  <si>
+    <t>905730382</t>
+  </si>
+  <si>
+    <t>888916743</t>
+  </si>
+  <si>
+    <t>895861932</t>
+  </si>
+  <si>
+    <t>890185857</t>
+  </si>
+  <si>
+    <t>834024246</t>
+  </si>
+  <si>
+    <t>881032241</t>
+  </si>
+  <si>
+    <t>882874435</t>
+  </si>
+  <si>
+    <t>876288444</t>
+  </si>
+  <si>
+    <t>875173530</t>
+  </si>
+  <si>
+    <t>862176769</t>
+  </si>
+  <si>
+    <t>860812688</t>
+  </si>
+  <si>
+    <t>843605365</t>
+  </si>
+  <si>
+    <t>845938194</t>
+  </si>
+  <si>
+    <t>836814495</t>
+  </si>
+  <si>
+    <t>831742238</t>
+  </si>
+  <si>
+    <t>829391675</t>
+  </si>
+  <si>
+    <t>928527930</t>
+  </si>
+  <si>
+    <t>913910513</t>
+  </si>
+  <si>
+    <t>910752256</t>
+  </si>
+  <si>
+    <t>971168111</t>
+  </si>
+  <si>
+    <t>769027719</t>
+  </si>
+  <si>
+    <t>766143170</t>
+  </si>
+  <si>
+    <t>764430843</t>
+  </si>
+  <si>
+    <t>761393044</t>
+  </si>
+  <si>
+    <t>739837536</t>
+  </si>
+  <si>
+    <t>637427638</t>
+  </si>
+  <si>
+    <t>181310867</t>
+  </si>
+  <si>
+    <t>181190673</t>
+  </si>
+  <si>
+    <t>176365207</t>
+  </si>
+  <si>
+    <t>971546449</t>
+  </si>
+  <si>
+    <t>828947170</t>
+  </si>
+  <si>
+    <t>942902754</t>
+  </si>
+  <si>
+    <t>913105312</t>
+  </si>
+  <si>
+    <t>893864086</t>
+  </si>
+  <si>
+    <t>893230981</t>
+  </si>
+  <si>
+    <t>830707570</t>
+  </si>
+  <si>
+    <t>875136313</t>
+  </si>
+  <si>
+    <t>883851176</t>
+  </si>
+  <si>
+    <t>921315622</t>
+  </si>
+  <si>
+    <t>973122553</t>
+  </si>
+  <si>
+    <t>972730448</t>
+  </si>
+  <si>
+    <t>953266560</t>
+  </si>
+  <si>
+    <t>811816689</t>
+  </si>
+  <si>
+    <t>198445722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
+  </si>
+  <si>
+    <t>198208393</t>
+  </si>
+  <si>
+    <t>199561113</t>
   </si>
 </sst>
 </file>
@@ -640,7 +703,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1135,7 +1198,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1146,9 +1209,229 @@
         <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C46" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1175,31 +1458,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FC48C7-721A-4CF2-8B35-8C4959BF0577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE856D77-AD77-4491-8BC2-0F9B6CF09055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="53">
   <si>
     <t>Status</t>
   </si>
@@ -48,130 +48,148 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>921131300</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>821149881</t>
-  </si>
-  <si>
-    <t>781449289</t>
-  </si>
-  <si>
-    <t>855133074</t>
-  </si>
-  <si>
-    <t>857650661</t>
-  </si>
-  <si>
-    <t>861492126</t>
-  </si>
-  <si>
-    <t>860968035</t>
-  </si>
-  <si>
-    <t>852869829</t>
-  </si>
-  <si>
-    <t>848198499</t>
-  </si>
-  <si>
-    <t>847640608</t>
-  </si>
-  <si>
-    <t>846216640</t>
-  </si>
-  <si>
-    <t>835459425</t>
-  </si>
-  <si>
-    <t>840564870</t>
-  </si>
-  <si>
-    <t>840767242</t>
-  </si>
-  <si>
-    <t>825270881</t>
-  </si>
-  <si>
-    <t>821254434</t>
-  </si>
-  <si>
-    <t>815814367</t>
-  </si>
-  <si>
-    <t>818080792</t>
-  </si>
-  <si>
-    <t>805588955</t>
-  </si>
-  <si>
-    <t>952401317</t>
-  </si>
-  <si>
-    <t>757421064</t>
-  </si>
-  <si>
-    <t>190282503</t>
-  </si>
-  <si>
-    <t>970827824</t>
-  </si>
-  <si>
-    <t>189048055</t>
-  </si>
-  <si>
-    <t>959043484</t>
-  </si>
-  <si>
-    <t>964209351</t>
-  </si>
-  <si>
-    <t>947010207</t>
-  </si>
-  <si>
-    <t>946136714</t>
-  </si>
-  <si>
-    <t>915779163</t>
-  </si>
-  <si>
-    <t>914554203</t>
-  </si>
-  <si>
-    <t>891887105</t>
-  </si>
-  <si>
-    <t>867891172</t>
-  </si>
-  <si>
-    <t>884188487</t>
-  </si>
-  <si>
-    <t>879305252</t>
-  </si>
-  <si>
-    <t>875164018</t>
-  </si>
-  <si>
-    <t>926052469</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>187312644</t>
-  </si>
-  <si>
-    <t>969228000</t>
-  </si>
-  <si>
-    <t>909142568</t>
-  </si>
-  <si>
-    <t>901486559</t>
+    <t>894868805</t>
+  </si>
+  <si>
+    <t>179043728</t>
+  </si>
+  <si>
+    <t>761215098</t>
+  </si>
+  <si>
+    <t>897219360</t>
+  </si>
+  <si>
+    <t>938522715</t>
+  </si>
+  <si>
+    <t>916688538</t>
+  </si>
+  <si>
+    <t>893937478</t>
+  </si>
+  <si>
+    <t>872946326</t>
+  </si>
+  <si>
+    <t>860445323</t>
+  </si>
+  <si>
+    <t>859003711</t>
+  </si>
+  <si>
+    <t>853829459</t>
+  </si>
+  <si>
+    <t>853785867</t>
+  </si>
+  <si>
+    <t>843498845</t>
+  </si>
+  <si>
+    <t>838243255</t>
+  </si>
+  <si>
+    <t>836887384</t>
+  </si>
+  <si>
+    <t>836763510</t>
+  </si>
+  <si>
+    <t>836428858</t>
+  </si>
+  <si>
+    <t>828729214</t>
+  </si>
+  <si>
+    <t>776415444</t>
+  </si>
+  <si>
+    <t>802943963</t>
+  </si>
+  <si>
+    <t>790857142</t>
+  </si>
+  <si>
+    <t>785755699</t>
+  </si>
+  <si>
+    <t>763666884</t>
+  </si>
+  <si>
+    <t>831925197</t>
+  </si>
+  <si>
+    <t>832198653</t>
+  </si>
+  <si>
+    <t>822459560</t>
+  </si>
+  <si>
+    <t>916474004</t>
+  </si>
+  <si>
+    <t>186943597</t>
+  </si>
+  <si>
+    <t>970653360</t>
+  </si>
+  <si>
+    <t>973560349</t>
+  </si>
+  <si>
+    <t>973051026</t>
+  </si>
+  <si>
+    <t>972784312</t>
+  </si>
+  <si>
+    <t>972733962</t>
+  </si>
+  <si>
+    <t>972674760</t>
+  </si>
+  <si>
+    <t>971964212</t>
+  </si>
+  <si>
+    <t>971155381</t>
+  </si>
+  <si>
+    <t>920054453</t>
+  </si>
+  <si>
+    <t>903351843</t>
+  </si>
+  <si>
+    <t>858914371</t>
+  </si>
+  <si>
+    <t>863705855</t>
+  </si>
+  <si>
+    <t>885883490</t>
+  </si>
+  <si>
+    <t>861808263</t>
+  </si>
+  <si>
+    <t>202807040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
+  </si>
+  <si>
+    <t>203679455</t>
+  </si>
+  <si>
+    <t>202955146</t>
   </si>
 </sst>
 </file>
@@ -637,7 +655,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -663,10 +681,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -675,10 +693,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -687,10 +705,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -699,10 +717,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -711,10 +729,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -723,10 +741,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -735,10 +753,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -747,10 +765,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -759,10 +777,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -771,10 +789,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -783,10 +801,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -795,10 +813,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -807,10 +825,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -819,10 +837,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -831,10 +849,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -843,10 +861,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -855,10 +873,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -867,10 +885,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -879,10 +897,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -891,10 +909,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -903,10 +921,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -915,10 +933,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -927,10 +945,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -939,10 +957,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -951,10 +969,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -963,7 +981,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>6</v>
@@ -975,7 +993,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>6</v>
@@ -987,7 +1005,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>6</v>
@@ -999,7 +1017,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>6</v>
@@ -1011,7 +1029,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>6</v>
@@ -1023,7 +1041,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>6</v>
@@ -1035,7 +1053,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>6</v>
@@ -1047,7 +1065,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>6</v>
@@ -1059,7 +1077,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>6</v>
@@ -1071,7 +1089,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>6</v>
@@ -1083,10 +1101,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1098,7 +1116,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1110,7 +1128,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1121,7 +1139,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1132,9 +1150,64 @@
         <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1161,31 +1234,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE856D77-AD77-4491-8BC2-0F9B6CF09055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641EA044-9DBB-4001-B84F-9D1E1FAE571B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="40">
   <si>
     <t>Status</t>
   </si>
@@ -54,142 +54,103 @@
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>894868805</t>
-  </si>
-  <si>
-    <t>179043728</t>
-  </si>
-  <si>
-    <t>761215098</t>
-  </si>
-  <si>
-    <t>897219360</t>
-  </si>
-  <si>
-    <t>938522715</t>
-  </si>
-  <si>
-    <t>916688538</t>
-  </si>
-  <si>
-    <t>893937478</t>
-  </si>
-  <si>
-    <t>872946326</t>
-  </si>
-  <si>
-    <t>860445323</t>
-  </si>
-  <si>
-    <t>859003711</t>
-  </si>
-  <si>
-    <t>853829459</t>
-  </si>
-  <si>
-    <t>853785867</t>
-  </si>
-  <si>
-    <t>843498845</t>
-  </si>
-  <si>
-    <t>838243255</t>
-  </si>
-  <si>
-    <t>836887384</t>
-  </si>
-  <si>
-    <t>836763510</t>
-  </si>
-  <si>
-    <t>836428858</t>
-  </si>
-  <si>
-    <t>828729214</t>
-  </si>
-  <si>
-    <t>776415444</t>
-  </si>
-  <si>
-    <t>802943963</t>
-  </si>
-  <si>
-    <t>790857142</t>
-  </si>
-  <si>
-    <t>785755699</t>
-  </si>
-  <si>
-    <t>763666884</t>
-  </si>
-  <si>
-    <t>831925197</t>
-  </si>
-  <si>
-    <t>832198653</t>
-  </si>
-  <si>
-    <t>822459560</t>
-  </si>
-  <si>
-    <t>916474004</t>
-  </si>
-  <si>
-    <t>186943597</t>
-  </si>
-  <si>
-    <t>970653360</t>
-  </si>
-  <si>
-    <t>973560349</t>
-  </si>
-  <si>
-    <t>973051026</t>
-  </si>
-  <si>
-    <t>972784312</t>
-  </si>
-  <si>
-    <t>972733962</t>
-  </si>
-  <si>
-    <t>972674760</t>
-  </si>
-  <si>
-    <t>971964212</t>
-  </si>
-  <si>
-    <t>971155381</t>
-  </si>
-  <si>
-    <t>920054453</t>
-  </si>
-  <si>
-    <t>903351843</t>
-  </si>
-  <si>
-    <t>858914371</t>
-  </si>
-  <si>
-    <t>863705855</t>
-  </si>
-  <si>
-    <t>885883490</t>
-  </si>
-  <si>
-    <t>861808263</t>
-  </si>
-  <si>
-    <t>202807040</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
   </si>
   <si>
-    <t>203679455</t>
-  </si>
-  <si>
-    <t>202955146</t>
+    <t>903372336</t>
+  </si>
+  <si>
+    <t>178968206</t>
+  </si>
+  <si>
+    <t>188745834</t>
+  </si>
+  <si>
+    <t>179731652</t>
+  </si>
+  <si>
+    <t>186793562</t>
+  </si>
+  <si>
+    <t>946345380</t>
+  </si>
+  <si>
+    <t>953450099</t>
+  </si>
+  <si>
+    <t>876915210</t>
+  </si>
+  <si>
+    <t>843313374</t>
+  </si>
+  <si>
+    <t>804582926</t>
+  </si>
+  <si>
+    <t>810940001</t>
+  </si>
+  <si>
+    <t>833686466</t>
+  </si>
+  <si>
+    <t>832911287</t>
+  </si>
+  <si>
+    <t>817290848</t>
+  </si>
+  <si>
+    <t>816121853</t>
+  </si>
+  <si>
+    <t>783267333</t>
+  </si>
+  <si>
+    <t>769572409</t>
+  </si>
+  <si>
+    <t>768015707</t>
+  </si>
+  <si>
+    <t>768004743</t>
+  </si>
+  <si>
+    <t>766989952</t>
+  </si>
+  <si>
+    <t>849833714</t>
+  </si>
+  <si>
+    <t>840391688</t>
+  </si>
+  <si>
+    <t>837793391</t>
+  </si>
+  <si>
+    <t>836336960</t>
+  </si>
+  <si>
+    <t>833943743</t>
+  </si>
+  <si>
+    <t>867156709</t>
+  </si>
+  <si>
+    <t>187298058</t>
+  </si>
+  <si>
+    <t>204752301</t>
+  </si>
+  <si>
+    <t>204994705</t>
+  </si>
+  <si>
+    <t>204961183</t>
+  </si>
+  <si>
+    <t>204803211</t>
+  </si>
+  <si>
+    <t>204401412</t>
   </si>
 </sst>
 </file>
@@ -681,7 +642,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>5</v>
@@ -693,7 +654,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>5</v>
@@ -705,7 +666,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
@@ -717,7 +678,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -729,7 +690,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>5</v>
@@ -741,7 +702,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>5</v>
@@ -753,7 +714,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>5</v>
@@ -765,7 +726,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>5</v>
@@ -777,7 +738,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>5</v>
@@ -789,7 +750,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>5</v>
@@ -801,7 +762,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>5</v>
@@ -813,7 +774,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>5</v>
@@ -825,7 +786,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>5</v>
@@ -837,7 +798,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>5</v>
@@ -849,7 +810,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>5</v>
@@ -861,7 +822,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>5</v>
@@ -873,7 +834,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>5</v>
@@ -885,7 +846,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>5</v>
@@ -897,7 +858,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>5</v>
@@ -909,7 +870,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>5</v>
@@ -921,7 +882,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>5</v>
@@ -933,7 +894,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>5</v>
@@ -945,7 +906,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>5</v>
@@ -957,7 +918,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>5</v>
@@ -969,7 +930,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>5</v>
@@ -981,7 +942,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>6</v>
@@ -993,7 +954,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>6</v>
@@ -1005,10 +966,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1017,10 +978,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1029,10 +990,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1041,10 +1002,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1053,10 +1014,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1064,152 +1025,48 @@
       <c r="D33"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C34" s="5"/>
       <c r="D34"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C35" s="5"/>
       <c r="D35"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C36" s="5"/>
       <c r="D36"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C37" s="5"/>
       <c r="D37"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C38" s="5"/>
       <c r="D38"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C39" s="5"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C40" s="5"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C41" s="5"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C42" s="5"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C43" s="5"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C44" s="5"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C45" s="5"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C46" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1234,31 +1091,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AB9490-DFF8-4D14-A6F2-0C5223FB8A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD6B5BE-E43C-44D3-983B-1CFC04E40238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RegularizarIncidencias" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="73">
   <si>
     <t>Status</t>
   </si>
@@ -48,166 +48,208 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>925896841</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>872030410</t>
-  </si>
-  <si>
-    <t>854664251</t>
-  </si>
-  <si>
-    <t>852868904</t>
-  </si>
-  <si>
-    <t>782071256</t>
-  </si>
-  <si>
-    <t>817140225</t>
-  </si>
-  <si>
-    <t>840734184</t>
-  </si>
-  <si>
-    <t>843975560</t>
-  </si>
-  <si>
-    <t>842749693</t>
-  </si>
-  <si>
-    <t>836357131</t>
-  </si>
-  <si>
-    <t>825301504</t>
-  </si>
-  <si>
-    <t>824546232</t>
-  </si>
-  <si>
-    <t>803983299</t>
-  </si>
-  <si>
-    <t>780013201</t>
-  </si>
-  <si>
-    <t>766082766</t>
-  </si>
-  <si>
-    <t>777114244</t>
-  </si>
-  <si>
-    <t>770337495</t>
-  </si>
-  <si>
-    <t>767778008</t>
-  </si>
-  <si>
-    <t>766317279</t>
-  </si>
-  <si>
-    <t>933273967</t>
-  </si>
-  <si>
-    <t>925453056</t>
-  </si>
-  <si>
-    <t>915735017</t>
-  </si>
-  <si>
-    <t>901617849</t>
-  </si>
-  <si>
-    <t>874400116</t>
-  </si>
-  <si>
-    <t>967779368</t>
-  </si>
-  <si>
-    <t>186408807</t>
-  </si>
-  <si>
-    <t>188827111</t>
-  </si>
-  <si>
-    <t>953531252</t>
-  </si>
-  <si>
-    <t>944468960</t>
-  </si>
-  <si>
-    <t>943251763</t>
-  </si>
-  <si>
-    <t>957869153</t>
-  </si>
-  <si>
-    <t>957217510</t>
-  </si>
-  <si>
-    <t>955889625</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>192745408</t>
-  </si>
-  <si>
-    <t>178458562</t>
-  </si>
-  <si>
-    <t>180834362</t>
-  </si>
-  <si>
-    <t>182445266</t>
-  </si>
-  <si>
-    <t>182444988</t>
-  </si>
-  <si>
-    <t>182434047</t>
-  </si>
-  <si>
-    <t>182432744</t>
-  </si>
-  <si>
-    <t>181662044</t>
-  </si>
-  <si>
-    <t>181593579</t>
-  </si>
-  <si>
-    <t>178482752</t>
-  </si>
-  <si>
-    <t>178476903</t>
-  </si>
-  <si>
-    <t>873231439</t>
-  </si>
-  <si>
-    <t>211638162</t>
-  </si>
-  <si>
-    <t>852752413</t>
-  </si>
-  <si>
-    <t>902577240</t>
-  </si>
-  <si>
-    <t>931440808</t>
-  </si>
-  <si>
-    <t>875715264</t>
-  </si>
-  <si>
-    <t>965789427</t>
-  </si>
-  <si>
-    <t>959037551</t>
+    <t>781205137</t>
+  </si>
+  <si>
+    <t>753882046</t>
+  </si>
+  <si>
+    <t>579477724</t>
+  </si>
+  <si>
+    <t>569780707</t>
+  </si>
+  <si>
+    <t>569780681</t>
+  </si>
+  <si>
+    <t>200576738</t>
+  </si>
+  <si>
+    <t>205047180</t>
+  </si>
+  <si>
+    <t>198021515</t>
+  </si>
+  <si>
+    <t>200402943</t>
+  </si>
+  <si>
+    <t>200399545</t>
+  </si>
+  <si>
+    <t>200243412</t>
+  </si>
+  <si>
+    <t>193007857</t>
+  </si>
+  <si>
+    <t>193344755</t>
+  </si>
+  <si>
+    <t>193344490</t>
+  </si>
+  <si>
+    <t>181212253</t>
+  </si>
+  <si>
+    <t>181209952</t>
+  </si>
+  <si>
+    <t>821202821</t>
+  </si>
+  <si>
+    <t>959030879</t>
+  </si>
+  <si>
+    <t>959725627</t>
+  </si>
+  <si>
+    <t>948566900</t>
+  </si>
+  <si>
+    <t>932213246</t>
+  </si>
+  <si>
+    <t>948519255</t>
+  </si>
+  <si>
+    <t>946797705</t>
+  </si>
+  <si>
+    <t>178336545</t>
+  </si>
+  <si>
+    <t>176834178</t>
+  </si>
+  <si>
+    <t>889296095</t>
+  </si>
+  <si>
+    <t>897158253</t>
+  </si>
+  <si>
+    <t>904877085</t>
+  </si>
+  <si>
+    <t>879286619</t>
+  </si>
+  <si>
+    <t>844700595</t>
+  </si>
+  <si>
+    <t>850909973</t>
+  </si>
+  <si>
+    <t>850340997</t>
+  </si>
+  <si>
+    <t>846814832</t>
+  </si>
+  <si>
+    <t>839532680</t>
+  </si>
+  <si>
+    <t>841875226</t>
+  </si>
+  <si>
+    <t>841015260</t>
+  </si>
+  <si>
+    <t>830293381</t>
+  </si>
+  <si>
+    <t>818016978</t>
+  </si>
+  <si>
+    <t>814233981</t>
+  </si>
+  <si>
+    <t>783258480</t>
+  </si>
+  <si>
+    <t>782818565</t>
+  </si>
+  <si>
+    <t>778087670</t>
+  </si>
+  <si>
+    <t>180853719</t>
+  </si>
+  <si>
+    <t>200130460</t>
+  </si>
+  <si>
+    <t>199776794</t>
+  </si>
+  <si>
+    <t>199072681</t>
+  </si>
+  <si>
+    <t>182453385</t>
+  </si>
+  <si>
+    <t>182452809</t>
+  </si>
+  <si>
+    <t>182452791</t>
+  </si>
+  <si>
+    <t>182452783</t>
+  </si>
+  <si>
+    <t>181654033</t>
+  </si>
+  <si>
+    <t>180850129</t>
+  </si>
+  <si>
+    <t>180832085</t>
+  </si>
+  <si>
+    <t>819447305</t>
+  </si>
+  <si>
+    <t>975108238</t>
+  </si>
+  <si>
+    <t>926614326</t>
+  </si>
+  <si>
+    <t>953510306</t>
+  </si>
+  <si>
+    <t>179260983</t>
+  </si>
+  <si>
+    <t>180831418</t>
+  </si>
+  <si>
+    <t>180802807</t>
+  </si>
+  <si>
+    <t>178479345</t>
+  </si>
+  <si>
+    <t>178479287</t>
+  </si>
+  <si>
+    <t>178477471</t>
+  </si>
+  <si>
+    <t>178477059</t>
+  </si>
+  <si>
+    <t>178458091</t>
+  </si>
+  <si>
+    <t>178445429</t>
   </si>
 </sst>
 </file>
@@ -673,7 +715,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -699,10 +741,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -711,10 +753,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -723,10 +765,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -735,10 +777,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -747,10 +789,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -759,10 +801,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -771,10 +813,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -783,10 +825,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -795,10 +837,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -807,10 +849,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -819,10 +861,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -831,10 +873,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -843,10 +885,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -855,10 +897,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -867,10 +909,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -879,10 +921,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -891,10 +933,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -903,10 +945,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -915,10 +957,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -927,10 +969,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -939,10 +981,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -951,10 +993,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -963,10 +1005,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -975,10 +1017,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -987,10 +1029,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -999,10 +1041,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1011,10 +1053,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1023,10 +1065,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1035,10 +1077,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1047,10 +1089,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1059,10 +1101,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1071,10 +1113,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1083,10 +1125,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1098,7 +1140,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1110,7 +1152,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1122,7 +1164,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1134,7 +1176,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1146,7 +1188,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1157,7 +1199,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1168,7 +1210,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1179,7 +1221,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1190,7 +1232,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1201,7 +1243,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1212,7 +1254,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1223,7 +1265,7 @@
         <v>51</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
@@ -1234,7 +1276,7 @@
         <v>52</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>4</v>
@@ -1245,7 +1287,7 @@
         <v>53</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>4</v>
@@ -1256,7 +1298,7 @@
         <v>54</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>4</v>
@@ -1267,7 +1309,7 @@
         <v>55</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>4</v>
@@ -1278,7 +1320,7 @@
         <v>56</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>4</v>
@@ -1289,7 +1331,7 @@
         <v>57</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>4</v>
@@ -1300,9 +1342,163 @@
         <v>58</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1329,31 +1525,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD6B5BE-E43C-44D3-983B-1CFC04E40238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235EA157-57C8-4BBF-AC70-9DD9931D41F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="83">
   <si>
     <t>Status</t>
   </si>
@@ -48,208 +48,238 @@
     <t>Processar</t>
   </si>
   <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>781205137</t>
-  </si>
-  <si>
-    <t>753882046</t>
-  </si>
-  <si>
-    <t>579477724</t>
-  </si>
-  <si>
-    <t>569780707</t>
-  </si>
-  <si>
-    <t>569780681</t>
-  </si>
-  <si>
-    <t>200576738</t>
-  </si>
-  <si>
-    <t>205047180</t>
-  </si>
-  <si>
-    <t>198021515</t>
-  </si>
-  <si>
-    <t>200402943</t>
-  </si>
-  <si>
-    <t>200399545</t>
-  </si>
-  <si>
-    <t>200243412</t>
-  </si>
-  <si>
-    <t>193007857</t>
-  </si>
-  <si>
-    <t>193344755</t>
-  </si>
-  <si>
-    <t>193344490</t>
-  </si>
-  <si>
-    <t>181212253</t>
-  </si>
-  <si>
-    <t>181209952</t>
-  </si>
-  <si>
-    <t>821202821</t>
-  </si>
-  <si>
-    <t>959030879</t>
-  </si>
-  <si>
-    <t>959725627</t>
-  </si>
-  <si>
-    <t>948566900</t>
-  </si>
-  <si>
-    <t>932213246</t>
-  </si>
-  <si>
-    <t>948519255</t>
-  </si>
-  <si>
-    <t>946797705</t>
-  </si>
-  <si>
-    <t>178336545</t>
-  </si>
-  <si>
-    <t>176834178</t>
-  </si>
-  <si>
-    <t>889296095</t>
-  </si>
-  <si>
-    <t>897158253</t>
-  </si>
-  <si>
-    <t>904877085</t>
-  </si>
-  <si>
-    <t>879286619</t>
-  </si>
-  <si>
-    <t>844700595</t>
-  </si>
-  <si>
-    <t>850909973</t>
-  </si>
-  <si>
-    <t>850340997</t>
-  </si>
-  <si>
-    <t>846814832</t>
-  </si>
-  <si>
-    <t>839532680</t>
-  </si>
-  <si>
-    <t>841875226</t>
-  </si>
-  <si>
-    <t>841015260</t>
-  </si>
-  <si>
-    <t>830293381</t>
-  </si>
-  <si>
-    <t>818016978</t>
-  </si>
-  <si>
-    <t>814233981</t>
-  </si>
-  <si>
-    <t>783258480</t>
-  </si>
-  <si>
-    <t>782818565</t>
-  </si>
-  <si>
-    <t>778087670</t>
-  </si>
-  <si>
-    <t>180853719</t>
-  </si>
-  <si>
-    <t>200130460</t>
-  </si>
-  <si>
-    <t>199776794</t>
-  </si>
-  <si>
-    <t>199072681</t>
-  </si>
-  <si>
-    <t>182453385</t>
-  </si>
-  <si>
-    <t>182452809</t>
-  </si>
-  <si>
-    <t>182452791</t>
-  </si>
-  <si>
-    <t>182452783</t>
-  </si>
-  <si>
-    <t>181654033</t>
-  </si>
-  <si>
-    <t>180850129</t>
-  </si>
-  <si>
-    <t>180832085</t>
-  </si>
-  <si>
-    <t>819447305</t>
-  </si>
-  <si>
-    <t>975108238</t>
-  </si>
-  <si>
-    <t>926614326</t>
-  </si>
-  <si>
-    <t>953510306</t>
-  </si>
-  <si>
-    <t>179260983</t>
-  </si>
-  <si>
-    <t>180831418</t>
-  </si>
-  <si>
-    <t>180802807</t>
-  </si>
-  <si>
-    <t>178479345</t>
-  </si>
-  <si>
-    <t>178479287</t>
-  </si>
-  <si>
-    <t>178477471</t>
-  </si>
-  <si>
-    <t>178477059</t>
-  </si>
-  <si>
-    <t>178458091</t>
-  </si>
-  <si>
-    <t>178445429</t>
+    <t>974708244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>912643628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>915166551</t>
+  </si>
+  <si>
+    <t>843381207</t>
+  </si>
+  <si>
+    <t>842970588</t>
+  </si>
+  <si>
+    <t>834491791</t>
+  </si>
+  <si>
+    <t>819639786</t>
+  </si>
+  <si>
+    <t>800502662</t>
+  </si>
+  <si>
+    <t>799603596</t>
+  </si>
+  <si>
+    <t>732110584</t>
+  </si>
+  <si>
+    <t>217796931</t>
+  </si>
+  <si>
+    <t>217482995</t>
+  </si>
+  <si>
+    <t>215000195</t>
+  </si>
+  <si>
+    <t>212486348</t>
+  </si>
+  <si>
+    <t>205792140</t>
+  </si>
+  <si>
+    <t>960278749</t>
+  </si>
+  <si>
+    <t>955695675</t>
+  </si>
+  <si>
+    <t>952837650</t>
+  </si>
+  <si>
+    <t>950940928</t>
+  </si>
+  <si>
+    <t>947614842</t>
+  </si>
+  <si>
+    <t>947151571</t>
+  </si>
+  <si>
+    <t>928571987</t>
+  </si>
+  <si>
+    <t>904806282</t>
+  </si>
+  <si>
+    <t>891761532</t>
+  </si>
+  <si>
+    <t>847101627</t>
+  </si>
+  <si>
+    <t>194100602</t>
+  </si>
+  <si>
+    <t>184865818</t>
+  </si>
+  <si>
+    <t>183765571</t>
+  </si>
+  <si>
+    <t>182877385</t>
+  </si>
+  <si>
+    <t>184556870</t>
+  </si>
+  <si>
+    <t>968454359</t>
+  </si>
+  <si>
+    <t>886858905</t>
+  </si>
+  <si>
+    <t>204543569</t>
+  </si>
+  <si>
+    <t>805567694</t>
+  </si>
+  <si>
+    <t>764308205</t>
+  </si>
+  <si>
+    <t>214942264</t>
+  </si>
+  <si>
+    <t>217447543</t>
+  </si>
+  <si>
+    <t>217711997</t>
+  </si>
+  <si>
+    <t>217411887</t>
+  </si>
+  <si>
+    <t>217310469</t>
+  </si>
+  <si>
+    <t>217212640</t>
+  </si>
+  <si>
+    <t>216825277</t>
+  </si>
+  <si>
+    <t>216304331</t>
+  </si>
+  <si>
+    <t>215527874</t>
+  </si>
+  <si>
+    <t>212552701</t>
+  </si>
+  <si>
+    <t>214935607</t>
+  </si>
+  <si>
+    <t>213430667</t>
+  </si>
+  <si>
+    <t>213163797</t>
+  </si>
+  <si>
+    <t>213095981</t>
+  </si>
+  <si>
+    <t>208520878</t>
+  </si>
+  <si>
+    <t>203548726</t>
+  </si>
+  <si>
+    <t>925412441</t>
+  </si>
+  <si>
+    <t>950464150</t>
+  </si>
+  <si>
+    <t>954526624</t>
+  </si>
+  <si>
+    <t>952048803</t>
+  </si>
+  <si>
+    <t>914722826</t>
+  </si>
+  <si>
+    <t>900242953</t>
+  </si>
+  <si>
+    <t>906363548</t>
+  </si>
+  <si>
+    <t>893439517</t>
+  </si>
+  <si>
+    <t>200893513</t>
+  </si>
+  <si>
+    <t>195650449</t>
+  </si>
+  <si>
+    <t>926114855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>195636836</t>
+  </si>
+  <si>
+    <t>932524691</t>
+  </si>
+  <si>
+    <t>210386995</t>
+  </si>
+  <si>
+    <t>210413229</t>
+  </si>
+  <si>
+    <t>210389155</t>
+  </si>
+  <si>
+    <t>906789494</t>
+  </si>
+  <si>
+    <t>859454260</t>
+  </si>
+  <si>
+    <t>860050289</t>
+  </si>
+  <si>
+    <t>178941104</t>
+  </si>
+  <si>
+    <t>873864569</t>
+  </si>
+  <si>
+    <t>951309693</t>
+  </si>
+  <si>
+    <t>885420772</t>
+  </si>
+  <si>
+    <t>883344834</t>
   </si>
 </sst>
 </file>
@@ -715,7 +745,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -741,10 +771,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -753,10 +783,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -768,7 +798,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -780,7 +810,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -792,7 +822,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -804,7 +834,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -816,7 +846,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -828,7 +858,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -840,7 +870,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -852,7 +882,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -864,7 +894,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -876,7 +906,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -888,7 +918,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -900,7 +930,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -912,7 +942,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -924,7 +954,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -936,7 +966,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -948,7 +978,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -960,7 +990,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -972,7 +1002,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -984,7 +1014,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -996,7 +1026,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -1008,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -1020,7 +1050,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -1032,7 +1062,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -1044,7 +1074,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1056,7 +1086,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1068,7 +1098,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1080,7 +1110,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1092,7 +1122,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1104,7 +1134,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1116,7 +1146,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1128,7 +1158,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1140,7 +1170,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1152,7 +1182,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1164,7 +1194,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1176,7 +1206,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1188,7 +1218,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1199,7 +1229,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1210,7 +1240,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1221,7 +1251,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1232,7 +1262,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1243,7 +1273,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1254,7 +1284,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1265,7 +1295,7 @@
         <v>51</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
@@ -1276,7 +1306,7 @@
         <v>52</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>4</v>
@@ -1287,7 +1317,7 @@
         <v>53</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>4</v>
@@ -1298,7 +1328,7 @@
         <v>54</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>4</v>
@@ -1309,7 +1339,7 @@
         <v>55</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>4</v>
@@ -1320,7 +1350,7 @@
         <v>56</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>4</v>
@@ -1331,7 +1361,7 @@
         <v>57</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>4</v>
@@ -1342,7 +1372,7 @@
         <v>58</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>4</v>
@@ -1353,7 +1383,7 @@
         <v>59</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
@@ -1364,7 +1394,7 @@
         <v>60</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>4</v>
@@ -1375,7 +1405,7 @@
         <v>61</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>4</v>
@@ -1386,7 +1416,7 @@
         <v>62</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>4</v>
@@ -1397,7 +1427,7 @@
         <v>63</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>4</v>
@@ -1408,7 +1438,7 @@
         <v>64</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>4</v>
@@ -1419,7 +1449,7 @@
         <v>65</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>4</v>
@@ -1430,7 +1460,7 @@
         <v>66</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
@@ -1441,7 +1471,7 @@
         <v>67</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
@@ -1452,7 +1482,7 @@
         <v>68</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
@@ -1460,7 +1490,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>6</v>
@@ -1471,7 +1501,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>6</v>
@@ -1482,7 +1512,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>6</v>
@@ -1493,12 +1523,111 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1525,31 +1654,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E82ADBB-62C7-4BBF-9CE0-7E751EC4437C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF82578B-1EAE-4848-8FCC-01910803CEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RegularizarIncidencias" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="329">
   <si>
     <t>Status</t>
   </si>
@@ -48,169 +48,976 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>945040099</t>
+    <t>924218641</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>179575620</t>
-  </si>
-  <si>
-    <t>804007940</t>
-  </si>
-  <si>
-    <t>840706547</t>
-  </si>
-  <si>
-    <t>848632042</t>
-  </si>
-  <si>
-    <t>839234782</t>
-  </si>
-  <si>
-    <t>821929860</t>
-  </si>
-  <si>
-    <t>838172397</t>
-  </si>
-  <si>
-    <t>830771501</t>
-  </si>
-  <si>
-    <t>827738414</t>
-  </si>
-  <si>
-    <t>814238550</t>
-  </si>
-  <si>
-    <t>811589344</t>
-  </si>
-  <si>
-    <t>810209134</t>
-  </si>
-  <si>
-    <t>805351289</t>
-  </si>
-  <si>
-    <t>773503648</t>
-  </si>
-  <si>
-    <t>785502802</t>
-  </si>
-  <si>
-    <t>794484794</t>
-  </si>
-  <si>
-    <t>794355424</t>
-  </si>
-  <si>
-    <t>780994848</t>
-  </si>
-  <si>
-    <t>772571661</t>
-  </si>
-  <si>
-    <t>771436494</t>
-  </si>
-  <si>
-    <t>653562979</t>
-  </si>
-  <si>
-    <t>756860858</t>
-  </si>
-  <si>
-    <t>910058399</t>
-  </si>
-  <si>
-    <t>916996311</t>
-  </si>
-  <si>
-    <t>887047771</t>
-  </si>
-  <si>
-    <t>874129723</t>
-  </si>
-  <si>
-    <t>858374659</t>
-  </si>
-  <si>
-    <t>857656452</t>
+    <t>864451954</t>
+  </si>
+  <si>
+    <t>891891123</t>
+  </si>
+  <si>
+    <t>889861369</t>
+  </si>
+  <si>
+    <t>874135357</t>
+  </si>
+  <si>
+    <t>871410662</t>
+  </si>
+  <si>
+    <t>868961255</t>
+  </si>
+  <si>
+    <t>824021863</t>
+  </si>
+  <si>
+    <t>859214144</t>
+  </si>
+  <si>
+    <t>857456515</t>
+  </si>
+  <si>
+    <t>853727000</t>
+  </si>
+  <si>
+    <t>848718544</t>
+  </si>
+  <si>
+    <t>842645131</t>
+  </si>
+  <si>
+    <t>839531401</t>
+  </si>
+  <si>
+    <t>207364559</t>
+  </si>
+  <si>
+    <t>799712926</t>
+  </si>
+  <si>
+    <t>970888214</t>
+  </si>
+  <si>
+    <t>179643519</t>
+  </si>
+  <si>
+    <t>178079301</t>
+  </si>
+  <si>
+    <t>177987843</t>
+  </si>
+  <si>
+    <t>956432045</t>
+  </si>
+  <si>
+    <t>947528893</t>
+  </si>
+  <si>
+    <t>954981159</t>
+  </si>
+  <si>
+    <t>920133570</t>
+  </si>
+  <si>
+    <t>893561880</t>
+  </si>
+  <si>
+    <t>919770028</t>
+  </si>
+  <si>
+    <t>904579335</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>938786609</t>
-  </si>
-  <si>
-    <t>967411699</t>
-  </si>
-  <si>
-    <t>974241527</t>
-  </si>
-  <si>
-    <t>973669215</t>
-  </si>
-  <si>
-    <t>937802183</t>
-  </si>
-  <si>
-    <t>937482655</t>
-  </si>
-  <si>
-    <t>795588247</t>
-  </si>
-  <si>
-    <t>831358183</t>
-  </si>
-  <si>
-    <t>842975330</t>
-  </si>
-  <si>
-    <t>823213883</t>
-  </si>
-  <si>
-    <t>812327769</t>
-  </si>
-  <si>
-    <t>910634983</t>
-  </si>
-  <si>
-    <t>934882584</t>
-  </si>
-  <si>
-    <t>929818908</t>
-  </si>
-  <si>
-    <t>926331186</t>
-  </si>
-  <si>
-    <t>926323225</t>
-  </si>
-  <si>
-    <t>907240018</t>
-  </si>
-  <si>
-    <t>877613921</t>
-  </si>
-  <si>
-    <t>877113625</t>
-  </si>
-  <si>
-    <t>868222542</t>
-  </si>
-  <si>
-    <t>850888730</t>
-  </si>
-  <si>
-    <t>856518521</t>
-  </si>
-  <si>
-    <t>853270233</t>
-  </si>
-  <si>
-    <t>193618703</t>
+    <t>902485683</t>
+  </si>
+  <si>
+    <t>893767834</t>
+  </si>
+  <si>
+    <t>899661841</t>
+  </si>
+  <si>
+    <t>898756998</t>
+  </si>
+  <si>
+    <t>897140632</t>
+  </si>
+  <si>
+    <t>896368390</t>
+  </si>
+  <si>
+    <t>894205289</t>
+  </si>
+  <si>
+    <t>866813177</t>
+  </si>
+  <si>
+    <t>868233564</t>
+  </si>
+  <si>
+    <t>891678876</t>
+  </si>
+  <si>
+    <t>891948303</t>
+  </si>
+  <si>
+    <t>888305236</t>
+  </si>
+  <si>
+    <t>874520988</t>
+  </si>
+  <si>
+    <t>886279730</t>
+  </si>
+  <si>
+    <t>877789846</t>
+  </si>
+  <si>
+    <t>871973974</t>
+  </si>
+  <si>
+    <t>860733405</t>
+  </si>
+  <si>
+    <t>864383769</t>
+  </si>
+  <si>
+    <t>862464082</t>
+  </si>
+  <si>
+    <t>795305428</t>
+  </si>
+  <si>
+    <t>212267318</t>
+  </si>
+  <si>
+    <t>217684483</t>
+  </si>
+  <si>
+    <t>217226103</t>
+  </si>
+  <si>
+    <t>217664626</t>
+  </si>
+  <si>
+    <t>217509862</t>
+  </si>
+  <si>
+    <t>197952132</t>
+  </si>
+  <si>
+    <t>200985301</t>
+  </si>
+  <si>
+    <t>951978281</t>
+  </si>
+  <si>
+    <t>178508093</t>
+  </si>
+  <si>
+    <t>190855407</t>
+  </si>
+  <si>
+    <t>189755139</t>
+  </si>
+  <si>
+    <t>187690015</t>
+  </si>
+  <si>
+    <t>187310028</t>
+  </si>
+  <si>
+    <t>181604178</t>
+  </si>
+  <si>
+    <t>181604160</t>
+  </si>
+  <si>
+    <t>180827051</t>
+  </si>
+  <si>
+    <t>181604137</t>
+  </si>
+  <si>
+    <t>181603279</t>
+  </si>
+  <si>
+    <t>955420785</t>
+  </si>
+  <si>
+    <t>177791732</t>
+  </si>
+  <si>
+    <t>972921252</t>
+  </si>
+  <si>
+    <t>963012020</t>
+  </si>
+  <si>
+    <t>959702535</t>
+  </si>
+  <si>
+    <t>958979902</t>
+  </si>
+  <si>
+    <t>958324901</t>
+  </si>
+  <si>
+    <t>951839905</t>
+  </si>
+  <si>
+    <t>948751056</t>
+  </si>
+  <si>
+    <t>948729763</t>
+  </si>
+  <si>
+    <t>948678598</t>
+  </si>
+  <si>
+    <t>948511492</t>
+  </si>
+  <si>
+    <t>947966630</t>
+  </si>
+  <si>
+    <t>946778473</t>
+  </si>
+  <si>
+    <t>946601048</t>
+  </si>
+  <si>
+    <t>946591090</t>
+  </si>
+  <si>
+    <t>945819666</t>
+  </si>
+  <si>
+    <t>927507990</t>
+  </si>
+  <si>
+    <t>931910958</t>
+  </si>
+  <si>
+    <t>939522748</t>
+  </si>
+  <si>
+    <t>939152967</t>
+  </si>
+  <si>
+    <t>938530072</t>
+  </si>
+  <si>
+    <t>938069089</t>
+  </si>
+  <si>
+    <t>930494798</t>
+  </si>
+  <si>
+    <t>930311992</t>
+  </si>
+  <si>
+    <t>925096954</t>
+  </si>
+  <si>
+    <t>925010526</t>
+  </si>
+  <si>
+    <t>924464278</t>
+  </si>
+  <si>
+    <t>913616615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>711941538</t>
+  </si>
+  <si>
+    <t>715692517</t>
+  </si>
+  <si>
+    <t>721118549</t>
+  </si>
+  <si>
+    <t>723048090</t>
+  </si>
+  <si>
+    <t>724116383</t>
+  </si>
+  <si>
+    <t>725509396</t>
+  </si>
+  <si>
+    <t>727004206</t>
+  </si>
+  <si>
+    <t>728187398</t>
+  </si>
+  <si>
+    <t>727769758</t>
+  </si>
+  <si>
+    <t>729459549</t>
+  </si>
+  <si>
+    <t>736461132</t>
+  </si>
+  <si>
+    <t>739589129</t>
+  </si>
+  <si>
+    <t>740207695</t>
+  </si>
+  <si>
+    <t>738902109</t>
+  </si>
+  <si>
+    <t>760789127</t>
+  </si>
+  <si>
+    <t>740455377</t>
+  </si>
+  <si>
+    <t>745364079</t>
+  </si>
+  <si>
+    <t>743898326</t>
+  </si>
+  <si>
+    <t>745042386</t>
+  </si>
+  <si>
+    <t>751406681</t>
+  </si>
+  <si>
+    <t>748166877</t>
+  </si>
+  <si>
+    <t>748712381</t>
+  </si>
+  <si>
+    <t>751691381</t>
+  </si>
+  <si>
+    <t>752481436</t>
+  </si>
+  <si>
+    <t>754978223</t>
+  </si>
+  <si>
+    <t>755942608</t>
+  </si>
+  <si>
+    <t>804969222</t>
+  </si>
+  <si>
+    <t>757168848</t>
+  </si>
+  <si>
+    <t>758492130</t>
+  </si>
+  <si>
+    <t>758944429</t>
+  </si>
+  <si>
+    <t>761911209</t>
+  </si>
+  <si>
+    <t>762751406</t>
+  </si>
+  <si>
+    <t>764241083</t>
+  </si>
+  <si>
+    <t>766573103</t>
+  </si>
+  <si>
+    <t>765873496</t>
+  </si>
+  <si>
+    <t>767582038</t>
+  </si>
+  <si>
+    <t>767575933</t>
+  </si>
+  <si>
+    <t>768256194</t>
+  </si>
+  <si>
+    <t>769960422</t>
+  </si>
+  <si>
+    <t>771159948</t>
+  </si>
+  <si>
+    <t>773657741</t>
+  </si>
+  <si>
+    <t>775071974</t>
+  </si>
+  <si>
+    <t>776643334</t>
+  </si>
+  <si>
+    <t>777733175</t>
+  </si>
+  <si>
+    <t>780117804</t>
+  </si>
+  <si>
+    <t>781343904</t>
+  </si>
+  <si>
+    <t>781895556</t>
+  </si>
+  <si>
+    <t>784327714</t>
+  </si>
+  <si>
+    <t>786422976</t>
+  </si>
+  <si>
+    <t>789341322</t>
+  </si>
+  <si>
+    <t>789356908</t>
+  </si>
+  <si>
+    <t>790490845</t>
+  </si>
+  <si>
+    <t>790367761</t>
+  </si>
+  <si>
+    <t>791702149</t>
+  </si>
+  <si>
+    <t>792209482</t>
+  </si>
+  <si>
+    <t>792305728</t>
+  </si>
+  <si>
+    <t>797563081</t>
+  </si>
+  <si>
+    <t>801098975</t>
+  </si>
+  <si>
+    <t>802998512</t>
+  </si>
+  <si>
+    <t>805118340</t>
+  </si>
+  <si>
+    <t>805551425</t>
+  </si>
+  <si>
+    <t>805988346</t>
+  </si>
+  <si>
+    <t>808920239</t>
+  </si>
+  <si>
+    <t>809387297</t>
+  </si>
+  <si>
+    <t>810724140</t>
+  </si>
+  <si>
+    <t>812264129</t>
+  </si>
+  <si>
+    <t>812826869</t>
+  </si>
+  <si>
+    <t>814612127</t>
+  </si>
+  <si>
+    <t>815590116</t>
+  </si>
+  <si>
+    <t>816784577</t>
+  </si>
+  <si>
+    <t>818926275</t>
+  </si>
+  <si>
+    <t>819588066</t>
+  </si>
+  <si>
+    <t>820703795</t>
+  </si>
+  <si>
+    <t>821684598</t>
+  </si>
+  <si>
+    <t>821778879</t>
+  </si>
+  <si>
+    <t>823620103</t>
+  </si>
+  <si>
+    <t>826186938</t>
+  </si>
+  <si>
+    <t>830417741</t>
+  </si>
+  <si>
+    <t>831591221</t>
+  </si>
+  <si>
+    <t>831170521</t>
+  </si>
+  <si>
+    <t>836739999</t>
+  </si>
+  <si>
+    <t>833185790</t>
+  </si>
+  <si>
+    <t>832477487</t>
+  </si>
+  <si>
+    <t>833006210</t>
+  </si>
+  <si>
+    <t>833892650</t>
+  </si>
+  <si>
+    <t>834224820</t>
+  </si>
+  <si>
+    <t>833527447</t>
+  </si>
+  <si>
+    <t>835444070</t>
+  </si>
+  <si>
+    <t>836238299</t>
+  </si>
+  <si>
+    <t>836214886</t>
+  </si>
+  <si>
+    <t>836547392</t>
+  </si>
+  <si>
+    <t>836703664</t>
+  </si>
+  <si>
+    <t>837877285</t>
+  </si>
+  <si>
+    <t>837798408</t>
+  </si>
+  <si>
+    <t>841262987</t>
+  </si>
+  <si>
+    <t>841995792</t>
+  </si>
+  <si>
+    <t>842167540</t>
+  </si>
+  <si>
+    <t>843408174</t>
+  </si>
+  <si>
+    <t>846548661</t>
+  </si>
+  <si>
+    <t>844588206</t>
+  </si>
+  <si>
+    <t>922168194</t>
+  </si>
+  <si>
+    <t>849516855</t>
+  </si>
+  <si>
+    <t>850606777</t>
+  </si>
+  <si>
+    <t>851565725</t>
+  </si>
+  <si>
+    <t>852947674</t>
+  </si>
+  <si>
+    <t>854839473</t>
+  </si>
+  <si>
+    <t>856600030</t>
+  </si>
+  <si>
+    <t>858292414</t>
+  </si>
+  <si>
+    <t>858530326</t>
+  </si>
+  <si>
+    <t>857854354</t>
+  </si>
+  <si>
+    <t>858896719</t>
+  </si>
+  <si>
+    <t>861108771</t>
+  </si>
+  <si>
+    <t>862153263</t>
+  </si>
+  <si>
+    <t>862980731</t>
+  </si>
+  <si>
+    <t>864213842</t>
+  </si>
+  <si>
+    <t>863390260</t>
+  </si>
+  <si>
+    <t>863473850</t>
+  </si>
+  <si>
+    <t>863665620</t>
+  </si>
+  <si>
+    <t>863710335</t>
+  </si>
+  <si>
+    <t>863799668</t>
+  </si>
+  <si>
+    <t>926502638</t>
+  </si>
+  <si>
+    <t>864702851</t>
+  </si>
+  <si>
+    <t>865877769</t>
+  </si>
+  <si>
+    <t>865541910</t>
+  </si>
+  <si>
+    <t>868371083</t>
+  </si>
+  <si>
+    <t>868594890</t>
+  </si>
+  <si>
+    <t>871436097</t>
+  </si>
+  <si>
+    <t>874929718</t>
+  </si>
+  <si>
+    <t>877559207</t>
+  </si>
+  <si>
+    <t>883112132</t>
+  </si>
+  <si>
+    <t>878876477</t>
+  </si>
+  <si>
+    <t>879169138</t>
+  </si>
+  <si>
+    <t>879736936</t>
+  </si>
+  <si>
+    <t>879959769</t>
+  </si>
+  <si>
+    <t>880043231</t>
+  </si>
+  <si>
+    <t>882055787</t>
+  </si>
+  <si>
+    <t>880992544</t>
+  </si>
+  <si>
+    <t>913203570</t>
+  </si>
+  <si>
+    <t>883561387</t>
+  </si>
+  <si>
+    <t>884512686</t>
+  </si>
+  <si>
+    <t>884037171</t>
+  </si>
+  <si>
+    <t>890378957</t>
+  </si>
+  <si>
+    <t>889499228</t>
+  </si>
+  <si>
+    <t>891858551</t>
+  </si>
+  <si>
+    <t>892432315</t>
+  </si>
+  <si>
+    <t>898150267</t>
+  </si>
+  <si>
+    <t>896899907</t>
+  </si>
+  <si>
+    <t>897817676</t>
+  </si>
+  <si>
+    <t>901170286</t>
+  </si>
+  <si>
+    <t>901829139</t>
+  </si>
+  <si>
+    <t>900796123</t>
+  </si>
+  <si>
+    <t>901346365</t>
+  </si>
+  <si>
+    <t>901824080</t>
+  </si>
+  <si>
+    <t>902403298</t>
+  </si>
+  <si>
+    <t>902989445</t>
+  </si>
+  <si>
+    <t>905076430</t>
+  </si>
+  <si>
+    <t>904211053</t>
+  </si>
+  <si>
+    <t>906036102</t>
+  </si>
+  <si>
+    <t>910449952</t>
+  </si>
+  <si>
+    <t>912250929</t>
+  </si>
+  <si>
+    <t>912682956</t>
+  </si>
+  <si>
+    <t>913428698</t>
+  </si>
+  <si>
+    <t>914613777</t>
+  </si>
+  <si>
+    <t>917991857</t>
+  </si>
+  <si>
+    <t>927627442</t>
+  </si>
+  <si>
+    <t>925879201</t>
+  </si>
+  <si>
+    <t>929530982</t>
+  </si>
+  <si>
+    <t>930600998</t>
+  </si>
+  <si>
+    <t>931848406</t>
+  </si>
+  <si>
+    <t>933305066</t>
+  </si>
+  <si>
+    <t>867959201</t>
+  </si>
+  <si>
+    <t>847886789</t>
+  </si>
+  <si>
+    <t>847864570</t>
+  </si>
+  <si>
+    <t>846096620</t>
+  </si>
+  <si>
+    <t>844515381</t>
+  </si>
+  <si>
+    <t>839738725</t>
+  </si>
+  <si>
+    <t>841088432</t>
+  </si>
+  <si>
+    <t>828660211</t>
+  </si>
+  <si>
+    <t>832207546</t>
+  </si>
+  <si>
+    <t>792676961</t>
+  </si>
+  <si>
+    <t>807395979</t>
+  </si>
+  <si>
+    <t>798715391</t>
+  </si>
+  <si>
+    <t>777019906</t>
+  </si>
+  <si>
+    <t>788656118</t>
+  </si>
+  <si>
+    <t>786660179</t>
+  </si>
+  <si>
+    <t>708419944</t>
+  </si>
+  <si>
+    <t>708419936</t>
+  </si>
+  <si>
+    <t>922109180</t>
+  </si>
+  <si>
+    <t>182506745</t>
+  </si>
+  <si>
+    <t>199869391</t>
+  </si>
+  <si>
+    <t>927440614</t>
+  </si>
+  <si>
+    <t>879166746</t>
+  </si>
+  <si>
+    <t>892591979</t>
+  </si>
+  <si>
+    <t>878939655</t>
+  </si>
+  <si>
+    <t>878147648</t>
+  </si>
+  <si>
+    <t>873230092</t>
+  </si>
+  <si>
+    <t>869335111</t>
+  </si>
+  <si>
+    <t>868968557</t>
+  </si>
+  <si>
+    <t>867168399</t>
+  </si>
+  <si>
+    <t>865699890</t>
+  </si>
+  <si>
+    <t>217588932</t>
+  </si>
+  <si>
+    <t>217369564</t>
+  </si>
+  <si>
+    <t>928754989</t>
+  </si>
+  <si>
+    <t>194799577</t>
+  </si>
+  <si>
+    <t>214141024</t>
+  </si>
+  <si>
+    <t>197483716</t>
+  </si>
+  <si>
+    <t>181626452</t>
+  </si>
+  <si>
+    <t>187739176</t>
+  </si>
+  <si>
+    <t>181623582</t>
+  </si>
+  <si>
+    <t>975715354</t>
+  </si>
+  <si>
+    <t>179232644</t>
+  </si>
+  <si>
+    <t>181608104</t>
+  </si>
+  <si>
+    <t>181602891</t>
+  </si>
+  <si>
+    <t>180853727</t>
+  </si>
+  <si>
+    <t>180806451</t>
+  </si>
+  <si>
+    <t>179228451</t>
+  </si>
+  <si>
+    <t>179214592</t>
+  </si>
+  <si>
+    <t>178477034</t>
+  </si>
+  <si>
+    <t>178477026</t>
+  </si>
+  <si>
+    <t>975715057</t>
+  </si>
+  <si>
+    <t>973286945</t>
+  </si>
+  <si>
+    <t>959164124</t>
+  </si>
+  <si>
+    <t>930307917</t>
+  </si>
+  <si>
+    <t>924991478</t>
+  </si>
+  <si>
+    <t>868542113</t>
+  </si>
+  <si>
+    <t>879876096</t>
+  </si>
+  <si>
+    <t>877921449</t>
   </si>
 </sst>
 </file>
@@ -676,7 +1483,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D322"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1017,7 +1824,7 @@
         <v>32</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1026,10 +1833,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1038,10 +1845,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1053,7 +1860,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1065,7 +1872,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1077,7 +1884,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1089,7 +1896,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1101,7 +1908,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1113,7 +1920,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1125,7 +1932,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1137,7 +1944,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1149,7 +1956,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1160,7 +1967,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1171,7 +1978,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1182,7 +1989,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1193,7 +2000,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1204,7 +2011,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1215,7 +2022,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1226,7 +2033,7 @@
         <v>51</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
@@ -1237,7 +2044,7 @@
         <v>52</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>4</v>
@@ -1248,7 +2055,7 @@
         <v>53</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>4</v>
@@ -1259,7 +2066,7 @@
         <v>54</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>4</v>
@@ -1270,7 +2077,7 @@
         <v>55</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>4</v>
@@ -1281,7 +2088,7 @@
         <v>56</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>4</v>
@@ -1292,7 +2099,7 @@
         <v>57</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>4</v>
@@ -1303,7 +2110,7 @@
         <v>58</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>4</v>
@@ -1314,9 +2121,2957 @@
         <v>59</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C322" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28218A73-82D1-4CCD-8C81-3ABF11342214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AE3022-7A35-400C-9798-154447165D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="99">
   <si>
     <t>Status</t>
   </si>
@@ -54,145 +54,280 @@
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>206602546</t>
-  </si>
-  <si>
-    <t>877904130</t>
-  </si>
-  <si>
-    <t>966365953</t>
-  </si>
-  <si>
-    <t>973764016</t>
-  </si>
-  <si>
-    <t>896907544</t>
-  </si>
-  <si>
-    <t>941997060</t>
-  </si>
-  <si>
-    <t>951747744</t>
-  </si>
-  <si>
-    <t>951418338</t>
-  </si>
-  <si>
-    <t>910217227</t>
-  </si>
-  <si>
-    <t>897723148</t>
-  </si>
-  <si>
-    <t>879245193</t>
-  </si>
-  <si>
-    <t>892332580</t>
-  </si>
-  <si>
-    <t>883961165</t>
-  </si>
-  <si>
-    <t>883337887</t>
-  </si>
-  <si>
-    <t>882407673</t>
-  </si>
-  <si>
-    <t>880533330</t>
-  </si>
-  <si>
-    <t>874251667</t>
-  </si>
-  <si>
-    <t>873173839</t>
-  </si>
-  <si>
-    <t>871756916</t>
-  </si>
-  <si>
-    <t>871545020</t>
-  </si>
-  <si>
-    <t>871227009</t>
-  </si>
-  <si>
-    <t>870263302</t>
-  </si>
-  <si>
-    <t>868633201</t>
-  </si>
-  <si>
-    <t>865909307</t>
-  </si>
-  <si>
-    <t>864971753</t>
-  </si>
-  <si>
-    <t>850154570</t>
-  </si>
-  <si>
-    <t>849336213</t>
-  </si>
-  <si>
-    <t>825278777</t>
-  </si>
-  <si>
-    <t>845192453</t>
-  </si>
-  <si>
-    <t>847760877</t>
-  </si>
-  <si>
-    <t>847430158</t>
-  </si>
-  <si>
-    <t>812136657</t>
-  </si>
-  <si>
-    <t>804420473</t>
-  </si>
-  <si>
-    <t>800448437</t>
-  </si>
-  <si>
-    <t>226437410</t>
-  </si>
-  <si>
-    <t>204277481</t>
-  </si>
-  <si>
-    <t>975715107</t>
-  </si>
-  <si>
-    <t>828571087</t>
-  </si>
-  <si>
-    <t>924501707</t>
-  </si>
-  <si>
-    <t>867097101</t>
-  </si>
-  <si>
-    <t>827797477</t>
-  </si>
-  <si>
-    <t>200130478</t>
-  </si>
-  <si>
-    <t>975714035</t>
-  </si>
-  <si>
-    <t>975714027</t>
-  </si>
-  <si>
-    <t>962363747</t>
-  </si>
-  <si>
-    <t>958853446</t>
-  </si>
-  <si>
-    <t>956826808</t>
+    <t>936188311</t>
+  </si>
+  <si>
+    <t>808471365</t>
+  </si>
+  <si>
+    <t>833566833</t>
+  </si>
+  <si>
+    <t>843943089</t>
+  </si>
+  <si>
+    <t>849837533</t>
+  </si>
+  <si>
+    <t>843293808</t>
+  </si>
+  <si>
+    <t>841510567</t>
+  </si>
+  <si>
+    <t>832598183</t>
+  </si>
+  <si>
+    <t>833360526</t>
+  </si>
+  <si>
+    <t>807334341</t>
+  </si>
+  <si>
+    <t>804082646</t>
+  </si>
+  <si>
+    <t>801811534</t>
+  </si>
+  <si>
+    <t>793403100</t>
+  </si>
+  <si>
+    <t>791769031</t>
+  </si>
+  <si>
+    <t>790729424</t>
+  </si>
+  <si>
+    <t>786816490</t>
+  </si>
+  <si>
+    <t>782268779</t>
+  </si>
+  <si>
+    <t>776740585</t>
+  </si>
+  <si>
+    <t>776740577</t>
+  </si>
+  <si>
+    <t>235063546</t>
+  </si>
+  <si>
+    <t>233347792</t>
+  </si>
+  <si>
+    <t>211697986</t>
+  </si>
+  <si>
+    <t>219110644</t>
+  </si>
+  <si>
+    <t>219110537</t>
+  </si>
+  <si>
+    <t>210915595</t>
+  </si>
+  <si>
+    <t>210642710</t>
+  </si>
+  <si>
+    <t>209652548</t>
+  </si>
+  <si>
+    <t>185041997</t>
+  </si>
+  <si>
+    <t>198763710</t>
+  </si>
+  <si>
+    <t>207820147</t>
+  </si>
+  <si>
+    <t>197250818</t>
+  </si>
+  <si>
+    <t>940489747</t>
+  </si>
+  <si>
+    <t>962722165</t>
+  </si>
+  <si>
+    <t>975085758</t>
+  </si>
+  <si>
+    <t>960667339</t>
+  </si>
+  <si>
+    <t>959332689</t>
+  </si>
+  <si>
+    <t>940104445</t>
+  </si>
+  <si>
+    <t>938750597</t>
+  </si>
+  <si>
+    <t>875456349</t>
+  </si>
+  <si>
+    <t>868328935</t>
+  </si>
+  <si>
+    <t>866509247</t>
+  </si>
+  <si>
+    <t>851224125</t>
+  </si>
+  <si>
+    <t>855543702</t>
+  </si>
+  <si>
+    <t>850502844</t>
+  </si>
+  <si>
+    <t>850304902</t>
+  </si>
+  <si>
+    <t>914081009</t>
+  </si>
+  <si>
+    <t>915945178</t>
+  </si>
+  <si>
+    <t>914979855</t>
+  </si>
+  <si>
+    <t>914945682</t>
+  </si>
+  <si>
+    <t>902456965</t>
+  </si>
+  <si>
+    <t>897421115</t>
+  </si>
+  <si>
+    <t>899143105</t>
+  </si>
+  <si>
+    <t>897805051</t>
+  </si>
+  <si>
+    <t>885311906</t>
+  </si>
+  <si>
+    <t>880731066</t>
+  </si>
+  <si>
+    <t>879844268</t>
+  </si>
+  <si>
+    <t>877754295</t>
+  </si>
+  <si>
+    <t>870905845</t>
+  </si>
+  <si>
+    <t>862880618</t>
+  </si>
+  <si>
+    <t>857294080</t>
+  </si>
+  <si>
+    <t>804975468</t>
+  </si>
+  <si>
+    <t>217006497</t>
+  </si>
+  <si>
+    <t>231260559</t>
+  </si>
+  <si>
+    <t>225043987</t>
+  </si>
+  <si>
+    <t>224862106</t>
+  </si>
+  <si>
+    <t>939235556</t>
+  </si>
+  <si>
+    <t>956570042</t>
+  </si>
+  <si>
+    <t>934761796</t>
+  </si>
+  <si>
+    <t>930901370</t>
+  </si>
+  <si>
+    <t>904876541</t>
+  </si>
+  <si>
+    <t>218918013</t>
+  </si>
+  <si>
+    <t>791482924</t>
+  </si>
+  <si>
+    <t>818306015</t>
+  </si>
+  <si>
+    <t>884439336</t>
+  </si>
+  <si>
+    <t>872880103</t>
+  </si>
+  <si>
+    <t>872808641</t>
+  </si>
+  <si>
+    <t>866582988</t>
+  </si>
+  <si>
+    <t>850574298</t>
+  </si>
+  <si>
+    <t>807144559</t>
+  </si>
+  <si>
+    <t>806097576</t>
+  </si>
+  <si>
+    <t>203263698</t>
+  </si>
+  <si>
+    <t>211711431</t>
+  </si>
+  <si>
+    <t>191354921</t>
+  </si>
+  <si>
+    <t>933112405</t>
+  </si>
+  <si>
+    <t>972166197</t>
+  </si>
+  <si>
+    <t>953045790</t>
+  </si>
+  <si>
+    <t>946797713</t>
+  </si>
+  <si>
+    <t>942613757</t>
+  </si>
+  <si>
+    <t>178336552</t>
+  </si>
+  <si>
+    <t>223266598</t>
+  </si>
+  <si>
+    <t>228631382</t>
+  </si>
+  <si>
+    <t>224785950</t>
   </si>
 </sst>
 </file>
@@ -658,7 +793,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1119,7 +1254,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1131,7 +1266,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1142,7 +1277,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1153,7 +1288,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1164,7 +1299,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1175,7 +1310,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1186,7 +1321,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1197,7 +1332,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1208,7 +1343,7 @@
         <v>51</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
@@ -1219,7 +1354,7 @@
         <v>52</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>4</v>
@@ -1230,9 +1365,504 @@
         <v>53</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1259,31 +1889,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AE3022-7A35-400C-9798-154447165D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343529F0-AC7F-48F4-8AAF-47A8C3E886D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="151">
   <si>
     <t>Status</t>
   </si>
@@ -54,280 +54,436 @@
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>936188311</t>
-  </si>
-  <si>
-    <t>808471365</t>
-  </si>
-  <si>
-    <t>833566833</t>
-  </si>
-  <si>
-    <t>843943089</t>
-  </si>
-  <si>
-    <t>849837533</t>
-  </si>
-  <si>
-    <t>843293808</t>
-  </si>
-  <si>
-    <t>841510567</t>
-  </si>
-  <si>
-    <t>832598183</t>
-  </si>
-  <si>
-    <t>833360526</t>
-  </si>
-  <si>
-    <t>807334341</t>
-  </si>
-  <si>
-    <t>804082646</t>
-  </si>
-  <si>
-    <t>801811534</t>
-  </si>
-  <si>
-    <t>793403100</t>
-  </si>
-  <si>
-    <t>791769031</t>
-  </si>
-  <si>
-    <t>790729424</t>
-  </si>
-  <si>
-    <t>786816490</t>
-  </si>
-  <si>
-    <t>782268779</t>
-  </si>
-  <si>
-    <t>776740585</t>
-  </si>
-  <si>
-    <t>776740577</t>
-  </si>
-  <si>
-    <t>235063546</t>
-  </si>
-  <si>
-    <t>233347792</t>
-  </si>
-  <si>
-    <t>211697986</t>
-  </si>
-  <si>
-    <t>219110644</t>
-  </si>
-  <si>
-    <t>219110537</t>
-  </si>
-  <si>
-    <t>210915595</t>
-  </si>
-  <si>
-    <t>210642710</t>
-  </si>
-  <si>
-    <t>209652548</t>
-  </si>
-  <si>
-    <t>185041997</t>
-  </si>
-  <si>
-    <t>198763710</t>
-  </si>
-  <si>
-    <t>207820147</t>
-  </si>
-  <si>
-    <t>197250818</t>
-  </si>
-  <si>
-    <t>940489747</t>
-  </si>
-  <si>
-    <t>962722165</t>
-  </si>
-  <si>
-    <t>975085758</t>
-  </si>
-  <si>
-    <t>960667339</t>
-  </si>
-  <si>
-    <t>959332689</t>
-  </si>
-  <si>
-    <t>940104445</t>
-  </si>
-  <si>
-    <t>938750597</t>
-  </si>
-  <si>
-    <t>875456349</t>
-  </si>
-  <si>
-    <t>868328935</t>
-  </si>
-  <si>
-    <t>866509247</t>
-  </si>
-  <si>
-    <t>851224125</t>
-  </si>
-  <si>
-    <t>855543702</t>
-  </si>
-  <si>
-    <t>850502844</t>
-  </si>
-  <si>
-    <t>850304902</t>
-  </si>
-  <si>
-    <t>914081009</t>
-  </si>
-  <si>
-    <t>915945178</t>
-  </si>
-  <si>
-    <t>914979855</t>
-  </si>
-  <si>
-    <t>914945682</t>
-  </si>
-  <si>
-    <t>902456965</t>
-  </si>
-  <si>
-    <t>897421115</t>
-  </si>
-  <si>
-    <t>899143105</t>
-  </si>
-  <si>
-    <t>897805051</t>
-  </si>
-  <si>
-    <t>885311906</t>
-  </si>
-  <si>
-    <t>880731066</t>
-  </si>
-  <si>
-    <t>879844268</t>
-  </si>
-  <si>
-    <t>877754295</t>
-  </si>
-  <si>
-    <t>870905845</t>
-  </si>
-  <si>
-    <t>862880618</t>
-  </si>
-  <si>
-    <t>857294080</t>
-  </si>
-  <si>
-    <t>804975468</t>
-  </si>
-  <si>
-    <t>217006497</t>
-  </si>
-  <si>
-    <t>231260559</t>
-  </si>
-  <si>
-    <t>225043987</t>
-  </si>
-  <si>
-    <t>224862106</t>
-  </si>
-  <si>
-    <t>939235556</t>
-  </si>
-  <si>
-    <t>956570042</t>
-  </si>
-  <si>
-    <t>934761796</t>
-  </si>
-  <si>
-    <t>930901370</t>
-  </si>
-  <si>
-    <t>904876541</t>
-  </si>
-  <si>
-    <t>218918013</t>
-  </si>
-  <si>
-    <t>791482924</t>
-  </si>
-  <si>
-    <t>818306015</t>
-  </si>
-  <si>
-    <t>884439336</t>
-  </si>
-  <si>
-    <t>872880103</t>
-  </si>
-  <si>
-    <t>872808641</t>
-  </si>
-  <si>
-    <t>866582988</t>
-  </si>
-  <si>
-    <t>850574298</t>
-  </si>
-  <si>
-    <t>807144559</t>
-  </si>
-  <si>
-    <t>806097576</t>
-  </si>
-  <si>
-    <t>203263698</t>
-  </si>
-  <si>
-    <t>211711431</t>
-  </si>
-  <si>
-    <t>191354921</t>
-  </si>
-  <si>
-    <t>933112405</t>
-  </si>
-  <si>
-    <t>972166197</t>
-  </si>
-  <si>
-    <t>953045790</t>
-  </si>
-  <si>
-    <t>946797713</t>
-  </si>
-  <si>
-    <t>942613757</t>
-  </si>
-  <si>
-    <t>178336552</t>
-  </si>
-  <si>
-    <t>223266598</t>
-  </si>
-  <si>
-    <t>228631382</t>
-  </si>
-  <si>
-    <t>224785950</t>
+    <t>789256710</t>
+  </si>
+  <si>
+    <t>959792783</t>
+  </si>
+  <si>
+    <t>970498105</t>
+  </si>
+  <si>
+    <t>953504861</t>
+  </si>
+  <si>
+    <t>911240749</t>
+  </si>
+  <si>
+    <t>194252262</t>
+  </si>
+  <si>
+    <t>771536897</t>
+  </si>
+  <si>
+    <t>719936431</t>
+  </si>
+  <si>
+    <t>196184695</t>
+  </si>
+  <si>
+    <t>177236662</t>
+  </si>
+  <si>
+    <t>177954439</t>
+  </si>
+  <si>
+    <t>177923855</t>
+  </si>
+  <si>
+    <t>177002148</t>
+  </si>
+  <si>
+    <t>870951229</t>
+  </si>
+  <si>
+    <t>869050108</t>
+  </si>
+  <si>
+    <t>847118381</t>
+  </si>
+  <si>
+    <t>852182538</t>
+  </si>
+  <si>
+    <t>838693178</t>
+  </si>
+  <si>
+    <t>841903523</t>
+  </si>
+  <si>
+    <t>841711777</t>
+  </si>
+  <si>
+    <t>840968691</t>
+  </si>
+  <si>
+    <t>839931056</t>
+  </si>
+  <si>
+    <t>835097662</t>
+  </si>
+  <si>
+    <t>831688233</t>
+  </si>
+  <si>
+    <t>821991779</t>
+  </si>
+  <si>
+    <t>811107154</t>
+  </si>
+  <si>
+    <t>799643212</t>
+  </si>
+  <si>
+    <t>789214164</t>
+  </si>
+  <si>
+    <t>784756326</t>
+  </si>
+  <si>
+    <t>973929361</t>
+  </si>
+  <si>
+    <t>967345178</t>
+  </si>
+  <si>
+    <t>187513845</t>
+  </si>
+  <si>
+    <t>187093079</t>
+  </si>
+  <si>
+    <t>838357063</t>
+  </si>
+  <si>
+    <t>808613297</t>
+  </si>
+  <si>
+    <t>782241610</t>
+  </si>
+  <si>
+    <t>777521786</t>
+  </si>
+  <si>
+    <t>863004382</t>
+  </si>
+  <si>
+    <t>852405798</t>
+  </si>
+  <si>
+    <t>844620694</t>
+  </si>
+  <si>
+    <t>843973748</t>
+  </si>
+  <si>
+    <t>840829653</t>
+  </si>
+  <si>
+    <t>839433566</t>
+  </si>
+  <si>
+    <t>815046929</t>
+  </si>
+  <si>
+    <t>938750969</t>
+  </si>
+  <si>
+    <t>916283504</t>
+  </si>
+  <si>
+    <t>887615510</t>
+  </si>
+  <si>
+    <t>923014710</t>
+  </si>
+  <si>
+    <t>742407236</t>
+  </si>
+  <si>
+    <t>775629334</t>
+  </si>
+  <si>
+    <t>208500805</t>
+  </si>
+  <si>
+    <t>969016132</t>
+  </si>
+  <si>
+    <t>972244622</t>
+  </si>
+  <si>
+    <t>187829563</t>
+  </si>
+  <si>
+    <t>187513787</t>
+  </si>
+  <si>
+    <t>184933699</t>
+  </si>
+  <si>
+    <t>187018886</t>
+  </si>
+  <si>
+    <t>186935940</t>
+  </si>
+  <si>
+    <t>186935478</t>
+  </si>
+  <si>
+    <t>181790290</t>
+  </si>
+  <si>
+    <t>940534310</t>
+  </si>
+  <si>
+    <t>782898153</t>
+  </si>
+  <si>
+    <t>779661648</t>
+  </si>
+  <si>
+    <t>771910217</t>
+  </si>
+  <si>
+    <t>779396161</t>
+  </si>
+  <si>
+    <t>772866913</t>
+  </si>
+  <si>
+    <t>769047436</t>
+  </si>
+  <si>
+    <t>766978245</t>
+  </si>
+  <si>
+    <t>746538036</t>
+  </si>
+  <si>
+    <t>662330970</t>
+  </si>
+  <si>
+    <t>194750117</t>
+  </si>
+  <si>
+    <t>919771976</t>
+  </si>
+  <si>
+    <t>925429353</t>
+  </si>
+  <si>
+    <t>904681891</t>
+  </si>
+  <si>
+    <t>904669607</t>
+  </si>
+  <si>
+    <t>900288212</t>
+  </si>
+  <si>
+    <t>895607913</t>
+  </si>
+  <si>
+    <t>883005260</t>
+  </si>
+  <si>
+    <t>888241985</t>
+  </si>
+  <si>
+    <t>886865413</t>
+  </si>
+  <si>
+    <t>874370210</t>
+  </si>
+  <si>
+    <t>874143096</t>
+  </si>
+  <si>
+    <t>840950434</t>
+  </si>
+  <si>
+    <t>853108821</t>
+  </si>
+  <si>
+    <t>855499137</t>
+  </si>
+  <si>
+    <t>855072207</t>
+  </si>
+  <si>
+    <t>854653163</t>
+  </si>
+  <si>
+    <t>854506148</t>
+  </si>
+  <si>
+    <t>838453946</t>
+  </si>
+  <si>
+    <t>838283152</t>
+  </si>
+  <si>
+    <t>835941448</t>
+  </si>
+  <si>
+    <t>819455449</t>
+  </si>
+  <si>
+    <t>835111091</t>
+  </si>
+  <si>
+    <t>824400893</t>
+  </si>
+  <si>
+    <t>821255282</t>
+  </si>
+  <si>
+    <t>820493322</t>
+  </si>
+  <si>
+    <t>819691431</t>
+  </si>
+  <si>
+    <t>806404756</t>
+  </si>
+  <si>
+    <t>969151566</t>
+  </si>
+  <si>
+    <t>962722157</t>
+  </si>
+  <si>
+    <t>961256231</t>
+  </si>
+  <si>
+    <t>181610316</t>
+  </si>
+  <si>
+    <t>181653076</t>
+  </si>
+  <si>
+    <t>193528654</t>
+  </si>
+  <si>
+    <t>182434583</t>
+  </si>
+  <si>
+    <t>181604475</t>
+  </si>
+  <si>
+    <t>834012266</t>
+  </si>
+  <si>
+    <t>938558230</t>
+  </si>
+  <si>
+    <t>776343638</t>
+  </si>
+  <si>
+    <t>818586343</t>
+  </si>
+  <si>
+    <t>853502775</t>
+  </si>
+  <si>
+    <t>844515373</t>
+  </si>
+  <si>
+    <t>837391303</t>
+  </si>
+  <si>
+    <t>837985690</t>
+  </si>
+  <si>
+    <t>836305429</t>
+  </si>
+  <si>
+    <t>836993083</t>
+  </si>
+  <si>
+    <t>832907517</t>
+  </si>
+  <si>
+    <t>831954544</t>
+  </si>
+  <si>
+    <t>820563314</t>
+  </si>
+  <si>
+    <t>829483290</t>
+  </si>
+  <si>
+    <t>828574347</t>
+  </si>
+  <si>
+    <t>819209523</t>
+  </si>
+  <si>
+    <t>818249058</t>
+  </si>
+  <si>
+    <t>783929577</t>
+  </si>
+  <si>
+    <t>791695848</t>
+  </si>
+  <si>
+    <t>775601051</t>
+  </si>
+  <si>
+    <t>178335869</t>
+  </si>
+  <si>
+    <t>177566191</t>
+  </si>
+  <si>
+    <t>871715425</t>
+  </si>
+  <si>
+    <t>892554100</t>
+  </si>
+  <si>
+    <t>897071951</t>
+  </si>
+  <si>
+    <t>895616518</t>
+  </si>
+  <si>
+    <t>959963947</t>
+  </si>
+  <si>
+    <t>904808197</t>
+  </si>
+  <si>
+    <t>845274707</t>
+  </si>
+  <si>
+    <t>178457010</t>
+  </si>
+  <si>
+    <t>180788378</t>
+  </si>
+  <si>
+    <t>181650312</t>
+  </si>
+  <si>
+    <t>181647912</t>
+  </si>
+  <si>
+    <t>179198704</t>
+  </si>
+  <si>
+    <t>180786703</t>
+  </si>
+  <si>
+    <t>178509471</t>
+  </si>
+  <si>
+    <t>178509414</t>
+  </si>
+  <si>
+    <t>875091427</t>
   </si>
 </sst>
 </file>
@@ -793,7 +949,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1158,7 +1314,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1170,7 +1326,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1182,7 +1338,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1194,7 +1350,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1206,7 +1362,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1218,7 +1374,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1230,7 +1386,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1242,7 +1398,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1254,7 +1410,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1420,7 +1576,7 @@
         <v>58</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>4</v>
@@ -1431,7 +1587,7 @@
         <v>59</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
@@ -1442,7 +1598,7 @@
         <v>60</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>4</v>
@@ -1453,7 +1609,7 @@
         <v>61</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>4</v>
@@ -1464,7 +1620,7 @@
         <v>62</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>4</v>
@@ -1475,7 +1631,7 @@
         <v>63</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>4</v>
@@ -1486,7 +1642,7 @@
         <v>64</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>4</v>
@@ -1519,7 +1675,7 @@
         <v>67</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
@@ -1530,7 +1686,7 @@
         <v>68</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
@@ -1541,7 +1697,7 @@
         <v>69</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>4</v>
@@ -1552,7 +1708,7 @@
         <v>70</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
@@ -1563,7 +1719,7 @@
         <v>71</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
@@ -1574,7 +1730,7 @@
         <v>72</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>4</v>
@@ -1585,7 +1741,7 @@
         <v>73</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>4</v>
@@ -1596,7 +1752,7 @@
         <v>74</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>4</v>
@@ -1607,7 +1763,7 @@
         <v>75</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>4</v>
@@ -1618,7 +1774,7 @@
         <v>76</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>4</v>
@@ -1838,7 +1994,7 @@
         <v>96</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>4</v>
@@ -1849,7 +2005,7 @@
         <v>97</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>4</v>
@@ -1860,9 +2016,581 @@
         <v>98</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1889,31 +2617,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D46E3E-8BF7-439D-BC31-D42213FEE728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98D8530-1952-4D60-8619-C3AD3AD5551C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="209">
   <si>
     <t>Status</t>
   </si>
@@ -48,412 +48,616 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>825270907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>911482267</t>
-  </si>
-  <si>
-    <t>932285616</t>
-  </si>
-  <si>
-    <t>956984003</t>
-  </si>
-  <si>
-    <t>956985596</t>
-  </si>
-  <si>
-    <t>956009272</t>
-  </si>
-  <si>
-    <t>932769734</t>
-  </si>
-  <si>
-    <t>944469455</t>
-  </si>
-  <si>
-    <t>947048207</t>
-  </si>
-  <si>
-    <t>929407876</t>
-  </si>
-  <si>
-    <t>930716984</t>
-  </si>
-  <si>
-    <t>920710948</t>
-  </si>
-  <si>
-    <t>928326200</t>
-  </si>
-  <si>
-    <t>927311328</t>
-  </si>
-  <si>
-    <t>919506752</t>
-  </si>
-  <si>
-    <t>910129984</t>
-  </si>
-  <si>
-    <t>908593787</t>
-  </si>
-  <si>
-    <t>898866748</t>
-  </si>
-  <si>
-    <t>903823973</t>
-  </si>
-  <si>
-    <t>902700602</t>
-  </si>
-  <si>
-    <t>901739981</t>
-  </si>
-  <si>
-    <t>897489708</t>
-  </si>
-  <si>
-    <t>895000176</t>
-  </si>
-  <si>
-    <t>882224011</t>
-  </si>
-  <si>
-    <t>893935373</t>
-  </si>
-  <si>
-    <t>891375911</t>
-  </si>
-  <si>
-    <t>880366228</t>
-  </si>
-  <si>
-    <t>877473979</t>
-  </si>
-  <si>
-    <t>876330634</t>
-  </si>
-  <si>
-    <t>876146600</t>
-  </si>
-  <si>
-    <t>850263637</t>
-  </si>
-  <si>
-    <t>870244484</t>
-  </si>
-  <si>
-    <t>874739984</t>
-  </si>
-  <si>
-    <t>866474913</t>
-  </si>
-  <si>
-    <t>860038870</t>
-  </si>
-  <si>
-    <t>849998301</t>
-  </si>
-  <si>
-    <t>834006326</t>
-  </si>
-  <si>
-    <t>841613759</t>
-  </si>
-  <si>
-    <t>840538189</t>
-  </si>
-  <si>
-    <t>840468700</t>
-  </si>
-  <si>
-    <t>827979059</t>
-  </si>
-  <si>
-    <t>814231647</t>
-  </si>
-  <si>
-    <t>817586930</t>
-  </si>
-  <si>
-    <t>800928487</t>
-  </si>
-  <si>
-    <t>805363110</t>
-  </si>
-  <si>
-    <t>809129558</t>
-  </si>
-  <si>
-    <t>808922185</t>
-  </si>
-  <si>
-    <t>801943550</t>
-  </si>
-  <si>
-    <t>780994863</t>
-  </si>
-  <si>
-    <t>794968960</t>
-  </si>
-  <si>
-    <t>797507039</t>
-  </si>
-  <si>
-    <t>768054060</t>
-  </si>
-  <si>
-    <t>231556899</t>
-  </si>
-  <si>
-    <t>231557285</t>
-  </si>
-  <si>
-    <t>231556915</t>
-  </si>
-  <si>
-    <t>223483920</t>
-  </si>
-  <si>
-    <t>223483938</t>
-  </si>
-  <si>
-    <t>204585222</t>
-  </si>
-  <si>
-    <t>203556505</t>
-  </si>
-  <si>
-    <t>203268317</t>
-  </si>
-  <si>
-    <t>199416516</t>
-  </si>
-  <si>
-    <t>203017490</t>
-  </si>
-  <si>
-    <t>200405094</t>
-  </si>
-  <si>
-    <t>973044732</t>
-  </si>
-  <si>
-    <t>182794580</t>
-  </si>
-  <si>
-    <t>181383583</t>
-  </si>
-  <si>
-    <t>179291137</t>
-  </si>
-  <si>
-    <t>177344037</t>
-  </si>
-  <si>
-    <t>969666258</t>
-  </si>
-  <si>
-    <t>968281125</t>
-  </si>
-  <si>
-    <t>924399706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>802111777</t>
-  </si>
-  <si>
-    <t>230998365</t>
-  </si>
-  <si>
-    <t>236166728</t>
-  </si>
-  <si>
-    <t>236900969</t>
-  </si>
-  <si>
-    <t>238513026</t>
-  </si>
-  <si>
-    <t>934264320</t>
-  </si>
-  <si>
-    <t>812647539</t>
-  </si>
-  <si>
-    <t>839386863</t>
-  </si>
-  <si>
-    <t>875606299</t>
-  </si>
-  <si>
-    <t>875144218</t>
-  </si>
-  <si>
-    <t>863210237</t>
-  </si>
-  <si>
-    <t>871876441</t>
-  </si>
-  <si>
-    <t>871259440</t>
-  </si>
-  <si>
-    <t>866340155</t>
-  </si>
-  <si>
-    <t>852018930</t>
-  </si>
-  <si>
-    <t>846908733</t>
-  </si>
-  <si>
-    <t>836814503</t>
-  </si>
-  <si>
-    <t>817677309</t>
-  </si>
-  <si>
-    <t>829013378</t>
-  </si>
-  <si>
-    <t>816067858</t>
-  </si>
-  <si>
-    <t>810638555</t>
-  </si>
-  <si>
-    <t>809695095</t>
-  </si>
-  <si>
-    <t>804763187</t>
-  </si>
-  <si>
-    <t>774855260</t>
-  </si>
-  <si>
-    <t>794978134</t>
-  </si>
-  <si>
-    <t>208379382</t>
-  </si>
-  <si>
-    <t>237001007</t>
-  </si>
-  <si>
-    <t>244689018</t>
-  </si>
-  <si>
-    <t>241578180</t>
-  </si>
-  <si>
-    <t>236899237</t>
-  </si>
-  <si>
-    <t>234397275</t>
-  </si>
-  <si>
-    <t>230126546</t>
-  </si>
-  <si>
-    <t>216983316</t>
-  </si>
-  <si>
-    <t>195406586</t>
-  </si>
-  <si>
-    <t>194843946</t>
-  </si>
-  <si>
-    <t>184468464</t>
-  </si>
-  <si>
-    <t>177746686</t>
-  </si>
-  <si>
-    <t>947549535</t>
-  </si>
-  <si>
-    <t>955891654</t>
-  </si>
-  <si>
-    <t>961131400</t>
-  </si>
-  <si>
-    <t>957553112</t>
-  </si>
-  <si>
-    <t>955844455</t>
-  </si>
-  <si>
-    <t>955670777</t>
-  </si>
-  <si>
-    <t>955387372</t>
-  </si>
-  <si>
-    <t>951147879</t>
-  </si>
-  <si>
-    <t>933493755</t>
-  </si>
-  <si>
-    <t>928212111</t>
-  </si>
-  <si>
-    <t>932008943</t>
-  </si>
-  <si>
-    <t>932196128</t>
-  </si>
-  <si>
-    <t>894255375</t>
-  </si>
-  <si>
-    <t>896579830</t>
-  </si>
-  <si>
-    <t>896818006</t>
-  </si>
-  <si>
-    <t>876020870</t>
-  </si>
-  <si>
-    <t>892059076</t>
-  </si>
-  <si>
-    <t>880310820</t>
-  </si>
-  <si>
-    <t>896373283</t>
-  </si>
-  <si>
-    <t>180857330</t>
-  </si>
-  <si>
-    <t>185327784</t>
-  </si>
-  <si>
-    <t>180855599</t>
-  </si>
-  <si>
-    <t>958372116</t>
-  </si>
-  <si>
-    <t>941070835</t>
-  </si>
-  <si>
-    <t>902586167</t>
-  </si>
-  <si>
-    <t>895607921</t>
+    <t>749346791</t>
+  </si>
+  <si>
+    <t>?????</t>
+  </si>
+  <si>
+    <t>763779950</t>
+  </si>
+  <si>
+    <t>756625947</t>
+  </si>
+  <si>
+    <t>759263860</t>
+  </si>
+  <si>
+    <t>761321284</t>
+  </si>
+  <si>
+    <t>761911225</t>
+  </si>
+  <si>
+    <t>765423169</t>
+  </si>
+  <si>
+    <t>763606088</t>
+  </si>
+  <si>
+    <t>763224569</t>
+  </si>
+  <si>
+    <t>762944282</t>
+  </si>
+  <si>
+    <t>767051216</t>
+  </si>
+  <si>
+    <t>767505328</t>
+  </si>
+  <si>
+    <t>771409087</t>
+  </si>
+  <si>
+    <t>184104119</t>
+  </si>
+  <si>
+    <t>771139460</t>
+  </si>
+  <si>
+    <t>772424549</t>
+  </si>
+  <si>
+    <t>773056126</t>
+  </si>
+  <si>
+    <t>774406759</t>
+  </si>
+  <si>
+    <t>774055663</t>
+  </si>
+  <si>
+    <t>775071990</t>
+  </si>
+  <si>
+    <t>780480251</t>
+  </si>
+  <si>
+    <t>781600675</t>
+  </si>
+  <si>
+    <t>970972489</t>
+  </si>
+  <si>
+    <t>782462091</t>
+  </si>
+  <si>
+    <t>785079272</t>
+  </si>
+  <si>
+    <t>784954020</t>
+  </si>
+  <si>
+    <t>785742390</t>
+  </si>
+  <si>
+    <t>892101449</t>
+  </si>
+  <si>
+    <t>785712609</t>
+  </si>
+  <si>
+    <t>785531454</t>
+  </si>
+  <si>
+    <t>787731102</t>
+  </si>
+  <si>
+    <t>787761406</t>
+  </si>
+  <si>
+    <t>789919937</t>
+  </si>
+  <si>
+    <t>790367787</t>
+  </si>
+  <si>
+    <t>791947348</t>
+  </si>
+  <si>
+    <t>792658050</t>
+  </si>
+  <si>
+    <t>793474960</t>
+  </si>
+  <si>
+    <t>793749965</t>
+  </si>
+  <si>
+    <t>794297618</t>
+  </si>
+  <si>
+    <t>793878061</t>
+  </si>
+  <si>
+    <t>799582402</t>
+  </si>
+  <si>
+    <t>797949801</t>
+  </si>
+  <si>
+    <t>795991334</t>
+  </si>
+  <si>
+    <t>797837790</t>
+  </si>
+  <si>
+    <t>804584385</t>
+  </si>
+  <si>
+    <t>805129479</t>
+  </si>
+  <si>
+    <t>806509273</t>
+  </si>
+  <si>
+    <t>806026401</t>
+  </si>
+  <si>
+    <t>808129765</t>
+  </si>
+  <si>
+    <t>809550522</t>
+  </si>
+  <si>
+    <t>811512684</t>
+  </si>
+  <si>
+    <t>812544421</t>
+  </si>
+  <si>
+    <t>812826885</t>
+  </si>
+  <si>
+    <t>814707117</t>
+  </si>
+  <si>
+    <t>814060434</t>
+  </si>
+  <si>
+    <t>814300590</t>
+  </si>
+  <si>
+    <t>815080944</t>
+  </si>
+  <si>
+    <t>819825989</t>
+  </si>
+  <si>
+    <t>818307476</t>
+  </si>
+  <si>
+    <t>820710345</t>
+  </si>
+  <si>
+    <t>820252439</t>
+  </si>
+  <si>
+    <t>823380583</t>
+  </si>
+  <si>
+    <t>834875951</t>
+  </si>
+  <si>
+    <t>828705917</t>
+  </si>
+  <si>
+    <t>831842897</t>
+  </si>
+  <si>
+    <t>832345189</t>
+  </si>
+  <si>
+    <t>833038320</t>
+  </si>
+  <si>
+    <t>833537826</t>
+  </si>
+  <si>
+    <t>834129987</t>
+  </si>
+  <si>
+    <t>835771068</t>
+  </si>
+  <si>
+    <t>837117286</t>
+  </si>
+  <si>
+    <t>835876438</t>
+  </si>
+  <si>
+    <t>836146013</t>
+  </si>
+  <si>
+    <t>840311280</t>
+  </si>
+  <si>
+    <t>837291024</t>
+  </si>
+  <si>
+    <t>837866361</t>
+  </si>
+  <si>
+    <t>838498073</t>
+  </si>
+  <si>
+    <t>839027699</t>
+  </si>
+  <si>
+    <t>839881616</t>
+  </si>
+  <si>
+    <t>906352947</t>
+  </si>
+  <si>
+    <t>840212884</t>
+  </si>
+  <si>
+    <t>842108031</t>
+  </si>
+  <si>
+    <t>841225158</t>
+  </si>
+  <si>
+    <t>841263001</t>
+  </si>
+  <si>
+    <t>841997350</t>
+  </si>
+  <si>
+    <t>843408190</t>
+  </si>
+  <si>
+    <t>849184951</t>
+  </si>
+  <si>
+    <t>850817911</t>
+  </si>
+  <si>
+    <t>850895123</t>
+  </si>
+  <si>
+    <t>851386148</t>
+  </si>
+  <si>
+    <t>851524052</t>
+  </si>
+  <si>
+    <t>852287352</t>
+  </si>
+  <si>
+    <t>852322787</t>
+  </si>
+  <si>
+    <t>906976075</t>
+  </si>
+  <si>
+    <t>852947690</t>
+  </si>
+  <si>
+    <t>856462571</t>
+  </si>
+  <si>
+    <t>856779495</t>
+  </si>
+  <si>
+    <t>856352392</t>
+  </si>
+  <si>
+    <t>857272466</t>
+  </si>
+  <si>
+    <t>858225158</t>
+  </si>
+  <si>
+    <t>860410970</t>
+  </si>
+  <si>
+    <t>861632119</t>
+  </si>
+  <si>
+    <t>862964859</t>
+  </si>
+  <si>
+    <t>863597526</t>
+  </si>
+  <si>
+    <t>866155223</t>
+  </si>
+  <si>
+    <t>867485884</t>
+  </si>
+  <si>
+    <t>868035944</t>
+  </si>
+  <si>
+    <t>868248315</t>
+  </si>
+  <si>
+    <t>868675418</t>
+  </si>
+  <si>
+    <t>869300289</t>
+  </si>
+  <si>
+    <t>882179603</t>
+  </si>
+  <si>
+    <t>878073612</t>
+  </si>
+  <si>
+    <t>10777289964QFILIPIAC</t>
+  </si>
+  <si>
+    <t>877516892</t>
+  </si>
+  <si>
+    <t>877607022</t>
+  </si>
+  <si>
+    <t>878457351</t>
+  </si>
+  <si>
+    <t>878486491</t>
+  </si>
+  <si>
+    <t>879398174</t>
+  </si>
+  <si>
+    <t>880481761</t>
+  </si>
+  <si>
+    <t>880029834</t>
+  </si>
+  <si>
+    <t>924250347</t>
+  </si>
+  <si>
+    <t>882992021</t>
+  </si>
+  <si>
+    <t>884744297</t>
+  </si>
+  <si>
+    <t>884263116</t>
+  </si>
+  <si>
+    <t>884724836</t>
+  </si>
+  <si>
+    <t>885426472</t>
+  </si>
+  <si>
+    <t>887258741</t>
+  </si>
+  <si>
+    <t>887489635</t>
+  </si>
+  <si>
+    <t>890372513</t>
+  </si>
+  <si>
+    <t>888607839</t>
+  </si>
+  <si>
+    <t>889076448</t>
+  </si>
+  <si>
+    <t>889664706</t>
+  </si>
+  <si>
+    <t>890864444</t>
+  </si>
+  <si>
+    <t>889752733</t>
+  </si>
+  <si>
+    <t>890159365</t>
+  </si>
+  <si>
+    <t>894195316</t>
+  </si>
+  <si>
+    <t>891902797</t>
+  </si>
+  <si>
+    <t>896206319</t>
+  </si>
+  <si>
+    <t>892661319</t>
+  </si>
+  <si>
+    <t>894024623</t>
+  </si>
+  <si>
+    <t>895257537</t>
+  </si>
+  <si>
+    <t>898281500</t>
+  </si>
+  <si>
+    <t>898647015</t>
+  </si>
+  <si>
+    <t>899142537</t>
+  </si>
+  <si>
+    <t>903102717</t>
+  </si>
+  <si>
+    <t>904780404</t>
+  </si>
+  <si>
+    <t>907304517</t>
+  </si>
+  <si>
+    <t>907940385</t>
+  </si>
+  <si>
+    <t>907471936</t>
+  </si>
+  <si>
+    <t>908246667</t>
+  </si>
+  <si>
+    <t>908928512</t>
+  </si>
+  <si>
+    <t>909084331</t>
+  </si>
+  <si>
+    <t>909173449</t>
+  </si>
+  <si>
+    <t>909916979</t>
+  </si>
+  <si>
+    <t>910872377</t>
+  </si>
+  <si>
+    <t>913579870</t>
+  </si>
+  <si>
+    <t>915406494</t>
+  </si>
+  <si>
+    <t>916607710</t>
+  </si>
+  <si>
+    <t>916316239</t>
+  </si>
+  <si>
+    <t>918806112</t>
+  </si>
+  <si>
+    <t>921061374</t>
+  </si>
+  <si>
+    <t>921270199</t>
+  </si>
+  <si>
+    <t>924000270</t>
+  </si>
+  <si>
+    <t>926175674</t>
+  </si>
+  <si>
+    <t>927956171</t>
+  </si>
+  <si>
+    <t>930014471</t>
+  </si>
+  <si>
+    <t>932235983</t>
+  </si>
+  <si>
+    <t>930940139</t>
+  </si>
+  <si>
+    <t>932146438</t>
+  </si>
+  <si>
+    <t>932867801</t>
+  </si>
+  <si>
+    <t>933110102</t>
+  </si>
+  <si>
+    <t>934249412</t>
+  </si>
+  <si>
+    <t>939256321</t>
+  </si>
+  <si>
+    <t>936311541</t>
+  </si>
+  <si>
+    <t>938930181</t>
+  </si>
+  <si>
+    <t>939522011</t>
+  </si>
+  <si>
+    <t>940794138</t>
+  </si>
+  <si>
+    <t>942000559</t>
+  </si>
+  <si>
+    <t>940448669</t>
+  </si>
+  <si>
+    <t>942310719</t>
+  </si>
+  <si>
+    <t>943100945</t>
+  </si>
+  <si>
+    <t>946602988</t>
+  </si>
+  <si>
+    <t>946860768</t>
+  </si>
+  <si>
+    <t>950852750</t>
+  </si>
+  <si>
+    <t>948342013</t>
+  </si>
+  <si>
+    <t>949400059</t>
+  </si>
+  <si>
+    <t>949858058</t>
+  </si>
+  <si>
+    <t>950183289</t>
+  </si>
+  <si>
+    <t>951134927</t>
+  </si>
+  <si>
+    <t>951833197</t>
+  </si>
+  <si>
+    <t>952172587</t>
+  </si>
+  <si>
+    <t>961969742</t>
+  </si>
+  <si>
+    <t>963721604</t>
+  </si>
+  <si>
+    <t>962884429</t>
+  </si>
+  <si>
+    <t>963650902</t>
+  </si>
+  <si>
+    <t>963748979</t>
+  </si>
+  <si>
+    <t>963757889</t>
+  </si>
+  <si>
+    <t>970101105</t>
+  </si>
+  <si>
+    <t>974971008</t>
+  </si>
+  <si>
+    <t>185545633</t>
+  </si>
+  <si>
+    <t>185927211</t>
+  </si>
+  <si>
+    <t>188577682</t>
+  </si>
+  <si>
+    <t>190003222</t>
   </si>
 </sst>
 </file>
@@ -919,7 +1123,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1755,7 +1959,7 @@
         <v>76</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
@@ -1763,10 +1967,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
@@ -1774,10 +1978,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
@@ -1785,10 +1989,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>4</v>
@@ -1796,10 +2000,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>4</v>
@@ -1807,10 +2011,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
@@ -1818,7 +2022,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>6</v>
@@ -1829,7 +2033,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>6</v>
@@ -1840,7 +2044,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>6</v>
@@ -1851,7 +2055,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>6</v>
@@ -1862,7 +2066,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>6</v>
@@ -1873,7 +2077,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>6</v>
@@ -1884,7 +2088,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>6</v>
@@ -1895,7 +2099,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>6</v>
@@ -1906,7 +2110,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>6</v>
@@ -1917,7 +2121,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>6</v>
@@ -1928,7 +2132,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>6</v>
@@ -1939,7 +2143,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>6</v>
@@ -1950,7 +2154,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>6</v>
@@ -1961,7 +2165,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>6</v>
@@ -1972,7 +2176,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>6</v>
@@ -1983,7 +2187,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>6</v>
@@ -1994,7 +2198,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>6</v>
@@ -2005,7 +2209,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>6</v>
@@ -2016,7 +2220,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>6</v>
@@ -2027,7 +2231,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>6</v>
@@ -2038,7 +2242,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>6</v>
@@ -2049,7 +2253,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>6</v>
@@ -2060,7 +2264,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>6</v>
@@ -2071,7 +2275,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>6</v>
@@ -2082,7 +2286,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>6</v>
@@ -2093,7 +2297,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>6</v>
@@ -2104,7 +2308,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>6</v>
@@ -2115,7 +2319,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>6</v>
@@ -2126,7 +2330,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>6</v>
@@ -2137,7 +2341,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>6</v>
@@ -2148,7 +2352,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>6</v>
@@ -2159,7 +2363,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>6</v>
@@ -2170,7 +2374,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>6</v>
@@ -2181,7 +2385,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>6</v>
@@ -2192,7 +2396,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>6</v>
@@ -2203,7 +2407,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>6</v>
@@ -2214,7 +2418,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>6</v>
@@ -2225,7 +2429,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>6</v>
@@ -2236,7 +2440,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>6</v>
@@ -2247,7 +2451,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>6</v>
@@ -2258,7 +2462,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>6</v>
@@ -2269,7 +2473,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>6</v>
@@ -2280,7 +2484,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>6</v>
@@ -2291,7 +2495,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>6</v>
@@ -2302,7 +2506,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>6</v>
@@ -2313,7 +2517,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>6</v>
@@ -2324,7 +2528,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>6</v>
@@ -2335,7 +2539,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>6</v>
@@ -2346,7 +2550,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>6</v>
@@ -2357,7 +2561,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>6</v>
@@ -2368,10 +2572,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>4</v>
@@ -2379,10 +2583,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>4</v>
@@ -2390,10 +2594,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>4</v>
@@ -2401,10 +2605,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>4</v>
@@ -2412,10 +2616,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>4</v>
@@ -2423,10 +2627,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>4</v>
@@ -2434,10 +2638,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>4</v>
@@ -2445,12 +2649,771 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B135" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C135" s="5" t="s">
+      <c r="B136" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C204" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2477,31 +3440,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98D8530-1952-4D60-8619-C3AD3AD5551C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E3A365-BAC7-4208-9845-85B5DA9169F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="164">
   <si>
     <t>Status</t>
   </si>
@@ -48,616 +48,481 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>749346791</t>
-  </si>
-  <si>
-    <t>?????</t>
-  </si>
-  <si>
-    <t>763779950</t>
-  </si>
-  <si>
-    <t>756625947</t>
-  </si>
-  <si>
-    <t>759263860</t>
-  </si>
-  <si>
-    <t>761321284</t>
-  </si>
-  <si>
-    <t>761911225</t>
-  </si>
-  <si>
-    <t>765423169</t>
-  </si>
-  <si>
-    <t>763606088</t>
-  </si>
-  <si>
-    <t>763224569</t>
-  </si>
-  <si>
-    <t>762944282</t>
-  </si>
-  <si>
-    <t>767051216</t>
-  </si>
-  <si>
-    <t>767505328</t>
-  </si>
-  <si>
-    <t>771409087</t>
-  </si>
-  <si>
-    <t>184104119</t>
-  </si>
-  <si>
-    <t>771139460</t>
-  </si>
-  <si>
-    <t>772424549</t>
-  </si>
-  <si>
-    <t>773056126</t>
-  </si>
-  <si>
-    <t>774406759</t>
-  </si>
-  <si>
-    <t>774055663</t>
-  </si>
-  <si>
-    <t>775071990</t>
-  </si>
-  <si>
-    <t>780480251</t>
-  </si>
-  <si>
-    <t>781600675</t>
-  </si>
-  <si>
-    <t>970972489</t>
-  </si>
-  <si>
-    <t>782462091</t>
-  </si>
-  <si>
-    <t>785079272</t>
-  </si>
-  <si>
-    <t>784954020</t>
-  </si>
-  <si>
-    <t>785742390</t>
-  </si>
-  <si>
-    <t>892101449</t>
-  </si>
-  <si>
-    <t>785712609</t>
-  </si>
-  <si>
-    <t>785531454</t>
-  </si>
-  <si>
-    <t>787731102</t>
-  </si>
-  <si>
-    <t>787761406</t>
-  </si>
-  <si>
-    <t>789919937</t>
-  </si>
-  <si>
-    <t>790367787</t>
-  </si>
-  <si>
-    <t>791947348</t>
-  </si>
-  <si>
-    <t>792658050</t>
-  </si>
-  <si>
-    <t>793474960</t>
-  </si>
-  <si>
-    <t>793749965</t>
-  </si>
-  <si>
-    <t>794297618</t>
-  </si>
-  <si>
-    <t>793878061</t>
-  </si>
-  <si>
-    <t>799582402</t>
-  </si>
-  <si>
-    <t>797949801</t>
-  </si>
-  <si>
-    <t>795991334</t>
-  </si>
-  <si>
-    <t>797837790</t>
-  </si>
-  <si>
-    <t>804584385</t>
-  </si>
-  <si>
-    <t>805129479</t>
-  </si>
-  <si>
-    <t>806509273</t>
-  </si>
-  <si>
-    <t>806026401</t>
-  </si>
-  <si>
-    <t>808129765</t>
-  </si>
-  <si>
-    <t>809550522</t>
-  </si>
-  <si>
-    <t>811512684</t>
-  </si>
-  <si>
-    <t>812544421</t>
-  </si>
-  <si>
-    <t>812826885</t>
-  </si>
-  <si>
-    <t>814707117</t>
-  </si>
-  <si>
-    <t>814060434</t>
-  </si>
-  <si>
-    <t>814300590</t>
-  </si>
-  <si>
-    <t>815080944</t>
-  </si>
-  <si>
-    <t>819825989</t>
-  </si>
-  <si>
-    <t>818307476</t>
-  </si>
-  <si>
-    <t>820710345</t>
-  </si>
-  <si>
-    <t>820252439</t>
-  </si>
-  <si>
-    <t>823380583</t>
-  </si>
-  <si>
-    <t>834875951</t>
-  </si>
-  <si>
-    <t>828705917</t>
-  </si>
-  <si>
-    <t>831842897</t>
-  </si>
-  <si>
-    <t>832345189</t>
-  </si>
-  <si>
-    <t>833038320</t>
-  </si>
-  <si>
-    <t>833537826</t>
-  </si>
-  <si>
-    <t>834129987</t>
-  </si>
-  <si>
-    <t>835771068</t>
-  </si>
-  <si>
-    <t>837117286</t>
-  </si>
-  <si>
-    <t>835876438</t>
-  </si>
-  <si>
-    <t>836146013</t>
-  </si>
-  <si>
-    <t>840311280</t>
-  </si>
-  <si>
-    <t>837291024</t>
-  </si>
-  <si>
-    <t>837866361</t>
-  </si>
-  <si>
-    <t>838498073</t>
-  </si>
-  <si>
-    <t>839027699</t>
-  </si>
-  <si>
-    <t>839881616</t>
-  </si>
-  <si>
-    <t>906352947</t>
-  </si>
-  <si>
-    <t>840212884</t>
-  </si>
-  <si>
-    <t>842108031</t>
-  </si>
-  <si>
-    <t>841225158</t>
-  </si>
-  <si>
-    <t>841263001</t>
-  </si>
-  <si>
-    <t>841997350</t>
-  </si>
-  <si>
-    <t>843408190</t>
-  </si>
-  <si>
-    <t>849184951</t>
-  </si>
-  <si>
-    <t>850817911</t>
-  </si>
-  <si>
-    <t>850895123</t>
-  </si>
-  <si>
-    <t>851386148</t>
-  </si>
-  <si>
-    <t>851524052</t>
-  </si>
-  <si>
-    <t>852287352</t>
-  </si>
-  <si>
-    <t>852322787</t>
-  </si>
-  <si>
-    <t>906976075</t>
-  </si>
-  <si>
-    <t>852947690</t>
-  </si>
-  <si>
-    <t>856462571</t>
-  </si>
-  <si>
-    <t>856779495</t>
-  </si>
-  <si>
-    <t>856352392</t>
-  </si>
-  <si>
-    <t>857272466</t>
-  </si>
-  <si>
-    <t>858225158</t>
-  </si>
-  <si>
-    <t>860410970</t>
-  </si>
-  <si>
-    <t>861632119</t>
-  </si>
-  <si>
-    <t>862964859</t>
-  </si>
-  <si>
-    <t>863597526</t>
-  </si>
-  <si>
-    <t>866155223</t>
-  </si>
-  <si>
-    <t>867485884</t>
-  </si>
-  <si>
-    <t>868035944</t>
-  </si>
-  <si>
-    <t>868248315</t>
-  </si>
-  <si>
-    <t>868675418</t>
-  </si>
-  <si>
-    <t>869300289</t>
-  </si>
-  <si>
-    <t>882179603</t>
-  </si>
-  <si>
-    <t>878073612</t>
-  </si>
-  <si>
-    <t>10777289964QFILIPIAC</t>
-  </si>
-  <si>
-    <t>877516892</t>
-  </si>
-  <si>
-    <t>877607022</t>
-  </si>
-  <si>
-    <t>878457351</t>
-  </si>
-  <si>
-    <t>878486491</t>
-  </si>
-  <si>
-    <t>879398174</t>
-  </si>
-  <si>
-    <t>880481761</t>
-  </si>
-  <si>
-    <t>880029834</t>
-  </si>
-  <si>
-    <t>924250347</t>
-  </si>
-  <si>
-    <t>882992021</t>
-  </si>
-  <si>
-    <t>884744297</t>
-  </si>
-  <si>
-    <t>884263116</t>
-  </si>
-  <si>
-    <t>884724836</t>
-  </si>
-  <si>
-    <t>885426472</t>
-  </si>
-  <si>
-    <t>887258741</t>
-  </si>
-  <si>
-    <t>887489635</t>
-  </si>
-  <si>
-    <t>890372513</t>
-  </si>
-  <si>
-    <t>888607839</t>
-  </si>
-  <si>
-    <t>889076448</t>
-  </si>
-  <si>
-    <t>889664706</t>
-  </si>
-  <si>
-    <t>890864444</t>
-  </si>
-  <si>
-    <t>889752733</t>
-  </si>
-  <si>
-    <t>890159365</t>
-  </si>
-  <si>
-    <t>894195316</t>
-  </si>
-  <si>
-    <t>891902797</t>
-  </si>
-  <si>
-    <t>896206319</t>
-  </si>
-  <si>
-    <t>892661319</t>
-  </si>
-  <si>
-    <t>894024623</t>
-  </si>
-  <si>
-    <t>895257537</t>
-  </si>
-  <si>
-    <t>898281500</t>
-  </si>
-  <si>
-    <t>898647015</t>
-  </si>
-  <si>
-    <t>899142537</t>
-  </si>
-  <si>
-    <t>903102717</t>
-  </si>
-  <si>
-    <t>904780404</t>
-  </si>
-  <si>
-    <t>907304517</t>
-  </si>
-  <si>
-    <t>907940385</t>
-  </si>
-  <si>
-    <t>907471936</t>
-  </si>
-  <si>
-    <t>908246667</t>
-  </si>
-  <si>
-    <t>908928512</t>
-  </si>
-  <si>
-    <t>909084331</t>
-  </si>
-  <si>
-    <t>909173449</t>
-  </si>
-  <si>
-    <t>909916979</t>
-  </si>
-  <si>
-    <t>910872377</t>
-  </si>
-  <si>
-    <t>913579870</t>
-  </si>
-  <si>
-    <t>915406494</t>
-  </si>
-  <si>
-    <t>916607710</t>
-  </si>
-  <si>
-    <t>916316239</t>
-  </si>
-  <si>
-    <t>918806112</t>
-  </si>
-  <si>
-    <t>921061374</t>
-  </si>
-  <si>
-    <t>921270199</t>
-  </si>
-  <si>
-    <t>924000270</t>
-  </si>
-  <si>
-    <t>926175674</t>
-  </si>
-  <si>
-    <t>927956171</t>
-  </si>
-  <si>
-    <t>930014471</t>
-  </si>
-  <si>
-    <t>932235983</t>
-  </si>
-  <si>
-    <t>930940139</t>
-  </si>
-  <si>
-    <t>932146438</t>
-  </si>
-  <si>
-    <t>932867801</t>
-  </si>
-  <si>
-    <t>933110102</t>
-  </si>
-  <si>
-    <t>934249412</t>
-  </si>
-  <si>
-    <t>939256321</t>
-  </si>
-  <si>
-    <t>936311541</t>
-  </si>
-  <si>
-    <t>938930181</t>
-  </si>
-  <si>
-    <t>939522011</t>
-  </si>
-  <si>
-    <t>940794138</t>
-  </si>
-  <si>
-    <t>942000559</t>
-  </si>
-  <si>
-    <t>940448669</t>
-  </si>
-  <si>
-    <t>942310719</t>
-  </si>
-  <si>
-    <t>943100945</t>
-  </si>
-  <si>
-    <t>946602988</t>
-  </si>
-  <si>
-    <t>946860768</t>
-  </si>
-  <si>
-    <t>950852750</t>
-  </si>
-  <si>
-    <t>948342013</t>
-  </si>
-  <si>
-    <t>949400059</t>
-  </si>
-  <si>
-    <t>949858058</t>
-  </si>
-  <si>
-    <t>950183289</t>
-  </si>
-  <si>
-    <t>951134927</t>
-  </si>
-  <si>
-    <t>951833197</t>
-  </si>
-  <si>
-    <t>952172587</t>
-  </si>
-  <si>
-    <t>961969742</t>
-  </si>
-  <si>
-    <t>963721604</t>
-  </si>
-  <si>
-    <t>962884429</t>
-  </si>
-  <si>
-    <t>963650902</t>
-  </si>
-  <si>
-    <t>963748979</t>
-  </si>
-  <si>
-    <t>963757889</t>
-  </si>
-  <si>
-    <t>970101105</t>
-  </si>
-  <si>
-    <t>974971008</t>
-  </si>
-  <si>
-    <t>185545633</t>
-  </si>
-  <si>
-    <t>185927211</t>
-  </si>
-  <si>
-    <t>188577682</t>
-  </si>
-  <si>
-    <t>190003222</t>
+    <t>854299371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>958395331</t>
+  </si>
+  <si>
+    <t>898444504</t>
+  </si>
+  <si>
+    <t>922764588</t>
+  </si>
+  <si>
+    <t>930487412</t>
+  </si>
+  <si>
+    <t>924963451</t>
+  </si>
+  <si>
+    <t>907728699</t>
+  </si>
+  <si>
+    <t>914554229</t>
+  </si>
+  <si>
+    <t>917941845</t>
+  </si>
+  <si>
+    <t>901919781</t>
+  </si>
+  <si>
+    <t>901540280</t>
+  </si>
+  <si>
+    <t>195751189</t>
+  </si>
+  <si>
+    <t>194803197</t>
+  </si>
+  <si>
+    <t>192842692</t>
+  </si>
+  <si>
+    <t>192616419</t>
+  </si>
+  <si>
+    <t>189833035</t>
+  </si>
+  <si>
+    <t>190202782</t>
+  </si>
+  <si>
+    <t>187692722</t>
+  </si>
+  <si>
+    <t>185362955</t>
+  </si>
+  <si>
+    <t>186966432</t>
+  </si>
+  <si>
+    <t>174513527</t>
+  </si>
+  <si>
+    <t>974576690</t>
+  </si>
+  <si>
+    <t>972249092</t>
+  </si>
+  <si>
+    <t>957192531</t>
+  </si>
+  <si>
+    <t>953071671</t>
+  </si>
+  <si>
+    <t>950548416</t>
+  </si>
+  <si>
+    <t>949115665</t>
+  </si>
+  <si>
+    <t>941146551</t>
+  </si>
+  <si>
+    <t>944200975</t>
+  </si>
+  <si>
+    <t>939783340</t>
+  </si>
+  <si>
+    <t>933410841</t>
+  </si>
+  <si>
+    <t>934958798</t>
+  </si>
+  <si>
+    <t>873173847</t>
+  </si>
+  <si>
+    <t>895220857</t>
+  </si>
+  <si>
+    <t>894407448</t>
+  </si>
+  <si>
+    <t>887057705</t>
+  </si>
+  <si>
+    <t>886773070</t>
+  </si>
+  <si>
+    <t>882870839</t>
+  </si>
+  <si>
+    <t>881873404</t>
+  </si>
+  <si>
+    <t>876915608</t>
+  </si>
+  <si>
+    <t>879741191</t>
+  </si>
+  <si>
+    <t>875377040</t>
+  </si>
+  <si>
+    <t>875160255</t>
+  </si>
+  <si>
+    <t>871227017</t>
+  </si>
+  <si>
+    <t>855441733</t>
+  </si>
+  <si>
+    <t>866639465</t>
+  </si>
+  <si>
+    <t>860512502</t>
+  </si>
+  <si>
+    <t>850909981</t>
+  </si>
+  <si>
+    <t>848718759</t>
+  </si>
+  <si>
+    <t>846814345</t>
+  </si>
+  <si>
+    <t>791091394</t>
+  </si>
+  <si>
+    <t>813117011</t>
+  </si>
+  <si>
+    <t>816915684</t>
+  </si>
+  <si>
+    <t>813139676</t>
+  </si>
+  <si>
+    <t>812533127</t>
+  </si>
+  <si>
+    <t>774335560</t>
+  </si>
+  <si>
+    <t>218917809</t>
+  </si>
+  <si>
+    <t>214592333</t>
+  </si>
+  <si>
+    <t>214592325</t>
+  </si>
+  <si>
+    <t>230801312</t>
+  </si>
+  <si>
+    <t>214908455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>216707194</t>
+  </si>
+  <si>
+    <t>211753813</t>
+  </si>
+  <si>
+    <t>211598572</t>
+  </si>
+  <si>
+    <t>211129436</t>
+  </si>
+  <si>
+    <t>210095653</t>
+  </si>
+  <si>
+    <t>188302909</t>
+  </si>
+  <si>
+    <t>197368479</t>
+  </si>
+  <si>
+    <t>205041480</t>
+  </si>
+  <si>
+    <t>207316450</t>
+  </si>
+  <si>
+    <t>201106642</t>
+  </si>
+  <si>
+    <t>190854707</t>
+  </si>
+  <si>
+    <t>193689787</t>
+  </si>
+  <si>
+    <t>193655895</t>
+  </si>
+  <si>
+    <t>190647523</t>
+  </si>
+  <si>
+    <t>189099439</t>
+  </si>
+  <si>
+    <t>938471525</t>
+  </si>
+  <si>
+    <t>926953294</t>
+  </si>
+  <si>
+    <t>930624550</t>
+  </si>
+  <si>
+    <t>929680555</t>
+  </si>
+  <si>
+    <t>922976836</t>
+  </si>
+  <si>
+    <t>924400900</t>
+  </si>
+  <si>
+    <t>900424882</t>
+  </si>
+  <si>
+    <t>916640356</t>
+  </si>
+  <si>
+    <t>921926816</t>
+  </si>
+  <si>
+    <t>921710434</t>
+  </si>
+  <si>
+    <t>919203590</t>
+  </si>
+  <si>
+    <t>910033129</t>
+  </si>
+  <si>
+    <t>896755448</t>
+  </si>
+  <si>
+    <t>898832021</t>
+  </si>
+  <si>
+    <t>900396213</t>
+  </si>
+  <si>
+    <t>950053623</t>
+  </si>
+  <si>
+    <t>972735488</t>
+  </si>
+  <si>
+    <t>184019689</t>
+  </si>
+  <si>
+    <t>183682552</t>
+  </si>
+  <si>
+    <t>183147218</t>
+  </si>
+  <si>
+    <t>972324606</t>
+  </si>
+  <si>
+    <t>957359239</t>
+  </si>
+  <si>
+    <t>964777654</t>
+  </si>
+  <si>
+    <t>964706489</t>
+  </si>
+  <si>
+    <t>959520770</t>
+  </si>
+  <si>
+    <t>956971091</t>
+  </si>
+  <si>
+    <t>956569358</t>
+  </si>
+  <si>
+    <t>955365402</t>
+  </si>
+  <si>
+    <t>955152644</t>
+  </si>
+  <si>
+    <t>953077272</t>
+  </si>
+  <si>
+    <t>953053141</t>
+  </si>
+  <si>
+    <t>940676905</t>
+  </si>
+  <si>
+    <t>943207146</t>
+  </si>
+  <si>
+    <t>948838077</t>
+  </si>
+  <si>
+    <t>944428121</t>
+  </si>
+  <si>
+    <t>933351730</t>
+  </si>
+  <si>
+    <t>933674370</t>
+  </si>
+  <si>
+    <t>932598919</t>
+  </si>
+  <si>
+    <t>931123339</t>
+  </si>
+  <si>
+    <t>930938737</t>
+  </si>
+  <si>
+    <t>801354923</t>
+  </si>
+  <si>
+    <t>249137906</t>
+  </si>
+  <si>
+    <t>244467340</t>
+  </si>
+  <si>
+    <t>244684167</t>
+  </si>
+  <si>
+    <t>244172569</t>
+  </si>
+  <si>
+    <t>242408734</t>
+  </si>
+  <si>
+    <t>243400888</t>
+  </si>
+  <si>
+    <t>242287906</t>
+  </si>
+  <si>
+    <t>242098113</t>
+  </si>
+  <si>
+    <t>240566459</t>
+  </si>
+  <si>
+    <t>861219990</t>
+  </si>
+  <si>
+    <t>868105762</t>
+  </si>
+  <si>
+    <t>893840201</t>
+  </si>
+  <si>
+    <t>891547667</t>
+  </si>
+  <si>
+    <t>891393468</t>
+  </si>
+  <si>
+    <t>875862512</t>
+  </si>
+  <si>
+    <t>865866747</t>
+  </si>
+  <si>
+    <t>865651495</t>
+  </si>
+  <si>
+    <t>864926971</t>
+  </si>
+  <si>
+    <t>832652691</t>
+  </si>
+  <si>
+    <t>839053422</t>
+  </si>
+  <si>
+    <t>832659514</t>
+  </si>
+  <si>
+    <t>834902565</t>
+  </si>
+  <si>
+    <t>822602581</t>
+  </si>
+  <si>
+    <t>828741052</t>
+  </si>
+  <si>
+    <t>796459489</t>
+  </si>
+  <si>
+    <t>223945514</t>
+  </si>
+  <si>
+    <t>228821686</t>
+  </si>
+  <si>
+    <t>221667193</t>
+  </si>
+  <si>
+    <t>236942417</t>
+  </si>
+  <si>
+    <t>238345213</t>
+  </si>
+  <si>
+    <t>240566442</t>
+  </si>
+  <si>
+    <t>240131254</t>
+  </si>
+  <si>
+    <t>239529567</t>
+  </si>
+  <si>
+    <t>238575579</t>
+  </si>
+  <si>
+    <t>238010627</t>
+  </si>
+  <si>
+    <t>237553064</t>
+  </si>
+  <si>
+    <t>233863343</t>
+  </si>
+  <si>
+    <t>232448807</t>
+  </si>
+  <si>
+    <t>232448799</t>
+  </si>
+  <si>
+    <t>231544168</t>
   </si>
 </sst>
 </file>
@@ -1849,7 +1714,7 @@
         <v>66</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
@@ -1857,10 +1722,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
@@ -1868,10 +1733,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>4</v>
@@ -1879,10 +1744,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
@@ -1890,10 +1755,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
@@ -1901,10 +1766,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>4</v>
@@ -1912,10 +1777,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>4</v>
@@ -1923,10 +1788,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>4</v>
@@ -1934,10 +1799,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>4</v>
@@ -1945,10 +1810,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>4</v>
@@ -1956,10 +1821,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
@@ -1967,10 +1832,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
@@ -1978,10 +1843,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
@@ -1989,10 +1854,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>4</v>
@@ -2000,10 +1865,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>4</v>
@@ -2011,10 +1876,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
@@ -2022,10 +1887,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>4</v>
@@ -2033,10 +1898,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>4</v>
@@ -2044,10 +1909,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>4</v>
@@ -2055,10 +1920,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>4</v>
@@ -2066,10 +1931,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>4</v>
@@ -2077,10 +1942,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>4</v>
@@ -2088,10 +1953,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
@@ -2099,10 +1964,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>4</v>
@@ -2110,10 +1975,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
@@ -2121,10 +1986,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>4</v>
@@ -2132,10 +1997,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>4</v>
@@ -2143,10 +2008,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>4</v>
@@ -2154,10 +2019,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>4</v>
@@ -2165,10 +2030,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>4</v>
@@ -2176,10 +2041,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>4</v>
@@ -2187,10 +2052,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>4</v>
@@ -2198,10 +2063,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>4</v>
@@ -2209,10 +2074,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>4</v>
@@ -2220,10 +2085,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>4</v>
@@ -2231,10 +2096,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>4</v>
@@ -2242,10 +2107,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>4</v>
@@ -2253,10 +2118,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>4</v>
@@ -2264,10 +2129,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>4</v>
@@ -2275,10 +2140,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>4</v>
@@ -2286,10 +2151,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>4</v>
@@ -2297,10 +2162,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>4</v>
@@ -2308,10 +2173,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>4</v>
@@ -2319,10 +2184,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>4</v>
@@ -2330,10 +2195,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>4</v>
@@ -2341,10 +2206,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>4</v>
@@ -2352,10 +2217,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>4</v>
@@ -2363,10 +2228,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>4</v>
@@ -2374,10 +2239,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>4</v>
@@ -2385,10 +2250,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>4</v>
@@ -2396,10 +2261,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>4</v>
@@ -2407,10 +2272,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>4</v>
@@ -2418,10 +2283,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>4</v>
@@ -2429,10 +2294,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>4</v>
@@ -2440,10 +2305,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>4</v>
@@ -2451,10 +2316,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>4</v>
@@ -2462,10 +2327,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>4</v>
@@ -2473,10 +2338,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>4</v>
@@ -2484,10 +2349,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>4</v>
@@ -2495,10 +2360,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>4</v>
@@ -2506,10 +2371,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>4</v>
@@ -2517,10 +2382,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>4</v>
@@ -2528,10 +2393,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>4</v>
@@ -2539,10 +2404,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>4</v>
@@ -2550,10 +2415,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>4</v>
@@ -2561,10 +2426,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>4</v>
@@ -2572,10 +2437,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>4</v>
@@ -2583,10 +2448,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>4</v>
@@ -2594,10 +2459,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>4</v>
@@ -2605,10 +2470,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>4</v>
@@ -2616,10 +2481,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>4</v>
@@ -2627,10 +2492,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>4</v>
@@ -2638,10 +2503,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>4</v>
@@ -2649,10 +2514,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>4</v>
@@ -2660,10 +2525,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>4</v>
@@ -2671,10 +2536,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>4</v>
@@ -2682,10 +2547,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>4</v>
@@ -2693,10 +2558,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>4</v>
@@ -2704,10 +2569,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>4</v>
@@ -2715,10 +2580,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>4</v>
@@ -2726,10 +2591,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>4</v>
@@ -2737,10 +2602,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>4</v>
@@ -2748,10 +2613,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>4</v>
@@ -2759,10 +2624,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>4</v>
@@ -2770,10 +2635,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>4</v>
@@ -2781,10 +2646,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>4</v>
@@ -2792,10 +2657,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>4</v>
@@ -2803,10 +2668,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>4</v>
@@ -2814,10 +2679,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>4</v>
@@ -2825,10 +2690,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>4</v>
@@ -2836,10 +2701,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>4</v>
@@ -2847,10 +2712,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C153" s="5" t="s">
         <v>4</v>
@@ -2858,10 +2723,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>4</v>
@@ -2869,10 +2734,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>4</v>
@@ -2880,10 +2745,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>4</v>
@@ -2891,10 +2756,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>4</v>
@@ -2902,520 +2767,152 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C159" s="5"/>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B178" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B180" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B186" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B187" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B188" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B190" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B191" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B192" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B193" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B200" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B201" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B202" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C202" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="C160" s="5"/>
+    </row>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C161" s="5"/>
+    </row>
+    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C162" s="5"/>
+    </row>
+    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C163" s="5"/>
+    </row>
+    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C164" s="5"/>
+    </row>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C165" s="5"/>
+    </row>
+    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C166" s="5"/>
+    </row>
+    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C167" s="5"/>
+    </row>
+    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C168" s="5"/>
+    </row>
+    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C169" s="5"/>
+    </row>
+    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C170" s="5"/>
+    </row>
+    <row r="171" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C171" s="5"/>
+    </row>
+    <row r="172" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C172" s="5"/>
+    </row>
+    <row r="173" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C173" s="5"/>
+    </row>
+    <row r="174" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C174" s="5"/>
+    </row>
+    <row r="175" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C175" s="5"/>
+    </row>
+    <row r="176" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C176" s="5"/>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C177" s="5"/>
+    </row>
+    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C178" s="5"/>
+    </row>
+    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C179" s="5"/>
+    </row>
+    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C180" s="5"/>
+    </row>
+    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C181" s="5"/>
+    </row>
+    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C182" s="5"/>
+    </row>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C183" s="5"/>
+    </row>
+    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C184" s="5"/>
+    </row>
+    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C185" s="5"/>
+    </row>
+    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C186" s="5"/>
+    </row>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C187" s="5"/>
+    </row>
+    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C188" s="5"/>
+    </row>
+    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C189" s="5"/>
+    </row>
+    <row r="190" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C190" s="5"/>
+    </row>
+    <row r="191" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C191" s="5"/>
+    </row>
+    <row r="192" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C192" s="5"/>
+    </row>
+    <row r="193" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C193" s="5"/>
+    </row>
+    <row r="194" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C194" s="5"/>
+    </row>
+    <row r="195" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C195" s="5"/>
+    </row>
+    <row r="196" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C196" s="5"/>
+    </row>
+    <row r="197" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C197" s="5"/>
+    </row>
+    <row r="198" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C198" s="5"/>
+    </row>
+    <row r="199" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C199" s="5"/>
+    </row>
+    <row r="200" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C200" s="5"/>
+    </row>
+    <row r="201" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C201" s="5"/>
+    </row>
+    <row r="202" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C202" s="5"/>
+    </row>
+    <row r="203" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C203" s="5"/>
+    </row>
+    <row r="204" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C204" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -3440,31 +2937,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA30E2D-DF5D-404E-ADF3-B4C286568C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FBD95D-6972-4860-A324-E88A8832E401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="126">
   <si>
     <t>Status</t>
   </si>
@@ -48,484 +48,367 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>818560181</t>
+    <t>970653386</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>201607292</t>
-  </si>
-  <si>
-    <t>245970797</t>
-  </si>
-  <si>
-    <t>244294991</t>
-  </si>
-  <si>
-    <t>234867012</t>
-  </si>
-  <si>
-    <t>205907276</t>
-  </si>
-  <si>
-    <t>213667557</t>
-  </si>
-  <si>
-    <t>217935828</t>
-  </si>
-  <si>
-    <t>210466946</t>
-  </si>
-  <si>
-    <t>210466052</t>
-  </si>
-  <si>
-    <t>202155556</t>
-  </si>
-  <si>
-    <t>202134890</t>
-  </si>
-  <si>
-    <t>201184664</t>
-  </si>
-  <si>
-    <t>198878609</t>
-  </si>
-  <si>
-    <t>196008928</t>
-  </si>
-  <si>
-    <t>194892653</t>
-  </si>
-  <si>
-    <t>194731455</t>
-  </si>
-  <si>
-    <t>188831675</t>
-  </si>
-  <si>
-    <t>184975070</t>
-  </si>
-  <si>
-    <t>970485862</t>
-  </si>
-  <si>
-    <t>971904044</t>
-  </si>
-  <si>
-    <t>954206615</t>
-  </si>
-  <si>
-    <t>963520451</t>
-  </si>
-  <si>
-    <t>958330064</t>
-  </si>
-  <si>
-    <t>958984159</t>
-  </si>
-  <si>
-    <t>916960051</t>
-  </si>
-  <si>
-    <t>937282360</t>
-  </si>
-  <si>
-    <t>943476212</t>
-  </si>
-  <si>
-    <t>936884331</t>
-  </si>
-  <si>
-    <t>915327518</t>
-  </si>
-  <si>
-    <t>912536079</t>
-  </si>
-  <si>
-    <t>911781387</t>
-  </si>
-  <si>
-    <t>907645950</t>
-  </si>
-  <si>
-    <t>911688665</t>
-  </si>
-  <si>
-    <t>909021895</t>
-  </si>
-  <si>
-    <t>906781640</t>
-  </si>
-  <si>
-    <t>182663447</t>
-  </si>
-  <si>
-    <t>174369151</t>
-  </si>
-  <si>
-    <t>852861404</t>
-  </si>
-  <si>
-    <t>903442881</t>
-  </si>
-  <si>
-    <t>901225171</t>
-  </si>
-  <si>
-    <t>892347968</t>
-  </si>
-  <si>
-    <t>875439923</t>
-  </si>
-  <si>
-    <t>877534606</t>
-  </si>
-  <si>
-    <t>877038848</t>
-  </si>
-  <si>
-    <t>876453014</t>
-  </si>
-  <si>
-    <t>869801203</t>
-  </si>
-  <si>
-    <t>856969518</t>
-  </si>
-  <si>
-    <t>869362313</t>
-  </si>
-  <si>
-    <t>845457302</t>
-  </si>
-  <si>
-    <t>837192784</t>
-  </si>
-  <si>
-    <t>805027384</t>
-  </si>
-  <si>
-    <t>807972983</t>
-  </si>
-  <si>
-    <t>801568985</t>
-  </si>
-  <si>
-    <t>793747696</t>
-  </si>
-  <si>
-    <t>773257906</t>
-  </si>
-  <si>
-    <t>765692946</t>
-  </si>
-  <si>
-    <t>891518924</t>
+    <t>906283357</t>
+  </si>
+  <si>
+    <t>920240995</t>
+  </si>
+  <si>
+    <t>927354542</t>
+  </si>
+  <si>
+    <t>922583822</t>
+  </si>
+  <si>
+    <t>920080227</t>
+  </si>
+  <si>
+    <t>913083857</t>
+  </si>
+  <si>
+    <t>915745156</t>
+  </si>
+  <si>
+    <t>905838912</t>
+  </si>
+  <si>
+    <t>895358632</t>
+  </si>
+  <si>
+    <t>893615777</t>
+  </si>
+  <si>
+    <t>892949532</t>
+  </si>
+  <si>
+    <t>891519039</t>
+  </si>
+  <si>
+    <t>890720174</t>
+  </si>
+  <si>
+    <t>890578622</t>
+  </si>
+  <si>
+    <t>889523118</t>
+  </si>
+  <si>
+    <t>888910472</t>
+  </si>
+  <si>
+    <t>217673940</t>
+  </si>
+  <si>
+    <t>877921456</t>
+  </si>
+  <si>
+    <t>849950922</t>
+  </si>
+  <si>
+    <t>862862657</t>
+  </si>
+  <si>
+    <t>848906156</t>
+  </si>
+  <si>
+    <t>846067514</t>
+  </si>
+  <si>
+    <t>844932404</t>
+  </si>
+  <si>
+    <t>836427520</t>
+  </si>
+  <si>
+    <t>804869844</t>
+  </si>
+  <si>
+    <t>818767216</t>
+  </si>
+  <si>
+    <t>816003655</t>
+  </si>
+  <si>
+    <t>817578499</t>
+  </si>
+  <si>
+    <t>816669810</t>
+  </si>
+  <si>
+    <t>712101215</t>
+  </si>
+  <si>
+    <t>884004007</t>
+  </si>
+  <si>
+    <t>879094740</t>
+  </si>
+  <si>
+    <t>877936801</t>
+  </si>
+  <si>
+    <t>871015636</t>
+  </si>
+  <si>
+    <t>869834493</t>
+  </si>
+  <si>
+    <t>868733951</t>
+  </si>
+  <si>
+    <t>864015718</t>
+  </si>
+  <si>
+    <t>863180745</t>
+  </si>
+  <si>
+    <t>217673957</t>
+  </si>
+  <si>
+    <t>202173138</t>
+  </si>
+  <si>
+    <t>209674864</t>
+  </si>
+  <si>
+    <t>205036514</t>
+  </si>
+  <si>
+    <t>202136234</t>
+  </si>
+  <si>
+    <t>197431525</t>
+  </si>
+  <si>
+    <t>191275076</t>
+  </si>
+  <si>
+    <t>194519926</t>
+  </si>
+  <si>
+    <t>189810371</t>
+  </si>
+  <si>
+    <t>188382703</t>
+  </si>
+  <si>
+    <t>185895129</t>
+  </si>
+  <si>
+    <t>183452212</t>
+  </si>
+  <si>
+    <t>181396775</t>
+  </si>
+  <si>
+    <t>958950358</t>
+  </si>
+  <si>
+    <t>958950366</t>
+  </si>
+  <si>
+    <t>966236006</t>
+  </si>
+  <si>
+    <t>955186634</t>
+  </si>
+  <si>
+    <t>941324232</t>
+  </si>
+  <si>
+    <t>940857455</t>
+  </si>
+  <si>
+    <t>931153187</t>
+  </si>
+  <si>
+    <t>933318945</t>
+  </si>
+  <si>
+    <t>933228367</t>
+  </si>
+  <si>
+    <t>950172688</t>
+  </si>
+  <si>
+    <t>951047293</t>
+  </si>
+  <si>
+    <t>950245005</t>
+  </si>
+  <si>
+    <t>948628569</t>
+  </si>
+  <si>
+    <t>944452717</t>
+  </si>
+  <si>
+    <t>943704985</t>
+  </si>
+  <si>
+    <t>942806146</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>970975763</t>
-  </si>
-  <si>
-    <t>917672622</t>
-  </si>
-  <si>
-    <t>946321514</t>
-  </si>
-  <si>
-    <t>946311903</t>
-  </si>
-  <si>
-    <t>935309678</t>
-  </si>
-  <si>
-    <t>929099582</t>
-  </si>
-  <si>
-    <t>919763379</t>
-  </si>
-  <si>
-    <t>918246087</t>
-  </si>
-  <si>
-    <t>898095330</t>
-  </si>
-  <si>
-    <t>894905284</t>
-  </si>
-  <si>
-    <t>893204598</t>
-  </si>
-  <si>
-    <t>215565478</t>
-  </si>
-  <si>
-    <t>234946097</t>
-  </si>
-  <si>
-    <t>242389249</t>
-  </si>
-  <si>
-    <t>236184739</t>
-  </si>
-  <si>
-    <t>232373138</t>
-  </si>
-  <si>
-    <t>232487912</t>
-  </si>
-  <si>
-    <t>831727619</t>
-  </si>
-  <si>
-    <t>939276543</t>
-  </si>
-  <si>
-    <t>965808979</t>
-  </si>
-  <si>
-    <t>973971546</t>
-  </si>
-  <si>
-    <t>974642443</t>
-  </si>
-  <si>
-    <t>973921376</t>
-  </si>
-  <si>
-    <t>971483965</t>
-  </si>
-  <si>
-    <t>968838692</t>
-  </si>
-  <si>
-    <t>957279585</t>
-  </si>
-  <si>
-    <t>958450326</t>
-  </si>
-  <si>
-    <t>962726760</t>
-  </si>
-  <si>
-    <t>957694205</t>
-  </si>
-  <si>
-    <t>955293273</t>
-  </si>
-  <si>
-    <t>951562929</t>
-  </si>
-  <si>
-    <t>948064997</t>
-  </si>
-  <si>
-    <t>948950609</t>
-  </si>
-  <si>
-    <t>947313171</t>
-  </si>
-  <si>
-    <t>940724671</t>
-  </si>
-  <si>
-    <t>937708521</t>
-  </si>
-  <si>
-    <t>938833310</t>
-  </si>
-  <si>
-    <t>937931669</t>
-  </si>
-  <si>
-    <t>933285276</t>
-  </si>
-  <si>
-    <t>930490556</t>
-  </si>
-  <si>
-    <t>923071934</t>
-  </si>
-  <si>
-    <t>926949326</t>
-  </si>
-  <si>
-    <t>198517223</t>
-  </si>
-  <si>
-    <t>233511249</t>
-  </si>
-  <si>
-    <t>234095697</t>
-  </si>
-  <si>
-    <t>234095689</t>
-  </si>
-  <si>
-    <t>209819659</t>
-  </si>
-  <si>
-    <t>216443949</t>
-  </si>
-  <si>
-    <t>215037148</t>
-  </si>
-  <si>
-    <t>207830922</t>
-  </si>
-  <si>
-    <t>201839408</t>
-  </si>
-  <si>
-    <t>201440975</t>
-  </si>
-  <si>
-    <t>201440942</t>
-  </si>
-  <si>
-    <t>197232238</t>
-  </si>
-  <si>
-    <t>197957487</t>
-  </si>
-  <si>
-    <t>194862359</t>
-  </si>
-  <si>
-    <t>189550639</t>
-  </si>
-  <si>
-    <t>186093823</t>
-  </si>
-  <si>
-    <t>184782542</t>
-  </si>
-  <si>
-    <t>869397319</t>
-  </si>
-  <si>
-    <t>903678294</t>
-  </si>
-  <si>
-    <t>919758692</t>
-  </si>
-  <si>
-    <t>903348732</t>
-  </si>
-  <si>
-    <t>894896913</t>
-  </si>
-  <si>
-    <t>902096738</t>
-  </si>
-  <si>
-    <t>882356151</t>
-  </si>
-  <si>
-    <t>885098784</t>
-  </si>
-  <si>
-    <t>869630263</t>
-  </si>
-  <si>
-    <t>831320233</t>
-  </si>
-  <si>
-    <t>812066193</t>
-  </si>
-  <si>
-    <t>816546745</t>
-  </si>
-  <si>
-    <t>816337624</t>
-  </si>
-  <si>
-    <t>808648160</t>
-  </si>
-  <si>
-    <t>891090189</t>
-  </si>
-  <si>
-    <t>206040242</t>
-  </si>
-  <si>
-    <t>233598865</t>
-  </si>
-  <si>
-    <t>237298447</t>
-  </si>
-  <si>
-    <t>238536191</t>
-  </si>
-  <si>
-    <t>237916139</t>
-  </si>
-  <si>
-    <t>237553718</t>
-  </si>
-  <si>
-    <t>234668436</t>
-  </si>
-  <si>
-    <t>236739052</t>
-  </si>
-  <si>
-    <t>236826453</t>
-  </si>
-  <si>
-    <t>216599989</t>
-  </si>
-  <si>
-    <t>212787364</t>
-  </si>
-  <si>
-    <t>211045327</t>
-  </si>
-  <si>
-    <t>210388801</t>
-  </si>
-  <si>
-    <t>209116874</t>
-  </si>
-  <si>
-    <t>188107290</t>
-  </si>
-  <si>
-    <t>957532025</t>
-  </si>
-  <si>
-    <t>970856054</t>
-  </si>
-  <si>
-    <t>969532195</t>
-  </si>
-  <si>
-    <t>965339959</t>
-  </si>
-  <si>
-    <t>924979143</t>
-  </si>
-  <si>
-    <t>944883986</t>
-  </si>
-  <si>
-    <t>953872714</t>
-  </si>
-  <si>
-    <t>945218158</t>
-  </si>
-  <si>
-    <t>948029321</t>
-  </si>
-  <si>
-    <t>933595203</t>
-  </si>
-  <si>
-    <t>894438138</t>
+    <t>935174502</t>
+  </si>
+  <si>
+    <t>938166125</t>
+  </si>
+  <si>
+    <t>937513616</t>
+  </si>
+  <si>
+    <t>891148722</t>
+  </si>
+  <si>
+    <t>917576583</t>
+  </si>
+  <si>
+    <t>918836085</t>
+  </si>
+  <si>
+    <t>918813613</t>
+  </si>
+  <si>
+    <t>918793518</t>
+  </si>
+  <si>
+    <t>895283798</t>
+  </si>
+  <si>
+    <t>902746969</t>
+  </si>
+  <si>
+    <t>900963095</t>
+  </si>
+  <si>
+    <t>211122910</t>
+  </si>
+  <si>
+    <t>872162122</t>
+  </si>
+  <si>
+    <t>887217523</t>
+  </si>
+  <si>
+    <t>886409964</t>
+  </si>
+  <si>
+    <t>238710986</t>
+  </si>
+  <si>
+    <t>238454296</t>
+  </si>
+  <si>
+    <t>238178648</t>
+  </si>
+  <si>
+    <t>238136851</t>
+  </si>
+  <si>
+    <t>236608976</t>
+  </si>
+  <si>
+    <t>237794270</t>
+  </si>
+  <si>
+    <t>237761477</t>
+  </si>
+  <si>
+    <t>237136738</t>
+  </si>
+  <si>
+    <t>236984179</t>
+  </si>
+  <si>
+    <t>235472267</t>
+  </si>
+  <si>
+    <t>224482541</t>
+  </si>
+  <si>
+    <t>232740518</t>
+  </si>
+  <si>
+    <t>228267757</t>
+  </si>
+  <si>
+    <t>213582723</t>
+  </si>
+  <si>
+    <t>213231933</t>
+  </si>
+  <si>
+    <t>212105252</t>
+  </si>
+  <si>
+    <t>953666744</t>
+  </si>
+  <si>
+    <t>184070583</t>
+  </si>
+  <si>
+    <t>194328229</t>
+  </si>
+  <si>
+    <t>187307479</t>
+  </si>
+  <si>
+    <t>184861924</t>
+  </si>
+  <si>
+    <t>975085766</t>
+  </si>
+  <si>
+    <t>973317021</t>
+  </si>
+  <si>
+    <t>973897147</t>
+  </si>
+  <si>
+    <t>973764024</t>
+  </si>
+  <si>
+    <t>972805018</t>
+  </si>
+  <si>
+    <t>968477673</t>
+  </si>
+  <si>
+    <t>964575868</t>
+  </si>
+  <si>
+    <t>959744081</t>
+  </si>
+  <si>
+    <t>952108052</t>
+  </si>
+  <si>
+    <t>952012189</t>
+  </si>
+  <si>
+    <t>950034276</t>
+  </si>
+  <si>
+    <t>947868612</t>
+  </si>
+  <si>
+    <t>949058766</t>
+  </si>
+  <si>
+    <t>948808435</t>
+  </si>
+  <si>
+    <t>946780255</t>
   </si>
 </sst>
 </file>
@@ -991,7 +874,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1684,7 +1567,7 @@
         <v>63</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>4</v>
@@ -1692,10 +1575,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>4</v>
@@ -1703,10 +1586,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
@@ -1714,10 +1597,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
@@ -1725,10 +1608,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
@@ -1736,10 +1619,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>4</v>
@@ -1747,10 +1630,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
@@ -1758,10 +1641,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
@@ -1769,10 +1652,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>4</v>
@@ -1780,10 +1663,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>4</v>
@@ -1791,10 +1674,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>4</v>
@@ -1805,7 +1688,7 @@
         <v>75</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>4</v>
@@ -1816,7 +1699,7 @@
         <v>76</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>4</v>
@@ -1827,7 +1710,7 @@
         <v>77</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
@@ -1838,7 +1721,7 @@
         <v>78</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
@@ -1849,7 +1732,7 @@
         <v>79</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
@@ -1860,7 +1743,7 @@
         <v>80</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>4</v>
@@ -1871,7 +1754,7 @@
         <v>81</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>4</v>
@@ -1882,7 +1765,7 @@
         <v>82</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
@@ -1893,7 +1776,7 @@
         <v>83</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>4</v>
@@ -1904,7 +1787,7 @@
         <v>84</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>4</v>
@@ -1915,7 +1798,7 @@
         <v>85</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>4</v>
@@ -1926,7 +1809,7 @@
         <v>86</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>4</v>
@@ -1937,7 +1820,7 @@
         <v>87</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>4</v>
@@ -1948,7 +1831,7 @@
         <v>88</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>4</v>
@@ -1959,7 +1842,7 @@
         <v>89</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
@@ -1970,7 +1853,7 @@
         <v>90</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>4</v>
@@ -1981,7 +1864,7 @@
         <v>91</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
@@ -1992,7 +1875,7 @@
         <v>92</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>4</v>
@@ -2003,7 +1886,7 @@
         <v>93</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>4</v>
@@ -2014,7 +1897,7 @@
         <v>94</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>4</v>
@@ -2025,7 +1908,7 @@
         <v>95</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>4</v>
@@ -2036,7 +1919,7 @@
         <v>96</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>4</v>
@@ -2047,7 +1930,7 @@
         <v>97</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>4</v>
@@ -2058,7 +1941,7 @@
         <v>98</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>4</v>
@@ -2069,7 +1952,7 @@
         <v>99</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>4</v>
@@ -2080,7 +1963,7 @@
         <v>100</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>4</v>
@@ -2091,7 +1974,7 @@
         <v>101</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>4</v>
@@ -2102,7 +1985,7 @@
         <v>102</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>4</v>
@@ -2113,7 +1996,7 @@
         <v>103</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>4</v>
@@ -2124,7 +2007,7 @@
         <v>104</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>4</v>
@@ -2135,7 +2018,7 @@
         <v>105</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>4</v>
@@ -2146,7 +2029,7 @@
         <v>106</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>4</v>
@@ -2157,7 +2040,7 @@
         <v>107</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>4</v>
@@ -2168,7 +2051,7 @@
         <v>108</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>4</v>
@@ -2179,7 +2062,7 @@
         <v>109</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>4</v>
@@ -2190,7 +2073,7 @@
         <v>110</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>4</v>
@@ -2201,7 +2084,7 @@
         <v>111</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>4</v>
@@ -2212,7 +2095,7 @@
         <v>112</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>4</v>
@@ -2223,7 +2106,7 @@
         <v>113</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>4</v>
@@ -2234,7 +2117,7 @@
         <v>114</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>4</v>
@@ -2245,7 +2128,7 @@
         <v>115</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>4</v>
@@ -2256,7 +2139,7 @@
         <v>116</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>4</v>
@@ -2267,7 +2150,7 @@
         <v>117</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>4</v>
@@ -2278,7 +2161,7 @@
         <v>118</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>4</v>
@@ -2289,7 +2172,7 @@
         <v>119</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>4</v>
@@ -2300,7 +2183,7 @@
         <v>120</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>4</v>
@@ -2311,7 +2194,7 @@
         <v>121</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>4</v>
@@ -2322,7 +2205,7 @@
         <v>122</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>4</v>
@@ -2333,7 +2216,7 @@
         <v>123</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>4</v>
@@ -2344,7 +2227,7 @@
         <v>124</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>4</v>
@@ -2355,438 +2238,9 @@
         <v>125</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C159" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FBD95D-6972-4860-A324-E88A8832E401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80E816E-BA47-49AE-A466-914E93C72177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="85">
   <si>
     <t>Status</t>
   </si>
@@ -48,367 +48,244 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>970653386</t>
+    <t>933935862</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>906283357</t>
-  </si>
-  <si>
-    <t>920240995</t>
-  </si>
-  <si>
-    <t>927354542</t>
-  </si>
-  <si>
-    <t>922583822</t>
-  </si>
-  <si>
-    <t>920080227</t>
-  </si>
-  <si>
-    <t>913083857</t>
-  </si>
-  <si>
-    <t>915745156</t>
-  </si>
-  <si>
-    <t>905838912</t>
-  </si>
-  <si>
-    <t>895358632</t>
-  </si>
-  <si>
-    <t>893615777</t>
-  </si>
-  <si>
-    <t>892949532</t>
-  </si>
-  <si>
-    <t>891519039</t>
-  </si>
-  <si>
-    <t>890720174</t>
-  </si>
-  <si>
-    <t>890578622</t>
-  </si>
-  <si>
-    <t>889523118</t>
-  </si>
-  <si>
-    <t>888910472</t>
-  </si>
-  <si>
-    <t>217673940</t>
-  </si>
-  <si>
-    <t>877921456</t>
-  </si>
-  <si>
-    <t>849950922</t>
-  </si>
-  <si>
-    <t>862862657</t>
-  </si>
-  <si>
-    <t>848906156</t>
-  </si>
-  <si>
-    <t>846067514</t>
-  </si>
-  <si>
-    <t>844932404</t>
-  </si>
-  <si>
-    <t>836427520</t>
-  </si>
-  <si>
-    <t>804869844</t>
-  </si>
-  <si>
-    <t>818767216</t>
-  </si>
-  <si>
-    <t>816003655</t>
-  </si>
-  <si>
-    <t>817578499</t>
-  </si>
-  <si>
-    <t>816669810</t>
-  </si>
-  <si>
-    <t>712101215</t>
-  </si>
-  <si>
-    <t>884004007</t>
-  </si>
-  <si>
-    <t>879094740</t>
-  </si>
-  <si>
-    <t>877936801</t>
-  </si>
-  <si>
-    <t>871015636</t>
-  </si>
-  <si>
-    <t>869834493</t>
-  </si>
-  <si>
-    <t>868733951</t>
-  </si>
-  <si>
-    <t>864015718</t>
-  </si>
-  <si>
-    <t>863180745</t>
-  </si>
-  <si>
-    <t>217673957</t>
-  </si>
-  <si>
-    <t>202173138</t>
-  </si>
-  <si>
-    <t>209674864</t>
-  </si>
-  <si>
-    <t>205036514</t>
-  </si>
-  <si>
-    <t>202136234</t>
-  </si>
-  <si>
-    <t>197431525</t>
-  </si>
-  <si>
-    <t>191275076</t>
-  </si>
-  <si>
-    <t>194519926</t>
-  </si>
-  <si>
-    <t>189810371</t>
-  </si>
-  <si>
-    <t>188382703</t>
-  </si>
-  <si>
-    <t>185895129</t>
-  </si>
-  <si>
-    <t>183452212</t>
-  </si>
-  <si>
-    <t>181396775</t>
-  </si>
-  <si>
-    <t>958950358</t>
-  </si>
-  <si>
-    <t>958950366</t>
-  </si>
-  <si>
-    <t>966236006</t>
-  </si>
-  <si>
-    <t>955186634</t>
-  </si>
-  <si>
-    <t>941324232</t>
-  </si>
-  <si>
-    <t>940857455</t>
-  </si>
-  <si>
-    <t>931153187</t>
-  </si>
-  <si>
-    <t>933318945</t>
-  </si>
-  <si>
-    <t>933228367</t>
-  </si>
-  <si>
-    <t>950172688</t>
-  </si>
-  <si>
-    <t>951047293</t>
-  </si>
-  <si>
-    <t>950245005</t>
-  </si>
-  <si>
-    <t>948628569</t>
-  </si>
-  <si>
-    <t>944452717</t>
-  </si>
-  <si>
-    <t>943704985</t>
-  </si>
-  <si>
-    <t>942806146</t>
+    <t>817552874</t>
+  </si>
+  <si>
+    <t>862071044</t>
+  </si>
+  <si>
+    <t>861737397</t>
+  </si>
+  <si>
+    <t>859696027</t>
+  </si>
+  <si>
+    <t>848229286</t>
+  </si>
+  <si>
+    <t>857434850</t>
+  </si>
+  <si>
+    <t>848780296</t>
+  </si>
+  <si>
+    <t>810454805</t>
+  </si>
+  <si>
+    <t>957570181</t>
+  </si>
+  <si>
+    <t>960870867</t>
+  </si>
+  <si>
+    <t>963947274</t>
+  </si>
+  <si>
+    <t>953663519</t>
+  </si>
+  <si>
+    <t>946863911</t>
+  </si>
+  <si>
+    <t>939503318</t>
+  </si>
+  <si>
+    <t>940136785</t>
+  </si>
+  <si>
+    <t>793514989</t>
+  </si>
+  <si>
+    <t>803672017</t>
+  </si>
+  <si>
+    <t>206203964</t>
+  </si>
+  <si>
+    <t>207244801</t>
+  </si>
+  <si>
+    <t>187328368</t>
+  </si>
+  <si>
+    <t>964297133</t>
+  </si>
+  <si>
+    <t>973899531</t>
+  </si>
+  <si>
+    <t>199848353</t>
+  </si>
+  <si>
+    <t>201125980</t>
+  </si>
+  <si>
+    <t>203575059</t>
+  </si>
+  <si>
+    <t>200493421</t>
+  </si>
+  <si>
+    <t>197771128</t>
+  </si>
+  <si>
+    <t>192646259</t>
+  </si>
+  <si>
+    <t>193092248</t>
+  </si>
+  <si>
+    <t>189490554</t>
+  </si>
+  <si>
+    <t>186910216</t>
+  </si>
+  <si>
+    <t>179452838</t>
+  </si>
+  <si>
+    <t>180890562</t>
+  </si>
+  <si>
+    <t>179731678</t>
+  </si>
+  <si>
+    <t>895719221</t>
+  </si>
+  <si>
+    <t>881289122</t>
+  </si>
+  <si>
+    <t>889185157</t>
+  </si>
+  <si>
+    <t>893867659</t>
+  </si>
+  <si>
+    <t>894566672</t>
+  </si>
+  <si>
+    <t>892099924</t>
+  </si>
+  <si>
+    <t>891637567</t>
+  </si>
+  <si>
+    <t>890829165</t>
+  </si>
+  <si>
+    <t>865141075</t>
+  </si>
+  <si>
+    <t>871152116</t>
+  </si>
+  <si>
+    <t>872085885</t>
+  </si>
+  <si>
+    <t>865321339</t>
+  </si>
+  <si>
+    <t>934027313</t>
+  </si>
+  <si>
+    <t>934350012</t>
+  </si>
+  <si>
+    <t>934152343</t>
+  </si>
+  <si>
+    <t>925881785</t>
+  </si>
+  <si>
+    <t>927603278</t>
+  </si>
+  <si>
+    <t>920688953</t>
+  </si>
+  <si>
+    <t>921115220</t>
+  </si>
+  <si>
+    <t>924428091</t>
+  </si>
+  <si>
+    <t>920072521</t>
+  </si>
+  <si>
+    <t>919777114</t>
+  </si>
+  <si>
+    <t>905765776</t>
+  </si>
+  <si>
+    <t>910861420</t>
+  </si>
+  <si>
+    <t>239555653</t>
+  </si>
+  <si>
+    <t>773014356</t>
+  </si>
+  <si>
+    <t>763110750</t>
+  </si>
+  <si>
+    <t>237717578</t>
+  </si>
+  <si>
+    <t>245755479</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>935174502</t>
-  </si>
-  <si>
-    <t>938166125</t>
-  </si>
-  <si>
-    <t>937513616</t>
-  </si>
-  <si>
-    <t>891148722</t>
-  </si>
-  <si>
-    <t>917576583</t>
-  </si>
-  <si>
-    <t>918836085</t>
-  </si>
-  <si>
-    <t>918813613</t>
-  </si>
-  <si>
-    <t>918793518</t>
-  </si>
-  <si>
-    <t>895283798</t>
-  </si>
-  <si>
-    <t>902746969</t>
-  </si>
-  <si>
-    <t>900963095</t>
-  </si>
-  <si>
-    <t>211122910</t>
-  </si>
-  <si>
-    <t>872162122</t>
-  </si>
-  <si>
-    <t>887217523</t>
-  </si>
-  <si>
-    <t>886409964</t>
-  </si>
-  <si>
-    <t>238710986</t>
-  </si>
-  <si>
-    <t>238454296</t>
-  </si>
-  <si>
-    <t>238178648</t>
-  </si>
-  <si>
-    <t>238136851</t>
-  </si>
-  <si>
-    <t>236608976</t>
-  </si>
-  <si>
-    <t>237794270</t>
-  </si>
-  <si>
-    <t>237761477</t>
-  </si>
-  <si>
-    <t>237136738</t>
-  </si>
-  <si>
-    <t>236984179</t>
-  </si>
-  <si>
-    <t>235472267</t>
-  </si>
-  <si>
-    <t>224482541</t>
-  </si>
-  <si>
-    <t>232740518</t>
-  </si>
-  <si>
-    <t>228267757</t>
-  </si>
-  <si>
-    <t>213582723</t>
-  </si>
-  <si>
-    <t>213231933</t>
-  </si>
-  <si>
-    <t>212105252</t>
-  </si>
-  <si>
-    <t>953666744</t>
-  </si>
-  <si>
-    <t>184070583</t>
-  </si>
-  <si>
-    <t>194328229</t>
-  </si>
-  <si>
-    <t>187307479</t>
-  </si>
-  <si>
-    <t>184861924</t>
-  </si>
-  <si>
-    <t>975085766</t>
-  </si>
-  <si>
-    <t>973317021</t>
-  </si>
-  <si>
-    <t>973897147</t>
-  </si>
-  <si>
-    <t>973764024</t>
-  </si>
-  <si>
-    <t>972805018</t>
-  </si>
-  <si>
-    <t>968477673</t>
-  </si>
-  <si>
-    <t>964575868</t>
-  </si>
-  <si>
-    <t>959744081</t>
-  </si>
-  <si>
-    <t>952108052</t>
-  </si>
-  <si>
-    <t>952012189</t>
-  </si>
-  <si>
-    <t>950034276</t>
-  </si>
-  <si>
-    <t>947868612</t>
-  </si>
-  <si>
-    <t>949058766</t>
-  </si>
-  <si>
-    <t>948808435</t>
-  </si>
-  <si>
-    <t>946780255</t>
+    <t>207430160</t>
+  </si>
+  <si>
+    <t>889537019</t>
+  </si>
+  <si>
+    <t>887192395</t>
+  </si>
+  <si>
+    <t>886364359</t>
+  </si>
+  <si>
+    <t>885628309</t>
+  </si>
+  <si>
+    <t>903365850</t>
+  </si>
+  <si>
+    <t>944074412</t>
+  </si>
+  <si>
+    <t>959950498</t>
+  </si>
+  <si>
+    <t>181651468</t>
+  </si>
+  <si>
+    <t>191358724</t>
+  </si>
+  <si>
+    <t>200677825</t>
+  </si>
+  <si>
+    <t>193404831</t>
+  </si>
+  <si>
+    <t>925080792</t>
+  </si>
+  <si>
+    <t>213303690</t>
   </si>
 </sst>
 </file>
@@ -874,7 +751,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1633,7 +1510,7 @@
         <v>69</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
@@ -1641,10 +1518,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
@@ -1652,10 +1529,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>4</v>
@@ -1663,10 +1540,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>4</v>
@@ -1674,10 +1551,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>4</v>
@@ -1688,7 +1565,7 @@
         <v>75</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>4</v>
@@ -1699,7 +1576,7 @@
         <v>76</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>4</v>
@@ -1710,7 +1587,7 @@
         <v>77</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
@@ -1721,7 +1598,7 @@
         <v>78</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
@@ -1732,7 +1609,7 @@
         <v>79</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
@@ -1743,7 +1620,7 @@
         <v>80</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>4</v>
@@ -1754,7 +1631,7 @@
         <v>81</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>4</v>
@@ -1765,7 +1642,7 @@
         <v>82</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
@@ -1776,7 +1653,7 @@
         <v>83</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>4</v>
@@ -1787,460 +1664,9 @@
         <v>84</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C120" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80E816E-BA47-49AE-A466-914E93C72177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4639D234-58A0-4DA0-9EA3-E8D36CFDDB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="135">
   <si>
     <t>Status</t>
   </si>
@@ -48,244 +48,394 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>933935862</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>817552874</t>
-  </si>
-  <si>
-    <t>862071044</t>
-  </si>
-  <si>
-    <t>861737397</t>
-  </si>
-  <si>
-    <t>859696027</t>
-  </si>
-  <si>
-    <t>848229286</t>
-  </si>
-  <si>
-    <t>857434850</t>
-  </si>
-  <si>
-    <t>848780296</t>
-  </si>
-  <si>
-    <t>810454805</t>
-  </si>
-  <si>
-    <t>957570181</t>
-  </si>
-  <si>
-    <t>960870867</t>
-  </si>
-  <si>
-    <t>963947274</t>
-  </si>
-  <si>
-    <t>953663519</t>
-  </si>
-  <si>
-    <t>946863911</t>
-  </si>
-  <si>
-    <t>939503318</t>
-  </si>
-  <si>
-    <t>940136785</t>
-  </si>
-  <si>
-    <t>793514989</t>
-  </si>
-  <si>
-    <t>803672017</t>
-  </si>
-  <si>
-    <t>206203964</t>
-  </si>
-  <si>
-    <t>207244801</t>
-  </si>
-  <si>
-    <t>187328368</t>
-  </si>
-  <si>
-    <t>964297133</t>
-  </si>
-  <si>
-    <t>973899531</t>
-  </si>
-  <si>
-    <t>199848353</t>
-  </si>
-  <si>
-    <t>201125980</t>
-  </si>
-  <si>
-    <t>203575059</t>
-  </si>
-  <si>
-    <t>200493421</t>
-  </si>
-  <si>
-    <t>197771128</t>
-  </si>
-  <si>
-    <t>192646259</t>
-  </si>
-  <si>
-    <t>193092248</t>
-  </si>
-  <si>
-    <t>189490554</t>
-  </si>
-  <si>
-    <t>186910216</t>
-  </si>
-  <si>
-    <t>179452838</t>
-  </si>
-  <si>
-    <t>180890562</t>
-  </si>
-  <si>
-    <t>179731678</t>
-  </si>
-  <si>
-    <t>895719221</t>
-  </si>
-  <si>
-    <t>881289122</t>
-  </si>
-  <si>
-    <t>889185157</t>
-  </si>
-  <si>
-    <t>893867659</t>
-  </si>
-  <si>
-    <t>894566672</t>
-  </si>
-  <si>
-    <t>892099924</t>
-  </si>
-  <si>
-    <t>891637567</t>
-  </si>
-  <si>
-    <t>890829165</t>
-  </si>
-  <si>
-    <t>865141075</t>
-  </si>
-  <si>
-    <t>871152116</t>
-  </si>
-  <si>
-    <t>872085885</t>
-  </si>
-  <si>
-    <t>865321339</t>
-  </si>
-  <si>
-    <t>934027313</t>
-  </si>
-  <si>
-    <t>934350012</t>
-  </si>
-  <si>
-    <t>934152343</t>
-  </si>
-  <si>
-    <t>925881785</t>
-  </si>
-  <si>
-    <t>927603278</t>
-  </si>
-  <si>
-    <t>920688953</t>
-  </si>
-  <si>
-    <t>921115220</t>
-  </si>
-  <si>
-    <t>924428091</t>
-  </si>
-  <si>
-    <t>920072521</t>
-  </si>
-  <si>
-    <t>919777114</t>
-  </si>
-  <si>
-    <t>905765776</t>
-  </si>
-  <si>
-    <t>910861420</t>
-  </si>
-  <si>
-    <t>239555653</t>
-  </si>
-  <si>
-    <t>773014356</t>
-  </si>
-  <si>
-    <t>763110750</t>
-  </si>
-  <si>
-    <t>237717578</t>
-  </si>
-  <si>
-    <t>245755479</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>207430160</t>
-  </si>
-  <si>
-    <t>889537019</t>
-  </si>
-  <si>
-    <t>887192395</t>
-  </si>
-  <si>
-    <t>886364359</t>
-  </si>
-  <si>
-    <t>885628309</t>
-  </si>
-  <si>
-    <t>903365850</t>
-  </si>
-  <si>
-    <t>944074412</t>
-  </si>
-  <si>
-    <t>959950498</t>
-  </si>
-  <si>
-    <t>181651468</t>
-  </si>
-  <si>
-    <t>191358724</t>
-  </si>
-  <si>
-    <t>200677825</t>
-  </si>
-  <si>
-    <t>193404831</t>
-  </si>
-  <si>
-    <t>925080792</t>
-  </si>
-  <si>
-    <t>213303690</t>
+    <t>801445721</t>
+  </si>
+  <si>
+    <t>861182396</t>
+  </si>
+  <si>
+    <t>880221076</t>
+  </si>
+  <si>
+    <t>883806386</t>
+  </si>
+  <si>
+    <t>880284512</t>
+  </si>
+  <si>
+    <t>879227571</t>
+  </si>
+  <si>
+    <t>879071896</t>
+  </si>
+  <si>
+    <t>874511458</t>
+  </si>
+  <si>
+    <t>875138053</t>
+  </si>
+  <si>
+    <t>877302863</t>
+  </si>
+  <si>
+    <t>867221909</t>
+  </si>
+  <si>
+    <t>870255993</t>
+  </si>
+  <si>
+    <t>870485426</t>
+  </si>
+  <si>
+    <t>870292467</t>
+  </si>
+  <si>
+    <t>867651097</t>
+  </si>
+  <si>
+    <t>865968865</t>
+  </si>
+  <si>
+    <t>860751555</t>
+  </si>
+  <si>
+    <t>859735643</t>
+  </si>
+  <si>
+    <t>852636244</t>
+  </si>
+  <si>
+    <t>851757868</t>
+  </si>
+  <si>
+    <t>844921050</t>
+  </si>
+  <si>
+    <t>850490818</t>
+  </si>
+  <si>
+    <t>849983592</t>
+  </si>
+  <si>
+    <t>846637316</t>
+  </si>
+  <si>
+    <t>846143992</t>
+  </si>
+  <si>
+    <t>841974128</t>
+  </si>
+  <si>
+    <t>218917858</t>
+  </si>
+  <si>
+    <t>207171707</t>
+  </si>
+  <si>
+    <t>948579580</t>
+  </si>
+  <si>
+    <t>202268797</t>
+  </si>
+  <si>
+    <t>200016792</t>
+  </si>
+  <si>
+    <t>185947425</t>
+  </si>
+  <si>
+    <t>195817378</t>
+  </si>
+  <si>
+    <t>196978104</t>
+  </si>
+  <si>
+    <t>193063843</t>
+  </si>
+  <si>
+    <t>188127546</t>
+  </si>
+  <si>
+    <t>186935734</t>
+  </si>
+  <si>
+    <t>186932343</t>
+  </si>
+  <si>
+    <t>185345117</t>
+  </si>
+  <si>
+    <t>203099027</t>
+  </si>
+  <si>
+    <t>203973874</t>
+  </si>
+  <si>
+    <t>203622802</t>
+  </si>
+  <si>
+    <t>203436716</t>
+  </si>
+  <si>
+    <t>202593046</t>
+  </si>
+  <si>
+    <t>972779478</t>
+  </si>
+  <si>
+    <t>175853948</t>
+  </si>
+  <si>
+    <t>182822969</t>
+  </si>
+  <si>
+    <t>183091721</t>
+  </si>
+  <si>
+    <t>178703546</t>
+  </si>
+  <si>
+    <t>181310883</t>
+  </si>
+  <si>
+    <t>179643527</t>
+  </si>
+  <si>
+    <t>175443864</t>
+  </si>
+  <si>
+    <t>972567535</t>
+  </si>
+  <si>
+    <t>955795707</t>
+  </si>
+  <si>
+    <t>962808295</t>
+  </si>
+  <si>
+    <t>960437113</t>
+  </si>
+  <si>
+    <t>957920857</t>
+  </si>
+  <si>
+    <t>957867991</t>
+  </si>
+  <si>
+    <t>957530409</t>
+  </si>
+  <si>
+    <t>954485821</t>
+  </si>
+  <si>
+    <t>953665258</t>
+  </si>
+  <si>
+    <t>952758021</t>
+  </si>
+  <si>
+    <t>950360598</t>
+  </si>
+  <si>
+    <t>951491467</t>
+  </si>
+  <si>
+    <t>951275480</t>
+  </si>
+  <si>
+    <t>949550234</t>
+  </si>
+  <si>
+    <t>948646017</t>
+  </si>
+  <si>
+    <t>948644731</t>
+  </si>
+  <si>
+    <t>944144959</t>
+  </si>
+  <si>
+    <t>946222530</t>
+  </si>
+  <si>
+    <t>937282436</t>
+  </si>
+  <si>
+    <t>920705757</t>
+  </si>
+  <si>
+    <t>923018190</t>
+  </si>
+  <si>
+    <t>929002289</t>
+  </si>
+  <si>
+    <t>924970399</t>
+  </si>
+  <si>
+    <t>918548227</t>
+  </si>
+  <si>
+    <t>918228689</t>
+  </si>
+  <si>
+    <t>917263059</t>
+  </si>
+  <si>
+    <t>912628223</t>
+  </si>
+  <si>
+    <t>912563834</t>
+  </si>
+  <si>
+    <t>908078367</t>
+  </si>
+  <si>
+    <t>905169953</t>
+  </si>
+  <si>
+    <t>902075864</t>
+  </si>
+  <si>
+    <t>903616781</t>
+  </si>
+  <si>
+    <t>902947799</t>
+  </si>
+  <si>
+    <t>899752285</t>
+  </si>
+  <si>
+    <t>892920541</t>
+  </si>
+  <si>
+    <t>895870511</t>
+  </si>
+  <si>
+    <t>891173027</t>
+  </si>
+  <si>
+    <t>889084186</t>
+  </si>
+  <si>
+    <t>910108186</t>
+  </si>
+  <si>
+    <t>911394181</t>
+  </si>
+  <si>
+    <t>912322892</t>
+  </si>
+  <si>
+    <t>911972663</t>
+  </si>
+  <si>
+    <t>906057785</t>
+  </si>
+  <si>
+    <t>940677846</t>
+  </si>
+  <si>
+    <t>942082003</t>
+  </si>
+  <si>
+    <t>934867064</t>
+  </si>
+  <si>
+    <t>934172085</t>
+  </si>
+  <si>
+    <t>228139949</t>
+  </si>
+  <si>
+    <t>813320649</t>
+  </si>
+  <si>
+    <t>819696778</t>
+  </si>
+  <si>
+    <t>818963328</t>
+  </si>
+  <si>
+    <t>813088451</t>
+  </si>
+  <si>
+    <t>791603727</t>
+  </si>
+  <si>
+    <t>777167077</t>
+  </si>
+  <si>
+    <t>773510999</t>
+  </si>
+  <si>
+    <t>250692807</t>
+  </si>
+  <si>
+    <t>869052344</t>
+  </si>
+  <si>
+    <t>878359466</t>
+  </si>
+  <si>
+    <t>928223449</t>
+  </si>
+  <si>
+    <t>931368785</t>
+  </si>
+  <si>
+    <t>946891268</t>
+  </si>
+  <si>
+    <t>201020520</t>
+  </si>
+  <si>
+    <t>186227371</t>
+  </si>
+  <si>
+    <t>188391167</t>
+  </si>
+  <si>
+    <t>974613592</t>
+  </si>
+  <si>
+    <t>969597396</t>
+  </si>
+  <si>
+    <t>957495553</t>
+  </si>
+  <si>
+    <t>953180092</t>
+  </si>
+  <si>
+    <t>244542662</t>
+  </si>
+  <si>
+    <t>245097187</t>
+  </si>
+  <si>
+    <t>240990717</t>
+  </si>
+  <si>
+    <t>229299239</t>
+  </si>
+  <si>
+    <t>218129249</t>
+  </si>
+  <si>
+    <t>221568250</t>
+  </si>
+  <si>
+    <t>206750139</t>
+  </si>
+  <si>
+    <t>211227248</t>
   </si>
 </sst>
 </file>
@@ -751,7 +901,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -777,10 +927,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -789,10 +939,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>4</v>
@@ -801,10 +951,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -813,10 +963,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -825,10 +975,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -837,10 +987,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
@@ -849,10 +999,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
@@ -861,10 +1011,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -873,10 +1023,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -885,10 +1035,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
@@ -897,10 +1047,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -909,10 +1059,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -921,10 +1071,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -933,10 +1083,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -945,10 +1095,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -957,10 +1107,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -969,10 +1119,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -981,10 +1131,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -993,10 +1143,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -1005,10 +1155,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -1017,10 +1167,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -1029,10 +1179,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -1041,10 +1191,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -1053,10 +1203,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -1065,10 +1215,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -1077,10 +1227,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1089,10 +1239,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1101,10 +1251,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
@@ -1113,10 +1263,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1125,10 +1275,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
@@ -1137,10 +1287,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
@@ -1149,10 +1299,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
@@ -1161,10 +1311,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1173,10 +1323,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
@@ -1185,10 +1335,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
@@ -1197,10 +1347,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
@@ -1209,10 +1359,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1221,10 +1371,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
@@ -1232,10 +1382,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
@@ -1243,10 +1393,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
@@ -1254,10 +1404,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>4</v>
@@ -1265,10 +1415,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
@@ -1276,10 +1426,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
@@ -1287,10 +1437,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
@@ -1298,10 +1448,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
@@ -1309,10 +1459,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>4</v>
@@ -1320,10 +1470,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>4</v>
@@ -1331,10 +1481,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>4</v>
@@ -1342,10 +1492,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>4</v>
@@ -1353,10 +1503,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>4</v>
@@ -1364,10 +1514,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>4</v>
@@ -1375,10 +1525,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>4</v>
@@ -1386,10 +1536,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
@@ -1397,10 +1547,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>4</v>
@@ -1408,10 +1558,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>4</v>
@@ -1419,10 +1569,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>4</v>
@@ -1430,10 +1580,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>4</v>
@@ -1441,10 +1591,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>4</v>
@@ -1452,10 +1602,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>4</v>
@@ -1463,10 +1613,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
@@ -1474,10 +1624,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
@@ -1485,10 +1635,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
@@ -1496,177 +1646,730 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1693,31 +2396,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3523C178-6792-432F-88DE-DA61BB0BFE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B5CE44-3E44-4A1B-9287-6DC8192F99AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="151">
   <si>
     <t>Status</t>
   </si>
@@ -48,700 +48,442 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>211638188</t>
+    <t>870002791</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>229999648</t>
-  </si>
-  <si>
-    <t>233458581</t>
-  </si>
-  <si>
-    <t>234558280</t>
-  </si>
-  <si>
-    <t>234558215</t>
-  </si>
-  <si>
-    <t>233704562</t>
-  </si>
-  <si>
-    <t>219519240</t>
-  </si>
-  <si>
-    <t>224147946</t>
-  </si>
-  <si>
-    <t>213559861</t>
-  </si>
-  <si>
-    <t>205642220</t>
-  </si>
-  <si>
-    <t>860891518</t>
-  </si>
-  <si>
-    <t>860734296</t>
-  </si>
-  <si>
-    <t>860552748</t>
-  </si>
-  <si>
-    <t>852412489</t>
-  </si>
-  <si>
-    <t>853040248</t>
-  </si>
-  <si>
-    <t>854798034</t>
-  </si>
-  <si>
-    <t>849949874</t>
-  </si>
-  <si>
-    <t>841094992</t>
-  </si>
-  <si>
-    <t>849073840</t>
-  </si>
-  <si>
-    <t>845939549</t>
-  </si>
-  <si>
-    <t>845720691</t>
-  </si>
-  <si>
-    <t>842975348</t>
-  </si>
-  <si>
-    <t>836869325</t>
-  </si>
-  <si>
-    <t>838204877</t>
-  </si>
-  <si>
-    <t>837985708</t>
-  </si>
-  <si>
-    <t>919260301</t>
-  </si>
-  <si>
-    <t>869738207</t>
-  </si>
-  <si>
-    <t>886010598</t>
-  </si>
-  <si>
-    <t>900092259</t>
-  </si>
-  <si>
-    <t>896505595</t>
-  </si>
-  <si>
-    <t>891866000</t>
-  </si>
-  <si>
-    <t>891150652</t>
-  </si>
-  <si>
-    <t>876021407</t>
-  </si>
-  <si>
-    <t>879803272</t>
-  </si>
-  <si>
-    <t>885248769</t>
-  </si>
-  <si>
-    <t>862870965</t>
-  </si>
-  <si>
-    <t>865866432</t>
-  </si>
-  <si>
-    <t>864039015</t>
-  </si>
-  <si>
-    <t>920125279</t>
-  </si>
-  <si>
-    <t>920069154</t>
-  </si>
-  <si>
-    <t>917943288</t>
-  </si>
-  <si>
-    <t>904243130</t>
-  </si>
-  <si>
-    <t>909480489</t>
-  </si>
-  <si>
-    <t>909439527</t>
-  </si>
-  <si>
-    <t>906575695</t>
-  </si>
-  <si>
-    <t>905629253</t>
-  </si>
-  <si>
-    <t>903213969</t>
-  </si>
-  <si>
-    <t>902577257</t>
-  </si>
-  <si>
-    <t>900860986</t>
-  </si>
-  <si>
-    <t>957868213</t>
-  </si>
-  <si>
-    <t>926961008</t>
-  </si>
-  <si>
-    <t>936443385</t>
-  </si>
-  <si>
-    <t>940573227</t>
-  </si>
-  <si>
-    <t>938216581</t>
-  </si>
-  <si>
-    <t>934511399</t>
-  </si>
-  <si>
-    <t>933098430</t>
-  </si>
-  <si>
-    <t>930493832</t>
-  </si>
-  <si>
-    <t>928343262</t>
-  </si>
-  <si>
-    <t>928042948</t>
-  </si>
-  <si>
-    <t>927975965</t>
-  </si>
-  <si>
-    <t>927752497</t>
-  </si>
-  <si>
-    <t>927354872</t>
-  </si>
-  <si>
-    <t>927253397</t>
-  </si>
-  <si>
-    <t>925091773</t>
-  </si>
-  <si>
-    <t>924430071</t>
-  </si>
-  <si>
-    <t>922381680</t>
-  </si>
-  <si>
-    <t>921881359</t>
-  </si>
-  <si>
-    <t>921368712</t>
-  </si>
-  <si>
-    <t>965293404</t>
-  </si>
-  <si>
-    <t>969714595</t>
-  </si>
-  <si>
-    <t>968629786</t>
-  </si>
-  <si>
-    <t>960204679</t>
-  </si>
-  <si>
-    <t>945147811</t>
-  </si>
-  <si>
-    <t>955931013</t>
-  </si>
-  <si>
-    <t>956985125</t>
-  </si>
-  <si>
-    <t>956982791</t>
-  </si>
-  <si>
-    <t>951698251</t>
-  </si>
-  <si>
-    <t>951053333</t>
-  </si>
-  <si>
-    <t>949294759</t>
-  </si>
-  <si>
-    <t>949292472</t>
-  </si>
-  <si>
-    <t>945514218</t>
-  </si>
-  <si>
-    <t>944469463</t>
-  </si>
-  <si>
-    <t>205118528</t>
-  </si>
-  <si>
-    <t>196169993</t>
-  </si>
-  <si>
-    <t>199645114</t>
-  </si>
-  <si>
-    <t>203544931</t>
-  </si>
-  <si>
-    <t>204068039</t>
-  </si>
-  <si>
-    <t>197685948</t>
-  </si>
-  <si>
-    <t>197425451</t>
-  </si>
-  <si>
-    <t>196993160</t>
-  </si>
-  <si>
-    <t>196232361</t>
-  </si>
-  <si>
-    <t>195335462</t>
-  </si>
-  <si>
-    <t>194679787</t>
-  </si>
-  <si>
-    <t>194391037</t>
-  </si>
-  <si>
-    <t>190487516</t>
-  </si>
-  <si>
-    <t>975016266</t>
-  </si>
-  <si>
-    <t>974418364</t>
-  </si>
-  <si>
-    <t>192930414</t>
-  </si>
-  <si>
-    <t>187054048</t>
-  </si>
-  <si>
-    <t>186117739</t>
-  </si>
-  <si>
-    <t>184865198</t>
-  </si>
-  <si>
-    <t>184322018</t>
-  </si>
-  <si>
-    <t>183393457</t>
-  </si>
-  <si>
-    <t>181848858</t>
-  </si>
-  <si>
-    <t>183111073</t>
-  </si>
-  <si>
-    <t>182821219</t>
-  </si>
-  <si>
-    <t>179068394</t>
-  </si>
-  <si>
-    <t>178622340</t>
-  </si>
-  <si>
-    <t>176318529</t>
-  </si>
-  <si>
-    <t>175087158</t>
-  </si>
-  <si>
-    <t>824583144</t>
-  </si>
-  <si>
-    <t>821315565</t>
-  </si>
-  <si>
-    <t>808917482</t>
-  </si>
-  <si>
-    <t>816373991</t>
-  </si>
-  <si>
-    <t>797756982</t>
-  </si>
-  <si>
-    <t>797545450</t>
-  </si>
-  <si>
-    <t>796317232</t>
-  </si>
-  <si>
-    <t>794797922</t>
-  </si>
-  <si>
-    <t>779477474</t>
-  </si>
-  <si>
-    <t>789256736</t>
-  </si>
-  <si>
-    <t>251246348</t>
-  </si>
-  <si>
-    <t>230875761</t>
+    <t>961734096</t>
+  </si>
+  <si>
+    <t>932455417</t>
+  </si>
+  <si>
+    <t>945805814</t>
+  </si>
+  <si>
+    <t>940876489</t>
+  </si>
+  <si>
+    <t>941388286</t>
+  </si>
+  <si>
+    <t>940804978</t>
+  </si>
+  <si>
+    <t>940534336</t>
+  </si>
+  <si>
+    <t>940349891</t>
+  </si>
+  <si>
+    <t>931165827</t>
+  </si>
+  <si>
+    <t>208261713</t>
+  </si>
+  <si>
+    <t>203094820</t>
+  </si>
+  <si>
+    <t>204042885</t>
+  </si>
+  <si>
+    <t>201768359</t>
+  </si>
+  <si>
+    <t>202097857</t>
+  </si>
+  <si>
+    <t>200362881</t>
+  </si>
+  <si>
+    <t>199033899</t>
+  </si>
+  <si>
+    <t>198692414</t>
+  </si>
+  <si>
+    <t>197326295</t>
+  </si>
+  <si>
+    <t>197031911</t>
+  </si>
+  <si>
+    <t>196967487</t>
+  </si>
+  <si>
+    <t>195672419</t>
+  </si>
+  <si>
+    <t>969526874</t>
+  </si>
+  <si>
+    <t>191393606</t>
+  </si>
+  <si>
+    <t>182793566</t>
+  </si>
+  <si>
+    <t>182066468</t>
+  </si>
+  <si>
+    <t>965715190</t>
+  </si>
+  <si>
+    <t>961588005</t>
+  </si>
+  <si>
+    <t>958084851</t>
+  </si>
+  <si>
+    <t>961065137</t>
+  </si>
+  <si>
+    <t>960266306</t>
+  </si>
+  <si>
+    <t>950888853</t>
+  </si>
+  <si>
+    <t>956431260</t>
+  </si>
+  <si>
+    <t>952449456</t>
+  </si>
+  <si>
+    <t>240046288</t>
+  </si>
+  <si>
+    <t>227375148</t>
+  </si>
+  <si>
+    <t>895400681</t>
+  </si>
+  <si>
+    <t>913280966</t>
+  </si>
+  <si>
+    <t>915993731</t>
+  </si>
+  <si>
+    <t>901486575</t>
+  </si>
+  <si>
+    <t>900201272</t>
+  </si>
+  <si>
+    <t>899428159</t>
+  </si>
+  <si>
+    <t>899127868</t>
+  </si>
+  <si>
+    <t>895946048</t>
+  </si>
+  <si>
+    <t>896692971</t>
+  </si>
+  <si>
+    <t>893561898</t>
+  </si>
+  <si>
+    <t>884101126</t>
+  </si>
+  <si>
+    <t>887623084</t>
+  </si>
+  <si>
+    <t>889827923</t>
+  </si>
+  <si>
+    <t>891135877</t>
+  </si>
+  <si>
+    <t>881914943</t>
+  </si>
+  <si>
+    <t>881255305</t>
+  </si>
+  <si>
+    <t>881246361</t>
+  </si>
+  <si>
+    <t>877294896</t>
+  </si>
+  <si>
+    <t>873669034</t>
+  </si>
+  <si>
+    <t>871750745</t>
+  </si>
+  <si>
+    <t>861179822</t>
+  </si>
+  <si>
+    <t>866769791</t>
+  </si>
+  <si>
+    <t>865008704</t>
+  </si>
+  <si>
+    <t>864441468</t>
+  </si>
+  <si>
+    <t>813512385</t>
+  </si>
+  <si>
+    <t>822948448</t>
+  </si>
+  <si>
+    <t>853810921</t>
+  </si>
+  <si>
+    <t>844136774</t>
+  </si>
+  <si>
+    <t>838752982</t>
+  </si>
+  <si>
+    <t>828726913</t>
+  </si>
+  <si>
+    <t>821105818</t>
+  </si>
+  <si>
+    <t>820828253</t>
+  </si>
+  <si>
+    <t>804866477</t>
+  </si>
+  <si>
+    <t>800165437</t>
+  </si>
+  <si>
+    <t>803626070</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>906837186</t>
-  </si>
-  <si>
-    <t>889887448</t>
-  </si>
-  <si>
-    <t>193892456</t>
-  </si>
-  <si>
-    <t>213832078</t>
-  </si>
-  <si>
-    <t>222898706</t>
-  </si>
-  <si>
-    <t>221309143</t>
-  </si>
-  <si>
-    <t>200937161</t>
-  </si>
-  <si>
-    <t>186990465</t>
-  </si>
-  <si>
-    <t>938823733</t>
-  </si>
-  <si>
-    <t>950110191</t>
-  </si>
-  <si>
-    <t>192190597</t>
-  </si>
-  <si>
-    <t>186591990</t>
-  </si>
-  <si>
-    <t>186243055</t>
-  </si>
-  <si>
-    <t>938471814</t>
-  </si>
-  <si>
-    <t>207804836</t>
-  </si>
-  <si>
-    <t>235055328</t>
-  </si>
-  <si>
-    <t>222151528</t>
-  </si>
-  <si>
-    <t>227366576</t>
-  </si>
-  <si>
-    <t>228957282</t>
-  </si>
-  <si>
-    <t>209893332</t>
-  </si>
-  <si>
-    <t>209297922</t>
-  </si>
-  <si>
-    <t>195681477</t>
-  </si>
-  <si>
-    <t>201012139</t>
-  </si>
-  <si>
-    <t>197638210</t>
-  </si>
-  <si>
-    <t>197338050</t>
-  </si>
-  <si>
-    <t>195883511</t>
-  </si>
-  <si>
-    <t>194862540</t>
-  </si>
-  <si>
-    <t>188937985</t>
-  </si>
-  <si>
-    <t>187747583</t>
-  </si>
-  <si>
-    <t>944749898</t>
-  </si>
-  <si>
-    <t>179850064</t>
-  </si>
-  <si>
-    <t>183859499</t>
-  </si>
-  <si>
-    <t>182571830</t>
-  </si>
-  <si>
-    <t>181528690</t>
-  </si>
-  <si>
-    <t>969496565</t>
-  </si>
-  <si>
-    <t>972244630</t>
-  </si>
-  <si>
-    <t>965716990</t>
-  </si>
-  <si>
-    <t>961245648</t>
-  </si>
-  <si>
-    <t>958245254</t>
-  </si>
-  <si>
-    <t>959778030</t>
-  </si>
-  <si>
-    <t>959594346</t>
-  </si>
-  <si>
-    <t>953326133</t>
-  </si>
-  <si>
-    <t>951620503</t>
-  </si>
-  <si>
-    <t>947825885</t>
-  </si>
-  <si>
-    <t>942430970</t>
-  </si>
-  <si>
-    <t>935217111</t>
-  </si>
-  <si>
-    <t>905456558</t>
-  </si>
-  <si>
-    <t>911652539</t>
-  </si>
-  <si>
-    <t>916588696</t>
-  </si>
-  <si>
-    <t>905302299</t>
-  </si>
-  <si>
-    <t>905260463</t>
-  </si>
-  <si>
-    <t>897467886</t>
-  </si>
-  <si>
-    <t>896401597</t>
-  </si>
-  <si>
-    <t>889481614</t>
-  </si>
-  <si>
-    <t>811019334</t>
-  </si>
-  <si>
-    <t>845225824</t>
-  </si>
-  <si>
-    <t>887645301</t>
-  </si>
-  <si>
-    <t>889157966</t>
-  </si>
-  <si>
-    <t>887615536</t>
-  </si>
-  <si>
-    <t>884401849</t>
-  </si>
-  <si>
-    <t>877938690</t>
-  </si>
-  <si>
-    <t>875167433</t>
-  </si>
-  <si>
-    <t>874511763</t>
-  </si>
-  <si>
-    <t>869705305</t>
-  </si>
-  <si>
-    <t>864353945</t>
-  </si>
-  <si>
-    <t>863038257</t>
-  </si>
-  <si>
-    <t>857943314</t>
-  </si>
-  <si>
-    <t>852158405</t>
-  </si>
-  <si>
-    <t>851010912</t>
-  </si>
-  <si>
-    <t>850058755</t>
-  </si>
-  <si>
-    <t>849939446</t>
-  </si>
-  <si>
-    <t>849653179</t>
-  </si>
-  <si>
-    <t>848924134</t>
-  </si>
-  <si>
-    <t>846574345</t>
-  </si>
-  <si>
-    <t>845857634</t>
-  </si>
-  <si>
-    <t>820943516</t>
-  </si>
-  <si>
-    <t>829365067</t>
-  </si>
-  <si>
-    <t>839147075</t>
-  </si>
-  <si>
-    <t>835801212</t>
-  </si>
-  <si>
-    <t>827829551</t>
-  </si>
-  <si>
-    <t>823304369</t>
-  </si>
-  <si>
-    <t>822008730</t>
-  </si>
-  <si>
-    <t>821113887</t>
-  </si>
-  <si>
-    <t>818014973</t>
-  </si>
-  <si>
-    <t>803749518</t>
-  </si>
-  <si>
-    <t>801330139</t>
-  </si>
-  <si>
-    <t>789864232</t>
-  </si>
-  <si>
-    <t>778431043</t>
-  </si>
-  <si>
-    <t>901293922</t>
-  </si>
-  <si>
-    <t>192587925</t>
-  </si>
-  <si>
-    <t>218004483</t>
-  </si>
-  <si>
-    <t>246412732</t>
-  </si>
-  <si>
-    <t>241777543</t>
-  </si>
-  <si>
-    <t>244671438</t>
-  </si>
-  <si>
-    <t>243927880</t>
-  </si>
-  <si>
-    <t>242837627</t>
-  </si>
-  <si>
-    <t>237809599</t>
-  </si>
-  <si>
-    <t>210896548</t>
-  </si>
-  <si>
-    <t>213047560</t>
-  </si>
-  <si>
-    <t>217715873</t>
-  </si>
-  <si>
-    <t>214130514</t>
-  </si>
-  <si>
-    <t>212720597</t>
-  </si>
-  <si>
-    <t>197779220</t>
-  </si>
-  <si>
-    <t>201179599</t>
-  </si>
-  <si>
-    <t>950693873</t>
-  </si>
-  <si>
-    <t>975714274</t>
-  </si>
-  <si>
-    <t>916455201</t>
-  </si>
-  <si>
-    <t>912629361</t>
+    <t>749162321</t>
+  </si>
+  <si>
+    <t>242373854</t>
+  </si>
+  <si>
+    <t>244588970</t>
+  </si>
+  <si>
+    <t>246173854</t>
+  </si>
+  <si>
+    <t>245095298</t>
+  </si>
+  <si>
+    <t>244175117</t>
+  </si>
+  <si>
+    <t>244065557</t>
+  </si>
+  <si>
+    <t>244037143</t>
+  </si>
+  <si>
+    <t>244005611</t>
+  </si>
+  <si>
+    <t>243964776</t>
+  </si>
+  <si>
+    <t>243949538</t>
+  </si>
+  <si>
+    <t>241400088</t>
+  </si>
+  <si>
+    <t>222117594</t>
+  </si>
+  <si>
+    <t>212418937</t>
+  </si>
+  <si>
+    <t>196111664</t>
+  </si>
+  <si>
+    <t>203258078</t>
+  </si>
+  <si>
+    <t>209337389</t>
+  </si>
+  <si>
+    <t>206509097</t>
+  </si>
+  <si>
+    <t>202659680</t>
+  </si>
+  <si>
+    <t>198731428</t>
+  </si>
+  <si>
+    <t>202031534</t>
+  </si>
+  <si>
+    <t>195935006</t>
+  </si>
+  <si>
+    <t>952019150</t>
+  </si>
+  <si>
+    <t>935000012</t>
+  </si>
+  <si>
+    <t>936253552</t>
+  </si>
+  <si>
+    <t>944158660</t>
+  </si>
+  <si>
+    <t>946610015</t>
+  </si>
+  <si>
+    <t>934634837</t>
+  </si>
+  <si>
+    <t>934177688</t>
+  </si>
+  <si>
+    <t>928042104</t>
+  </si>
+  <si>
+    <t>927519128</t>
+  </si>
+  <si>
+    <t>927483713</t>
+  </si>
+  <si>
+    <t>924796448</t>
+  </si>
+  <si>
+    <t>970047290</t>
+  </si>
+  <si>
+    <t>191150600</t>
+  </si>
+  <si>
+    <t>191513906</t>
+  </si>
+  <si>
+    <t>192082240</t>
+  </si>
+  <si>
+    <t>190907018</t>
+  </si>
+  <si>
+    <t>187308592</t>
+  </si>
+  <si>
+    <t>188631489</t>
+  </si>
+  <si>
+    <t>186173567</t>
+  </si>
+  <si>
+    <t>974242137</t>
+  </si>
+  <si>
+    <t>975447156</t>
+  </si>
+  <si>
+    <t>973108131</t>
+  </si>
+  <si>
+    <t>968818066</t>
+  </si>
+  <si>
+    <t>966972667</t>
+  </si>
+  <si>
+    <t>960084436</t>
+  </si>
+  <si>
+    <t>965352630</t>
+  </si>
+  <si>
+    <t>965351756</t>
+  </si>
+  <si>
+    <t>960028474</t>
+  </si>
+  <si>
+    <t>960021230</t>
+  </si>
+  <si>
+    <t>953902826</t>
+  </si>
+  <si>
+    <t>953666595</t>
+  </si>
+  <si>
+    <t>950362750</t>
+  </si>
+  <si>
+    <t>951950033</t>
+  </si>
+  <si>
+    <t>237207729</t>
+  </si>
+  <si>
+    <t>234024986</t>
+  </si>
+  <si>
+    <t>215733092</t>
+  </si>
+  <si>
+    <t>221251964</t>
+  </si>
+  <si>
+    <t>220963106</t>
+  </si>
+  <si>
+    <t>215017587</t>
+  </si>
+  <si>
+    <t>875115960</t>
+  </si>
+  <si>
+    <t>897188805</t>
+  </si>
+  <si>
+    <t>918477880</t>
+  </si>
+  <si>
+    <t>923126803</t>
+  </si>
+  <si>
+    <t>919739064</t>
+  </si>
+  <si>
+    <t>909811501</t>
+  </si>
+  <si>
+    <t>906744283</t>
+  </si>
+  <si>
+    <t>897193086</t>
+  </si>
+  <si>
+    <t>900581095</t>
+  </si>
+  <si>
+    <t>900473079</t>
+  </si>
+  <si>
+    <t>883848396</t>
+  </si>
+  <si>
+    <t>884885280</t>
   </si>
 </sst>
 </file>
@@ -1207,7 +949,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -2043,7 +1785,7 @@
         <v>76</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
@@ -2051,10 +1793,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
@@ -2062,10 +1804,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
@@ -2073,10 +1815,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>4</v>
@@ -2084,10 +1826,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>4</v>
@@ -2095,10 +1837,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
@@ -2106,10 +1848,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>4</v>
@@ -2117,10 +1859,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>4</v>
@@ -2128,10 +1870,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>4</v>
@@ -2139,10 +1881,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>4</v>
@@ -2150,10 +1892,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>4</v>
@@ -2161,10 +1903,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>4</v>
@@ -2172,10 +1914,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
@@ -2183,10 +1925,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>4</v>
@@ -2194,10 +1936,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
@@ -2205,10 +1947,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>4</v>
@@ -2216,10 +1958,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>4</v>
@@ -2227,10 +1969,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>4</v>
@@ -2238,10 +1980,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>4</v>
@@ -2249,10 +1991,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>4</v>
@@ -2260,10 +2002,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>4</v>
@@ -2271,10 +2013,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>4</v>
@@ -2282,10 +2024,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>4</v>
@@ -2293,10 +2035,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>4</v>
@@ -2304,10 +2046,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>4</v>
@@ -2315,10 +2057,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>4</v>
@@ -2326,10 +2068,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>4</v>
@@ -2337,10 +2079,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>4</v>
@@ -2348,10 +2090,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>4</v>
@@ -2359,10 +2101,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>4</v>
@@ -2370,10 +2112,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>4</v>
@@ -2381,10 +2123,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>4</v>
@@ -2392,10 +2134,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>4</v>
@@ -2403,10 +2145,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>4</v>
@@ -2414,10 +2156,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>4</v>
@@ -2425,10 +2167,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>4</v>
@@ -2436,10 +2178,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>4</v>
@@ -2447,10 +2189,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>4</v>
@@ -2458,10 +2200,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>4</v>
@@ -2469,10 +2211,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>4</v>
@@ -2480,10 +2222,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>4</v>
@@ -2491,10 +2233,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>4</v>
@@ -2502,10 +2244,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>4</v>
@@ -2513,10 +2255,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>4</v>
@@ -2524,10 +2266,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>4</v>
@@ -2535,10 +2277,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>4</v>
@@ -2546,10 +2288,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>4</v>
@@ -2557,10 +2299,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>4</v>
@@ -2568,10 +2310,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>4</v>
@@ -2579,10 +2321,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>4</v>
@@ -2590,10 +2332,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>4</v>
@@ -2601,10 +2343,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>4</v>
@@ -2615,7 +2357,7 @@
         <v>129</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>4</v>
@@ -2626,7 +2368,7 @@
         <v>130</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>4</v>
@@ -2637,7 +2379,7 @@
         <v>131</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>4</v>
@@ -2648,7 +2390,7 @@
         <v>132</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>4</v>
@@ -2659,7 +2401,7 @@
         <v>133</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>4</v>
@@ -2670,7 +2412,7 @@
         <v>134</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>4</v>
@@ -2681,7 +2423,7 @@
         <v>135</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>4</v>
@@ -2692,7 +2434,7 @@
         <v>136</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>4</v>
@@ -2703,7 +2445,7 @@
         <v>137</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>4</v>
@@ -2714,7 +2456,7 @@
         <v>138</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>4</v>
@@ -2725,7 +2467,7 @@
         <v>139</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>4</v>
@@ -2736,7 +2478,7 @@
         <v>140</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>4</v>
@@ -2747,7 +2489,7 @@
         <v>141</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>4</v>
@@ -2758,7 +2500,7 @@
         <v>142</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>4</v>
@@ -2769,7 +2511,7 @@
         <v>143</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>4</v>
@@ -2780,7 +2522,7 @@
         <v>144</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>4</v>
@@ -2791,7 +2533,7 @@
         <v>145</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>4</v>
@@ -2802,7 +2544,7 @@
         <v>146</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>4</v>
@@ -2813,7 +2555,7 @@
         <v>147</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>4</v>
@@ -2824,7 +2566,7 @@
         <v>148</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>4</v>
@@ -2835,7 +2577,7 @@
         <v>149</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>4</v>
@@ -2846,955 +2588,9 @@
         <v>150</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B178" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B180" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B186" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B187" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B188" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B190" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B191" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B192" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B193" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B200" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B201" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B202" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C202" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B205" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B206" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B207" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B208" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B209" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B210" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C210" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B211" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B212" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C212" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B213" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B214" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C214" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B215" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B216" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C216" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C217" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B218" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C218" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B219" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B220" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C220" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B221" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C221" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B222" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B223" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B224" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B225" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B226" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C226" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B227" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C228" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B229" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B230" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B231" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C231" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B5CE44-3E44-4A1B-9287-6DC8192F99AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609F0500-27FB-4B59-8ED9-0AED6B3AED25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="140">
   <si>
     <t>Status</t>
   </si>
@@ -48,442 +48,409 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>870002791</t>
+    <t>943226690</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>961734096</t>
-  </si>
-  <si>
-    <t>932455417</t>
-  </si>
-  <si>
-    <t>945805814</t>
-  </si>
-  <si>
-    <t>940876489</t>
-  </si>
-  <si>
-    <t>941388286</t>
-  </si>
-  <si>
-    <t>940804978</t>
-  </si>
-  <si>
-    <t>940534336</t>
-  </si>
-  <si>
-    <t>940349891</t>
-  </si>
-  <si>
-    <t>931165827</t>
-  </si>
-  <si>
-    <t>208261713</t>
-  </si>
-  <si>
-    <t>203094820</t>
-  </si>
-  <si>
-    <t>204042885</t>
-  </si>
-  <si>
-    <t>201768359</t>
-  </si>
-  <si>
-    <t>202097857</t>
-  </si>
-  <si>
-    <t>200362881</t>
-  </si>
-  <si>
-    <t>199033899</t>
-  </si>
-  <si>
-    <t>198692414</t>
-  </si>
-  <si>
-    <t>197326295</t>
-  </si>
-  <si>
-    <t>197031911</t>
-  </si>
-  <si>
-    <t>196967487</t>
-  </si>
-  <si>
-    <t>195672419</t>
-  </si>
-  <si>
-    <t>969526874</t>
-  </si>
-  <si>
-    <t>191393606</t>
-  </si>
-  <si>
-    <t>182793566</t>
-  </si>
-  <si>
-    <t>182066468</t>
-  </si>
-  <si>
-    <t>965715190</t>
-  </si>
-  <si>
-    <t>961588005</t>
-  </si>
-  <si>
-    <t>958084851</t>
-  </si>
-  <si>
-    <t>961065137</t>
-  </si>
-  <si>
-    <t>960266306</t>
-  </si>
-  <si>
-    <t>950888853</t>
-  </si>
-  <si>
-    <t>956431260</t>
-  </si>
-  <si>
-    <t>952449456</t>
-  </si>
-  <si>
-    <t>240046288</t>
-  </si>
-  <si>
-    <t>227375148</t>
-  </si>
-  <si>
-    <t>895400681</t>
-  </si>
-  <si>
-    <t>913280966</t>
-  </si>
-  <si>
-    <t>915993731</t>
-  </si>
-  <si>
-    <t>901486575</t>
-  </si>
-  <si>
-    <t>900201272</t>
-  </si>
-  <si>
-    <t>899428159</t>
-  </si>
-  <si>
-    <t>899127868</t>
-  </si>
-  <si>
-    <t>895946048</t>
-  </si>
-  <si>
-    <t>896692971</t>
-  </si>
-  <si>
-    <t>893561898</t>
-  </si>
-  <si>
-    <t>884101126</t>
-  </si>
-  <si>
-    <t>887623084</t>
-  </si>
-  <si>
-    <t>889827923</t>
-  </si>
-  <si>
-    <t>891135877</t>
-  </si>
-  <si>
-    <t>881914943</t>
-  </si>
-  <si>
-    <t>881255305</t>
-  </si>
-  <si>
-    <t>881246361</t>
-  </si>
-  <si>
-    <t>877294896</t>
-  </si>
-  <si>
-    <t>873669034</t>
-  </si>
-  <si>
-    <t>871750745</t>
-  </si>
-  <si>
-    <t>861179822</t>
-  </si>
-  <si>
-    <t>866769791</t>
-  </si>
-  <si>
-    <t>865008704</t>
-  </si>
-  <si>
-    <t>864441468</t>
-  </si>
-  <si>
-    <t>813512385</t>
-  </si>
-  <si>
-    <t>822948448</t>
-  </si>
-  <si>
-    <t>853810921</t>
-  </si>
-  <si>
-    <t>844136774</t>
-  </si>
-  <si>
-    <t>838752982</t>
-  </si>
-  <si>
-    <t>828726913</t>
-  </si>
-  <si>
-    <t>821105818</t>
-  </si>
-  <si>
-    <t>820828253</t>
-  </si>
-  <si>
-    <t>804866477</t>
-  </si>
-  <si>
-    <t>800165437</t>
-  </si>
-  <si>
-    <t>803626070</t>
+    <t>945267353</t>
+  </si>
+  <si>
+    <t>951547607</t>
+  </si>
+  <si>
+    <t>951881998</t>
+  </si>
+  <si>
+    <t>951578354</t>
+  </si>
+  <si>
+    <t>945414617</t>
+  </si>
+  <si>
+    <t>194083386</t>
+  </si>
+  <si>
+    <t>204608792</t>
+  </si>
+  <si>
+    <t>206197760</t>
+  </si>
+  <si>
+    <t>208136881</t>
+  </si>
+  <si>
+    <t>213188943</t>
+  </si>
+  <si>
+    <t>213084761</t>
+  </si>
+  <si>
+    <t>207391198</t>
+  </si>
+  <si>
+    <t>207316534</t>
+  </si>
+  <si>
+    <t>204210771</t>
+  </si>
+  <si>
+    <t>202567370</t>
+  </si>
+  <si>
+    <t>201991852</t>
+  </si>
+  <si>
+    <t>200772170</t>
+  </si>
+  <si>
+    <t>197973666</t>
+  </si>
+  <si>
+    <t>198148318</t>
+  </si>
+  <si>
+    <t>197037579</t>
+  </si>
+  <si>
+    <t>196760460</t>
+  </si>
+  <si>
+    <t>194914499</t>
+  </si>
+  <si>
+    <t>194649913</t>
+  </si>
+  <si>
+    <t>192166548</t>
+  </si>
+  <si>
+    <t>191838071</t>
+  </si>
+  <si>
+    <t>189099157</t>
+  </si>
+  <si>
+    <t>185691197</t>
+  </si>
+  <si>
+    <t>183493901</t>
+  </si>
+  <si>
+    <t>177942160</t>
+  </si>
+  <si>
+    <t>974500682</t>
+  </si>
+  <si>
+    <t>972168730</t>
+  </si>
+  <si>
+    <t>971869452</t>
+  </si>
+  <si>
+    <t>970291997</t>
+  </si>
+  <si>
+    <t>968604714</t>
+  </si>
+  <si>
+    <t>962747717</t>
+  </si>
+  <si>
+    <t>962324319</t>
+  </si>
+  <si>
+    <t>962101881</t>
+  </si>
+  <si>
+    <t>961865270</t>
+  </si>
+  <si>
+    <t>958236758</t>
+  </si>
+  <si>
+    <t>956663292</t>
+  </si>
+  <si>
+    <t>954617951</t>
+  </si>
+  <si>
+    <t>953485905</t>
+  </si>
+  <si>
+    <t>183313422</t>
+  </si>
+  <si>
+    <t>942525753</t>
+  </si>
+  <si>
+    <t>942065222</t>
+  </si>
+  <si>
+    <t>940878220</t>
+  </si>
+  <si>
+    <t>931955888</t>
+  </si>
+  <si>
+    <t>938794488</t>
+  </si>
+  <si>
+    <t>937711954</t>
+  </si>
+  <si>
+    <t>936913742</t>
+  </si>
+  <si>
+    <t>931023158</t>
+  </si>
+  <si>
+    <t>926052485</t>
+  </si>
+  <si>
+    <t>928495492</t>
+  </si>
+  <si>
+    <t>928488885</t>
+  </si>
+  <si>
+    <t>924606241</t>
+  </si>
+  <si>
+    <t>924311966</t>
+  </si>
+  <si>
+    <t>902167380</t>
+  </si>
+  <si>
+    <t>856147669</t>
+  </si>
+  <si>
+    <t>862634668</t>
+  </si>
+  <si>
+    <t>862632688</t>
+  </si>
+  <si>
+    <t>862630484</t>
+  </si>
+  <si>
+    <t>862625831</t>
+  </si>
+  <si>
+    <t>862614496</t>
+  </si>
+  <si>
+    <t>862605387</t>
+  </si>
+  <si>
+    <t>862595810</t>
+  </si>
+  <si>
+    <t>862592601</t>
+  </si>
+  <si>
+    <t>862586702</t>
+  </si>
+  <si>
+    <t>862581539</t>
+  </si>
+  <si>
+    <t>862567330</t>
+  </si>
+  <si>
+    <t>862554023</t>
+  </si>
+  <si>
+    <t>861384836</t>
+  </si>
+  <si>
+    <t>860966997</t>
+  </si>
+  <si>
+    <t>855090282</t>
+  </si>
+  <si>
+    <t>220895985</t>
+  </si>
+  <si>
+    <t>775988086</t>
+  </si>
+  <si>
+    <t>814190983</t>
+  </si>
+  <si>
+    <t>844584668</t>
+  </si>
+  <si>
+    <t>853061939</t>
+  </si>
+  <si>
+    <t>844922397</t>
+  </si>
+  <si>
+    <t>837829237</t>
+  </si>
+  <si>
+    <t>828462956</t>
+  </si>
+  <si>
+    <t>826880761</t>
+  </si>
+  <si>
+    <t>824505873</t>
+  </si>
+  <si>
+    <t>824021871</t>
+  </si>
+  <si>
+    <t>823851336</t>
+  </si>
+  <si>
+    <t>815445501</t>
+  </si>
+  <si>
+    <t>791566395</t>
+  </si>
+  <si>
+    <t>782526028</t>
+  </si>
+  <si>
+    <t>241855562</t>
+  </si>
+  <si>
+    <t>221726007</t>
+  </si>
+  <si>
+    <t>233942881</t>
+  </si>
+  <si>
+    <t>233781149</t>
+  </si>
+  <si>
+    <t>220621274</t>
+  </si>
+  <si>
+    <t>217935836</t>
+  </si>
+  <si>
+    <t>217183833</t>
+  </si>
+  <si>
+    <t>216214621</t>
+  </si>
+  <si>
+    <t>215531033</t>
+  </si>
+  <si>
+    <t>913206813</t>
+  </si>
+  <si>
+    <t>917103875</t>
+  </si>
+  <si>
+    <t>923610590</t>
+  </si>
+  <si>
+    <t>915494334</t>
+  </si>
+  <si>
+    <t>910396088</t>
+  </si>
+  <si>
+    <t>908851144</t>
+  </si>
+  <si>
+    <t>908474657</t>
+  </si>
+  <si>
+    <t>907947372</t>
+  </si>
+  <si>
+    <t>892329016</t>
+  </si>
+  <si>
+    <t>891887113</t>
+  </si>
+  <si>
+    <t>889895557</t>
+  </si>
+  <si>
+    <t>889090415</t>
+  </si>
+  <si>
+    <t>876544465</t>
+  </si>
+  <si>
+    <t>885069488</t>
+  </si>
+  <si>
+    <t>876912886</t>
+  </si>
+  <si>
+    <t>873674463</t>
+  </si>
+  <si>
+    <t>875287371</t>
+  </si>
+  <si>
+    <t>874170917</t>
+  </si>
+  <si>
+    <t>872717438</t>
+  </si>
+  <si>
+    <t>869312151</t>
+  </si>
+  <si>
+    <t>868417423</t>
+  </si>
+  <si>
+    <t>884053228</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>749162321</t>
-  </si>
-  <si>
-    <t>242373854</t>
-  </si>
-  <si>
-    <t>244588970</t>
-  </si>
-  <si>
-    <t>246173854</t>
-  </si>
-  <si>
-    <t>245095298</t>
-  </si>
-  <si>
-    <t>244175117</t>
-  </si>
-  <si>
-    <t>244065557</t>
-  </si>
-  <si>
-    <t>244037143</t>
-  </si>
-  <si>
-    <t>244005611</t>
-  </si>
-  <si>
-    <t>243964776</t>
-  </si>
-  <si>
-    <t>243949538</t>
-  </si>
-  <si>
-    <t>241400088</t>
-  </si>
-  <si>
-    <t>222117594</t>
-  </si>
-  <si>
-    <t>212418937</t>
-  </si>
-  <si>
-    <t>196111664</t>
-  </si>
-  <si>
-    <t>203258078</t>
-  </si>
-  <si>
-    <t>209337389</t>
-  </si>
-  <si>
-    <t>206509097</t>
-  </si>
-  <si>
-    <t>202659680</t>
-  </si>
-  <si>
-    <t>198731428</t>
-  </si>
-  <si>
-    <t>202031534</t>
-  </si>
-  <si>
-    <t>195935006</t>
-  </si>
-  <si>
-    <t>952019150</t>
-  </si>
-  <si>
-    <t>935000012</t>
-  </si>
-  <si>
-    <t>936253552</t>
-  </si>
-  <si>
-    <t>944158660</t>
-  </si>
-  <si>
-    <t>946610015</t>
-  </si>
-  <si>
-    <t>934634837</t>
-  </si>
-  <si>
-    <t>934177688</t>
-  </si>
-  <si>
-    <t>928042104</t>
-  </si>
-  <si>
-    <t>927519128</t>
-  </si>
-  <si>
-    <t>927483713</t>
-  </si>
-  <si>
-    <t>924796448</t>
-  </si>
-  <si>
-    <t>970047290</t>
-  </si>
-  <si>
-    <t>191150600</t>
-  </si>
-  <si>
-    <t>191513906</t>
-  </si>
-  <si>
-    <t>192082240</t>
-  </si>
-  <si>
-    <t>190907018</t>
-  </si>
-  <si>
-    <t>187308592</t>
-  </si>
-  <si>
-    <t>188631489</t>
-  </si>
-  <si>
-    <t>186173567</t>
-  </si>
-  <si>
-    <t>974242137</t>
-  </si>
-  <si>
-    <t>975447156</t>
-  </si>
-  <si>
-    <t>973108131</t>
-  </si>
-  <si>
-    <t>968818066</t>
-  </si>
-  <si>
-    <t>966972667</t>
-  </si>
-  <si>
-    <t>960084436</t>
-  </si>
-  <si>
-    <t>965352630</t>
-  </si>
-  <si>
-    <t>965351756</t>
-  </si>
-  <si>
-    <t>960028474</t>
-  </si>
-  <si>
-    <t>960021230</t>
-  </si>
-  <si>
-    <t>953902826</t>
-  </si>
-  <si>
-    <t>953666595</t>
-  </si>
-  <si>
-    <t>950362750</t>
-  </si>
-  <si>
-    <t>951950033</t>
-  </si>
-  <si>
-    <t>237207729</t>
-  </si>
-  <si>
-    <t>234024986</t>
-  </si>
-  <si>
-    <t>215733092</t>
-  </si>
-  <si>
-    <t>221251964</t>
-  </si>
-  <si>
-    <t>220963106</t>
-  </si>
-  <si>
-    <t>215017587</t>
-  </si>
-  <si>
-    <t>875115960</t>
-  </si>
-  <si>
-    <t>897188805</t>
-  </si>
-  <si>
-    <t>918477880</t>
-  </si>
-  <si>
-    <t>923126803</t>
-  </si>
-  <si>
-    <t>919739064</t>
-  </si>
-  <si>
-    <t>909811501</t>
-  </si>
-  <si>
-    <t>906744283</t>
-  </si>
-  <si>
-    <t>897193086</t>
-  </si>
-  <si>
-    <t>900581095</t>
-  </si>
-  <si>
-    <t>900473079</t>
-  </si>
-  <si>
-    <t>883848396</t>
-  </si>
-  <si>
-    <t>884885280</t>
+    <t>218270266</t>
+  </si>
+  <si>
+    <t>834118378</t>
+  </si>
+  <si>
+    <t>221847720</t>
+  </si>
+  <si>
+    <t>222189593</t>
+  </si>
+  <si>
+    <t>926705801</t>
+  </si>
+  <si>
+    <t>976361851</t>
+  </si>
+  <si>
+    <t>976361133</t>
+  </si>
+  <si>
+    <t>976361125</t>
+  </si>
+  <si>
+    <t>954496646</t>
+  </si>
+  <si>
+    <t>963113653</t>
+  </si>
+  <si>
+    <t>189498409</t>
+  </si>
+  <si>
+    <t>202828335</t>
+  </si>
+  <si>
+    <t>885253488</t>
   </si>
 </sst>
 </file>
@@ -949,7 +916,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1785,7 +1752,7 @@
         <v>76</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
@@ -1793,10 +1760,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
@@ -1804,10 +1771,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
@@ -1815,10 +1782,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>4</v>
@@ -1826,10 +1793,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>4</v>
@@ -1837,10 +1804,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
@@ -1848,10 +1815,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>4</v>
@@ -1859,10 +1826,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>4</v>
@@ -1870,10 +1837,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>4</v>
@@ -1881,10 +1848,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>4</v>
@@ -1892,10 +1859,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>4</v>
@@ -1903,10 +1870,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>4</v>
@@ -1914,10 +1881,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
@@ -1925,10 +1892,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>4</v>
@@ -1936,10 +1903,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
@@ -1947,10 +1914,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>4</v>
@@ -1958,10 +1925,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>4</v>
@@ -1969,10 +1936,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>4</v>
@@ -1980,10 +1947,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>4</v>
@@ -1991,10 +1958,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>4</v>
@@ -2002,10 +1969,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>4</v>
@@ -2013,10 +1980,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>4</v>
@@ -2024,10 +1991,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>4</v>
@@ -2035,10 +2002,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>4</v>
@@ -2046,10 +2013,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>4</v>
@@ -2057,10 +2024,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>4</v>
@@ -2068,10 +2035,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>4</v>
@@ -2079,10 +2046,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>4</v>
@@ -2090,10 +2057,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>4</v>
@@ -2101,10 +2068,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>4</v>
@@ -2112,10 +2079,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>4</v>
@@ -2123,10 +2090,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>4</v>
@@ -2134,10 +2101,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>4</v>
@@ -2145,10 +2112,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>4</v>
@@ -2156,10 +2123,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>4</v>
@@ -2167,10 +2134,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>4</v>
@@ -2178,10 +2145,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>4</v>
@@ -2189,10 +2156,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>4</v>
@@ -2200,10 +2167,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>4</v>
@@ -2211,10 +2178,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>4</v>
@@ -2222,10 +2189,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>4</v>
@@ -2233,10 +2200,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>4</v>
@@ -2244,10 +2211,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>4</v>
@@ -2255,10 +2222,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>4</v>
@@ -2266,10 +2233,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>4</v>
@@ -2277,10 +2244,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>4</v>
@@ -2288,10 +2255,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>4</v>
@@ -2299,10 +2266,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>4</v>
@@ -2310,10 +2277,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>4</v>
@@ -2321,10 +2288,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B121" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>4</v>
@@ -2335,7 +2302,7 @@
         <v>127</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>4</v>
@@ -2346,7 +2313,7 @@
         <v>128</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>4</v>
@@ -2357,7 +2324,7 @@
         <v>129</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>4</v>
@@ -2368,7 +2335,7 @@
         <v>130</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>4</v>
@@ -2379,7 +2346,7 @@
         <v>131</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>4</v>
@@ -2390,7 +2357,7 @@
         <v>132</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>4</v>
@@ -2401,7 +2368,7 @@
         <v>133</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>4</v>
@@ -2412,7 +2379,7 @@
         <v>134</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>4</v>
@@ -2423,7 +2390,7 @@
         <v>135</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>4</v>
@@ -2434,7 +2401,7 @@
         <v>136</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>4</v>
@@ -2445,7 +2412,7 @@
         <v>137</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>4</v>
@@ -2456,7 +2423,7 @@
         <v>138</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>4</v>
@@ -2467,130 +2434,9 @@
         <v>139</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C145" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609F0500-27FB-4B59-8ED9-0AED6B3AED25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665A6304-D569-44CA-9C46-65F922B0E675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="98">
   <si>
     <t>Status</t>
   </si>
@@ -48,409 +48,283 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>943226690</t>
+    <t>864695808</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>945267353</t>
-  </si>
-  <si>
-    <t>951547607</t>
-  </si>
-  <si>
-    <t>951881998</t>
-  </si>
-  <si>
-    <t>951578354</t>
-  </si>
-  <si>
-    <t>945414617</t>
-  </si>
-  <si>
-    <t>194083386</t>
-  </si>
-  <si>
-    <t>204608792</t>
-  </si>
-  <si>
-    <t>206197760</t>
-  </si>
-  <si>
-    <t>208136881</t>
-  </si>
-  <si>
-    <t>213188943</t>
-  </si>
-  <si>
-    <t>213084761</t>
-  </si>
-  <si>
-    <t>207391198</t>
-  </si>
-  <si>
-    <t>207316534</t>
-  </si>
-  <si>
-    <t>204210771</t>
-  </si>
-  <si>
-    <t>202567370</t>
-  </si>
-  <si>
-    <t>201991852</t>
-  </si>
-  <si>
-    <t>200772170</t>
-  </si>
-  <si>
-    <t>197973666</t>
-  </si>
-  <si>
-    <t>198148318</t>
-  </si>
-  <si>
-    <t>197037579</t>
-  </si>
-  <si>
-    <t>196760460</t>
-  </si>
-  <si>
-    <t>194914499</t>
-  </si>
-  <si>
-    <t>194649913</t>
-  </si>
-  <si>
-    <t>192166548</t>
-  </si>
-  <si>
-    <t>191838071</t>
-  </si>
-  <si>
-    <t>189099157</t>
-  </si>
-  <si>
-    <t>185691197</t>
-  </si>
-  <si>
-    <t>183493901</t>
-  </si>
-  <si>
-    <t>177942160</t>
-  </si>
-  <si>
-    <t>974500682</t>
-  </si>
-  <si>
-    <t>972168730</t>
-  </si>
-  <si>
-    <t>971869452</t>
-  </si>
-  <si>
-    <t>970291997</t>
-  </si>
-  <si>
-    <t>968604714</t>
-  </si>
-  <si>
-    <t>962747717</t>
-  </si>
-  <si>
-    <t>962324319</t>
-  </si>
-  <si>
-    <t>962101881</t>
-  </si>
-  <si>
-    <t>961865270</t>
-  </si>
-  <si>
-    <t>958236758</t>
-  </si>
-  <si>
-    <t>956663292</t>
-  </si>
-  <si>
-    <t>954617951</t>
-  </si>
-  <si>
-    <t>953485905</t>
-  </si>
-  <si>
-    <t>183313422</t>
-  </si>
-  <si>
-    <t>942525753</t>
-  </si>
-  <si>
-    <t>942065222</t>
-  </si>
-  <si>
-    <t>940878220</t>
-  </si>
-  <si>
-    <t>931955888</t>
-  </si>
-  <si>
-    <t>938794488</t>
-  </si>
-  <si>
-    <t>937711954</t>
-  </si>
-  <si>
-    <t>936913742</t>
-  </si>
-  <si>
-    <t>931023158</t>
-  </si>
-  <si>
-    <t>926052485</t>
-  </si>
-  <si>
-    <t>928495492</t>
-  </si>
-  <si>
-    <t>928488885</t>
-  </si>
-  <si>
-    <t>924606241</t>
-  </si>
-  <si>
-    <t>924311966</t>
-  </si>
-  <si>
-    <t>902167380</t>
-  </si>
-  <si>
-    <t>856147669</t>
-  </si>
-  <si>
-    <t>862634668</t>
-  </si>
-  <si>
-    <t>862632688</t>
-  </si>
-  <si>
-    <t>862630484</t>
-  </si>
-  <si>
-    <t>862625831</t>
-  </si>
-  <si>
-    <t>862614496</t>
-  </si>
-  <si>
-    <t>862605387</t>
-  </si>
-  <si>
-    <t>862595810</t>
-  </si>
-  <si>
-    <t>862592601</t>
-  </si>
-  <si>
-    <t>862586702</t>
-  </si>
-  <si>
-    <t>862581539</t>
-  </si>
-  <si>
-    <t>862567330</t>
-  </si>
-  <si>
-    <t>862554023</t>
-  </si>
-  <si>
-    <t>861384836</t>
-  </si>
-  <si>
-    <t>860966997</t>
-  </si>
-  <si>
-    <t>855090282</t>
-  </si>
-  <si>
-    <t>220895985</t>
-  </si>
-  <si>
-    <t>775988086</t>
-  </si>
-  <si>
-    <t>814190983</t>
-  </si>
-  <si>
-    <t>844584668</t>
-  </si>
-  <si>
-    <t>853061939</t>
-  </si>
-  <si>
-    <t>844922397</t>
-  </si>
-  <si>
-    <t>837829237</t>
-  </si>
-  <si>
-    <t>828462956</t>
-  </si>
-  <si>
-    <t>826880761</t>
-  </si>
-  <si>
-    <t>824505873</t>
-  </si>
-  <si>
-    <t>824021871</t>
-  </si>
-  <si>
-    <t>823851336</t>
-  </si>
-  <si>
-    <t>815445501</t>
-  </si>
-  <si>
-    <t>791566395</t>
-  </si>
-  <si>
-    <t>782526028</t>
-  </si>
-  <si>
-    <t>241855562</t>
-  </si>
-  <si>
-    <t>221726007</t>
-  </si>
-  <si>
-    <t>233942881</t>
-  </si>
-  <si>
-    <t>233781149</t>
-  </si>
-  <si>
-    <t>220621274</t>
-  </si>
-  <si>
-    <t>217935836</t>
-  </si>
-  <si>
-    <t>217183833</t>
-  </si>
-  <si>
-    <t>216214621</t>
-  </si>
-  <si>
-    <t>215531033</t>
-  </si>
-  <si>
-    <t>913206813</t>
-  </si>
-  <si>
-    <t>917103875</t>
-  </si>
-  <si>
-    <t>923610590</t>
-  </si>
-  <si>
-    <t>915494334</t>
-  </si>
-  <si>
-    <t>910396088</t>
-  </si>
-  <si>
-    <t>908851144</t>
-  </si>
-  <si>
-    <t>908474657</t>
-  </si>
-  <si>
-    <t>907947372</t>
-  </si>
-  <si>
-    <t>892329016</t>
-  </si>
-  <si>
-    <t>891887113</t>
-  </si>
-  <si>
-    <t>889895557</t>
-  </si>
-  <si>
-    <t>889090415</t>
-  </si>
-  <si>
-    <t>876544465</t>
-  </si>
-  <si>
-    <t>885069488</t>
-  </si>
-  <si>
-    <t>876912886</t>
-  </si>
-  <si>
-    <t>873674463</t>
-  </si>
-  <si>
-    <t>875287371</t>
-  </si>
-  <si>
-    <t>874170917</t>
-  </si>
-  <si>
-    <t>872717438</t>
-  </si>
-  <si>
-    <t>869312151</t>
-  </si>
-  <si>
-    <t>868417423</t>
-  </si>
-  <si>
-    <t>884053228</t>
+    <t>233712011</t>
+  </si>
+  <si>
+    <t>233945546</t>
+  </si>
+  <si>
+    <t>233945538</t>
+  </si>
+  <si>
+    <t>233712003</t>
+  </si>
+  <si>
+    <t>219825597</t>
+  </si>
+  <si>
+    <t>229781830</t>
+  </si>
+  <si>
+    <t>966497558</t>
+  </si>
+  <si>
+    <t>185380700</t>
+  </si>
+  <si>
+    <t>198532529</t>
+  </si>
+  <si>
+    <t>195516525</t>
+  </si>
+  <si>
+    <t>181455209</t>
+  </si>
+  <si>
+    <t>178292813</t>
+  </si>
+  <si>
+    <t>972130375</t>
+  </si>
+  <si>
+    <t>967643333</t>
+  </si>
+  <si>
+    <t>966708582</t>
+  </si>
+  <si>
+    <t>967367404</t>
+  </si>
+  <si>
+    <t>963977297</t>
+  </si>
+  <si>
+    <t>961610247</t>
+  </si>
+  <si>
+    <t>860075740</t>
+  </si>
+  <si>
+    <t>833754678</t>
+  </si>
+  <si>
+    <t>829051154</t>
+  </si>
+  <si>
+    <t>828660229</t>
+  </si>
+  <si>
+    <t>823809151</t>
+  </si>
+  <si>
+    <t>808613313</t>
+  </si>
+  <si>
+    <t>803741895</t>
+  </si>
+  <si>
+    <t>800363917</t>
+  </si>
+  <si>
+    <t>781722743</t>
+  </si>
+  <si>
+    <t>793649413</t>
+  </si>
+  <si>
+    <t>791636990</t>
+  </si>
+  <si>
+    <t>791290426</t>
+  </si>
+  <si>
+    <t>788333403</t>
+  </si>
+  <si>
+    <t>954876946</t>
+  </si>
+  <si>
+    <t>958840187</t>
+  </si>
+  <si>
+    <t>961597675</t>
+  </si>
+  <si>
+    <t>961330390</t>
+  </si>
+  <si>
+    <t>957138708</t>
+  </si>
+  <si>
+    <t>956359081</t>
+  </si>
+  <si>
+    <t>932255221</t>
+  </si>
+  <si>
+    <t>865164812</t>
+  </si>
+  <si>
+    <t>883870606</t>
+  </si>
+  <si>
+    <t>880372416</t>
+  </si>
+  <si>
+    <t>873675098</t>
+  </si>
+  <si>
+    <t>951747751</t>
+  </si>
+  <si>
+    <t>942996111</t>
+  </si>
+  <si>
+    <t>940383403</t>
+  </si>
+  <si>
+    <t>939858936</t>
+  </si>
+  <si>
+    <t>939720979</t>
+  </si>
+  <si>
+    <t>939443382</t>
+  </si>
+  <si>
+    <t>938522731</t>
+  </si>
+  <si>
+    <t>937491268</t>
+  </si>
+  <si>
+    <t>933932356</t>
+  </si>
+  <si>
+    <t>932544715</t>
+  </si>
+  <si>
+    <t>932342987</t>
+  </si>
+  <si>
+    <t>931572642</t>
+  </si>
+  <si>
+    <t>921411512</t>
+  </si>
+  <si>
+    <t>923025351</t>
+  </si>
+  <si>
+    <t>920794934</t>
+  </si>
+  <si>
+    <t>920487588</t>
+  </si>
+  <si>
+    <t>919518096</t>
+  </si>
+  <si>
+    <t>919357255</t>
+  </si>
+  <si>
+    <t>917519450</t>
+  </si>
+  <si>
+    <t>914638303</t>
+  </si>
+  <si>
+    <t>913105338</t>
+  </si>
+  <si>
+    <t>911219164</t>
+  </si>
+  <si>
+    <t>910259898</t>
+  </si>
+  <si>
+    <t>907947315</t>
+  </si>
+  <si>
+    <t>902580590</t>
+  </si>
+  <si>
+    <t>901740799</t>
+  </si>
+  <si>
+    <t>901238497</t>
+  </si>
+  <si>
+    <t>901225528</t>
+  </si>
+  <si>
+    <t>894258684</t>
+  </si>
+  <si>
+    <t>893864102</t>
+  </si>
+  <si>
+    <t>893035554</t>
+  </si>
+  <si>
+    <t>891683447</t>
+  </si>
+  <si>
+    <t>890601150</t>
+  </si>
+  <si>
+    <t>889791590</t>
+  </si>
+  <si>
+    <t>885407209</t>
+  </si>
+  <si>
+    <t>890741642</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>218270266</t>
-  </si>
-  <si>
-    <t>834118378</t>
-  </si>
-  <si>
-    <t>221847720</t>
-  </si>
-  <si>
-    <t>222189593</t>
-  </si>
-  <si>
-    <t>926705801</t>
-  </si>
-  <si>
-    <t>976361851</t>
-  </si>
-  <si>
-    <t>976361133</t>
-  </si>
-  <si>
-    <t>976361125</t>
-  </si>
-  <si>
-    <t>954496646</t>
-  </si>
-  <si>
-    <t>963113653</t>
-  </si>
-  <si>
-    <t>189498409</t>
-  </si>
-  <si>
-    <t>202828335</t>
-  </si>
-  <si>
-    <t>885253488</t>
+    <t>976362123</t>
+  </si>
+  <si>
+    <t>218836751</t>
+  </si>
+  <si>
+    <t>218049892</t>
+  </si>
+  <si>
+    <t>194975334</t>
+  </si>
+  <si>
+    <t>198727582</t>
+  </si>
+  <si>
+    <t>191727225</t>
+  </si>
+  <si>
+    <t>976362040</t>
+  </si>
+  <si>
+    <t>872669985</t>
+  </si>
+  <si>
+    <t>926602255</t>
+  </si>
+  <si>
+    <t>937820441</t>
+  </si>
+  <si>
+    <t>948629427</t>
+  </si>
+  <si>
+    <t>892177787</t>
   </si>
 </sst>
 </file>
@@ -916,7 +790,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1840,7 +1714,7 @@
         <v>84</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>4</v>
@@ -1848,10 +1722,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>4</v>
@@ -1859,10 +1733,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>4</v>
@@ -1870,10 +1744,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>4</v>
@@ -1881,10 +1755,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
@@ -1892,10 +1766,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>4</v>
@@ -1903,10 +1777,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
@@ -1914,10 +1788,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>4</v>
@@ -1925,10 +1799,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>4</v>
@@ -1936,10 +1810,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>4</v>
@@ -1947,10 +1821,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>4</v>
@@ -1958,10 +1832,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>4</v>
@@ -1969,474 +1843,12 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C134" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665A6304-D569-44CA-9C46-65F922B0E675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5486ED7-F5D7-4A53-8FF4-E884B0ABF19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="103">
   <si>
     <t>Status</t>
   </si>
@@ -48,283 +48,298 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>864695808</t>
+    <t>192711582</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>233712011</t>
-  </si>
-  <si>
-    <t>233945546</t>
-  </si>
-  <si>
-    <t>233945538</t>
-  </si>
-  <si>
-    <t>233712003</t>
-  </si>
-  <si>
-    <t>219825597</t>
-  </si>
-  <si>
-    <t>229781830</t>
-  </si>
-  <si>
-    <t>966497558</t>
-  </si>
-  <si>
-    <t>185380700</t>
-  </si>
-  <si>
-    <t>198532529</t>
-  </si>
-  <si>
-    <t>195516525</t>
-  </si>
-  <si>
-    <t>181455209</t>
-  </si>
-  <si>
-    <t>178292813</t>
-  </si>
-  <si>
-    <t>972130375</t>
-  </si>
-  <si>
-    <t>967643333</t>
-  </si>
-  <si>
-    <t>966708582</t>
-  </si>
-  <si>
-    <t>967367404</t>
-  </si>
-  <si>
-    <t>963977297</t>
-  </si>
-  <si>
-    <t>961610247</t>
-  </si>
-  <si>
-    <t>860075740</t>
-  </si>
-  <si>
-    <t>833754678</t>
-  </si>
-  <si>
-    <t>829051154</t>
-  </si>
-  <si>
-    <t>828660229</t>
-  </si>
-  <si>
-    <t>823809151</t>
-  </si>
-  <si>
-    <t>808613313</t>
-  </si>
-  <si>
-    <t>803741895</t>
-  </si>
-  <si>
-    <t>800363917</t>
-  </si>
-  <si>
-    <t>781722743</t>
-  </si>
-  <si>
-    <t>793649413</t>
-  </si>
-  <si>
-    <t>791636990</t>
-  </si>
-  <si>
-    <t>791290426</t>
-  </si>
-  <si>
-    <t>788333403</t>
-  </si>
-  <si>
-    <t>954876946</t>
-  </si>
-  <si>
-    <t>958840187</t>
-  </si>
-  <si>
-    <t>961597675</t>
-  </si>
-  <si>
-    <t>961330390</t>
-  </si>
-  <si>
-    <t>957138708</t>
-  </si>
-  <si>
-    <t>956359081</t>
-  </si>
-  <si>
-    <t>932255221</t>
-  </si>
-  <si>
-    <t>865164812</t>
-  </si>
-  <si>
-    <t>883870606</t>
-  </si>
-  <si>
-    <t>880372416</t>
-  </si>
-  <si>
-    <t>873675098</t>
-  </si>
-  <si>
-    <t>951747751</t>
-  </si>
-  <si>
-    <t>942996111</t>
-  </si>
-  <si>
-    <t>940383403</t>
-  </si>
-  <si>
-    <t>939858936</t>
-  </si>
-  <si>
-    <t>939720979</t>
-  </si>
-  <si>
-    <t>939443382</t>
-  </si>
-  <si>
-    <t>938522731</t>
-  </si>
-  <si>
-    <t>937491268</t>
-  </si>
-  <si>
-    <t>933932356</t>
-  </si>
-  <si>
-    <t>932544715</t>
-  </si>
-  <si>
-    <t>932342987</t>
-  </si>
-  <si>
-    <t>931572642</t>
-  </si>
-  <si>
-    <t>921411512</t>
-  </si>
-  <si>
-    <t>923025351</t>
-  </si>
-  <si>
-    <t>920794934</t>
-  </si>
-  <si>
-    <t>920487588</t>
-  </si>
-  <si>
-    <t>919518096</t>
-  </si>
-  <si>
-    <t>919357255</t>
-  </si>
-  <si>
-    <t>917519450</t>
-  </si>
-  <si>
-    <t>914638303</t>
-  </si>
-  <si>
-    <t>913105338</t>
-  </si>
-  <si>
-    <t>911219164</t>
-  </si>
-  <si>
-    <t>910259898</t>
-  </si>
-  <si>
-    <t>907947315</t>
-  </si>
-  <si>
-    <t>902580590</t>
-  </si>
-  <si>
-    <t>901740799</t>
-  </si>
-  <si>
-    <t>901238497</t>
-  </si>
-  <si>
-    <t>901225528</t>
-  </si>
-  <si>
-    <t>894258684</t>
-  </si>
-  <si>
-    <t>893864102</t>
-  </si>
-  <si>
-    <t>893035554</t>
-  </si>
-  <si>
-    <t>891683447</t>
-  </si>
-  <si>
-    <t>890601150</t>
-  </si>
-  <si>
-    <t>889791590</t>
-  </si>
-  <si>
-    <t>885407209</t>
-  </si>
-  <si>
-    <t>890741642</t>
+    <t>973051034</t>
+  </si>
+  <si>
+    <t>968564868</t>
+  </si>
+  <si>
+    <t>971016245</t>
+  </si>
+  <si>
+    <t>964580306</t>
+  </si>
+  <si>
+    <t>959366083</t>
+  </si>
+  <si>
+    <t>960230369</t>
+  </si>
+  <si>
+    <t>957416526</t>
+  </si>
+  <si>
+    <t>954703702</t>
+  </si>
+  <si>
+    <t>955793942</t>
+  </si>
+  <si>
+    <t>954721506</t>
+  </si>
+  <si>
+    <t>951450620</t>
+  </si>
+  <si>
+    <t>938384124</t>
+  </si>
+  <si>
+    <t>928177447</t>
+  </si>
+  <si>
+    <t>927460968</t>
+  </si>
+  <si>
+    <t>926274568</t>
+  </si>
+  <si>
+    <t>892410576</t>
+  </si>
+  <si>
+    <t>922173897</t>
+  </si>
+  <si>
+    <t>918799564</t>
+  </si>
+  <si>
+    <t>919976047</t>
+  </si>
+  <si>
+    <t>914145648</t>
+  </si>
+  <si>
+    <t>917723789</t>
+  </si>
+  <si>
+    <t>918767009</t>
+  </si>
+  <si>
+    <t>918233499</t>
+  </si>
+  <si>
+    <t>912740986</t>
+  </si>
+  <si>
+    <t>911464067</t>
+  </si>
+  <si>
+    <t>910549629</t>
+  </si>
+  <si>
+    <t>909412292</t>
+  </si>
+  <si>
+    <t>906981521</t>
+  </si>
+  <si>
+    <t>905494401</t>
+  </si>
+  <si>
+    <t>903795866</t>
+  </si>
+  <si>
+    <t>895953184</t>
+  </si>
+  <si>
+    <t>895632515</t>
+  </si>
+  <si>
+    <t>885383459</t>
+  </si>
+  <si>
+    <t>891166310</t>
+  </si>
+  <si>
+    <t>891091302</t>
+  </si>
+  <si>
+    <t>946828377</t>
+  </si>
+  <si>
+    <t>946956392</t>
+  </si>
+  <si>
+    <t>943583223</t>
+  </si>
+  <si>
+    <t>940799681</t>
+  </si>
+  <si>
+    <t>936213440</t>
+  </si>
+  <si>
+    <t>935676183</t>
+  </si>
+  <si>
+    <t>935074397</t>
+  </si>
+  <si>
+    <t>934072277</t>
+  </si>
+  <si>
+    <t>931508539</t>
+  </si>
+  <si>
+    <t>217317431</t>
+  </si>
+  <si>
+    <t>825249661</t>
+  </si>
+  <si>
+    <t>870263310</t>
+  </si>
+  <si>
+    <t>882874450</t>
+  </si>
+  <si>
+    <t>878184351</t>
+  </si>
+  <si>
+    <t>876199591</t>
+  </si>
+  <si>
+    <t>870447798</t>
+  </si>
+  <si>
+    <t>866639473</t>
+  </si>
+  <si>
+    <t>861918641</t>
+  </si>
+  <si>
+    <t>866450905</t>
+  </si>
+  <si>
+    <t>856079995</t>
+  </si>
+  <si>
+    <t>859207577</t>
+  </si>
+  <si>
+    <t>852693088</t>
+  </si>
+  <si>
+    <t>852097199</t>
+  </si>
+  <si>
+    <t>843147186</t>
+  </si>
+  <si>
+    <t>839714460</t>
+  </si>
+  <si>
+    <t>832872257</t>
+  </si>
+  <si>
+    <t>825217775</t>
+  </si>
+  <si>
+    <t>824029270</t>
+  </si>
+  <si>
+    <t>806802348</t>
+  </si>
+  <si>
+    <t>791987336</t>
+  </si>
+  <si>
+    <t>234155012</t>
+  </si>
+  <si>
+    <t>255550042</t>
+  </si>
+  <si>
+    <t>226676082</t>
+  </si>
+  <si>
+    <t>200805665</t>
+  </si>
+  <si>
+    <t>210192542</t>
+  </si>
+  <si>
+    <t>206602553</t>
+  </si>
+  <si>
+    <t>206201901</t>
+  </si>
+  <si>
+    <t>204247765</t>
+  </si>
+  <si>
+    <t>201543034</t>
+  </si>
+  <si>
+    <t>200932279</t>
+  </si>
+  <si>
+    <t>193572678</t>
+  </si>
+  <si>
+    <t>197741758</t>
+  </si>
+  <si>
+    <t>183720071</t>
+  </si>
+  <si>
+    <t>182089783</t>
+  </si>
+  <si>
+    <t>177333212</t>
+  </si>
+  <si>
+    <t>177002163</t>
+  </si>
+  <si>
+    <t>975085410</t>
+  </si>
+  <si>
+    <t>973465408</t>
+  </si>
+  <si>
+    <t>973971553</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>976362123</t>
-  </si>
-  <si>
-    <t>218836751</t>
-  </si>
-  <si>
-    <t>218049892</t>
-  </si>
-  <si>
-    <t>194975334</t>
-  </si>
-  <si>
-    <t>198727582</t>
-  </si>
-  <si>
-    <t>191727225</t>
-  </si>
-  <si>
-    <t>976362040</t>
-  </si>
-  <si>
-    <t>872669985</t>
-  </si>
-  <si>
-    <t>926602255</t>
-  </si>
-  <si>
-    <t>937820441</t>
-  </si>
-  <si>
-    <t>948629427</t>
-  </si>
-  <si>
-    <t>892177787</t>
+    <t>931447027</t>
+  </si>
+  <si>
+    <t>925603247</t>
+  </si>
+  <si>
+    <t>920051491</t>
+  </si>
+  <si>
+    <t>947470088</t>
+  </si>
+  <si>
+    <t>208453997</t>
+  </si>
+  <si>
+    <t>249873302</t>
+  </si>
+  <si>
+    <t>249107008</t>
+  </si>
+  <si>
+    <t>247159811</t>
+  </si>
+  <si>
+    <t>249038484</t>
+  </si>
+  <si>
+    <t>223049903</t>
+  </si>
+  <si>
+    <t>218480915</t>
   </si>
 </sst>
 </file>
@@ -790,7 +805,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1714,7 +1729,7 @@
         <v>84</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>4</v>
@@ -1722,10 +1737,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>4</v>
@@ -1733,10 +1748,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>4</v>
@@ -1744,10 +1759,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>4</v>
@@ -1755,10 +1770,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
@@ -1766,10 +1781,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>4</v>
@@ -1777,10 +1792,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
@@ -1791,7 +1806,7 @@
         <v>92</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>4</v>
@@ -1802,7 +1817,7 @@
         <v>93</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>4</v>
@@ -1813,7 +1828,7 @@
         <v>94</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>4</v>
@@ -1824,7 +1839,7 @@
         <v>95</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>4</v>
@@ -1835,7 +1850,7 @@
         <v>96</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>4</v>
@@ -1846,9 +1861,64 @@
         <v>97</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6CFC63-A378-4B98-9AB0-24DB02EC889D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F75290F-C7D9-4903-A57A-061E85328CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="188">
   <si>
     <t>Status</t>
   </si>
@@ -334,6 +334,267 @@
   </si>
   <si>
     <t>850085345</t>
+  </si>
+  <si>
+    <t>948562339</t>
+  </si>
+  <si>
+    <t>973885357</t>
+  </si>
+  <si>
+    <t>973410842</t>
+  </si>
+  <si>
+    <t>963078930</t>
+  </si>
+  <si>
+    <t>951244106</t>
+  </si>
+  <si>
+    <t>945428740</t>
+  </si>
+  <si>
+    <t>944426521</t>
+  </si>
+  <si>
+    <t>941606968</t>
+  </si>
+  <si>
+    <t>936412240</t>
+  </si>
+  <si>
+    <t>931961803</t>
+  </si>
+  <si>
+    <t>930326453</t>
+  </si>
+  <si>
+    <t>928582067</t>
+  </si>
+  <si>
+    <t>925148748</t>
+  </si>
+  <si>
+    <t>915696029</t>
+  </si>
+  <si>
+    <t>921139287</t>
+  </si>
+  <si>
+    <t>923681104</t>
+  </si>
+  <si>
+    <t>915017846</t>
+  </si>
+  <si>
+    <t>911714800</t>
+  </si>
+  <si>
+    <t>910863897</t>
+  </si>
+  <si>
+    <t>909227518</t>
+  </si>
+  <si>
+    <t>206451951</t>
+  </si>
+  <si>
+    <t>261158194</t>
+  </si>
+  <si>
+    <t>216681852</t>
+  </si>
+  <si>
+    <t>228179911</t>
+  </si>
+  <si>
+    <t>208770770</t>
+  </si>
+  <si>
+    <t>208002315</t>
+  </si>
+  <si>
+    <t>205071834</t>
+  </si>
+  <si>
+    <t>205071826</t>
+  </si>
+  <si>
+    <t>185332230</t>
+  </si>
+  <si>
+    <t>199492764</t>
+  </si>
+  <si>
+    <t>193951898</t>
+  </si>
+  <si>
+    <t>188109734</t>
+  </si>
+  <si>
+    <t>187136217</t>
+  </si>
+  <si>
+    <t>183670854</t>
+  </si>
+  <si>
+    <t>884594668</t>
+  </si>
+  <si>
+    <t>895813883</t>
+  </si>
+  <si>
+    <t>895778813</t>
+  </si>
+  <si>
+    <t>893806012</t>
+  </si>
+  <si>
+    <t>890907227</t>
+  </si>
+  <si>
+    <t>876146618</t>
+  </si>
+  <si>
+    <t>875526430</t>
+  </si>
+  <si>
+    <t>874131505</t>
+  </si>
+  <si>
+    <t>873828903</t>
+  </si>
+  <si>
+    <t>836993091</t>
+  </si>
+  <si>
+    <t>862185323</t>
+  </si>
+  <si>
+    <t>872251040</t>
+  </si>
+  <si>
+    <t>869831317</t>
+  </si>
+  <si>
+    <t>866725421</t>
+  </si>
+  <si>
+    <t>865885846</t>
+  </si>
+  <si>
+    <t>865486702</t>
+  </si>
+  <si>
+    <t>850305032</t>
+  </si>
+  <si>
+    <t>851951487</t>
+  </si>
+  <si>
+    <t>857950210</t>
+  </si>
+  <si>
+    <t>850304738</t>
+  </si>
+  <si>
+    <t>848851477</t>
+  </si>
+  <si>
+    <t>841876935</t>
+  </si>
+  <si>
+    <t>846361115</t>
+  </si>
+  <si>
+    <t>821929878</t>
+  </si>
+  <si>
+    <t>832646024</t>
+  </si>
+  <si>
+    <t>830772079</t>
+  </si>
+  <si>
+    <t>827776042</t>
+  </si>
+  <si>
+    <t>820588550</t>
+  </si>
+  <si>
+    <t>268317371</t>
+  </si>
+  <si>
+    <t>254103223</t>
+  </si>
+  <si>
+    <t>199774872</t>
+  </si>
+  <si>
+    <t>250315144</t>
+  </si>
+  <si>
+    <t>250180183</t>
+  </si>
+  <si>
+    <t>250177403</t>
+  </si>
+  <si>
+    <t>250051459</t>
+  </si>
+  <si>
+    <t>249930094</t>
+  </si>
+  <si>
+    <t>249831698</t>
+  </si>
+  <si>
+    <t>249683156</t>
+  </si>
+  <si>
+    <t>249313259</t>
+  </si>
+  <si>
+    <t>239962966</t>
+  </si>
+  <si>
+    <t>238967669</t>
+  </si>
+  <si>
+    <t>873040079</t>
+  </si>
+  <si>
+    <t>970619536</t>
+  </si>
+  <si>
+    <t>955743707</t>
+  </si>
+  <si>
+    <t>962967356</t>
+  </si>
+  <si>
+    <t>908618733</t>
+  </si>
+  <si>
+    <t>908236635</t>
+  </si>
+  <si>
+    <t>899401727</t>
+  </si>
+  <si>
+    <t>186943613</t>
+  </si>
+  <si>
+    <t>191008436</t>
+  </si>
+  <si>
+    <t>194215053</t>
+  </si>
+  <si>
+    <t>188977213</t>
+  </si>
+  <si>
+    <t>187513803</t>
   </si>
 </sst>
 </file>
@@ -799,7 +1060,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D182"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1891,6 +2152,963 @@
         <v>81</v>
       </c>
       <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C182" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39A71F3-A92B-40C8-9DBF-3CE3A47E007C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5CFEFD-16E0-463D-A369-5B4D6623EB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="103">
   <si>
     <t>Status</t>
   </si>
@@ -48,235 +48,298 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>207353263</t>
+    <t>206372900</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>961108051</t>
-  </si>
-  <si>
-    <t>969930118</t>
-  </si>
-  <si>
-    <t>968102545</t>
-  </si>
-  <si>
-    <t>965914017</t>
-  </si>
-  <si>
-    <t>965678943</t>
-  </si>
-  <si>
-    <t>964730604</t>
-  </si>
-  <si>
-    <t>962491175</t>
-  </si>
-  <si>
-    <t>959868476</t>
-  </si>
-  <si>
-    <t>956237063</t>
-  </si>
-  <si>
-    <t>925797593</t>
-  </si>
-  <si>
-    <t>954613539</t>
-  </si>
-  <si>
-    <t>954419879</t>
-  </si>
-  <si>
-    <t>947248559</t>
-  </si>
-  <si>
-    <t>944819287</t>
-  </si>
-  <si>
-    <t>944628639</t>
-  </si>
-  <si>
-    <t>938759077</t>
-  </si>
-  <si>
-    <t>932059300</t>
-  </si>
-  <si>
-    <t>931354355</t>
-  </si>
-  <si>
-    <t>930582303</t>
-  </si>
-  <si>
-    <t>927501662</t>
-  </si>
-  <si>
-    <t>920645748</t>
-  </si>
-  <si>
-    <t>911400483</t>
-  </si>
-  <si>
-    <t>910480692</t>
-  </si>
-  <si>
-    <t>907985976</t>
-  </si>
-  <si>
-    <t>909478178</t>
-  </si>
-  <si>
-    <t>898946219</t>
-  </si>
-  <si>
-    <t>904114927</t>
-  </si>
-  <si>
-    <t>899973212</t>
-  </si>
-  <si>
-    <t>899150712</t>
-  </si>
-  <si>
-    <t>880359959</t>
-  </si>
-  <si>
-    <t>897387050</t>
-  </si>
-  <si>
-    <t>893711394</t>
-  </si>
-  <si>
-    <t>892364609</t>
-  </si>
-  <si>
-    <t>890805876</t>
-  </si>
-  <si>
-    <t>888590464</t>
-  </si>
-  <si>
-    <t>879344764</t>
-  </si>
-  <si>
-    <t>875066742</t>
-  </si>
-  <si>
-    <t>874665395</t>
-  </si>
-  <si>
-    <t>837079619</t>
-  </si>
-  <si>
-    <t>872954783</t>
-  </si>
-  <si>
-    <t>871038570</t>
-  </si>
-  <si>
-    <t>872007723</t>
-  </si>
-  <si>
-    <t>867087565</t>
-  </si>
-  <si>
-    <t>867083523</t>
-  </si>
-  <si>
-    <t>862497231</t>
-  </si>
-  <si>
-    <t>861818619</t>
-  </si>
-  <si>
-    <t>854027293</t>
-  </si>
-  <si>
-    <t>847363177</t>
-  </si>
-  <si>
-    <t>851536650</t>
-  </si>
-  <si>
-    <t>848787259</t>
-  </si>
-  <si>
-    <t>245727221</t>
-  </si>
-  <si>
-    <t>221103702</t>
-  </si>
-  <si>
-    <t>221717410</t>
-  </si>
-  <si>
-    <t>224463350</t>
-  </si>
-  <si>
-    <t>185037532</t>
-  </si>
-  <si>
-    <t>203342336</t>
-  </si>
-  <si>
-    <t>201205402</t>
-  </si>
-  <si>
-    <t>200937641</t>
-  </si>
-  <si>
-    <t>200740151</t>
-  </si>
-  <si>
-    <t>197490166</t>
-  </si>
-  <si>
-    <t>194302448</t>
-  </si>
-  <si>
-    <t>191285752</t>
-  </si>
-  <si>
-    <t>187321322</t>
-  </si>
-  <si>
-    <t>975387014</t>
-  </si>
-  <si>
-    <t>975210083</t>
-  </si>
-  <si>
-    <t>974900759</t>
-  </si>
-  <si>
-    <t>972763969</t>
-  </si>
-  <si>
-    <t>976362032</t>
+    <t>945185555</t>
+  </si>
+  <si>
+    <t>945790958</t>
+  </si>
+  <si>
+    <t>949815066</t>
+  </si>
+  <si>
+    <t>948816446</t>
+  </si>
+  <si>
+    <t>932700036</t>
+  </si>
+  <si>
+    <t>260732197</t>
+  </si>
+  <si>
+    <t>898805746</t>
+  </si>
+  <si>
+    <t>906837194</t>
+  </si>
+  <si>
+    <t>919466544</t>
+  </si>
+  <si>
+    <t>915727352</t>
+  </si>
+  <si>
+    <t>914544154</t>
+  </si>
+  <si>
+    <t>913034199</t>
+  </si>
+  <si>
+    <t>906115773</t>
+  </si>
+  <si>
+    <t>897760009</t>
+  </si>
+  <si>
+    <t>897591503</t>
+  </si>
+  <si>
+    <t>877811988</t>
+  </si>
+  <si>
+    <t>890116993</t>
+  </si>
+  <si>
+    <t>897493122</t>
+  </si>
+  <si>
+    <t>894917891</t>
+  </si>
+  <si>
+    <t>883963146</t>
+  </si>
+  <si>
+    <t>887905069</t>
+  </si>
+  <si>
+    <t>887812836</t>
+  </si>
+  <si>
+    <t>872853480</t>
+  </si>
+  <si>
+    <t>871153817</t>
+  </si>
+  <si>
+    <t>862916396</t>
+  </si>
+  <si>
+    <t>858654241</t>
+  </si>
+  <si>
+    <t>842421525</t>
+  </si>
+  <si>
+    <t>852100084</t>
+  </si>
+  <si>
+    <t>856716620</t>
+  </si>
+  <si>
+    <t>856129691</t>
+  </si>
+  <si>
+    <t>853664823</t>
+  </si>
+  <si>
+    <t>847864224</t>
+  </si>
+  <si>
+    <t>846313132</t>
+  </si>
+  <si>
+    <t>838336034</t>
+  </si>
+  <si>
+    <t>838243263</t>
+  </si>
+  <si>
+    <t>832712172</t>
+  </si>
+  <si>
+    <t>836425359</t>
+  </si>
+  <si>
+    <t>833937125</t>
+  </si>
+  <si>
+    <t>819295340</t>
+  </si>
+  <si>
+    <t>824554889</t>
+  </si>
+  <si>
+    <t>800862090</t>
+  </si>
+  <si>
+    <t>809588266</t>
+  </si>
+  <si>
+    <t>784234928</t>
+  </si>
+  <si>
+    <t>784198164</t>
+  </si>
+  <si>
+    <t>262134616</t>
+  </si>
+  <si>
+    <t>260732189</t>
+  </si>
+  <si>
+    <t>260649854</t>
+  </si>
+  <si>
+    <t>225418130</t>
+  </si>
+  <si>
+    <t>213615804</t>
+  </si>
+  <si>
+    <t>215977921</t>
+  </si>
+  <si>
+    <t>210574434</t>
+  </si>
+  <si>
+    <t>211477074</t>
+  </si>
+  <si>
+    <t>211073352</t>
+  </si>
+  <si>
+    <t>209078025</t>
+  </si>
+  <si>
+    <t>210234203</t>
+  </si>
+  <si>
+    <t>204005403</t>
+  </si>
+  <si>
+    <t>202555078</t>
+  </si>
+  <si>
+    <t>200515496</t>
+  </si>
+  <si>
+    <t>199554282</t>
+  </si>
+  <si>
+    <t>199048582</t>
+  </si>
+  <si>
+    <t>198645107</t>
+  </si>
+  <si>
+    <t>196094936</t>
+  </si>
+  <si>
+    <t>195903483</t>
+  </si>
+  <si>
+    <t>195385541</t>
+  </si>
+  <si>
+    <t>195194372</t>
+  </si>
+  <si>
+    <t>189911799</t>
+  </si>
+  <si>
+    <t>192207896</t>
+  </si>
+  <si>
+    <t>191751159</t>
+  </si>
+  <si>
+    <t>189790680</t>
+  </si>
+  <si>
+    <t>189707205</t>
+  </si>
+  <si>
+    <t>184610057</t>
+  </si>
+  <si>
+    <t>186589622</t>
+  </si>
+  <si>
+    <t>187142165</t>
+  </si>
+  <si>
+    <t>973511433</t>
+  </si>
+  <si>
+    <t>174992549</t>
+  </si>
+  <si>
+    <t>954644351</t>
+  </si>
+  <si>
+    <t>966365961</t>
+  </si>
+  <si>
+    <t>969108160</t>
+  </si>
+  <si>
+    <t>969058670</t>
+  </si>
+  <si>
+    <t>968559009</t>
+  </si>
+  <si>
+    <t>968210199</t>
+  </si>
+  <si>
+    <t>961698556</t>
+  </si>
+  <si>
+    <t>958690863</t>
+  </si>
+  <si>
+    <t>960919938</t>
+  </si>
+  <si>
+    <t>953671306</t>
+  </si>
+  <si>
+    <t>953666116</t>
+  </si>
+  <si>
+    <t>952925893</t>
+  </si>
+  <si>
+    <t>925181954</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>966104790</t>
-  </si>
-  <si>
-    <t>215251384</t>
-  </si>
-  <si>
-    <t>253838134</t>
-  </si>
-  <si>
-    <t>189714029</t>
-  </si>
-  <si>
-    <t>201074642</t>
-  </si>
-  <si>
-    <t>207326350</t>
+    <t>251994608</t>
+  </si>
+  <si>
+    <t>837253321</t>
+  </si>
+  <si>
+    <t>253656601</t>
+  </si>
+  <si>
+    <t>192819252</t>
+  </si>
+  <si>
+    <t>955900166</t>
+  </si>
+  <si>
+    <t>961578873</t>
+  </si>
+  <si>
+    <t>958826954</t>
   </si>
 </sst>
 </file>
@@ -742,7 +805,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1556,7 +1619,7 @@
         <v>74</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>4</v>
@@ -1564,10 +1627,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>4</v>
@@ -1575,10 +1638,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
@@ -1586,10 +1649,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
@@ -1597,10 +1660,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
@@ -1608,10 +1671,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>4</v>
@@ -1619,12 +1682,243 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="5" t="s">
+      <c r="B77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5CFEFD-16E0-463D-A369-5B4D6623EB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96633A8D-36CB-4DB5-9A10-C213A4951A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="73">
   <si>
     <t>Status</t>
   </si>
@@ -48,298 +48,208 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>206372900</t>
+    <t>259442675</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>945185555</t>
-  </si>
-  <si>
-    <t>945790958</t>
-  </si>
-  <si>
-    <t>949815066</t>
-  </si>
-  <si>
-    <t>948816446</t>
-  </si>
-  <si>
-    <t>932700036</t>
-  </si>
-  <si>
-    <t>260732197</t>
-  </si>
-  <si>
-    <t>898805746</t>
-  </si>
-  <si>
-    <t>906837194</t>
-  </si>
-  <si>
-    <t>919466544</t>
-  </si>
-  <si>
-    <t>915727352</t>
-  </si>
-  <si>
-    <t>914544154</t>
-  </si>
-  <si>
-    <t>913034199</t>
-  </si>
-  <si>
-    <t>906115773</t>
-  </si>
-  <si>
-    <t>897760009</t>
-  </si>
-  <si>
-    <t>897591503</t>
-  </si>
-  <si>
-    <t>877811988</t>
-  </si>
-  <si>
-    <t>890116993</t>
-  </si>
-  <si>
-    <t>897493122</t>
-  </si>
-  <si>
-    <t>894917891</t>
-  </si>
-  <si>
-    <t>883963146</t>
-  </si>
-  <si>
-    <t>887905069</t>
-  </si>
-  <si>
-    <t>887812836</t>
-  </si>
-  <si>
-    <t>872853480</t>
-  </si>
-  <si>
-    <t>871153817</t>
-  </si>
-  <si>
-    <t>862916396</t>
-  </si>
-  <si>
-    <t>858654241</t>
-  </si>
-  <si>
-    <t>842421525</t>
-  </si>
-  <si>
-    <t>852100084</t>
-  </si>
-  <si>
-    <t>856716620</t>
-  </si>
-  <si>
-    <t>856129691</t>
-  </si>
-  <si>
-    <t>853664823</t>
-  </si>
-  <si>
-    <t>847864224</t>
-  </si>
-  <si>
-    <t>846313132</t>
-  </si>
-  <si>
-    <t>838336034</t>
-  </si>
-  <si>
-    <t>838243263</t>
-  </si>
-  <si>
-    <t>832712172</t>
-  </si>
-  <si>
-    <t>836425359</t>
-  </si>
-  <si>
-    <t>833937125</t>
-  </si>
-  <si>
-    <t>819295340</t>
-  </si>
-  <si>
-    <t>824554889</t>
-  </si>
-  <si>
-    <t>800862090</t>
-  </si>
-  <si>
-    <t>809588266</t>
-  </si>
-  <si>
-    <t>784234928</t>
-  </si>
-  <si>
-    <t>784198164</t>
-  </si>
-  <si>
-    <t>262134616</t>
-  </si>
-  <si>
-    <t>260732189</t>
-  </si>
-  <si>
-    <t>260649854</t>
-  </si>
-  <si>
-    <t>225418130</t>
-  </si>
-  <si>
-    <t>213615804</t>
-  </si>
-  <si>
-    <t>215977921</t>
-  </si>
-  <si>
-    <t>210574434</t>
-  </si>
-  <si>
-    <t>211477074</t>
-  </si>
-  <si>
-    <t>211073352</t>
-  </si>
-  <si>
-    <t>209078025</t>
-  </si>
-  <si>
-    <t>210234203</t>
-  </si>
-  <si>
-    <t>204005403</t>
-  </si>
-  <si>
-    <t>202555078</t>
-  </si>
-  <si>
-    <t>200515496</t>
-  </si>
-  <si>
-    <t>199554282</t>
-  </si>
-  <si>
-    <t>199048582</t>
-  </si>
-  <si>
-    <t>198645107</t>
-  </si>
-  <si>
-    <t>196094936</t>
-  </si>
-  <si>
-    <t>195903483</t>
-  </si>
-  <si>
-    <t>195385541</t>
-  </si>
-  <si>
-    <t>195194372</t>
-  </si>
-  <si>
-    <t>189911799</t>
-  </si>
-  <si>
-    <t>192207896</t>
-  </si>
-  <si>
-    <t>191751159</t>
-  </si>
-  <si>
-    <t>189790680</t>
-  </si>
-  <si>
-    <t>189707205</t>
-  </si>
-  <si>
-    <t>184610057</t>
-  </si>
-  <si>
-    <t>186589622</t>
-  </si>
-  <si>
-    <t>187142165</t>
-  </si>
-  <si>
-    <t>973511433</t>
-  </si>
-  <si>
-    <t>174992549</t>
-  </si>
-  <si>
-    <t>954644351</t>
-  </si>
-  <si>
-    <t>966365961</t>
-  </si>
-  <si>
-    <t>969108160</t>
-  </si>
-  <si>
-    <t>969058670</t>
-  </si>
-  <si>
-    <t>968559009</t>
-  </si>
-  <si>
-    <t>968210199</t>
-  </si>
-  <si>
-    <t>961698556</t>
-  </si>
-  <si>
-    <t>958690863</t>
-  </si>
-  <si>
-    <t>960919938</t>
-  </si>
-  <si>
-    <t>953671306</t>
-  </si>
-  <si>
-    <t>953666116</t>
-  </si>
-  <si>
-    <t>952925893</t>
-  </si>
-  <si>
-    <t>925181954</t>
+    <t>908834629</t>
+  </si>
+  <si>
+    <t>929818924</t>
+  </si>
+  <si>
+    <t>949176246</t>
+  </si>
+  <si>
+    <t>954482620</t>
+  </si>
+  <si>
+    <t>953867912</t>
+  </si>
+  <si>
+    <t>952460016</t>
+  </si>
+  <si>
+    <t>946160755</t>
+  </si>
+  <si>
+    <t>942757679</t>
+  </si>
+  <si>
+    <t>941203154</t>
+  </si>
+  <si>
+    <t>937749541</t>
+  </si>
+  <si>
+    <t>937417263</t>
+  </si>
+  <si>
+    <t>935769160</t>
+  </si>
+  <si>
+    <t>926978283</t>
+  </si>
+  <si>
+    <t>922362193</t>
+  </si>
+  <si>
+    <t>922333509</t>
+  </si>
+  <si>
+    <t>912307968</t>
+  </si>
+  <si>
+    <t>919998488</t>
+  </si>
+  <si>
+    <t>914852573</t>
+  </si>
+  <si>
+    <t>897616003</t>
+  </si>
+  <si>
+    <t>893845002</t>
+  </si>
+  <si>
+    <t>780259556</t>
+  </si>
+  <si>
+    <t>862121294</t>
+  </si>
+  <si>
+    <t>877115653</t>
+  </si>
+  <si>
+    <t>884984885</t>
+  </si>
+  <si>
+    <t>880323195</t>
+  </si>
+  <si>
+    <t>879973653</t>
+  </si>
+  <si>
+    <t>875941555</t>
+  </si>
+  <si>
+    <t>869511281</t>
+  </si>
+  <si>
+    <t>852058423</t>
+  </si>
+  <si>
+    <t>853663221</t>
+  </si>
+  <si>
+    <t>832419968</t>
+  </si>
+  <si>
+    <t>827527338</t>
+  </si>
+  <si>
+    <t>821567884</t>
+  </si>
+  <si>
+    <t>826546081</t>
+  </si>
+  <si>
+    <t>252550946</t>
+  </si>
+  <si>
+    <t>964831089</t>
+  </si>
+  <si>
+    <t>954665281</t>
+  </si>
+  <si>
+    <t>956309490</t>
+  </si>
+  <si>
+    <t>200880783</t>
+  </si>
+  <si>
+    <t>222443552</t>
+  </si>
+  <si>
+    <t>206395182</t>
+  </si>
+  <si>
+    <t>204517043</t>
+  </si>
+  <si>
+    <t>203460393</t>
+  </si>
+  <si>
+    <t>202860296</t>
+  </si>
+  <si>
+    <t>201177270</t>
+  </si>
+  <si>
+    <t>199010426</t>
+  </si>
+  <si>
+    <t>191297005</t>
+  </si>
+  <si>
+    <t>191155971</t>
+  </si>
+  <si>
+    <t>189811270</t>
+  </si>
+  <si>
+    <t>188178515</t>
+  </si>
+  <si>
+    <t>187555416</t>
+  </si>
+  <si>
+    <t>187550680</t>
+  </si>
+  <si>
+    <t>184933921</t>
+  </si>
+  <si>
+    <t>972249100</t>
+  </si>
+  <si>
+    <t>971962711</t>
+  </si>
+  <si>
+    <t>961317066</t>
+  </si>
+  <si>
+    <t>961725433</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>251994608</t>
-  </si>
-  <si>
-    <t>837253321</t>
-  </si>
-  <si>
-    <t>253656601</t>
-  </si>
-  <si>
-    <t>192819252</t>
-  </si>
-  <si>
-    <t>955900166</t>
-  </si>
-  <si>
-    <t>961578873</t>
-  </si>
-  <si>
-    <t>958826954</t>
+    <t>958825204</t>
+  </si>
+  <si>
+    <t>908269602</t>
+  </si>
+  <si>
+    <t>953234766</t>
+  </si>
+  <si>
+    <t>886445851</t>
+  </si>
+  <si>
+    <t>886976624</t>
+  </si>
+  <si>
+    <t>253586642</t>
+  </si>
+  <si>
+    <t>209583479</t>
+  </si>
+  <si>
+    <t>181651443</t>
   </si>
 </sst>
 </file>
@@ -805,7 +715,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1498,7 +1408,7 @@
         <v>63</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>4</v>
@@ -1506,10 +1416,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>4</v>
@@ -1517,10 +1427,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
@@ -1528,10 +1438,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
@@ -1539,10 +1449,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
@@ -1550,10 +1460,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>4</v>
@@ -1561,10 +1471,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
@@ -1572,10 +1482,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
@@ -1583,342 +1493,12 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C97" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96633A8D-36CB-4DB5-9A10-C213A4951A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCAAACC-3D07-4CD2-9B15-F2F0B9D420CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RegularizarIncidencias" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="100">
   <si>
     <t>Status</t>
   </si>
@@ -48,208 +48,289 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>259442675</t>
+    <t>932658184</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>908834629</t>
-  </si>
-  <si>
-    <t>929818924</t>
-  </si>
-  <si>
-    <t>949176246</t>
-  </si>
-  <si>
-    <t>954482620</t>
-  </si>
-  <si>
-    <t>953867912</t>
-  </si>
-  <si>
-    <t>952460016</t>
-  </si>
-  <si>
-    <t>946160755</t>
-  </si>
-  <si>
-    <t>942757679</t>
-  </si>
-  <si>
-    <t>941203154</t>
-  </si>
-  <si>
-    <t>937749541</t>
-  </si>
-  <si>
-    <t>937417263</t>
-  </si>
-  <si>
-    <t>935769160</t>
-  </si>
-  <si>
-    <t>926978283</t>
-  </si>
-  <si>
-    <t>922362193</t>
-  </si>
-  <si>
-    <t>922333509</t>
-  </si>
-  <si>
-    <t>912307968</t>
-  </si>
-  <si>
-    <t>919998488</t>
-  </si>
-  <si>
-    <t>914852573</t>
-  </si>
-  <si>
-    <t>897616003</t>
-  </si>
-  <si>
-    <t>893845002</t>
-  </si>
-  <si>
-    <t>780259556</t>
-  </si>
-  <si>
-    <t>862121294</t>
-  </si>
-  <si>
-    <t>877115653</t>
-  </si>
-  <si>
-    <t>884984885</t>
-  </si>
-  <si>
-    <t>880323195</t>
-  </si>
-  <si>
-    <t>879973653</t>
-  </si>
-  <si>
-    <t>875941555</t>
-  </si>
-  <si>
-    <t>869511281</t>
-  </si>
-  <si>
-    <t>852058423</t>
-  </si>
-  <si>
-    <t>853663221</t>
-  </si>
-  <si>
-    <t>832419968</t>
-  </si>
-  <si>
-    <t>827527338</t>
-  </si>
-  <si>
-    <t>821567884</t>
-  </si>
-  <si>
-    <t>826546081</t>
-  </si>
-  <si>
-    <t>252550946</t>
-  </si>
-  <si>
-    <t>964831089</t>
-  </si>
-  <si>
-    <t>954665281</t>
-  </si>
-  <si>
-    <t>956309490</t>
-  </si>
-  <si>
-    <t>200880783</t>
-  </si>
-  <si>
-    <t>222443552</t>
-  </si>
-  <si>
-    <t>206395182</t>
-  </si>
-  <si>
-    <t>204517043</t>
-  </si>
-  <si>
-    <t>203460393</t>
-  </si>
-  <si>
-    <t>202860296</t>
-  </si>
-  <si>
-    <t>201177270</t>
-  </si>
-  <si>
-    <t>199010426</t>
-  </si>
-  <si>
-    <t>191297005</t>
-  </si>
-  <si>
-    <t>191155971</t>
-  </si>
-  <si>
-    <t>189811270</t>
-  </si>
-  <si>
-    <t>188178515</t>
-  </si>
-  <si>
-    <t>187555416</t>
-  </si>
-  <si>
-    <t>187550680</t>
-  </si>
-  <si>
-    <t>184933921</t>
-  </si>
-  <si>
-    <t>972249100</t>
-  </si>
-  <si>
-    <t>971962711</t>
-  </si>
-  <si>
-    <t>961317066</t>
-  </si>
-  <si>
-    <t>961725433</t>
+    <t>936348394</t>
+  </si>
+  <si>
+    <t>936114259</t>
+  </si>
+  <si>
+    <t>935968903</t>
+  </si>
+  <si>
+    <t>931475283</t>
+  </si>
+  <si>
+    <t>931279420</t>
+  </si>
+  <si>
+    <t>925863700</t>
+  </si>
+  <si>
+    <t>929856858</t>
+  </si>
+  <si>
+    <t>919338107</t>
+  </si>
+  <si>
+    <t>916215589</t>
+  </si>
+  <si>
+    <t>915726222</t>
+  </si>
+  <si>
+    <t>914688217</t>
+  </si>
+  <si>
+    <t>913662627</t>
+  </si>
+  <si>
+    <t>912210360</t>
+  </si>
+  <si>
+    <t>909563615</t>
+  </si>
+  <si>
+    <t>909531802</t>
+  </si>
+  <si>
+    <t>909531794</t>
+  </si>
+  <si>
+    <t>906156264</t>
+  </si>
+  <si>
+    <t>905059261</t>
+  </si>
+  <si>
+    <t>899113918</t>
+  </si>
+  <si>
+    <t>901942387</t>
+  </si>
+  <si>
+    <t>903229049</t>
+  </si>
+  <si>
+    <t>891143806</t>
+  </si>
+  <si>
+    <t>884637780</t>
+  </si>
+  <si>
+    <t>890816956</t>
+  </si>
+  <si>
+    <t>888229782</t>
+  </si>
+  <si>
+    <t>875909271</t>
+  </si>
+  <si>
+    <t>884232921</t>
+  </si>
+  <si>
+    <t>879047839</t>
+  </si>
+  <si>
+    <t>812741654</t>
+  </si>
+  <si>
+    <t>841613767</t>
+  </si>
+  <si>
+    <t>861775389</t>
+  </si>
+  <si>
+    <t>855614636</t>
+  </si>
+  <si>
+    <t>855565275</t>
+  </si>
+  <si>
+    <t>853962185</t>
+  </si>
+  <si>
+    <t>847655531</t>
+  </si>
+  <si>
+    <t>831447523</t>
+  </si>
+  <si>
+    <t>838024713</t>
+  </si>
+  <si>
+    <t>836059885</t>
+  </si>
+  <si>
+    <t>810493324</t>
+  </si>
+  <si>
+    <t>805086232</t>
+  </si>
+  <si>
+    <t>255259149</t>
+  </si>
+  <si>
+    <t>774587863</t>
+  </si>
+  <si>
+    <t>190475248</t>
+  </si>
+  <si>
+    <t>224236798</t>
+  </si>
+  <si>
+    <t>242274847</t>
+  </si>
+  <si>
+    <t>240602494</t>
+  </si>
+  <si>
+    <t>240602387</t>
+  </si>
+  <si>
+    <t>220882009</t>
+  </si>
+  <si>
+    <t>209802085</t>
+  </si>
+  <si>
+    <t>206899597</t>
+  </si>
+  <si>
+    <t>206625018</t>
+  </si>
+  <si>
+    <t>205745270</t>
+  </si>
+  <si>
+    <t>203494996</t>
+  </si>
+  <si>
+    <t>200538837</t>
+  </si>
+  <si>
+    <t>962986265</t>
+  </si>
+  <si>
+    <t>965785391</t>
+  </si>
+  <si>
+    <t>186095992</t>
+  </si>
+  <si>
+    <t>185946765</t>
+  </si>
+  <si>
+    <t>973947678</t>
+  </si>
+  <si>
+    <t>973636347</t>
+  </si>
+  <si>
+    <t>971276526</t>
+  </si>
+  <si>
+    <t>951000466</t>
+  </si>
+  <si>
+    <t>953401936</t>
+  </si>
+  <si>
+    <t>951355506</t>
+  </si>
+  <si>
+    <t>948478635</t>
+  </si>
+  <si>
+    <t>946222563</t>
+  </si>
+  <si>
+    <t>945813438</t>
+  </si>
+  <si>
+    <t>945798399</t>
+  </si>
+  <si>
+    <t>945229577</t>
+  </si>
+  <si>
+    <t>942044912</t>
+  </si>
+  <si>
+    <t>939917575</t>
+  </si>
+  <si>
+    <t>939439349</t>
+  </si>
+  <si>
+    <t>937175754</t>
+  </si>
+  <si>
+    <t>936674955</t>
+  </si>
+  <si>
+    <t>940882172</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>958825204</t>
-  </si>
-  <si>
-    <t>908269602</t>
-  </si>
-  <si>
-    <t>953234766</t>
-  </si>
-  <si>
-    <t>886445851</t>
-  </si>
-  <si>
-    <t>886976624</t>
-  </si>
-  <si>
-    <t>253586642</t>
-  </si>
-  <si>
-    <t>209583479</t>
-  </si>
-  <si>
-    <t>181651443</t>
+    <t>934206842</t>
+  </si>
+  <si>
+    <t>929266561</t>
+  </si>
+  <si>
+    <t>253957249</t>
+  </si>
+  <si>
+    <t>899999332</t>
+  </si>
+  <si>
+    <t>253654150</t>
+  </si>
+  <si>
+    <t>253237824</t>
+  </si>
+  <si>
+    <t>239766284</t>
+  </si>
+  <si>
+    <t>253216729</t>
+  </si>
+  <si>
+    <t>239134137</t>
+  </si>
+  <si>
+    <t>226190985</t>
+  </si>
+  <si>
+    <t>232069504</t>
+  </si>
+  <si>
+    <t>228178020</t>
+  </si>
+  <si>
+    <t>964954998</t>
+  </si>
+  <si>
+    <t>182432876</t>
+  </si>
+  <si>
+    <t>183357502</t>
+  </si>
+  <si>
+    <t>187658616</t>
+  </si>
+  <si>
+    <t>955534965</t>
   </si>
 </sst>
 </file>
@@ -715,7 +796,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1408,7 +1489,7 @@
         <v>63</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>4</v>
@@ -1416,10 +1497,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>4</v>
@@ -1427,10 +1508,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
@@ -1438,10 +1519,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
@@ -1449,10 +1530,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
@@ -1460,10 +1541,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>4</v>
@@ -1471,10 +1552,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
@@ -1482,10 +1563,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
@@ -1493,12 +1574,309 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C67" s="5" t="s">
+      <c r="B68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCAAACC-3D07-4CD2-9B15-F2F0B9D420CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62D2AC0-8A07-48A4-922F-32208B9C564F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="103">
   <si>
     <t>Status</t>
   </si>
@@ -48,289 +48,298 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>932658184</t>
+    <t>861225856</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>936348394</t>
-  </si>
-  <si>
-    <t>936114259</t>
-  </si>
-  <si>
-    <t>935968903</t>
-  </si>
-  <si>
-    <t>931475283</t>
-  </si>
-  <si>
-    <t>931279420</t>
-  </si>
-  <si>
-    <t>925863700</t>
-  </si>
-  <si>
-    <t>929856858</t>
-  </si>
-  <si>
-    <t>919338107</t>
-  </si>
-  <si>
-    <t>916215589</t>
-  </si>
-  <si>
-    <t>915726222</t>
-  </si>
-  <si>
-    <t>914688217</t>
-  </si>
-  <si>
-    <t>913662627</t>
-  </si>
-  <si>
-    <t>912210360</t>
-  </si>
-  <si>
-    <t>909563615</t>
-  </si>
-  <si>
-    <t>909531802</t>
-  </si>
-  <si>
-    <t>909531794</t>
-  </si>
-  <si>
-    <t>906156264</t>
-  </si>
-  <si>
-    <t>905059261</t>
-  </si>
-  <si>
-    <t>899113918</t>
-  </si>
-  <si>
-    <t>901942387</t>
-  </si>
-  <si>
-    <t>903229049</t>
-  </si>
-  <si>
-    <t>891143806</t>
-  </si>
-  <si>
-    <t>884637780</t>
-  </si>
-  <si>
-    <t>890816956</t>
-  </si>
-  <si>
-    <t>888229782</t>
-  </si>
-  <si>
-    <t>875909271</t>
-  </si>
-  <si>
-    <t>884232921</t>
-  </si>
-  <si>
-    <t>879047839</t>
-  </si>
-  <si>
-    <t>812741654</t>
-  </si>
-  <si>
-    <t>841613767</t>
-  </si>
-  <si>
-    <t>861775389</t>
-  </si>
-  <si>
-    <t>855614636</t>
-  </si>
-  <si>
-    <t>855565275</t>
-  </si>
-  <si>
-    <t>853962185</t>
-  </si>
-  <si>
-    <t>847655531</t>
-  </si>
-  <si>
-    <t>831447523</t>
-  </si>
-  <si>
-    <t>838024713</t>
-  </si>
-  <si>
-    <t>836059885</t>
-  </si>
-  <si>
-    <t>810493324</t>
-  </si>
-  <si>
-    <t>805086232</t>
-  </si>
-  <si>
-    <t>255259149</t>
-  </si>
-  <si>
-    <t>774587863</t>
-  </si>
-  <si>
-    <t>190475248</t>
-  </si>
-  <si>
-    <t>224236798</t>
-  </si>
-  <si>
-    <t>242274847</t>
-  </si>
-  <si>
-    <t>240602494</t>
-  </si>
-  <si>
-    <t>240602387</t>
-  </si>
-  <si>
-    <t>220882009</t>
-  </si>
-  <si>
-    <t>209802085</t>
-  </si>
-  <si>
-    <t>206899597</t>
-  </si>
-  <si>
-    <t>206625018</t>
-  </si>
-  <si>
-    <t>205745270</t>
-  </si>
-  <si>
-    <t>203494996</t>
-  </si>
-  <si>
-    <t>200538837</t>
-  </si>
-  <si>
-    <t>962986265</t>
-  </si>
-  <si>
-    <t>965785391</t>
-  </si>
-  <si>
-    <t>186095992</t>
-  </si>
-  <si>
-    <t>185946765</t>
-  </si>
-  <si>
-    <t>973947678</t>
-  </si>
-  <si>
-    <t>973636347</t>
-  </si>
-  <si>
-    <t>971276526</t>
-  </si>
-  <si>
-    <t>951000466</t>
-  </si>
-  <si>
-    <t>953401936</t>
-  </si>
-  <si>
-    <t>951355506</t>
-  </si>
-  <si>
-    <t>948478635</t>
-  </si>
-  <si>
-    <t>946222563</t>
-  </si>
-  <si>
-    <t>945813438</t>
-  </si>
-  <si>
-    <t>945798399</t>
-  </si>
-  <si>
-    <t>945229577</t>
-  </si>
-  <si>
-    <t>942044912</t>
-  </si>
-  <si>
-    <t>939917575</t>
-  </si>
-  <si>
-    <t>939439349</t>
-  </si>
-  <si>
-    <t>937175754</t>
-  </si>
-  <si>
-    <t>936674955</t>
-  </si>
-  <si>
-    <t>940882172</t>
+    <t>184496168</t>
+  </si>
+  <si>
+    <t>973596871</t>
+  </si>
+  <si>
+    <t>971480847</t>
+  </si>
+  <si>
+    <t>970536045</t>
+  </si>
+  <si>
+    <t>968150320</t>
+  </si>
+  <si>
+    <t>967369368</t>
+  </si>
+  <si>
+    <t>966933222</t>
+  </si>
+  <si>
+    <t>965942737</t>
+  </si>
+  <si>
+    <t>964321446</t>
+  </si>
+  <si>
+    <t>964246924</t>
+  </si>
+  <si>
+    <t>242523268</t>
+  </si>
+  <si>
+    <t>262118775</t>
+  </si>
+  <si>
+    <t>263196754</t>
+  </si>
+  <si>
+    <t>242407173</t>
+  </si>
+  <si>
+    <t>217999196</t>
+  </si>
+  <si>
+    <t>208018998</t>
+  </si>
+  <si>
+    <t>205161833</t>
+  </si>
+  <si>
+    <t>199933965</t>
+  </si>
+  <si>
+    <t>200577447</t>
+  </si>
+  <si>
+    <t>204460541</t>
+  </si>
+  <si>
+    <t>203268325</t>
+  </si>
+  <si>
+    <t>198413936</t>
+  </si>
+  <si>
+    <t>196945731</t>
+  </si>
+  <si>
+    <t>196203388</t>
+  </si>
+  <si>
+    <t>190406300</t>
+  </si>
+  <si>
+    <t>189534179</t>
+  </si>
+  <si>
+    <t>188172526</t>
+  </si>
+  <si>
+    <t>963005701</t>
+  </si>
+  <si>
+    <t>961536327</t>
+  </si>
+  <si>
+    <t>959198015</t>
+  </si>
+  <si>
+    <t>904678855</t>
+  </si>
+  <si>
+    <t>928103740</t>
+  </si>
+  <si>
+    <t>945773822</t>
+  </si>
+  <si>
+    <t>957070372</t>
+  </si>
+  <si>
+    <t>959037577</t>
+  </si>
+  <si>
+    <t>958687471</t>
+  </si>
+  <si>
+    <t>957846235</t>
+  </si>
+  <si>
+    <t>956255420</t>
+  </si>
+  <si>
+    <t>955840131</t>
+  </si>
+  <si>
+    <t>955101591</t>
+  </si>
+  <si>
+    <t>954706762</t>
+  </si>
+  <si>
+    <t>954026773</t>
+  </si>
+  <si>
+    <t>938149451</t>
+  </si>
+  <si>
+    <t>938124082</t>
+  </si>
+  <si>
+    <t>934449467</t>
+  </si>
+  <si>
+    <t>933076709</t>
+  </si>
+  <si>
+    <t>929407884</t>
+  </si>
+  <si>
+    <t>926313705</t>
+  </si>
+  <si>
+    <t>924975000</t>
+  </si>
+  <si>
+    <t>912422080</t>
+  </si>
+  <si>
+    <t>924596459</t>
+  </si>
+  <si>
+    <t>922710730</t>
+  </si>
+  <si>
+    <t>918540851</t>
+  </si>
+  <si>
+    <t>917648812</t>
+  </si>
+  <si>
+    <t>915368645</t>
+  </si>
+  <si>
+    <t>915161149</t>
+  </si>
+  <si>
+    <t>911470221</t>
+  </si>
+  <si>
+    <t>909498945</t>
+  </si>
+  <si>
+    <t>908235397</t>
+  </si>
+  <si>
+    <t>908235389</t>
+  </si>
+  <si>
+    <t>907026060</t>
+  </si>
+  <si>
+    <t>906446863</t>
+  </si>
+  <si>
+    <t>903458044</t>
+  </si>
+  <si>
+    <t>903441768</t>
+  </si>
+  <si>
+    <t>902853658</t>
+  </si>
+  <si>
+    <t>896579848</t>
+  </si>
+  <si>
+    <t>895719239</t>
+  </si>
+  <si>
+    <t>893953921</t>
+  </si>
+  <si>
+    <t>893163026</t>
+  </si>
+  <si>
+    <t>872008341</t>
+  </si>
+  <si>
+    <t>878345127</t>
+  </si>
+  <si>
+    <t>877510549</t>
+  </si>
+  <si>
+    <t>877038855</t>
+  </si>
+  <si>
+    <t>866080041</t>
+  </si>
+  <si>
+    <t>872008333</t>
+  </si>
+  <si>
+    <t>871624429</t>
+  </si>
+  <si>
+    <t>871007625</t>
+  </si>
+  <si>
+    <t>856788736</t>
+  </si>
+  <si>
+    <t>856215169</t>
+  </si>
+  <si>
+    <t>841581816</t>
+  </si>
+  <si>
+    <t>848756940</t>
+  </si>
+  <si>
+    <t>835498209</t>
+  </si>
+  <si>
+    <t>789999228</t>
+  </si>
+  <si>
+    <t>821394479</t>
+  </si>
+  <si>
+    <t>827414800</t>
+  </si>
+  <si>
+    <t>797372343</t>
+  </si>
+  <si>
+    <t>791436342</t>
+  </si>
+  <si>
+    <t>919473078</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>934206842</t>
-  </si>
-  <si>
-    <t>929266561</t>
-  </si>
-  <si>
-    <t>253957249</t>
-  </si>
-  <si>
-    <t>899999332</t>
-  </si>
-  <si>
-    <t>253654150</t>
-  </si>
-  <si>
-    <t>253237824</t>
-  </si>
-  <si>
-    <t>239766284</t>
-  </si>
-  <si>
-    <t>253216729</t>
-  </si>
-  <si>
-    <t>239134137</t>
-  </si>
-  <si>
-    <t>226190985</t>
-  </si>
-  <si>
-    <t>232069504</t>
-  </si>
-  <si>
-    <t>228178020</t>
-  </si>
-  <si>
-    <t>964954998</t>
-  </si>
-  <si>
-    <t>182432876</t>
-  </si>
-  <si>
-    <t>183357502</t>
-  </si>
-  <si>
-    <t>187658616</t>
-  </si>
-  <si>
-    <t>955534965</t>
+    <t>975165626</t>
+  </si>
+  <si>
+    <t>260455443</t>
+  </si>
+  <si>
+    <t>260350859</t>
+  </si>
+  <si>
+    <t>253913796</t>
+  </si>
+  <si>
+    <t>192711590</t>
+  </si>
+  <si>
+    <t>186794594</t>
+  </si>
+  <si>
+    <t>944112451</t>
   </si>
 </sst>
 </file>
@@ -796,7 +805,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1687,7 +1696,7 @@
         <v>81</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
@@ -1695,10 +1704,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>4</v>
@@ -1706,10 +1715,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>4</v>
@@ -1717,10 +1726,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>4</v>
@@ -1728,10 +1737,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>4</v>
@@ -1739,10 +1748,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>4</v>
@@ -1750,10 +1759,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>4</v>
@@ -1761,10 +1770,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
@@ -1772,10 +1781,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>4</v>
@@ -1783,10 +1792,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
@@ -1794,10 +1803,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>4</v>
@@ -1805,10 +1814,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>4</v>
@@ -1816,10 +1825,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>4</v>
@@ -1827,10 +1836,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>4</v>
@@ -1841,7 +1850,7 @@
         <v>96</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>4</v>
@@ -1852,7 +1861,7 @@
         <v>97</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>4</v>
@@ -1863,7 +1872,7 @@
         <v>98</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>4</v>
@@ -1874,9 +1883,1098 @@
         <v>99</v>
       </c>
       <c r="B94" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="B174" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C193" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1903,31 +3001,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394D4158-7F2E-4C0C-A65C-486B8239124B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5A8C2A-B7EB-467B-B415-872A4946FF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="61">
   <si>
     <t>Status</t>
   </si>
@@ -48,277 +48,172 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>267060402</t>
+    <t>852333859</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>948670280</t>
-  </si>
-  <si>
-    <t>962077164</t>
-  </si>
-  <si>
-    <t>964249290</t>
-  </si>
-  <si>
-    <t>958372124</t>
-  </si>
-  <si>
-    <t>959393293</t>
-  </si>
-  <si>
-    <t>957359247</t>
-  </si>
-  <si>
-    <t>953510322</t>
-  </si>
-  <si>
-    <t>956181089</t>
-  </si>
-  <si>
-    <t>953593419</t>
-  </si>
-  <si>
-    <t>948090281</t>
-  </si>
-  <si>
-    <t>943897128</t>
-  </si>
-  <si>
-    <t>941929642</t>
-  </si>
-  <si>
-    <t>938213844</t>
-  </si>
-  <si>
-    <t>941593174</t>
-  </si>
-  <si>
-    <t>941350443</t>
-  </si>
-  <si>
-    <t>941067849</t>
-  </si>
-  <si>
-    <t>939938571</t>
-  </si>
-  <si>
-    <t>937990913</t>
-  </si>
-  <si>
-    <t>927834543</t>
-  </si>
-  <si>
-    <t>931908507</t>
-  </si>
-  <si>
-    <t>931873834</t>
-  </si>
-  <si>
-    <t>915056802</t>
-  </si>
-  <si>
-    <t>925425450</t>
-  </si>
-  <si>
-    <t>920132705</t>
-  </si>
-  <si>
-    <t>920008681</t>
-  </si>
-  <si>
-    <t>911188898</t>
-  </si>
-  <si>
-    <t>908784022</t>
-  </si>
-  <si>
-    <t>267221921</t>
-  </si>
-  <si>
-    <t>191746621</t>
-  </si>
-  <si>
-    <t>260739648</t>
-  </si>
-  <si>
-    <t>227546714</t>
-  </si>
-  <si>
-    <t>211752484</t>
-  </si>
-  <si>
-    <t>222476578</t>
-  </si>
-  <si>
-    <t>222434882</t>
-  </si>
-  <si>
-    <t>194428425</t>
-  </si>
-  <si>
-    <t>207307129</t>
-  </si>
-  <si>
-    <t>206326476</t>
-  </si>
-  <si>
-    <t>204910693</t>
-  </si>
-  <si>
-    <t>204558062</t>
-  </si>
-  <si>
-    <t>201764986</t>
-  </si>
-  <si>
-    <t>200975831</t>
-  </si>
-  <si>
-    <t>200583676</t>
-  </si>
-  <si>
-    <t>199326822</t>
-  </si>
-  <si>
-    <t>198048898</t>
-  </si>
-  <si>
-    <t>197361557</t>
-  </si>
-  <si>
-    <t>195389659</t>
-  </si>
-  <si>
-    <t>194516252</t>
-  </si>
-  <si>
-    <t>185768912</t>
-  </si>
-  <si>
-    <t>184627176</t>
-  </si>
-  <si>
-    <t>183582190</t>
-  </si>
-  <si>
-    <t>892744297</t>
-  </si>
-  <si>
-    <t>904948852</t>
-  </si>
-  <si>
-    <t>908207941</t>
-  </si>
-  <si>
-    <t>903039901</t>
-  </si>
-  <si>
-    <t>900008826</t>
-  </si>
-  <si>
-    <t>897158279</t>
-  </si>
-  <si>
-    <t>895033359</t>
-  </si>
-  <si>
-    <t>894988819</t>
-  </si>
-  <si>
-    <t>893645071</t>
-  </si>
-  <si>
-    <t>888916776</t>
-  </si>
-  <si>
-    <t>840503738</t>
-  </si>
-  <si>
-    <t>878060247</t>
-  </si>
-  <si>
-    <t>872472760</t>
-  </si>
-  <si>
-    <t>861090128</t>
-  </si>
-  <si>
-    <t>858385358</t>
-  </si>
-  <si>
-    <t>857943322</t>
-  </si>
-  <si>
-    <t>850655006</t>
-  </si>
-  <si>
-    <t>852930423</t>
-  </si>
-  <si>
-    <t>838869364</t>
-  </si>
-  <si>
-    <t>821433913</t>
-  </si>
-  <si>
-    <t>828285266</t>
-  </si>
-  <si>
-    <t>836763528</t>
-  </si>
-  <si>
-    <t>836336978</t>
-  </si>
-  <si>
-    <t>835459433</t>
-  </si>
-  <si>
-    <t>832846483</t>
-  </si>
-  <si>
-    <t>819894340</t>
-  </si>
-  <si>
-    <t>801568993</t>
-  </si>
-  <si>
-    <t>814706838</t>
-  </si>
-  <si>
-    <t>774575710</t>
-  </si>
-  <si>
-    <t>970259531</t>
-  </si>
-  <si>
-    <t>973637428</t>
-  </si>
-  <si>
-    <t>177746694</t>
-  </si>
-  <si>
-    <t>972987923</t>
-  </si>
-  <si>
-    <t>972181816</t>
-  </si>
-  <si>
-    <t>210095661</t>
+    <t>936961956</t>
+  </si>
+  <si>
+    <t>260739432</t>
+  </si>
+  <si>
+    <t>267624983</t>
+  </si>
+  <si>
+    <t>265655450</t>
+  </si>
+  <si>
+    <t>265444129</t>
+  </si>
+  <si>
+    <t>209689045</t>
+  </si>
+  <si>
+    <t>209554009</t>
+  </si>
+  <si>
+    <t>203341817</t>
+  </si>
+  <si>
+    <t>200637472</t>
+  </si>
+  <si>
+    <t>198686846</t>
+  </si>
+  <si>
+    <t>199827183</t>
+  </si>
+  <si>
+    <t>179505312</t>
+  </si>
+  <si>
+    <t>929415010</t>
+  </si>
+  <si>
+    <t>925482683</t>
+  </si>
+  <si>
+    <t>925313888</t>
+  </si>
+  <si>
+    <t>922381698</t>
+  </si>
+  <si>
+    <t>855072215</t>
+  </si>
+  <si>
+    <t>916215597</t>
+  </si>
+  <si>
+    <t>914554237</t>
+  </si>
+  <si>
+    <t>912735218</t>
+  </si>
+  <si>
+    <t>911211146</t>
+  </si>
+  <si>
+    <t>910480502</t>
+  </si>
+  <si>
+    <t>883894093</t>
+  </si>
+  <si>
+    <t>902293020</t>
+  </si>
+  <si>
+    <t>900194519</t>
+  </si>
+  <si>
+    <t>894668098</t>
+  </si>
+  <si>
+    <t>870244492</t>
+  </si>
+  <si>
+    <t>865765766</t>
+  </si>
+  <si>
+    <t>853862609</t>
+  </si>
+  <si>
+    <t>846272908</t>
+  </si>
+  <si>
+    <t>822933366</t>
+  </si>
+  <si>
+    <t>828741060</t>
+  </si>
+  <si>
+    <t>823676873</t>
+  </si>
+  <si>
+    <t>797447467</t>
+  </si>
+  <si>
+    <t>793508601</t>
+  </si>
+  <si>
+    <t>971483973</t>
+  </si>
+  <si>
+    <t>970299875</t>
+  </si>
+  <si>
+    <t>967602495</t>
+  </si>
+  <si>
+    <t>965493095</t>
+  </si>
+  <si>
+    <t>961560293</t>
+  </si>
+  <si>
+    <t>965378221</t>
+  </si>
+  <si>
+    <t>963933555</t>
+  </si>
+  <si>
+    <t>963461086</t>
+  </si>
+  <si>
+    <t>956908796</t>
+  </si>
+  <si>
+    <t>955158617</t>
+  </si>
+  <si>
+    <t>954876953</t>
+  </si>
+  <si>
+    <t>943241293</t>
+  </si>
+  <si>
+    <t>941416137</t>
+  </si>
+  <si>
+    <t>955930940</t>
+  </si>
+  <si>
+    <t>955844463</t>
+  </si>
+  <si>
+    <t>260262450</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>908434024</t>
-  </si>
-  <si>
-    <t>942815188</t>
-  </si>
-  <si>
-    <t>254626736</t>
+    <t>256694112</t>
+  </si>
+  <si>
+    <t>258075484</t>
   </si>
 </sst>
 </file>
@@ -784,7 +679,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1411,7 +1306,7 @@
         <v>57</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>4</v>
@@ -1419,10 +1314,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
@@ -1430,397 +1325,12 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C90" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5A8C2A-B7EB-467B-B415-872A4946FF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1A8B2B-A1F8-41C6-A34E-2BEC8EE69E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="74">
   <si>
     <t>Status</t>
   </si>
@@ -48,172 +48,211 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>852333859</t>
+    <t>889296111</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>936961956</t>
-  </si>
-  <si>
-    <t>260739432</t>
-  </si>
-  <si>
-    <t>267624983</t>
-  </si>
-  <si>
-    <t>265655450</t>
-  </si>
-  <si>
-    <t>265444129</t>
-  </si>
-  <si>
-    <t>209689045</t>
-  </si>
-  <si>
-    <t>209554009</t>
-  </si>
-  <si>
-    <t>203341817</t>
-  </si>
-  <si>
-    <t>200637472</t>
-  </si>
-  <si>
-    <t>198686846</t>
-  </si>
-  <si>
-    <t>199827183</t>
-  </si>
-  <si>
-    <t>179505312</t>
-  </si>
-  <si>
-    <t>929415010</t>
-  </si>
-  <si>
-    <t>925482683</t>
-  </si>
-  <si>
-    <t>925313888</t>
-  </si>
-  <si>
-    <t>922381698</t>
-  </si>
-  <si>
-    <t>855072215</t>
-  </si>
-  <si>
-    <t>916215597</t>
-  </si>
-  <si>
-    <t>914554237</t>
-  </si>
-  <si>
-    <t>912735218</t>
-  </si>
-  <si>
-    <t>911211146</t>
-  </si>
-  <si>
-    <t>910480502</t>
-  </si>
-  <si>
-    <t>883894093</t>
-  </si>
-  <si>
-    <t>902293020</t>
-  </si>
-  <si>
-    <t>900194519</t>
-  </si>
-  <si>
-    <t>894668098</t>
-  </si>
-  <si>
-    <t>870244492</t>
-  </si>
-  <si>
-    <t>865765766</t>
-  </si>
-  <si>
-    <t>853862609</t>
-  </si>
-  <si>
-    <t>846272908</t>
-  </si>
-  <si>
-    <t>822933366</t>
-  </si>
-  <si>
-    <t>828741060</t>
-  </si>
-  <si>
-    <t>823676873</t>
-  </si>
-  <si>
-    <t>797447467</t>
-  </si>
-  <si>
-    <t>793508601</t>
-  </si>
-  <si>
-    <t>971483973</t>
-  </si>
-  <si>
-    <t>970299875</t>
-  </si>
-  <si>
-    <t>967602495</t>
-  </si>
-  <si>
-    <t>965493095</t>
-  </si>
-  <si>
-    <t>961560293</t>
-  </si>
-  <si>
-    <t>965378221</t>
-  </si>
-  <si>
-    <t>963933555</t>
-  </si>
-  <si>
-    <t>963461086</t>
-  </si>
-  <si>
-    <t>956908796</t>
-  </si>
-  <si>
-    <t>955158617</t>
-  </si>
-  <si>
-    <t>954876953</t>
-  </si>
-  <si>
-    <t>943241293</t>
-  </si>
-  <si>
-    <t>941416137</t>
-  </si>
-  <si>
-    <t>955930940</t>
-  </si>
-  <si>
-    <t>955844463</t>
-  </si>
-  <si>
-    <t>260262450</t>
+    <t>199416524</t>
+  </si>
+  <si>
+    <t>220952240</t>
+  </si>
+  <si>
+    <t>235793167</t>
+  </si>
+  <si>
+    <t>226384513</t>
+  </si>
+  <si>
+    <t>220930303</t>
+  </si>
+  <si>
+    <t>216443956</t>
+  </si>
+  <si>
+    <t>215546171</t>
+  </si>
+  <si>
+    <t>196547396</t>
+  </si>
+  <si>
+    <t>198729810</t>
+  </si>
+  <si>
+    <t>198878617</t>
+  </si>
+  <si>
+    <t>189289741</t>
+  </si>
+  <si>
+    <t>185163528</t>
+  </si>
+  <si>
+    <t>184198582</t>
+  </si>
+  <si>
+    <t>831355627</t>
+  </si>
+  <si>
+    <t>853665275</t>
+  </si>
+  <si>
+    <t>834010807</t>
+  </si>
+  <si>
+    <t>832911295</t>
+  </si>
+  <si>
+    <t>824508489</t>
+  </si>
+  <si>
+    <t>790034619</t>
+  </si>
+  <si>
+    <t>791613361</t>
+  </si>
+  <si>
+    <t>962307884</t>
+  </si>
+  <si>
+    <t>183303068</t>
+  </si>
+  <si>
+    <t>179899871</t>
+  </si>
+  <si>
+    <t>975309653</t>
+  </si>
+  <si>
+    <t>973289238</t>
+  </si>
+  <si>
+    <t>940165438</t>
+  </si>
+  <si>
+    <t>958840195</t>
+  </si>
+  <si>
+    <t>958451183</t>
+  </si>
+  <si>
+    <t>955889641</t>
+  </si>
+  <si>
+    <t>951299977</t>
+  </si>
+  <si>
+    <t>945290272</t>
+  </si>
+  <si>
+    <t>935122295</t>
+  </si>
+  <si>
+    <t>924559838</t>
+  </si>
+  <si>
+    <t>928623887</t>
+  </si>
+  <si>
+    <t>927760649</t>
+  </si>
+  <si>
+    <t>925941084</t>
+  </si>
+  <si>
+    <t>909044707</t>
+  </si>
+  <si>
+    <t>915647279</t>
+  </si>
+  <si>
+    <t>913222562</t>
+  </si>
+  <si>
+    <t>903442899</t>
+  </si>
+  <si>
+    <t>902830938</t>
+  </si>
+  <si>
+    <t>899068955</t>
+  </si>
+  <si>
+    <t>900299086</t>
+  </si>
+  <si>
+    <t>899198679</t>
+  </si>
+  <si>
+    <t>891199519</t>
+  </si>
+  <si>
+    <t>894695679</t>
+  </si>
+  <si>
+    <t>892357306</t>
+  </si>
+  <si>
+    <t>881907921</t>
+  </si>
+  <si>
+    <t>877790943</t>
+  </si>
+  <si>
+    <t>866339611</t>
+  </si>
+  <si>
+    <t>854299389</t>
+  </si>
+  <si>
+    <t>875377057</t>
+  </si>
+  <si>
+    <t>873647543</t>
+  </si>
+  <si>
+    <t>261901478</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>256694112</t>
-  </si>
-  <si>
-    <t>258075484</t>
+    <t>189270097</t>
+  </si>
+  <si>
+    <t>235811605</t>
+  </si>
+  <si>
+    <t>241219173</t>
+  </si>
+  <si>
+    <t>241970809</t>
+  </si>
+  <si>
+    <t>192613457</t>
+  </si>
+  <si>
+    <t>260131929</t>
+  </si>
+  <si>
+    <t>259874901</t>
+  </si>
+  <si>
+    <t>259858821</t>
+  </si>
+  <si>
+    <t>258986854</t>
+  </si>
+  <si>
+    <t>258978661</t>
+  </si>
+  <si>
+    <t>971905298</t>
+  </si>
+  <si>
+    <t>968736664</t>
   </si>
 </sst>
 </file>
@@ -679,7 +718,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1306,7 +1345,7 @@
         <v>57</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>4</v>
@@ -1314,10 +1353,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
@@ -1325,12 +1364,155 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="5" t="s">
+      <c r="B56" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoRegularizacaoIncidencias.xlsx
+++ b/Treinamento/GestaoRegularizacaoIncidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1A8B2B-A1F8-41C6-A34E-2BEC8EE69E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E093781-AB0C-48E6-9644-9348330F8759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="87">
   <si>
     <t>Status</t>
   </si>
@@ -48,211 +48,250 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>889296111</t>
+    <t>865307890</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>199416524</t>
-  </si>
-  <si>
-    <t>220952240</t>
-  </si>
-  <si>
-    <t>235793167</t>
-  </si>
-  <si>
-    <t>226384513</t>
-  </si>
-  <si>
-    <t>220930303</t>
-  </si>
-  <si>
-    <t>216443956</t>
-  </si>
-  <si>
-    <t>215546171</t>
-  </si>
-  <si>
-    <t>196547396</t>
-  </si>
-  <si>
-    <t>198729810</t>
-  </si>
-  <si>
-    <t>198878617</t>
-  </si>
-  <si>
-    <t>189289741</t>
-  </si>
-  <si>
-    <t>185163528</t>
-  </si>
-  <si>
-    <t>184198582</t>
-  </si>
-  <si>
-    <t>831355627</t>
-  </si>
-  <si>
-    <t>853665275</t>
-  </si>
-  <si>
-    <t>834010807</t>
-  </si>
-  <si>
-    <t>832911295</t>
-  </si>
-  <si>
-    <t>824508489</t>
-  </si>
-  <si>
-    <t>790034619</t>
-  </si>
-  <si>
-    <t>791613361</t>
-  </si>
-  <si>
-    <t>962307884</t>
-  </si>
-  <si>
-    <t>183303068</t>
-  </si>
-  <si>
-    <t>179899871</t>
-  </si>
-  <si>
-    <t>975309653</t>
-  </si>
-  <si>
-    <t>973289238</t>
-  </si>
-  <si>
-    <t>940165438</t>
-  </si>
-  <si>
-    <t>958840195</t>
-  </si>
-  <si>
-    <t>958451183</t>
-  </si>
-  <si>
-    <t>955889641</t>
-  </si>
-  <si>
-    <t>951299977</t>
-  </si>
-  <si>
-    <t>945290272</t>
-  </si>
-  <si>
-    <t>935122295</t>
-  </si>
-  <si>
-    <t>924559838</t>
-  </si>
-  <si>
-    <t>928623887</t>
-  </si>
-  <si>
-    <t>927760649</t>
-  </si>
-  <si>
-    <t>925941084</t>
-  </si>
-  <si>
-    <t>909044707</t>
-  </si>
-  <si>
-    <t>915647279</t>
-  </si>
-  <si>
-    <t>913222562</t>
-  </si>
-  <si>
-    <t>903442899</t>
-  </si>
-  <si>
-    <t>902830938</t>
-  </si>
-  <si>
-    <t>899068955</t>
-  </si>
-  <si>
-    <t>900299086</t>
-  </si>
-  <si>
-    <t>899198679</t>
-  </si>
-  <si>
-    <t>891199519</t>
-  </si>
-  <si>
-    <t>894695679</t>
-  </si>
-  <si>
-    <t>892357306</t>
-  </si>
-  <si>
-    <t>881907921</t>
-  </si>
-  <si>
-    <t>877790943</t>
-  </si>
-  <si>
-    <t>866339611</t>
-  </si>
-  <si>
-    <t>854299389</t>
-  </si>
-  <si>
-    <t>875377057</t>
-  </si>
-  <si>
-    <t>873647543</t>
-  </si>
-  <si>
-    <t>261901478</t>
+    <t>938169707</t>
+  </si>
+  <si>
+    <t>939335000</t>
+  </si>
+  <si>
+    <t>921184648</t>
+  </si>
+  <si>
+    <t>927354559</t>
+  </si>
+  <si>
+    <t>935394761</t>
+  </si>
+  <si>
+    <t>934680061</t>
+  </si>
+  <si>
+    <t>926950191</t>
+  </si>
+  <si>
+    <t>910861438</t>
+  </si>
+  <si>
+    <t>911790248</t>
+  </si>
+  <si>
+    <t>915932242</t>
+  </si>
+  <si>
+    <t>915779189</t>
+  </si>
+  <si>
+    <t>914596907</t>
+  </si>
+  <si>
+    <t>912368010</t>
+  </si>
+  <si>
+    <t>267848079</t>
+  </si>
+  <si>
+    <t>265645857</t>
+  </si>
+  <si>
+    <t>264913975</t>
+  </si>
+  <si>
+    <t>224370902</t>
+  </si>
+  <si>
+    <t>219605718</t>
+  </si>
+  <si>
+    <t>216271274</t>
+  </si>
+  <si>
+    <t>215815865</t>
+  </si>
+  <si>
+    <t>204009173</t>
+  </si>
+  <si>
+    <t>212393387</t>
+  </si>
+  <si>
+    <t>208962989</t>
+  </si>
+  <si>
+    <t>207142989</t>
+  </si>
+  <si>
+    <t>206379756</t>
+  </si>
+  <si>
+    <t>205144128</t>
+  </si>
+  <si>
+    <t>189746831</t>
+  </si>
+  <si>
+    <t>962542985</t>
+  </si>
+  <si>
+    <t>970653394</t>
+  </si>
+  <si>
+    <t>970471557</t>
+  </si>
+  <si>
+    <t>966414884</t>
+  </si>
+  <si>
+    <t>965339520</t>
+  </si>
+  <si>
+    <t>964429041</t>
+  </si>
+  <si>
+    <t>961539404</t>
+  </si>
+  <si>
+    <t>961494949</t>
+  </si>
+  <si>
+    <t>960266314</t>
+  </si>
+  <si>
+    <t>959004635</t>
+  </si>
+  <si>
+    <t>195640895</t>
+  </si>
+  <si>
+    <t>202682393</t>
+  </si>
+  <si>
+    <t>200832610</t>
+  </si>
+  <si>
+    <t>200492043</t>
+  </si>
+  <si>
+    <t>196521227</t>
+  </si>
+  <si>
+    <t>195060102</t>
+  </si>
+  <si>
+    <t>190076806</t>
+  </si>
+  <si>
+    <t>190062525</t>
+  </si>
+  <si>
+    <t>190058150</t>
+  </si>
+  <si>
+    <t>190005789</t>
+  </si>
+  <si>
+    <t>183393465</t>
+  </si>
+  <si>
+    <t>187731603</t>
+  </si>
+  <si>
+    <t>187127422</t>
+  </si>
+  <si>
+    <t>186291872</t>
+  </si>
+  <si>
+    <t>186117747</t>
+  </si>
+  <si>
+    <t>177107863</t>
+  </si>
+  <si>
+    <t>175552789</t>
+  </si>
+  <si>
+    <t>906283365</t>
+  </si>
+  <si>
+    <t>902586175</t>
+  </si>
+  <si>
+    <t>896127713</t>
+  </si>
+  <si>
+    <t>901987028</t>
+  </si>
+  <si>
+    <t>900801386</t>
+  </si>
+  <si>
+    <t>899428167</t>
+  </si>
+  <si>
+    <t>891687133</t>
+  </si>
+  <si>
+    <t>885535439</t>
+  </si>
+  <si>
+    <t>881841682</t>
+  </si>
+  <si>
+    <t>876763040</t>
+  </si>
+  <si>
+    <t>828745889</t>
+  </si>
+  <si>
+    <t>852182553</t>
+  </si>
+  <si>
+    <t>855879395</t>
+  </si>
+  <si>
+    <t>854371204</t>
+  </si>
+  <si>
+    <t>853164758</t>
+  </si>
+  <si>
+    <t>803187453</t>
+  </si>
+  <si>
+    <t>821148743</t>
+  </si>
+  <si>
+    <t>800862108</t>
+  </si>
+  <si>
+    <t>771740556</t>
+  </si>
+  <si>
+    <t>283474140</t>
+  </si>
+  <si>
+    <t>213199189</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>189270097</t>
-  </si>
-  <si>
-    <t>235811605</t>
-  </si>
-  <si>
-    <t>241219173</t>
-  </si>
-  <si>
-    <t>241970809</t>
-  </si>
-  <si>
-    <t>192613457</t>
-  </si>
-  <si>
-    <t>260131929</t>
-  </si>
-  <si>
-    <t>259874901</t>
-  </si>
-  <si>
-    <t>259858821</t>
-  </si>
-  <si>
-    <t>258986854</t>
-  </si>
-  <si>
-    <t>258978661</t>
-  </si>
-  <si>
-    <t>971905298</t>
-  </si>
-  <si>
-    <t>968736664</t>
+    <t>891172292</t>
+  </si>
+  <si>
+    <t>920994815</t>
+  </si>
+  <si>
+    <t>924428109</t>
+  </si>
+  <si>
+    <t>898773647</t>
   </si>
 </sst>
 </file>
@@ -718,7 +757,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1" collapsed="1"/>
@@ -1378,7 +1417,7 @@
         <v>60</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>4</v>
@@ -1386,10 +1425,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>4</v>
@@ -1397,10 +1436,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>4</v>
@@ -1408,10 +1447,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>4</v>
@@ -1419,10 +1458,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>4</v>
@@ -1430,10 +1469,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
@@ -1441,10 +1480,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
@@ -1452,10 +1491,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
@@ -1463,10 +1502,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>4</v>
@@ -1474,10 +1513,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
@@ -1485,10 +1524,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
@@ -1496,10 +1535,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>4</v>
@@ -1507,12 +1546,155 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C68" s="5" t="s">
+      <c r="B69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>4</v>
       </c>
     </row>
